--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4171,6 +4171,672 @@
       <c r="F101" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor now provides automatic secure server-to-server integration with Google's ad platforms</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/mediatailor-automatic-google-ad-platform-integration</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 21:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental MediaTailor now automatically secures server-to-server connections with Google's ad platforms, enhancing integration and reducing manual setup.
+2. Outcome (impact):
+This update simplifies the integration process for customers using Google's ad platforms, ensuring secure connections without manual intervention, leading to more accurate ad reporting and fewer rejected impressions.
+3. Where to use (use case):
+Ideal for video streaming services that use Google Ad Manager, Campaign Manager, and Display &amp; Video 360 for personalized ad insertion and tracking.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AWS SAM CLI adds BuildKit support for AWS Lambda functions packaged as container images</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-sam-cli-buildkit-aws-lambda/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 18:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS SAM CLI now supports Docker BuildKit for faster, more efficient container image builds for Lambda functions.
+2. Outcome (impact):  
+   Developers can now leverage advanced BuildKit features like multi-stage builds, improved caching, and cross-architecture builds, resulting in optimized and secure container images.
+3. Where to use (use case):  
+   Ideal for developers packaging AWS Lambda functions as container images who require efficient and secure build processes.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>SAM CLI</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AWS SAM now supports WebSocket APIs for Amazon API Gateway</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-sam-websocket-apis-api-gateway/</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 18:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS SAM now supports WebSocket APIs for Amazon API Gateway, simplifying the creation and management of real-time applications.
+2. Outcome (impact):
+Easier and more efficient setup of WebSocket APIs, reducing manual configuration and debugging efforts, and ensuring automatic generation of necessary resources and permissions.
+3. Where to use (use case):
+Ideal for real-time applications like chat services, live dashboards, AI/ML streaming, and IoT.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS Serverless Application Model (SAM)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache adds thirteen new Amazon CloudWatch metrics for network capacity planning and engine diagnostics</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-elasticache-cloudwatch-metrics-network-engine-diagnostics/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ElastiCache introduces thirteen new CloudWatch metrics for network capacity and engine diagnostics, enhancing monitoring and performance tuning.
+2. Outcome (impact):
+   These metrics enable better detection of network throttling, memory issues, and connection problems, leading to improved performance and reliability of ElastiCache clusters.
+3. Where to use (use case):
+   Ideal for administrators and developers managing ElastiCache clusters to proactively address performance bottlenecks and ensure optimal resource utilization.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces now lets AI agents operate desktop applications (Preview)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/workspaces-ai-agents/</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 17:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon WorkSpaces now allows AI agents to operate desktop applications securely, enabling automation of workflows without application modernization.
+2. Outcome (impact):  
+   Enterprises can automate critical business processes on legacy desktop applications at scale, improving efficiency and reducing IT overhead.
+3. Where to use (use case):  
+   Ideal for industries like financial services, healthcare, and regulated sectors needing to automate tasks such as claims processing, trade settlement, and candidate screening.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AWS IoT Core for Device Location adds Confidence Level Configuration and Measurement Type support</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-iot-core-device-location/</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 16:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IoT Core for Device Location now allows developers to set confidence levels and view measurement types for device locations, enhancing accuracy and metadata.
+2. Outcome (impact):
+Developers can now balance accuracy and confidence in device location data, and gain better insights into the quality and source of location data.
+3. Where to use (use case):
+Useful for applications requiring precise device tracking and location-based services, such as asset management, logistics, and indoor navigation.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS IoT Core for Device Location</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Amazon MQ now supports in-place major version upgrades for RabbitMQ 4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-mq-inplace-upgrades-rabbitmq4/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 16:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon MQ now supports in-place major version upgrades for RabbitMQ 4, allowing seamless upgrades from 3.13 to 4.2 while preserving configurations and data.
+2. Outcome (impact):  
+Easier and more efficient upgrades to RabbitMQ 4.2, minimizing downtime and preserving existing setups, while introducing new features and improvements.
+3. Where to use (use case):  
+Ideal for organizations needing to update their RabbitMQ brokers to the latest version without downtime or data migration, ensuring continuity and leveraging new RabbitMQ 4.2 features.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Amazon MQ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Amazon Quick now integrates with New Relic for observability-driven AI agents</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-quick-new-relic/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 16:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick integrates with New Relic to enhance incident investigation and root cause analysis with AI-driven insights directly within the Quick workspace.
+2. Outcome (impact):
+This integration allows on-call engineers, SREs, and engineering leaders to efficiently investigate incidents, generate RCA briefs, and automate workflows without switching tools.
+3. Where to use (use case):
+Ideal for IT operations teams needing to manage and resolve incidents quickly while leveraging AI for deeper insights and automation.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EC2 Instance Store CSI driver now generally available in EKS add-ons</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/ec2-csi-eks/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 16:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EKS now supports the EC2 Instance Store CSI driver for managing instance store volumes as Kubernetes persistent volumes.
+2. Outcome (impact):
+   Simplifies the process of attaching EC2 local instance store to EKS clusters, enhancing storage flexibility and management.
+3. Where to use (use case):
+   Ideal for applications requiring high-performance, ephemeral storage within EKS clusters, such as big data processing or high-throughput workloads.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Amazon Elastic Kubernetes Service (EKS)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Amazon Connect Cases now supports customer profile identity resolution</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-cases-customer-profiles-id-res/</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 15:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Connect Cases now automatically reassociates cases when customer profiles are merged, ensuring agents have a complete view of customer interactions.
+2. Outcome (impact):  
+   Agents can efficiently manage customer cases without manually piecing together histories from multiple profiles, improving service quality and productivity.
+3. Where to use (use case):  
+   Ideal for customer support teams in contact centers to maintain a unified customer interaction history across various channels and touchpoints.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Amazon Connect Cases</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Customer Engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore is now available in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/bedrock-agentcore-launch-aws-govcloud-us/</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore is now available in AWS GovCloud (US-West), offering secure, scalable AI agent capabilities for government and regulated workloads.
+2. Outcome (impact):
+Organizations can accelerate the development and deployment of AI agents while ensuring compliance with stringent security and regulatory requirements.
+3. Where to use (use case):
+Ideal for government agencies and regulated industries needing to implement AI solutions with elevated compliance needs.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AWS Backup improves performance for Amazon EKS cluster backups</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-backup-amazon-eks-performance-improvement/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Backup now completes Amazon EKS cluster backups up to 10x faster, reducing backup windows from days to hours.
+2. Outcome (impact):  
+This improvement allows for significantly faster backups of large Amazon EKS clusters, minimizing downtime and increasing operational efficiency.
+3. Where to use (use case):  
+Ideal for organizations with large-scale Kubernetes deployments on Amazon EKS, ensuring rapid and reliable data protection.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service expands Cluster Insights with a new insight</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-opensearch-cluster-insights/</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Service now offers expanded Cluster Insights, including a new Unused Index insight, to enhance cluster health visibility and cost optimization across supported versions.
+2. Outcome (impact):
+Customers can proactively identify and resolve performance and stability risks, and optimize costs by detecting and acting on unused indices, leading to improved cluster efficiency and reduced operational overhead.
+3. Where to use (use case):
+This feature is ideal for managing and optimizing OpenSearch clusters, ensuring they run smoothly and cost-effectively by identifying and acting on unused indices.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AWS IAM now provides higher maximum quotas for roles, role trust policies, instance profiles, managed policies, and identity providers</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-iam-increased-quotas/</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 02:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IAM has increased its maximum quotas for customer managed policies, instance profiles, managed policies per role, role trust policy length, roles per account, and OpenID Connect providers to support larger-scale environments.
+2. Outcome (Impact):
+These updates allow customers to manage more IAM resources, enhancing scalability and flexibility in managing access and identity across their AWS environments.
+3. Where to Use (Use Case):
+Ideal for organizations with growing workloads and complex IAM requirements, such as large enterprises, financial institutions, and tech companies needing to manage thousands of IAM resources.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>IAM</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>4 new Qwen models for multimodal reasoning, agentic coding, and multilingual applications are now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/qwen-models-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS introduces four new Qwen models in Amazon SageMaker JumpStart for enhanced multimodal reasoning, agentic coding, and multilingual applications.
+2. Outcome (impact):  
+   These models enable advanced AI applications, improving efficiency in coding, multilingual communication, and complex reasoning tasks.
+3. Where to use (use case):  
+   Ideal for agentic tool use, coding assistance, multilingual communication, and rapid prototyping in various AI applications.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I8ge instances are now generally available in additional AWS regions</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/ec2-i8ge-available-new-regions/</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched EC2 I8ge instances in five new regions, powered by Graviton4 processors, offering enhanced compute and storage performance.
+2. Outcome (impact):
+Customers can now leverage up to 60% better compute and 55% better storage performance with lower latency in additional regions, enhancing their application performance.
+3. Where to use (use case):
+Ideal for data-intensive applications requiring high-speed local storage and low-latency access, such as big data analytics, high-performance computing (HPC), and large-scale database workloads.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Amazon VPC Lattice resource configurations now support private domain-name targets</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-vpc-lattice/</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   AWS VPC Lattice now supports private domain-name targets, allowing secure cross-account access to privately-hosted resources.
+2. Outcome (Impact)
+   Enables secure sharing of private FQDNs across accounts, enhancing network security and resource management.
+3. Where to Use (Use Case)
+   Ideal for organizations needing to securely share privately-hosted resources across different AWS accounts without exposing them publicly.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>VPC Lattice</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch RUM now supports Session Replay for Web Applications</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-cloudwatch-rum-session/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Fri, 01 May 2026 21:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch RUM now offers Session Replay to visualize user interactions on web applications, aiding in diagnosing issues without user reports.
+2. Outcome (impact):
+Developers can quickly identify and resolve user experience issues, improving application performance and user engagement.
+3. Where to use (use case):
+Ideal for front-end developers and application owners to diagnose and fix silent issues impacting user experience.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch RUM</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4902,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-05 07:36:26</t>
+          <t>2026-05-06 05:18:55</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4913,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -4257,7 +4923,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37657</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="7">
@@ -4267,7 +4933,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12569</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="8">
@@ -4277,7 +4943,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002674</v>
+        <v>0.000483</v>
       </c>
     </row>
     <row r="9">
@@ -4287,7 +4953,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00357</v>
+        <v>0.000627</v>
       </c>
     </row>
     <row r="10">
@@ -4297,7 +4963,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.006243</v>
+        <v>0.00111</v>
       </c>
     </row>
     <row r="11">
@@ -4307,7 +4973,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.006243</v>
+        <v>0.007353</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4837,6 +4837,450 @@
       <c r="F119" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AWS Site-to-Site VPN now supports modifying tunnel bandwidth on existing VPN connections</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-site-to-site-vpn-modify-bandwidth/</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 21:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Site-to-Site VPN now allows bandwidth modification on existing connections without disrupting existing configurations.
+2. Outcome (impact):
+Eliminates the need to reconfigure on-premises VPN devices and firewall rules when changing tunnel bandwidth.
+3. Where to use (use case):
+Ideal for organizations needing to scale their VPN bandwidth dynamically without downtime or complex reconfiguration.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS Site-to-Site VPN</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B300 instances are now available in the US East (N. Virginia) Region</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-p6-b300-us-east</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 19:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 P6-B300 instances, featuring 8xNVIDIA Blackwell Ultra GPUs and 6.4 Tbps EFA networking, are now available in the US East (N. Virginia) Region.
+2. Outcome (impact):
+P6-B300 instances offer enhanced performance for AI workloads, delivering faster training times and higher throughput for large-scale models.
+3. Where to use (use case):
+Ideal for training and deploying large trillion-parameter foundation models (FMs) and large language models (LLMs).</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AWS Marketplace now supports programmatic procurement with Agreements API</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-marketplace-agreements-api/</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces the Agreements API for programmatic procurement on AWS Marketplace, enabling automated product purchasing and agreement management.
+2. Outcome (impact):
+   This API allows organizations to streamline procurement processes, integrate seamlessly with existing tools, and enhance operational efficiency by automating purchase workflows.
+3. Where to use (use case):
+   Ideal for large enterprises needing to manage multiple AWS Marketplace subscriptions programmatically, as well as for partners developing custom procurement solutions.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Amazon Neptune now supports 1-click connect with CloudShell</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-neptune-cloudshell/</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Neptune now offers a 1-click connect feature to quickly access Neptune Database and Analytics via AWS CloudShell, eliminating manual network setup.
+2. Outcome (impact):  
+Reduces setup time and technical complexity for database administrators, developers, and data analysts, enabling faster querying and experimentation with Neptune resources.
+3. Where to use (use case):  
+Ideal for testing, development workflows, troubleshooting, and for new users wanting to explore Neptune graph databases quickly.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Amazon Neptune</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory announces metadata for long-term memory</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/agentcore-longterm-memory-metadata</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Memory now supports metadata on long-term memory records, allowing agents to tag, filter, and retrieve memories using structured attributes.
+2. Outcome (impact):
+This enhancement improves the accuracy and relevance of agent responses by enabling more precise retrieval of memories based on structured metadata.
+3. Where to use (use case):
+Use this feature in customer service chatbots, support tickets, and any application requiring precise and context-aware responses.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AWS Elastic Beanstalk now supports TLS listeners for Network Load Balancers</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/elastic-beanstalk-tls-support/</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elastic Beanstalk now supports TLS listeners for Network Load Balancers, enabling secure connections directly through Elastic Beanstalk.
+2. Outcome (impact):  
+This update allows developers to configure secure connections for their applications running on Elastic Beanstalk with Network Load Balancers, enhancing security and compliance.
+3. Where to use (use case):  
+Ideal for web applications and services that require secure communication between clients and servers, ensuring encrypted data transfer.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Elastic Beanstalk</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor now supports ad trickplay personalization and compact DASH manifest optimization via dynamic transcoding</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/mediatail-ad-trickplay-and-compact-dash-manifest-optimization</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 14:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+AWS Elemental MediaTailor now natively supports ad trickplay personalization and compact DASH manifest optimization through dynamic transcoding, enhancing ad delivery for HLS and DASH formats.
+2. Outcome (Impact)
+This update improves ad personalization during trickplay, ensuring ads are properly transcoded for fast-forwarding and rewinding, and optimizes manifest delivery for better compatibility and efficiency.
+3. Where to Use (Use Case)
+Ideal for streaming platforms needing seamless ad experiences during trickplay navigation, and for those requiring efficient manifest delivery to enhance player performance.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Announcing Agent Toolkit for AWS — help AI coding agents build effectively on AWS</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/agent-toolkit/</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS launches the Agent Toolkit for AWS to assist AI coding agents in building on AWS with fewer errors and lower costs, featuring agent skills, a managed MCP server, and plugins.
+2. Outcome (impact):
+   Improved accuracy, reliability, and security in AI coding agents' workflows, reducing wasted time and tokens, and enabling safer production deployment.
+3. Where to use (use case):
+   Ideal for developers using AI coding agents to build, deploy, and manage AWS resources, particularly in complex multi-service environments.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>The AWS MCP Server is now generally available</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-mcp-server/</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the AWS MCP Server, enabling secure and auditable access for AI coding agents to AWS services through the Model Context Protocol (MCP).
+2. Outcome (impact):
+Organizations can safely allow coding agents to interact with AWS services while maintaining visibility and control, enhancing productivity and security.
+3. Where to use (use case):
+Ideal for organizations that need to automate and manage AWS resources through AI coding agents, ensuring secure and efficient operations.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS MCP Server</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family web apps are now available in the AWS Asia Pacific (New Zealand) Region</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-transfer-family-asia-pacific/</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transfer Family web apps are now available in New Zealand, offering a secure, branded portal for S3 data management via web browsers.
+2. Outcome (impact):
+This enables New Zealand-based businesses to easily manage and secure their data in Amazon S3 with a user-friendly web interface.
+3. Where to use (use case):
+Ideal for organizations needing a secure, branded interface for their workforce to manage data in Amazon S3, such as file sharing, data uploads/downloads, and browsing.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AWS Directory Service expands directory security settings with STIG-aligned controls for Managed AD</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/add-security-settings-stig-aws-microsoft-ad/</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Directory Service for Microsoft Active Directory now includes STIG-aligned security settings to enhance directory-level security and compliance configurations.
+2. Outcome (impact):
+   This update enables customers, especially those in regulated or security-focused environments, to meet stringent security requirements by aligning with DISA STIG guidelines for Windows Server and Active Directory.
+3. Where to use (use case):
+   Ideal for organizations needing robust directory security and compliance, such as government agencies, financial institutions, and enterprises with strict security policies.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS Directory Service</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AWS Console Mobile App adds interactive graphs, AI log ssummaries, and natural language logs search to CloudWatch Alarms</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-console-mobile-app/</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 17:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Console Mobile App now features interactive graphs, AI-generated log summaries, and natural language log search for faster CloudWatch Alarms investigation.
+2. Outcome (Impact):
+Reduces time from alarm notification to root cause identification, enhancing operational efficiency and incident resolution speed.
+3. Where to Use (Use Case):
+Ideal for DevOps engineers and SREs needing quick, on-the-go access to detailed CloudWatch Alarms data and insights.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>CloudWatch</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -4902,7 +5346,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-06 05:18:55</t>
+          <t>2026-05-07 04:39:18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +5357,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4923,7 +5367,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6807</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="7">
@@ -4933,7 +5377,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2207</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="8">
@@ -4943,7 +5387,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000483</v>
+        <v>0.000303</v>
       </c>
     </row>
     <row r="9">
@@ -4953,7 +5397,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000627</v>
+        <v>0.000416</v>
       </c>
     </row>
     <row r="10">
@@ -4963,7 +5407,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00111</v>
+        <v>0.00072</v>
       </c>
     </row>
     <row r="11">
@@ -4973,7 +5417,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.007353</v>
+        <v>0.008073</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -5281,6 +5281,933 @@
       <c r="F131" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Amazon EC2 G6 instances now available in AWS European Sovereign Cloud (Germany)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-g6-aws-european-sovereign-cloud/</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 21:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon EC2 G6 instances, powered by NVIDIA L4 GPUs, are now available in AWS European Sovereign Cloud (Germany) for graphics-intensive and ML workloads.
+2. Outcome (impact):  
+   This launch enables customers in Germany to leverage high-performance GPU instances for advanced ML and graphics applications, enhancing computational capabilities and efficiency.
+3. Where to use (use case):  
+   Ideal for natural language processing, language translation, video and image analysis, speech recognition, personalization, and real-time, cinematic-quality graphics and game streaming.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Amazon EC2 X8i instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/02/amazon-ec2-x8i-instances-BOM-DUB-region/</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 20:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched X8i instances in Europe (Ireland) and Asia Pacific (Mumbai) regions, offering enhanced performance and memory capacity.
+2. Outcome (impact):
+   Users can now leverage these instances for memory-intensive workloads with up to 43% higher performance and 1.5x more memory capacity compared to previous generations.
+3. Where to use (use case):
+   Ideal for SAP HANA, large databases, data analytics, and Electronic Design Automation (EDA) applications.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio adds identity and user management features</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/smus-identity-user-management/</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio introduces enhanced identity and user management features, enabling administrators to manage IAM and Identity Center users more effectively.
+2. Outcome (impact):
+These new features improve collaboration and security in SageMaker projects by allowing flexible user management and single sign-on capabilities, ensuring that users can work together without compromising data integrity.
+3. Where to use (use case):
+Ideal for data science teams and ML practitioners who need to collaborate on projects within SageMaker, ensuring secure and efficient access management.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Amazon EC2 G7e instances now available in Europe (London) region</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-g7e-london-region/</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 18:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 G7e instances with advanced GPUs are now available in Europe (London), offering enhanced inference performance for AI workloads.
+2. Outcome (impact):
+   Users can achieve up to 2.3x better inference performance for large language models, agentic AI, and spatial computing tasks.
+3. Where to use (use case):
+   Ideal for deploying large language models, multimodal generative AI, and spatial computing applications requiring high-performance graphics and AI processing.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AWS Capabilities by Region now supports availability notifications</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-regional-planning-tool-notification</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 17:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces availability notifications for AWS Capabilities by Region, alerting builders when services and features become available in their target Regions.
+2. Outcome (impact):  
+Accelerates infrastructure planning and deployment decisions by providing timely updates on the availability of over 1,500 services and features across 37 AWS Regions.
+3. Where to use (use case):  
+Ideal for solutions architects expanding applications into new Regions, monitoring service parity, and preparing for migrations or Regional expansions.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS Builder Center</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor launches Monetization Functions</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-elemental-mediatailor-monetization-functions</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 17:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Elemental MediaTailor now offers monetization functions to customize ad requests and manage session data during ad-personalized playback.
+2. Outcome (impact):
+   Customers can call external APIs and run data transformations at specific playback points, eliminating the need for middleware and ensuring uninterrupted playback.
+3. Where to use (use case):
+   Common use cases include resolving hashed email addresses, appending contextual metadata, activating header bidding workflows, and running A/B tests.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AWS Advanced JDBC Wrapper now provides client-side encryption</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-advanced-jdbc-wrapper-encryption/</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Advanced JDBC Wrapper now offers client-side encryption for sensitive data using KMS, ensuring data remains encrypted until it reaches the application.
+2. Outcome (impact):
+Enhances data security by encrypting sensitive data at the application level, mitigating risks from compromised credentials or SQL injection attacks, and ensuring compliance with regulations like PCI DSS, HIPAA, and GDPR.
+3. Where to use (use case):
+Ideal for Java applications interacting with Amazon RDS and Amazon Aurora PostgreSQL and MySQL databases, ensuring sensitive data remains encrypted before it reaches the database.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS Advanced JDBC Wrapper</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Amazon Connect Outbound Campaigns adds multi-contact time zone detection</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-campaign-multitimezone</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Outbound Campaigns now detects customer time zones using all contact information, ensuring messages are sent within configured hours across all detected time zones.
+2. Outcome (impact):
+Improved accuracy in time zone detection leads to better scheduling of outbound campaign messages, enhancing customer engagement and compliance with time zone-specific delivery windows.
+3. Where to use (use case):
+Use this feature for multi-location businesses needing to ensure their outbound campaigns respect local time zones, improving communication effectiveness and customer satisfaction.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Amazon Connect Outbound Campaigns</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports AMI-based node lifecycle configuration for Slurm clusters</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-hyperpod-ami-based-node/</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon SageMaker HyperPod now offers AMI-based node lifecycle configuration for Slurm clusters, streamlining cluster setup and reducing creation time.
+2. Outcome (impact):  
+   This update simplifies the process of setting up production-ready AI/ML training environments by eliminating the need for lifecycle scripts, thereby significantly reducing cluster creation time.
+3. Where to use (use case):  
+   Ideal for organizations running large-scale AI/ML training workloads that require quick and efficient cluster provisioning.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8gn and M8gb instances are now available in AWS Europe (Ireland) region</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-m8gn-m8gb-aws-europe/</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has launched M8gn and M8gb instances in the Europe (Ireland) region, powered by AWS Graviton4 processors, offering enhanced compute and network performance.
+2. Outcome (impact):
+These new instances provide up to 30% better compute performance and higher network bandwidth, making them suitable for high-performance and storage-intensive workloads.
+3. Where to use (use case):
+- M8gn: Network-intensive applications like high-performance file systems, real-time big data analytics, and 5G UPF.
+- M8gb: High block storage performance needs such as high-performance databases and NoSQL databases.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AWS India customers can now use UPI Scan and Pay for sign-up and payments</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/aws-india-upi-scanandpay/</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS India customers can now use UPI Scan and Pay for easy sign-up and payment via QR code.
+2. Outcome (impact):
+   Simplifies and secures the payment process, reducing errors and friction for Indian customers.
+3. Where to use (use case):
+   For signing up for AWS services and making one-time or recurring payments up to INR 15,000.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS Billing</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Introducing Amazon EC2 R8idn and R8idb instances</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/03/amazon-ec2-r8idn-r8idb/</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched EC2 R8idn and R8idb instances with custom Intel Xeon Scalable processors and enhanced networking, offering significant performance improvements.
+2. Outcome (Impact):
+   These instances provide up to 43% better compute performance per vCPU, with R8idn instances offering up to 600 Gbps network bandwidth and R8idb instances delivering up to 300 Gbps EBS bandwidth and 1,440K IOPS.
+3. Where to Use (Use Case):
+   - R8idn Instances: Ideal for memory-intensive workloads requiring high network throughput and local storage, such as in-memory databases and real-time big data analytics.
+   - R8idb Instances: Suitable for workloads needing high block storage performance, such as large-scale commercial databases and enterprise analytics platforms.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Introducing Amazon EC2 M8idn and M8idb instances</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-m8idn-m8idb/</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched M8idn and M8idb instances, powered by custom Intel Xeon Scalable processors, offering enhanced compute and network performance.
+2. Outcome (impact):
+   These instances provide up to 43% better compute performance per vCPU and up to 600 Gbps network bandwidth for M8idn, making them ideal for high-performance and storage-intensive workloads.
+3. Where to use (use case):
+   M8idn instances are suited for network-intensive tasks like distributed compute and data analytics, while M8idb instances are perfect for storage-heavy applications such as large databases and data lakes.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Agents that transact: Amazon Bedrock AgentCore now includes Payments (preview)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/amazon-bedrock-agentcore-payments-preview</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore introduces a preview of AgentCore payments, enabling AI agents to autonomously transact with APIs, servers, and other agents using integrated payment solutions.
+2. Outcome (impact):
+Developers can now create AI agents that can autonomously access and pay for services without needing to build complex billing and credential management systems from scratch.
+3. Where to use (use case):
+Ideal for scenarios where AI agents need to interact with paid resources, such as accessing premium APIs, purchasing web content, or interacting with other paid services.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AWS Resource Explorer is now available in AWS GovCloud (US-East) and (US-West)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-resource-explorer-available-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Resource Explorer is now available in AWS GovCloud (US-East) and (US-West), enabling simplified resource search and discovery.
+2. Outcome (impact):
+   Simplifies the search and discovery of AWS resources, enhancing efficiency and management in compliance-sensitive environments.
+3. Where to use (use case):
+   Ideal for government agencies and contractors needing to manage and discover resources within the AWS GovCloud regions securely.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS Resource Explorer</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server now supports instances powered by AMD EPYC processors</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/rds-sqlserver-supports-amd-instances/</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for SQL Server now offers M8a and R8a instances with AMD EPYC processors, delivering up to 70% higher throughput.
+2. Outcome (impact):  
+Enhanced performance and cost efficiency for SQL Server workloads, with significant throughput improvements and reduced licensing costs.
+3. Where to use (use case):  
+Ideal for high-performance SQL Server databases with demanding I/O requirements, such as enterprise applications and data analytics.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Amazon SES Mail Manager now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/ses-mail-manager-available-aws-govcloud-regions</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon SES Mail Manager is now available in AWS GovCloud (US) regions, expanding its coverage to 30 AWS regions, offering centralized email management.
+2. Outcome (impact)
+Organizations gain enhanced visibility, control, and simplified management of their email infrastructure, reducing operational overhead and costs.
+3. Where to use (use case)
+Use cases include managing email traffic for government agencies and organizations requiring compliance with stringent data security and privacy regulations.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Amazon Redshift now scales data ingestion automatically with concurrency scaling for batch workloads</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/concurrencyscaling-support-for-copy</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 02:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Redshift now automatically scales data ingestion with concurrency scaling for batch workloads, improving COPY query performance.
+2. Outcome (impact):
+   Organizations can achieve faster data ingestion and maintain query performance during peak demand without manual intervention.
+3. Where to use (use case):
+   Ideal for real-time analytics, continuous ETL, and high-frequency reporting where ingestion bottlenecks can occur during traffic spikes.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service now supports VPC egress for private connectivity to resources in your VPC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-opensearch-service-vpc</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 00:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Service now supports VPC egress, enabling private connectivity to VPC resources without public internet exposure.
+2. Outcome (impact):
+   Enhanced security and privacy by keeping traffic within the VPC, reducing exposure to the public internet.
+3. Where to use (use case):
+   Ideal for securely accessing ML models, AWS services, and custom applications within a VPC from OpenSearch Service domains.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B200 instances are now available in the AWS GovCloud (US-West) Region</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-p6-b200-aws-govcloud</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 19:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 P6-B200 instances with enhanced AI capabilities are now available in AWS GovCloud (US-West) Region.
+2. Outcome (Impact):
+Users can achieve up to 2x performance improvement for AI training and inference tasks, leveraging advanced GPU and networking features.
+3. Where to Use (Use Case):
+Ideal for AI/ML workloads requiring high computational power and memory, such as large-scale machine learning training and inference.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Runtime now supports bring-your-own file system from Amazon S3 Files and Amazon EFS</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-bedrock-agentcore-runtime/</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 19:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Runtime now supports attaching custom file systems from Amazon S3 Files and Amazon EFS, allowing seamless file access for agents.
+2. Outcome (impact):
+This feature enables agents to share and persist data across sessions, improving efficiency and collaboration without the need for custom code or privileged containers.
+3. Where to use (use case):
+Ideal for sharing skills, datasets, and intermediate results across multiple agent sessions and workflows, facilitating collaborative and persistent agent operations.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache now supports real-time aggregations</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-elasticache-aggregations/</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ElastiCache now supports real-time aggregations, enabling developers to filter, group, and summarize data directly in the cache with microsecond latencies.
+2. Outcome (impact):
+Reduces architectural complexity, improves response times, and allows for real-time insights and application experiences without needing a separate analytics engine.
+3. Where to use (use case):
+Ideal for applications requiring real-time analytics, such as e-commerce marketplaces, streaming services, AI-powered personalization, and operational dashboards.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache now supports real-time hybrid search with vector and full-text</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-elasticache-hybrid-search/</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ElastiCache now supports real-time hybrid search combining vector and full-text search, enhancing search relevance and performance.
+2. Outcome (impact):
+Improved search relevance and performance for applications using both semantic meaning and exact keyword matching, reducing token costs and latency.
+3. Where to use (use case):
+E-commerce platforms, streaming services, AI agent memory, and Retrieval-Augmented Generation (RAG) systems to deliver more accurate search results.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache now supports real-time full-text, exact-match, and numeric range search</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-elasticache-enchanced-search/</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Wed, 06 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ElastiCache now supports real-time full-text, exact-match, and numeric range search directly in the cache, enabling scalable and low-latency search operations.
+2. Outcome (impact):
+Developers can perform complex search queries directly within ElastiCache, reducing latency and increasing throughput for search operations, ensuring applications always access the most current data.
+3. Where to use (use case):
+Ideal for applications requiring real-time search capabilities, such as e-commerce product discovery, financial transaction filtering, and gaming leaderboards.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Announcing Valkey 9.0 for Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/valkey-amazon-elasticache/</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tue, 05 May 2026 22:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ElastiCache now supports Valkey 9.0, offering enhanced search capabilities, performance improvements, and operational flexibility for real-time applications.
+2. Outcome (Impact):
+Valkey 9.0 enables developers to build more efficient, scalable, and high-performance applications with built-in search, higher throughput, and fine-grained data lifecycle management.
+3. Where to Use (Use Case):
+Ideal for real-time, AI-driven applications requiring high throughput and low latency, such as recommendation systems, live search, and data analytics.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -5346,7 +6273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-07 04:39:18</t>
+          <t>2026-05-08 05:50:43</t>
         </is>
       </c>
     </row>
@@ -5357,7 +6284,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -5367,7 +6294,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4270</v>
+        <v>10366</v>
       </c>
     </row>
     <row r="7">
@@ -5377,7 +6304,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1466</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="8">
@@ -5387,7 +6314,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000303</v>
+        <v>0.000736</v>
       </c>
     </row>
     <row r="9">
@@ -5397,7 +6324,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000416</v>
+        <v>0.000926</v>
       </c>
     </row>
     <row r="10">
@@ -5407,7 +6334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00072</v>
+        <v>0.001662</v>
       </c>
     </row>
     <row r="11">
@@ -5417,7 +6344,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.008073</v>
+        <v>0.009735000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -6208,6 +6208,265 @@
       <c r="F156" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AWS Client VPN now supports Ubuntu OS version 26.04 LTS</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-client-vpn-ubuntu-26/</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 22:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Client VPN now supports Ubuntu OS version 26.04 LTS, enhancing remote access for Linux users.
+2. Outcome (impact):  
+This update allows users to securely connect to AWS or on-premises networks using the latest Ubuntu OS version, improving compatibility and security.
+3. Where to use (use case):  
+Ideal for remote workforces needing secure access to AWS resources using the latest Ubuntu OS.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS Client VPN</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Amazon Connect adds default Step-by-Step Guides for After Contact Work</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-adds-default-step-by-step-guides-for-after-contact-work</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 20:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect now offers Default Guides for After Contact Work (ACW) to automate task completion for agents, enhancing efficiency and consistency.
+2. Outcome (impact):
+This feature reduces handle time, minimizes errors, and boosts agent productivity by guiding agents through post-contact tasks automatically.
+3. Where to use (use case):
+Ideal for contact centers aiming to standardize post-contact workflows and improve operational efficiency.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Global Resolver now lets you add and remove AWS Regions for anycast DNS resolution</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-route-global-resolver-aws/</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 17:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   Amazon Route 53 Global Resolver now allows dynamic addition and removal of AWS Regions for anycast DNS resolution.
+2. Outcome (impact)
+   This update provides flexibility to expand DNS coverage as your organization grows or to adjust regional deployment for compliance needs without recreating configurations.
+3. Where to use (use case)
+   Ideal for organizations needing scalable DNS resolution that can dynamically adjust to changing business needs or regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Amazon Route 53</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>AWS Service Catalog is now available in the AWS Asia Pacific (New Zealand) and Canada West (Calgary) regions</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-service-catalog-calgary-new-zealand-regions/</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 16:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Service Catalog is now available in the Asia Pacific (New Zealand) and Canada West (Calgary) regions, enabling better governance and distribution of IaC products.
+2. Outcome (impact):  
+This expansion allows organizations in these regions to efficiently manage and deploy approved AWS resources with enhanced governance and self-service access.
+3. Where to use (use case):  
+Use cases include managing multi-tier application deployments, ensuring compliance with organizational policies, and providing consistent access to resources across different teams and accounts.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS Service Catalog</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>IAM Policy Autopilot adds Java support and Terraform-aware policy generation</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/iam-policy-autopilot/</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+IAM Policy Autopilot now supports Java applications and generates more precise IAM policies by integrating with Terraform.
+2. Outcome (impact):
+Reduces time spent writing IAM policies and minimizes access issues by generating deterministic, least-privilege policies based on actual application code and infrastructure definitions.
+3. Where to use (use case):
+Ideal for Java developers managing IAM policies for applications that use AWS services and are defined with Terraform.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>IAM Policy Autopilot</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Resolver endpoints now support additional capabilities for IPv6 query traffic</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-route-53-resolver-ipv6/</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 23:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Route 53 Resolver now supports DNS64 on inbound and IPv6 forwarding on outbound endpoints, facilitating hybrid DNS management across IPv4 and IPv6 networks.
+2. Outcome (impact):
+Eases transition to IPv6 by allowing IPv6-only clients to access IPv4 services on AWS and enabling seamless communication between IPv4 and IPv6 resources.
+3. Where to use (use case):
+Ideal for organizations transitioning to IPv6, managing hybrid cloud environments, and needing to resolve DNS queries between on-premises networks and AWS VPCs.</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Resolver</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>AWS Marketplace introduces Tax management portal for sellers</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-marketplace-tax/</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 21:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Marketplace has launched a new Tax management portal to streamline invoice retrieval and record-keeping for sellers.
+2. Outcome (impact):
+   This new portal enhances efficiency for sellers by providing a self-service process to view, download, and manage invoices, reducing the need for support requests and improving financial transparency.
+3. Where to use (use case):
+   The portal is ideal for sellers managing AWS Marketplace operations, especially those needing to prepare for audits, reconcile financial records, or track revenue across multiple regions.</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6532,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-08 05:50:43</t>
+          <t>2026-05-09 06:08:33</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6543,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -6294,7 +6553,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10366</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="7">
@@ -6304,7 +6563,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3262</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8">
@@ -6314,7 +6573,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000736</v>
+        <v>0.000165</v>
       </c>
     </row>
     <row r="9">
@@ -6324,7 +6583,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000926</v>
+        <v>0.000239</v>
       </c>
     </row>
     <row r="10">
@@ -6334,7 +6593,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001662</v>
+        <v>0.000403</v>
       </c>
     </row>
     <row r="11">
@@ -6344,7 +6603,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.009735000000000001</v>
+        <v>0.010138</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -6467,6 +6467,376 @@
       <c r="F163" t="inlineStr">
         <is>
           <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of P6-B200 instances on SageMaker Studio notebooks</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/p6-b200-region-expansion-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 23:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched P6-B200 instances in US East (N. Virginia) on SageMaker Studio, featuring 8 NVIDIA Blackwell GPUs and 1440 GB of GPU memory, enhancing AI training performance.
+2. Outcome (impact):
+These instances offer up to 2x better performance for AI training, enabling efficient development and fine-tuning of large foundation models for generative AI applications.
+3. Where to use (use case):
+Ideal for interactive development and fine-tuning of large language models, mixture of experts models, and multi-modal reasoning models in JupyterLab or CodeEditor environments.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of G6e instances on SageMaker Studio notebooks</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/g6e-region-expansion-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded the availability of G6e instances on SageMaker Studio notebooks to new regions, enhancing performance for AI/ML tasks.
+2. Outcome (Impact):
+Customers in Dubai, Tokyo, Seoul, Frankfurt, Stockholm, and Spain can now leverage high-performance G6e instances for better model training and deployment.
+3. Where to Use (Use Case):
+Ideal for interactive model training, generative AI fine-tuning, deploying large language models, and generating images, video, and audio.</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of G6 instances on SageMaker Studio notebooks</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/03/g6-region-expansion-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has expanded the availability of G6 instances to the Middle East (Dubai) and Asia Pacific (Malaysia) regions for SageMaker Studio notebooks, enhancing deep learning capabilities.
+2. Outcome (impact):
+   Customers can now leverage improved deep learning inference performance with G6 instances, which offer 2x better performance compared to G4dn instances, for various AI/ML tasks.
+3. Where to use (use case):
+   Ideal for generative AI fine-tuning, natural language processing, language translation, computer vision, and recommender engines.</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ENA Express for Amazon EC2 instances now supports traffic between Availability Zones</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/ena-express-availability-zones/</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   ENA Express now supports up to 25 Gbps single-flow bandwidth between Availability Zones, enhancing network performance for distributed applications.
+2. Outcome (impact):
+   Improved network performance for cross-AZ traffic, enabling higher throughput for workloads like distributed storage, databases, and file systems.
+3. Where to use (use case):
+   Ideal for applications requiring high-throughput cross-AZ communication, such as distributed databases, storage systems, and high-performance computing tasks.</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Elastic Network Adapter (ENA) Express</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of P4de instances on SageMaker Studio notebooks</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/02/p4de-region-expansion-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has expanded the availability of P4de instances, featuring 8 A100 GPUs with 640GB of memory, to Asia Pacific (Tokyo, Singapore) and Europe (Frankfurt) on SageMaker Studio notebooks.
+2. Outcome (impact):
+   Customers can achieve up to 60% better ML training performance and 20% lower costs compared to P4d instances, accelerating model training times and reducing time to market.
+3. Where to use (use case):
+   Ideal for machine learning workloads requiring large datasets and high-resolution data, such as computer vision, natural language processing, and deep learning applications.</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL is now available in five additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-aurora-dsql-five-additional-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 19:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora DSQL is now available in five additional regions, expanding its global footprint and accessibility for developers.
+2. Outcome (impact):
+This expansion enables developers in new regions to build highly scalable, resilient, and always available applications with ease, leveraging Aurora DSQL's serverless architecture and high performance.
+3. Where to use (use case):
+Aurora DSQL is ideal for applications requiring high availability, scalability, and minimal infrastructure management, such as e-commerce platforms, financial services, and real-time analytics systems.</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports caching of cancelled workflow runs</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-healthomics-caching-cancelled-runs/</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now caches outputs of cancelled workflow runs, allowing reuse and cost savings.
+2. Outcome (impact):
+Enables efficient debugging and iterative development by storing intermediate files and completed task outputs, reducing recomputation costs.
+3. Where to use (use case):
+Ideal for researchers, bioinformaticians, and workflow developers in healthcare and life sciences to accelerate scientific breakthroughs.</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>HealthOmics</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AWS WAF introduces dynamic label interpolation for custom request and response handling</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-waf-dynamic-label-interpolation/</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS WAF now supports dynamic label interpolation, allowing security engineers to forward classification signals and embed context in responses using a single rule.
+2. Outcome (impact):
+Security engineers can simplify rule management and enhance adaptive responses by embedding context in requests and responses, improving both security and user experience.
+3. Where to use (use case):
+Use dynamic label interpolation to forward IP reputation signals to applications for adaptive responses like enforcing MFA, or embed synthetic labels in custom pages for user reference.</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS WAF</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Claude Platform on AWS is now generally available</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/claude-platform-aws/</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the general availability of the Claude Platform on AWS, offering developers and organizations access to Anthropic's native platform experience through their existing AWS accounts.
+2. Outcome (impact):
+This integration allows users to leverage Anthropic's advanced AI capabilities without managing separate accounts or billing, enhancing developer productivity and simplifying access to cutting-edge AI tools.
+3. Where to use (use case):
+Ideal for development teams and enterprises looking to integrate sophisticated AI functionalities like natural language processing, code execution, and web search into their applications without the hassle of separate account management.</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AWS Transform adds containerization capability during migrations</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-transform-containerization/</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 08:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform now automates containerization of applications during migrations to AWS, integrating with popular source code repositories and supporting large-scale migrations.
+2. Outcome (impact):
+This feature reduces migration time and complexity by enabling parallel migration and modernization, allowing teams to leverage cloud-native architectures more efficiently.
+3. Where to use (use case):
+Ideal for organizations looking to migrate on-premises applications to AWS while modernizing them to containerized architectures, facilitating easier management and scalability.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6902,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09 06:08:33</t>
+          <t>2026-05-12 06:30:56</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6913,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -6553,7 +6923,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2319</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="7">
@@ -6563,7 +6933,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>840</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="8">
@@ -6573,7 +6943,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000165</v>
+        <v>0.000266</v>
       </c>
     </row>
     <row r="9">
@@ -6583,7 +6953,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000239</v>
+        <v>0.000379</v>
       </c>
     </row>
     <row r="10">
@@ -6593,7 +6963,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000403</v>
+        <v>0.000645</v>
       </c>
     </row>
     <row r="11">
@@ -6603,7 +6973,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.010138</v>
+        <v>0.010783</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -6837,6 +6837,379 @@
       <c r="F173" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AWS Lambda supports scheduled scaling for functions on Lambda Managed Instances</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-lambda-managed-instances/</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now offers scheduled scaling for functions on Lambda Managed Instances, allowing proactive capacity adjustments using Amazon EventBridge Scheduler.
+2. Outcome (impact):
+This feature enables automatic scaling of Lambda function capacity based on predefined schedules, optimizing performance during peak times and reducing costs during idle periods.
+3. Where to use (use case):
+Ideal for applications with predictable traffic patterns, such as business-hours operations or marketing campaigns, ensuring resources are available when needed and scaled down when not.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Amazon EventBridge Scheduler adds 619 new SDK API actions, including Lambda Managed Instances</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-eventbridge-sdk-integrations/</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EventBridge Scheduler now supports 619 new SDK API actions, including Lambda Managed Instances, across 13 additional services.
+2. Outcome (impact):
+   Users can schedule a wider range of AWS services directly from EventBridge Scheduler, enhancing automation and capacity management without custom code.
+3. Where to use (use case):
+   Ideal for automating tasks such as scaling Lambda managed instances based on time-based schedules, improving resource provisioning efficiency.</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>EventBridge Scheduler</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>AWS Security Agent now supports full repository code reviews</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-security-agent-full-repository-code-review/</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 17:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Agent now offers full repository code review, providing deep, context-aware security analysis of your entire codebase to uncover systemic vulnerabilities.
+2. Outcome (impact):
+Faster identification and remediation of security vulnerabilities in your codebase, leading to stronger defenses and improved overall security posture.
+3. Where to use (use case):
+Ideal for developers and security teams to perform comprehensive security assessments across their entire code repositories.</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS Security Agent</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Feature Store now supports SageMaker Python SDK V3</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-feature-store-pyv3/</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 17:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Feature Store now supports SageMaker Python SDK v3, enhancing access control and storage optimization.
+2. Outcome (impact):
+Data scientists can manage feature groups with fine-grained access controls and optimized storage using modern SDK interfaces, improving governance and performance.
+3. Where to use (use case):
+Ideal for data scientists working on machine learning projects who need to manage feature data with enhanced security and performance.</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Feature Store</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Karpenter now supports Amazon Application Recovery Controller zonal shift</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/karpenter-arc-zonal-shift/</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Karpenter now supports Amazon ARC zonal shift for Amazon EKS, enabling automated traffic redirection away from impaired AZs to maintain application availability.
+2. Outcome (impact):
+   This integration allows for better management of application recovery across AWS Regions and AZs, ensuring higher availability and resilience of Kubernetes applications in Amazon EKS.
+3. Where to use (use case):
+   Ideal for customers deploying highly available applications in Amazon EKS across multiple AZs to prevent single points of failure and ensure continuous operation during AZ impairments.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Karpenter</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Amazon Redshift launches RG instances powered by AWS Graviton</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-redshift-rg-instances-powered-by-graviton</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift introduces RG instances powered by AWS Graviton processors, offering up to 2.4x faster performance and 30% lower cost per vCPU for data warehouse and data lake workloads.
+2. Outcome (Impact):
+Users can achieve significant performance improvements and cost savings, with up to 2.4x faster data processing, and a 30% reduction in price per vCPU.
+3. Where to Use (Use Case):
+Ideal for running data warehouse and data lake workloads, particularly for organizations needing to process large volumes of data with high performance and cost efficiency.</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront Premium flat-rate plan now supports configurable usage allowances</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/cloudfront-configurable-premium-flat-rate-plans/</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudFront's Premium flat-rate plan now allows customers to configure usage allowances from 500 million to 6 billion requests and 50 TB to 600 TB, enabling scalable pricing.
+2. Outcome (impact):
+   Enterprises and mid-sized businesses can now adopt CloudFront's Premium plan without needing custom pricing, allowing them to scale their usage as their application grows.
+3. Where to use (use case):
+   Ideal for businesses with variable or growing content delivery needs, ensuring predictable costs without overage charges.</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports embedding Cases and Customer Profiles in custom agent applications</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-sdk-cases-customer-profiles/</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect Customer now allows embedding Cases and Customer Profiles in custom agent applications for better context and efficiency.
+2. Outcome (impact):  
+Agents can access case details and customer context directly within their custom tools, streamlining issue resolution and enhancing productivity.
+3. Where to use (use case):  
+Ideal for customer service teams using custom applications who need seamless access to customer data and case histories.</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio adds getting started tutorials and in-product release notes</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/smus-getting-started</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 17:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now features getting started tutorials and in-product release notes to enhance user productivity and awareness of new capabilities.
+2. Outcome (impact):
+   Users can quickly learn core workflows and stay updated on new features, improving efficiency and feature adoption.
+3. Where to use (use case):
+   Ideal for data scientists, ML practitioners, and developers looking to streamline their onboarding and keep up with the latest updates in AWS services.</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Domains adds support for 34 new Top Level Domains including .app, .dev, and .health.</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-route-53-domains/</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 15:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Route 53 Domains now supports 34 new TLDs, including .app,.dev, and .health, enhancing domain registration and DNS management capabilities.
+2. Outcome (impact):
+This expansion provides businesses and individuals with industry-specific and purpose-driven domain options, improving their online presence and brand identity.
+3. Where to use (use case):
+- .app: Digital products, mobile apps, SaaS platforms.
+- .dev: Development projects, technical portfolios.
+- .health: Medical services, wellness platforms.
+- .realty: Real estate professionals.</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Amazon Route 53</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -6902,7 +7275,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12 06:30:56</t>
+          <t>2026-05-13 06:41:29</t>
         </is>
       </c>
     </row>
@@ -6923,7 +7296,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3749</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="7">
@@ -6933,7 +7306,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1335</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="8">
@@ -6943,7 +7316,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000266</v>
+        <v>0.000276</v>
       </c>
     </row>
     <row r="9">
@@ -6953,7 +7326,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000379</v>
+        <v>0.000358</v>
       </c>
     </row>
     <row r="10">
@@ -6963,7 +7336,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000645</v>
+        <v>0.000635</v>
       </c>
     </row>
     <row r="11">
@@ -6973,7 +7346,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.010783</v>
+        <v>0.011418</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -7210,6 +7210,228 @@
       <c r="F183" t="inlineStr">
         <is>
           <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Data Agent now available for IAM Identity Center domains</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-data-agent-idc/</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 21:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon SageMaker Data Agent now available in SageMaker Unified Studio domains with IAM Identity Center, enabling data analysts to use natural language for generating code and debugging.
+2. Outcome (impact)
+Data analysts and engineers can significantly reduce time spent on writing complex code by using natural language, leading to faster data analysis and improved productivity.
+3. Where to use (use case)
+Use Data Agent to streamline analytics workflows in SageMaker notebooks and Query Editor for tasks like generating SQL queries, Python code, calculating metrics, and debugging errors.</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Amazon FSx for OpenZFS now supports creating Multi-AZ file systems in shared VPCs</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-fsx-openzfs-multi-az-vpcs/</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon FSx for OpenZFS now supports creating Multi-AZ file systems in shared VPCs, enabling decentralized network and storage administration within AWS organizations.
+2. Outcome (impact):
+Organizations can now run highly available file systems with centralized network management, improving resource accessibility and administration across accounts.
+3. Where to use (use case):
+Ideal for organizations with multiple accounts needing shared, highly available file storage solutions within a centralized VPC management structure.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Amazon FSx for OpenZFS</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now supports M8i and R8i instances with Oracle SE2 License Included</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/amazon-oracle-m8i-r8i-license-included</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for Oracle now supports M8i and R8i instances with Oracle SE2 License Included, offering enhanced performance and cost-efficiency.
+2. Outcome (impact):
+   Customers benefit from up to 15% better price-performance and 2.5x more memory bandwidth, simplifying operations and reducing costs by eliminating the need for separate Oracle licenses and support.
+3. Where to use (use case):
+   Ideal for running Oracle databases in the cloud, especially for applications requiring high performance and cost optimization.</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of P5.48xl instances on SageMaker Studio notebooks</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/p5-48xl-region-expansion-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 04:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has expanded the availability of P5.48xl instances in multiple regions, enhancing performance for deep learning and HPC applications.
+2. Outcome (impact):
+   Accelerates time to solution by up to 4x and reduces ML training costs by up to 40% with powerful H100 GPUs.
+3. Where to use (use case):
+   Ideal for training and deploying complex models in generative AI applications like question answering, code generation, and image/video generation.</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of G6 instances on SageMaker Notebook Instances</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/g6-region-expansion-sagemaker-notebook-instances/</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Tue, 12 May 2026 03:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded the availability of G6 instances on SageMaker notebook instances to several regions, enhancing deep learning capabilities.
+2. Outcome (Impact):
+Customers can now leverage improved deep learning performance for tasks such as generative AI, NLP, and computer vision in multiple regions.
+3. Where to Use (Use Case):
+Generative AI fine-tuning, natural language processing, language translation, computer vision, and recommender engines.</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio notebooks now support P5.4xl instance types</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/p5.4xl-new-launch-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Mon, 11 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker Studio now supports P5.4xl instances with H100 GPUs for enhanced deep learning and HPC performance.
+2. Outcome (impact):  
+Accelerates ML model training by up to 4x and reduces costs by up to 40%, ideal for large language and diffusion models.
+3. Where to use (use case):  
+Training and deploying complex generative AI applications like question answering, code generation, and image/video generation.</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -7275,7 +7497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13 06:41:29</t>
+          <t>2026-05-14 06:39:56</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7508,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -7296,7 +7518,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3891</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="7">
@@ -7306,7 +7528,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1262</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8">
@@ -7316,7 +7538,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000276</v>
+        <v>0.000165</v>
       </c>
     </row>
     <row r="9">
@@ -7326,7 +7548,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000358</v>
+        <v>0.000214</v>
       </c>
     </row>
     <row r="10">
@@ -7336,7 +7558,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000635</v>
+        <v>0.000379</v>
       </c>
     </row>
     <row r="11">
@@ -7346,7 +7568,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.011418</v>
+        <v>0.011797</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -7432,6 +7432,746 @@
       <c r="F189" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront announces Passthrough Mode for mutual TLS (Viewer)</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-cloudfront-mtls-passthrough/</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 22:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudFront now supports passthrough mode for viewer mutual TLS (mTLS) authentication, allowing clients to forward certificates to their origin for validation without CloudFront verification.
+2. Outcome (impact):
+This enables customers to maintain their existing mTLS validation infrastructure at their origin without needing to configure trust stores on CloudFront, simplifying the integration process.
+3. Where to use (use case):
+Ideal for organizations that already have mTLS implementations at their origins and want to leverage CloudFront without altering their current security setup.</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront announces support for OCSP Revocation for Mutual TLS (Viewer)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-cloudfront-mtls-ocsp/</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 22:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudFront now supports OCSP revocation checking for viewer mTLS, enabling real-time validation of client certificate status.
+2. Outcome (impact):
+   This feature allows customers to ensure client certificates are not revoked before accepting connections, enhancing security for regulated industries and zero-trust architectures.
+3. Where to use (use case):
+   Ideal for regulated industries requiring strict certificate validation and environments implementing zero-trust security models.</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Introduces Advanced Prompt Optimization and Migration Tool</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-bedrock-advanced-prompt-optimization-migration-tool/</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 21:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock introduces Advanced Prompt Optimization, a tool to streamline prompt optimization and model migration by comparing original and optimized prompts across multiple models.
+2. Outcome (impact):
+This tool significantly reduces the time spent on prompt optimization and model migration, improving model performance and enabling quicker adaptation to new models.
+3. Where to use (use case):
+Use this tool when migrating to a new model or enhancing the performance of the current model by optimizing prompts and evaluating responses.</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Announcing general availability of Amazon EC2 M3 Ultra Mac instances</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-m3-ultra-mac-instances-generally-available/</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 21:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched M3 Ultra Mac instances, powered by Mac Studio hardware, for developers to handle demanding build and test workloads on Apple platforms.
+2. Outcome (impact):
+These instances offer enhanced performance with more CPU, GPU, and Neural Engine cores, and double the unified memory, enabling faster development cycles and more efficient ML workflows.
+3. Where to use (use case):
+Ideal for Apple developers needing to build, test, and optimize applications for iOS, macOS, iPadOS, tvOS, watchOS, visionOS, and Safari.</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SageMaker AI now supports serverless model customization for Qwen3.6</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-ft-qwen3-6/</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 19:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker now supports serverless model customization for Qwen3.6 27B, enabling fine-tuning with proprietary data.
+2. Outcome (impact):
+Users can now fine-tune Qwen3.6 models for specific domains, improving accuracy and performance without managing infrastructure.
+3. Where to use (use case):
+Adapt Qwen3.6 models for domain-specific tasks, improving accuracy, aligning outputs, and enhancing performance on new tasks.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>AWS Transform agents now available in Kiro, Claude, Cursor, and Codex</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/aws-transform-developer-tools/</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform agents are now available in Kiro, Claude, Cursor, and Codex, offering flexible access to transformation capabilities across various environments.
+2. Outcome (impact):  
+Developers can now seamlessly integrate AWS Transform's migration and modernization expertise into their preferred development workflows, enhancing efficiency and collaboration.
+3. Where to use (use case):  
+Ideal for developers working in agentic IDEs, managing migration jobs via the web console, or integrating programmatically using the MCP server.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AWS Transform introduces the agent builder toolkit Kiro power for building customized transformation agents</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-transform-agent-builder-toolkit/</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the agent builder toolkit Kiro power for AWS Transform, enabling partners and customers to create customized transformation agents for modernization needs.
+2. Outcome (impact):
+This toolkit allows Migration and Modernization Competency Partners, ISVs, and customers to develop unique transformation solutions by integrating their tools and workflows with AWS Transform's AI capabilities.
+3. Where to use (use case):
+Use this toolkit to build and deploy specialized agents for modernizing applications and systems, integrating them seamlessly within AWS Transform.</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>AWS Transform now supports customer-owned artifact stores</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-transform-customer-owned-artifact/</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform now allows enterprises to store transformation artifacts in their own Amazon S3 buckets, enhancing control over data security and compliance.
+2. Outcome (impact):
+This update enables enterprises, especially in regulated industries, to meet data sovereignty and compliance requirements without altering their AWS Transform usage.
+3. Where to use (use case):
+Ideal for enterprises needing centralized artifact storage across multiple AWS accounts while maintaining control over data storage and security.</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>New models for image generation and text embeddings are now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/image-embeddings-models-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces FLUX.2-klein-base-4B for image generation and Qwen3-Embedding-0.6B for text embeddings in SageMaker JumpStart.
+2. Outcome (impact):  
+These new models enhance creative AI applications and multilingual search systems, offering high-quality image synthesis and efficient text representations.
+3. Where to use (use case):  
+Ideal for creative content pipelines, product visualization, semantic search systems, and multilingual document retrieval.</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ARC Region switch adds Lambda event source mapping execution block for event handling during failover</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/region-switch-lambda-esm-execution-block/</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS ARC Region Switch now automates the failover of Lambda event source mappings to prevent duplicate processing during multi-Region application failovers.
+2. Outcome (impact):
+   This update reduces manual intervention and errors during failovers, ensuring smooth and reliable event stream processing across multiple regions.
+3. Where to use (use case):
+   Ideal for event-driven architectures requiring coordinated failover of Lambda functions processing event streams from services like Kinesis, DynamoDB Streams, MSK, or SQS.</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Amazon Application Recovery Controller (ARC)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL now supports change data capture (Preview)</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-aurora-dsql-change-data-capture-preview/</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Aurora DSQL now offers a preview of Change Data Capture (CDC) to stream database changes to Kinesis Data Streams in real-time.
+2. Outcome (impact):
+   Simplifies the process of building event-driven applications and real-time analytics pipelines by eliminating the need for custom streaming pipelines.
+3. Where to use (use case):
+   Ideal for synchronizing data across microservices, triggering AWS Lambda functions, and feeding data to analytics services like Amazon S3, Redshift, and OpenSearch.</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Three new models for speech recognition and text-to-speech are now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/speech-models-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces three new speech models in SageMaker JumpStart for advanced text-to-speech and speech recognition across multiple languages.
+2. Outcome (Impact):
+These models enhance the ability to build multilingual, intelligent voice-powered applications with natural speech synthesis and accurate speech recognition.
+3. Where to Use (Use Case):
+Ideal for real-time interactive voice applications, virtual assistants, transcription services, multilingual customer support, and robust speech-to-text solutions.</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Two new models for agentic coding and efficient AI are now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/agentic-reasoning-models-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces GLM-5.1-FP8 and Phi-4-mini-instruct in SageMaker JumpStart, enhancing agentic coding and efficient AI capabilities.
+2. Outcome (impact):
+These models offer advanced agentic software engineering and efficient reasoning, improving code generation, debugging, and multilingual applications.
+3. Where to use (use case):
+Ideal for automated code review pipelines, edge deployment, latency-sensitive applications, and multilingual chatbots.</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Reference stack outputs across accounts and Regions with AWS CloudFormation and CDK</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-cloudformation-cdk-stack/</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS CloudFormation now allows referencing stack outputs across accounts and regions using the `Fn::GetStackOutput` function, simplifying multi-account and multi-region deployments.
+2. Outcome (impact):  
+This feature reduces manual coordination, minimizes configuration drift, and eliminates deployment deadlocks in CDK applications by enabling direct cross-account and cross-region stack output references.
+3. Where to use (use case):  
+Ideal for managing infrastructure values like VPC IDs or database endpoints across multiple AWS accounts and regions, streamlining the provisioning and management of complex, distributed workloads.</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>CloudFormation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Amazon EC2 X8aedz instances are now available in Europe (Ireland) region</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-x8aedz-europe-ireland/</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 X8aedz instances, powered by 5th Gen AMD EPYC processors, are now available in Europe (Ireland) for high-performance EDA and database workloads.
+2. Outcome (impact):
+These instances provide the highest CPU frequency in the cloud, enabling faster processing of memory-intensive tasks and improved performance for EDA and database applications.
+3. Where to use (use case):
+Ideal for electronic design automation (EDA) workloads, physical layout and verification jobs, and relational databases requiring high single-threaded performance and large memory.</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches permission for agents to view only their own performance evaluations</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-customer-permission-view-own-performance-evaluations/</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now allows agents to view only their own performance evaluations, ensuring privacy and enabling self-improvement.
+2. Outcome (impact):
+Agents can review their feedback privately, leading to better performance and self-improvement without compromising peer data confidentiality.
+3. Where to use (use case):
+Ideal for contact centers aiming to enhance agent performance through personal feedback while maintaining data privacy.</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL supports minor versions 18.4, 17.10, 16.14, 15.18, and 14.23</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-rds-postgresql/</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 16:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for PostgreSQL now supports minor versions 18.4, 17.10, 16.14, 15.18, and 14.23, including PostGIS 3.6.3 for topological queries.
+2. Outcome (impact):
+   Users can upgrade to the latest PostgreSQL minor versions to address security vulnerabilities, benefit from bug fixes, and leverage new PostGIS features for topological data management.
+3. Where to use (use case):
+   Ideal for applications requiring secure, scalable, and high-performance PostgreSQL databases, especially those needing advanced spatial and topological data querying.</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>AWS Transform adds agentic AI assistant to the AWS Toolkit for Visual Studio</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-transform-ai-assistant</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Transform introduces an AI assistant in the AWS Toolkit for Visual Studio, enabling .NET developers to modernize applications interactively within their IDE.
+2. Outcome (impact):
+   Enhances developer productivity by providing a guided, step-by-step modernization experience directly in Visual Studio, reducing context-switching and manual effort.
+3. Where to use (use case):
+   Ideal for.NET developers looking to modernize their applications by leveraging granular control, interactive guidance, and detailed assessment reports within their preferred development environment.</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>AWS RTB Fabric supports custom domains for real-time bidding workloads</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-rtb-fabric-custom-domains/</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS RTB Fabric now allows AdTech companies to use custom domains for real-time bidding without changing their partners' endpoint configurations.
+2. Outcome (impact):
+This update simplifies the setup process between AdTech partners by preserving public endpoints and enabling seamless traffic routing through RTB Fabric.
+3. Where to use (use case):
+AdTech companies can use this feature to maintain their established traffic contracts and route partner traffic through RTB Fabric without requiring changes to their own endpoint configurations.</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AWS RTB Fabric</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports cross-account access for Amazon Athena data sources</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-quick-athena/</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now supports querying Amazon Athena data across different AWS accounts using IAM role chaining, with costs billed to the account where the data resides.
+2. Outcome (impact):
+This feature enhances cross-account data access management, allowing organizations to securely query Athena data from multiple accounts within their Quick deployment while maintaining cost transparency.
+3. Where to use (use case):
+Use this feature to enable multiple teams within an organization to query Athena data from different accounts without compromising security, facilitating better data governance and cost management.</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -7497,7 +8237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14 06:39:56</t>
+          <t>2026-05-15 06:49:36</t>
         </is>
       </c>
     </row>
@@ -7508,7 +8248,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -7518,7 +8258,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2324</v>
+        <v>7746</v>
       </c>
     </row>
     <row r="7">
@@ -7528,7 +8268,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>752</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="8">
@@ -7538,7 +8278,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000165</v>
+        <v>0.00055</v>
       </c>
     </row>
     <row r="9">
@@ -7548,7 +8288,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000214</v>
+        <v>0.00072</v>
       </c>
     </row>
     <row r="10">
@@ -7558,7 +8298,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000379</v>
+        <v>0.00127</v>
       </c>
     </row>
     <row r="11">
@@ -7568,7 +8308,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.011797</v>
+        <v>0.013067</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:F218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8172,6 +8172,339 @@
       <c r="F209" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs announces increased query result limits</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/cloudwatch-logs-query-results/</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch Logs now allows retrieval of up to 100,000 results per query, enhancing data analysis capabilities.
+2. Outcome (impact):
+Customers can now analyze larger datasets without splitting queries, improving efficiency and enabling more comprehensive log analysis.
+3. Where to use (use case):
+Ideal for large-scale log analysis, debugging, and monitoring in environments requiring extensive log data retrieval, such as security audits and performance monitoring.</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless is now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-emr-serverless-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 19:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR Serverless is now available in six new regions, enabling cost-effective, serverless data analytics with automatic scaling and fast launch times.
+2. Outcome (Impact):
+This expansion allows data engineers and analysts to run large-scale analytics workloads in additional geographic locations, enhancing accessibility and reducing latency.
+3. Where to Use (Use Case):
+Ideal for running Apache Spark and Apache Hive applications in regions like Asia Pacific and Latin America, supporting batch, interactive, and streaming workloads.</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>AWS Partner Central agents now accelerates opportunity creation</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-partner-central-agents-oppo</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 18:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Partner Central agents streamline opportunity creation via natural language conversations, reducing data entry time for sales teams.
+2. Outcome (impact):  
+Partners can create higher-quality opportunities faster, improve pipeline hygiene, and shorten sales cycles.
+3. Where to use (use case):  
+Ideal for sales teams looking to efficiently manage and enhance their sales pipeline using AI-driven insights.</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Amazon Connect Cases now lets you edit related items and delete cases from the agent workspace</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-cases-related-item/</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 17:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Cases now allows agents to edit related items and delete cases directly from the agent workspace without needing administrator assistance.
+2. Outcome (impact):
+This update enhances agent efficiency by reducing the need for administrative intervention, enabling quicker resolution of errors and better case management.
+3. Where to use (use case):
+Use this feature in customer service environments where agents need to quickly correct case-related errors or update associated items to improve service accuracy and efficiency.</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Amazon Connect Cases</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL announces Extended Support minor versions 11.22-rds.20260224, 12.22-rds.20260224, and 13.23-rds.20260224</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-rds-postgresql-extended-support/</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 16:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for PostgreSQL introduces Extended Support minor versions 11.22, 12.22, and 13.23 to address security vulnerabilities and bugs, extending support up to three years beyond standard support.
+2. Outcome (impact):
+Users can extend the lifecycle of their PostgreSQL databases with critical security and bug fixes, reducing the urgency to upgrade to new major versions immediately.
+3. Where to use (use case):
+Ideal for organizations needing more time to transition to newer PostgreSQL versions while ensuring their databases remain secure and stable.</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana now supports in-place upgrade to Grafana version 12.4</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-managed-grafana-v12-update/</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 16:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Managed Grafana now supports in-place upgrades to Grafana 12.4, offering enhanced dashboards and new features.
+2. Outcome (impact):  
+   Users can easily upgrade to Grafana 12.4 with improved dashboard performance, new visualization options, and enhanced log analysis capabilities.
+3. Where to use (use case):  
+   Ideal for monitoring and observability teams needing advanced dashboards and query capabilities for metrics, logs, and traces.</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>AWS announces AWS Interconnect - multicloud connectivity with Oracle Cloud Infrastructure in preview</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-announces-AWS-interconnect-multicloud-oci-preview/</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the public preview of AWS Interconnect, enabling seamless multicloud connectivity with Oracle Cloud Infrastructure (OCI) to simplify cross-cloud networking.
+2. Outcome (impact):
+AWS Interconnect simplifies the complexities of multicloud networking, allowing customers to provision resilient and scalable private connections between AWS and OCI, reducing the need for DIY approaches.
+3. Where to use (use case):
+Ideal for organizations adopting multicloud strategies to ensure interoperability, flexibility in technology choices, and ease of application deployment across different cloud environments.</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>AWS Interconnect</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>AWS Organizations now supports higher quotas for service control policies (SCPs)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-organizations-increased-scp-quotas/</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Organizations has increased the quotas for service control policies (SCPs), allowing up to 10 SCPs per node and a maximum size of 10,240 characters per SCP.
+2. Outcome (impact):
+This update enables more granular and comprehensive security controls across your organization, allowing for more detailed permissions and conditions in SCPs.
+3. Where to use (use case):
+Use this feature to implement fine-grained access control policies across your AWS accounts, ensuring better security and compliance management within your organization.</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>AWS Organizations</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7i instances now available in AWS Europe (Paris) region</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-u7i-aws-europe-paris/</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched High Memory U7i instances with up to 16 TiB of DDR5 memory in the Europe (Paris) region, offering enhanced performance and price efficiency.
+2. Outcome (impact):
+U7i instances provide up to 45% better price performance, enabling faster transaction processing and data handling for mission-critical applications.
+3. Where to use (use case):
+Ideal for in-memory databases such as SAP HANA, Oracle, and SQL Server, as well as other data-intensive applications.</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8570,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15 06:49:36</t>
+          <t>2026-05-16 06:14:11</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8581,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -8258,7 +8591,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7746</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="7">
@@ -8268,7 +8601,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2534</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="8">
@@ -8278,7 +8611,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00055</v>
+        <v>0.000224</v>
       </c>
     </row>
     <row r="9">
@@ -8288,7 +8621,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00072</v>
+        <v>0.000318</v>
       </c>
     </row>
     <row r="10">
@@ -8298,7 +8631,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00127</v>
+        <v>0.0005419999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -8308,7 +8641,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.013067</v>
+        <v>0.013609</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F218"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8505,6 +8505,302 @@
       <c r="F218" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>AWS Management Console now displays AWS Local Zones in the Region Selector</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-local-zones-region-selector/</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 21:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Management Console now integrates AWS Local Zones into the Region Selector, enhancing navigation and resource management across global infrastructure.
+2. Outcome (impact):
+This update simplifies the management of resources across multiple Local Zones by providing a unified view and direct access to Local Zone management within the parent Region's Console.
+3. Where to use (use case):
+Ideal for organizations that operate across multiple AWS Local Zones and need streamlined navigation and management of their resources in these zones.</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>AWS Management Console</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>AWS Glue zero-ETL is now available in Asia Pacific (Mumbai) region</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-glue-zero-etl-mumbai-region</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 21:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Glue zero-ETL integrations are now available in the Asia Pacific (Mumbai) region, simplifying data pipelines and reducing latency.
+2. Outcome (impact):  
+Customers can now replicate data in near real-time without managing complex ETL pipelines, accelerating time-to-insight for analytics and machine learning.
+3. Where to use (use case):  
+Ideal for replicating data from various sources like Amazon DynamoDB, Oracle Database@AWS, self-managed databases, and SaaS applications into analytics data stores.</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Amazon Lightsail CDN distributions now support IPv6-only instances as origins</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-lightsail-cdn-ipv6/</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 18:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Lightsail CDN now supports IPv6-only instances as origins, enabling low-latency content delivery globally.
+2. Outcome (impact):
+Customers can now use cost-effective IPv6-only instances for their Lightsail CDN, ensuring content is accessible to all users, including those on non-IPv6 networks.
+3. Where to use (use case):
+Ideal for running websites and applications on IPv6-only instances while delivering content with high speed and low latency to a global audience.</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Amazon Lightsail</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Amazon EVS enables support for 32 hosts per environment</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-evs-32-hosts</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 17:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon EVS now supports up to 32 ESXi hosts per environment, doubling the previous limit of 16 hosts.
+2. Outcome (impact):  
+   This update reduces operational overhead by allowing larger clusters and more flexible configurations within a single environment.
+3. Where to use (use case):  
+   Ideal for organizations needing to manage larger VMware environments with fewer resources and administrative efforts.</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Amazon Elastic VMware Service (Amazon EVS)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>AWS SAM CLI adds AWS CloudFormation Language Extensions support to accelerate local serverless development</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-sam-cli-cloudformation/</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 16:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS SAM CLI now supports AWS CloudFormation Language Extensions, allowing developers to reduce template duplication and accelerate local serverless development.
+2. Outcome (impact):
+   This update enables developers to define resources once and iterate locally without waiting for cloud deployments, shortening iteration cycles and reducing debugging time.
+3. Where to use (use case):
+   Ideal for serverless application development where multiple similar resources need to be defined, such as Lambda functions, DynamoDB tables, or SNS topics.</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AWS Serverless Application Model (SAM) CLI</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Amazon Redshift adds ALTER TABLE for Iceberg tables and writes via the AWS Glue Data Catalog mount</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-redshift-alter-table-iceberg/</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 16:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now supports ALTER TABLE operations for Apache Iceberg tables via the AWS Glue Data Catalog, enabling schema and partitioning modifications without data deletion.
+2. Outcome (impact):
+This update simplifies data pipeline management by allowing schema and partitioning changes directly in Redshift, reducing complexity and latency associated with previous methods.
+3. Where to use (use case):
+Ideal for data engineers managing data lakes, facilitating seamless integration and transformation of data in Redshift while maintaining compatibility with other Iceberg-compatible engines.</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio now supports GPU capacity reservation through SageMaker Flexible Training Plans</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-training-plan-support-for-studio/</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Studio now allows GPU capacity reservations via Flexible Training Plans, providing predictable access to high-performance resources with potential cost savings of up to 65%.
+2. Outcome (impact):
+   Users can achieve significant cost savings and ensure access to high-demand computational resources for machine learning workflows in JupyterLab and Code Editor.
+3. Where to use (use case):
+   Ideal for machine learning practitioners and data scientists who require consistent access to high-performance GPUs for training and development in Amazon SageMaker Studio.</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL now supports new minor versions 8.0.46 and 8.4.9</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-rds-mysql-minor-versions/</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for MySQL now supports new minor versions 8.0.46 and 8.4.9, offering enhanced security, performance, and new features.
+2. Outcome (impact):
+Users can upgrade to the latest MySQL minor versions to fix security vulnerabilities, benefit from performance improvements, and access new functionalities.
+3. Where to use (use case):
+Ideal for web applications, enterprise databases, and any use case requiring a managed MySQL database service with the latest features and security.</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8866,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16 06:14:11</t>
+          <t>2026-05-19 07:34:34</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8877,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -8591,7 +8887,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3151</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="7">
@@ -8601,7 +8897,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1121</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="8">
@@ -8611,7 +8907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000224</v>
+        <v>0.000199</v>
       </c>
     </row>
     <row r="9">
@@ -8621,7 +8917,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000318</v>
+        <v>0.000285</v>
       </c>
     </row>
     <row r="10">
@@ -8631,7 +8927,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0005419999999999999</v>
+        <v>0.000484</v>
       </c>
     </row>
     <row r="11">
@@ -8641,7 +8937,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.013609</v>
+        <v>0.014093</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F226"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8801,6 +8801,233 @@
       <c r="F226" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports data capture for inference workloads</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-hyperpod-data-capture</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 01:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker HyperPod now supports data capture for inference workloads, allowing organizations to monitor and analyze model inputs and outputs.
+2. Outcome (impact):
+   This feature provides enhanced visibility into model performance, aids in debugging, ensures compliance, and supports the creation of datasets for model improvement.
+3. Where to use (use case):
+   Ideal for organizations deploying generative AI and machine learning models that require detailed monitoring and analysis of inference data for performance tuning and compliance.</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Amazon MWAA now supports Apache Airflow 3.2</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/amazon-mwaa-now-supports-apache-airflow-3-2/</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MWAA now supports Apache Airflow 3.2, enhancing data-aware scheduling and developer productivity.
+2. Outcome (impact):
+Enables precise control over data pipeline execution, improved HITL capabilities, and faster rendering of large DAGs.
+3. Where to use (use case):
+Ideal for data engineering teams building and operating data pipelines on AWS.</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow (MWAA)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Amazon Inspector is now available in the AWS Asia Pacific (Taipei) Region</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-inspector-taipei/</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS has launched Amazon Inspector in the Asia Pacific (Taipei) Region, enhancing vulnerability management for EC2, Lambda, and ECR.
+2. Outcome (impact):  
+   This expansion enables continuous vulnerability assessments and security monitoring for workloads in the Taipei region, improving overall security posture.
+3. Where to use (use case):  
+   Ideal for organizations needing automated security assessments for EC2 instances, Lambda functions, and container images in the Asia Pacific region.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Amazon Inspector</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Amazon ECS introduces pause and continue controls for service deployments</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ecs-pause-continue-deployments/</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECS now allows pausing and resuming service deployments at critical stages for manual checks and automation workflows.
+2. Outcome (impact):
+   This feature enhances deployment control, enabling manual approvals, operational checks, and integration tests without disrupting the deployment process.
+3. Where to use (use case):
+   Ideal for scenarios requiring manual intervention, such as security checks, compliance validations, or integration with external systems before proceeding with deployments.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana now supports dual-stack connectivity (IPv6 and IPv4)</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-managed-grafana-ipv6/</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tue, 19 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Managed Grafana now supports dual-stack connectivity, allowing workspaces to use both IPv4 and IPv6.
+2. Outcome (impact):
+   Simplifies network management by eliminating the need for separate address spaces and supports both IPv4 and IPv6, easing the transition to IPv6.
+3. Where to use (use case):
+   Ideal for organizations migrating to IPv6 or those needing to maintain IPv4 compatibility while transitioning.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Introducing pre-fetching and IAM role assumption for AWS Secrets Manager Agent</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/secrets-manager-agent-prefetch-and-role-assumption/</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Secrets Manager Agent now supports pre-fetching secrets at startup and IAM role assumption for cross-account secret retrieval, enhancing security and reducing latency.
+2. Outcome (impact):
+- Reduces application startup latency by caching secrets.
+- Optimizes costs through batch API calls.
+- Strengthens security with role-based secret access.
+- Simplifies multi-account architectures.
+3. Where to use (use case):
+- Microservices requiring multiple secrets at startup.
+- Applications needing secure, cross-account secret retrieval.
+- Environments where minimizing startup time and operational overhead is critical.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -8866,7 +9093,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19 07:34:34</t>
+          <t>2026-05-20 07:34:00</t>
         </is>
       </c>
     </row>
@@ -8877,7 +9104,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -8887,7 +9114,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2797</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="7">
@@ -8897,7 +9124,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1004</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -8907,7 +9134,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000199</v>
+        <v>0.000167</v>
       </c>
     </row>
     <row r="9">
@@ -8917,7 +9144,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000285</v>
+        <v>0.000206</v>
       </c>
     </row>
     <row r="10">
@@ -8927,7 +9154,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000484</v>
+        <v>0.000373</v>
       </c>
     </row>
     <row r="11">
@@ -8937,7 +9164,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.014093</v>
+        <v>0.014466</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F232"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9026,6 +9026,266 @@
         </is>
       </c>
       <c r="F232" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>AWS Security Hub now uncovers identity risks from unused access</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-security-hub-unused-access/</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 20:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Security Hub now identifies and manages identity risks from unused access, integrating these findings into its unified console.
+2. Outcome (impact):
+   Central security teams can now easily detect and remediate unused IAM permissions, roles, and credentials across multiple accounts, reducing identity risks and attack surfaces.
+3. Where to use (use case):
+   This feature is ideal for organizations looking to streamline their identity risk management processes, ensuring that unused access is identified and mitigated efficiently.</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Security Hub Extended expands to 21 curated partner solutions across 9 categories</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-security-hub-extended/</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Hub Extended now includes 21 curated partner solutions across 9 security categories, enhancing flexibility and choice for enterprise security needs.
+2. Outcome (impact):
+This expansion provides users with more options to tailor their security solutions, ensuring better alignment with enterprise security requirements and improved risk identification and response capabilities.
+3. Where to use (use case):
+Ideal for organizations looking to implement a comprehensive, multi-layered security strategy across various domains including endpoint, identity, email, data, and more.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Security Hub</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>AWS announces ExtendDB, an open source DynamoDB-compatible adapter</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-extenddb-dynamodb/</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS launched ExtendDB, an open-source DynamoDB-compatible adapter, enabling DynamoDB-like functionality in environments without managed service access.
+2. Outcome (impact):  
+ExtendDB allows developers to use DynamoDB's programming model locally and in on-premises environments without code changes, enhancing flexibility and development efficiency.
+3. Where to use (use case):  
+Ideal for local development, continuous integration testing, and running DynamoDB-shaped workloads in on-premises data centers using supported databases.</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Service Name: ExtendDB  
+Category: Database</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>AWS Billing Conductor Improves Account Visibility with Billing Transfer Inventory</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-billing-conductor-billing-transfer/</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 16:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Billing Conductor now offers enhanced visibility into accounts that have accepted billing transfer invitations but lack access to pro forma billing data.
+2. Outcome (impact):  
+Customers can now easily identify and resolve gaps in billing visibility, ensuring complete access to pro forma cost data across their Billing and Cost Management tools.
+3. Where to use (use case):  
+Ideal for organizations managing multiple AWS accounts, ensuring all accounts have the necessary billing data for accurate cost management and budgeting.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>AWS Billing Conductor</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ECS supports native integration with Amazon EBS volumes in GovCloud Regions</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/ecs-amazon-ebs-govcloud/</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 15:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon ECS now natively integrates with Amazon EBS volumes in AWS GovCloud Regions, enabling easier deployment of storage-intensive applications.
+2. Outcome (impact):  
+This integration simplifies the management of EBS volumes for ECS tasks, enhancing the flexibility and efficiency of deploying data-intensive workloads.
+3. Where to use (use case):  
+Ideal for ETL jobs, media transcoding, and machine learning inference workloads that require persistent storage.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Announcing the general availability of a new AWS Local Zone in Istanbul, Türkiye</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-local-zones-istanbul-turkiye/</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched a new Local Zone in Istanbul, Türkiye, providing low-latency access to AWS services and meeting data residency needs.
+2. Outcome (impact):
+This new Local Zone enables businesses in Istanbul to achieve lower latency for end-user applications, meet local data regulations, and support AI/ML inference workloads.
+3. Where to use (use case):
+Ideal for applications requiring low latency, such as real-time analytics, AI/ML inference, and content delivery, as well as for businesses needing to comply with local data residency requirements.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family web apps now support federated permissions with IAM Identity Center across AWS Regions</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-transfer-family-federated-permissions-across-regions/</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Transfer Family web apps now support federated permissions with IAM Identity Center across multiple AWS Regions, enhancing user access and reliability.
+2. Outcome (impact):
+   This update allows users to create Transfer Family web apps in any region where IAM Identity Center is enabled, reducing latency and improving reliability for global users.
+3. Where to use (use case):
+   Ideal for organizations needing to provide secure, region-specific access to file transfer services for global users, ensuring low-latency access and consistent user management.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
@@ -9093,7 +9353,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20 07:34:00</t>
+          <t>2026-05-21 07:39:24</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9364,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -9114,7 +9374,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2350</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="7">
@@ -9124,7 +9384,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>726</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8">
@@ -9134,7 +9394,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000167</v>
+        <v>0.000191</v>
       </c>
     </row>
     <row r="9">
@@ -9144,7 +9404,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000206</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="10">
@@ -9154,7 +9414,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000373</v>
+        <v>0.000441</v>
       </c>
     </row>
     <row r="11">
@@ -9164,7 +9424,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.014466</v>
+        <v>0.014907</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9288,6 +9288,339 @@
       <c r="F239" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs Insights adds new query commands and functions</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-logs-insights/</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch Logs Insights now supports 13 new commands and functions for enhanced log querying, transforming, and analysis.
+2. Outcome (impact):
+   Users can now perform advanced string manipulation, encode/decode values, parse various log formats, and calculate geographic distances, leading to deeper insights from log data.
+3. Where to use (use case):
+   Ideal for developers, DevOps engineers, and data analysts who need to analyze and derive meaningful insights from complex log data in AWS environments.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs Insights</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C7i-flex, M7i-flex &amp; M7i instances now available in Asia Pacific (Hyderabad) region</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-c7i-flex-m7i-flex-m7i-instances-HYD-region/</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 19:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched C7i-flex, M7i-flex, and M7i instances in the Asia Pacific (Hyderabad) region, powered by custom 4th Gen Intel Xeon Scalable processors, offering better performance and price-performance.
+2. Outcome (impact):
+Customers can achieve up to 19% better price-performance for general-purpose workloads and up to 15% for compute-intensive tasks, enhancing efficiency and cost-effectiveness.
+3. Where to use (use case):
+Ideal for web and application servers, virtual desktops, batch processing, microservices, gaming servers, CPU-based machine learning, and video streaming.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SageMaker Unified Studio automates Glue connector provisioning for cross-subnet job retries</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/sagemaker-unified-studio-glue/</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 19:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio now automatically provisions Glue connectors across subnets to enable job retries, enhancing data pipeline resilience.
+2. Outcome (impact):
+Reduces unplanned downtime and improves SLA compliance for data pipelines by automatically handling subnet failures.
+3. Where to use (use case):
+Ideal for organizations running critical data pipelines that require high availability and minimal manual intervention.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI now supports OpenAI-compatible APIs for inference endpoints</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-ai-openai-apis/</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 17:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker now supports OpenAI-compatible APIs for inference endpoints, enabling seamless integration with existing tools and frameworks.
+2. Outcome (impact):
+   Users can switch to SageMaker inference endpoints without changing their SDK calls, streaming logic, or framework integrations, simplifying migration and enhancing flexibility.
+3. Where to use (use case):
+   Ideal for developers and data scientists who want to leverage existing tools like the OpenAI SDK, LangChain, and Strands Agents while utilizing SageMaker's scalable and customizable infrastructure.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Amazon Aurora MySQL 8.4  is now generally available</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-aurora-mysql/8-4/</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora MySQL 8.4 is now available, featuring enhanced security defaults, aligned version numbering, and simplified upgrade processes.
+2. Outcome (impact):
+Aurora MySQL 8.4 improves security, simplifies management, and ensures compatibility with community MySQL 8.4, providing a more secure and streamlined database experience.
+3. Where to use (use case):
+Ideal for applications requiring high performance, scalability, and robust security features, such as e-commerce platforms, financial services, and large-scale web applications.</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom now supports the latest GDR updates for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-custom-sql-server-latest-gdr-updates-microsoft-sql-server</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 07:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS Custom for SQL Server now supports the latest GDR updates, including SQL Server 2019 CU32+GDR and SQL Server 2022 CU24+GDR, to address critical vulnerabilities.
+2. Outcome (impact):
+   Users can now upgrade their RDS Custom SQL Server instances to the latest GDR updates, ensuring their databases are secure against recent vulnerabilities.
+3. Where to use (use case):
+   Ideal for enterprises running critical SQL Server applications that require the latest security patches and updates to maintain compliance and security.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock expands support for request-level usage attribution</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-bedrock-request-level-usage-attribution/</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 23:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock now offers request-level usage attribution for model inference, allowing customers to tag and analyze usage by team, project, or environment.
+2. Outcome (impact):
+Customers gain fine-grained visibility into model inference usage, enabling better consumption pattern understanding, cost optimization, and streamlined reporting.
+3. Where to use (use case):
+Use this feature to monitor and manage model inference usage across different teams, applications, and environments within an organization.</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB (with MongoDB compatibility) Serverless is now available on DocumentDB 8.0</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/5/docdb8-serverless</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 18:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon DocumentDB (with MongoDB compatibility) Serverless is now available on DocumentDB 8.0, offering auto-scaling, up to 90% cost savings, and improved performance.
+2. Outcome (impact):
+Users can achieve significant cost savings and performance improvements with automatic scaling and enhanced query capabilities.
+3. Where to use (use case):
+Ideal for applications with variable workloads that require scalable, cost-effective database solutions without managing infrastructure.</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports data quality rule authoring and evaluation</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/smus-data-quality</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 17:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio now supports data quality rule authoring and evaluation, powered by AWS Glue Data Quality, to catch issues before they affect analytics and ML workloads.
+2. Outcome (impact):
+Improves data quality by enabling early detection of data issues in both static and streaming data, ensuring more reliable analytics and machine learning models.
+3. Where to use (use case):
+Ideal for data engineers, analysts, and data scientists working within Amazon SageMaker Unified Studio to maintain high data quality standards in their data pipelines.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21 07:39:24</t>
+          <t>2026-05-22 06:54:38</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9697,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -9374,7 +9707,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2694</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="7">
@@ -9384,7 +9717,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>879</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="8">
@@ -9394,7 +9727,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000191</v>
+        <v>0.00025</v>
       </c>
     </row>
     <row r="9">
@@ -9404,7 +9737,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00025</v>
+        <v>0.000329</v>
       </c>
     </row>
     <row r="10">
@@ -9414,7 +9747,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000441</v>
+        <v>0.00058</v>
       </c>
     </row>
     <row r="11">
@@ -9424,7 +9757,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.014907</v>
+        <v>0.015487</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9621,6 +9621,302 @@
       <c r="F248" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker expands domain management across domain types</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/domain-management-iam-idc/</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 19:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker now allows unified domain management for Identity Center and IAM-based domains within the SageMaker Studio, enabling enhanced project and user management.
+2. Outcome (impact):
+Administrators can now manage Identity Center-based domains more effectively, ensuring consistent VPC configurations and seamless user permissions across projects.
+3. Where to use (use case):
+Ideal for data science teams and administrators managing multi-account environments, ensuring streamlined project creation, user access, and data sharing within SageMaker Studio.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>New agentic migration assessment capabilities now available with AWS Transform</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/assessment-capabilities-transform</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 18:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform now provides enhanced migration assessment capabilities with what-if scenarios, customizable assumptions, and multiple TCO features to accelerate migration decisions.
+2. Outcome (impact):  
+Users can quickly build migration business cases, compare scenarios, and optimize total cost of ownership (TCO) for a more informed migration strategy.
+3. Where to use (use case):  
+Ideal for organizations planning to migrate workloads to AWS, enabling them to evaluate different migration strategies and their financial implications.</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker adds business metadata and governance in IAM-based domains</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/sagemaker-catalog-iam-domains/</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 18:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio now supports business metadata and governance in IAM-based domains, enhancing data cataloging and access management.
+2. Outcome (impact):
+This update enables users to add business context to AWS Glue Data Catalog tables, automate metadata generation, and enforce consistent data definitions and governance policies across the organization.
+3. Where to use (use case):
+Ideal for data engineers, analysts, and data scientists who need to manage and discover data tables efficiently within a governed framework.</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>AWS Security Agent adds verification scripts for pentest findings</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-security-agent/</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 17:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Agent now automates the generation of verification scripts for pentest findings, streamlining vulnerability validation.
+2. Outcome (impact):
+Security teams can more efficiently reproduce and validate vulnerabilities, accelerating the remediation process and improving overall security posture.
+3. Where to use (use case):
+Ideal for security teams performing penetration tests to quickly verify identified vulnerabilities and expedite remediation efforts.</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Personal now supports WorkSpace Migration for Linux WorkSpaces</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/workspaces-linux-migration</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 16:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon WorkSpaces Personal now supports automated migration of Linux WorkSpaces, ensuring seamless transitions between different Linux OS versions.
+2. Outcome (impact):
+This feature allows for effortless upgrades and migrations of Linux WorkSpaces, reducing manual intervention and potential downtime for end users.
+3. Where to use (use case):
+Ideal for IT administrators managing Linux WorkSpaces who need to upgrade to newer OS versions or switch between different Linux distributions without disrupting user data.</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces (for Apache Cassandra) expands to Asia Pacific (Malaysia) and Asia Pacific (Thailand) Regions</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-keyspaces-malaysia-thailand/</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Keyspaces (for Apache Cassandra) is now available in Asia Pacific (Malaysia) and Asia Pacific (Thailand) Regions, offering low-latency, data-residency compliant solutions.
+2. Outcome (impact):
+Organizations in Asia Pacific can now build scalable, low-latency applications with Amazon Keyspaces, meeting data residency requirements while reducing latency.
+3. Where to use (use case):
+Ideal for businesses needing to deploy Cassandra-compatible applications in Asia Pacific, ensuring compliance with regional data laws and improving application performance.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms now supports mutable payment configurations for collaborations</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-clean-rooms-mutable-payments</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Clean Rooms now allows flexible payment configurations for collaboration members, enabling partners to specify cost responsibilities for different analyses.
+2. Outcome (impact):
+Customers gain greater control over payment responsibilities, allowing for tailored cost management in collaborative data analysis projects.
+3. Where to use (use case):
+Ideal for pharmaceutical companies collaborating with healthcare organizations to analyze clinical trial data, where different partners can be assigned to pay for different types of analyses.</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager adds managed external secrets support for Datadog vended keys and Snowflake Programmatic Access Tokens</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/secrets-manager-managed-external-secrets-datadog-snowflake/</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Secrets Manager now supports automatic rotation for Datadog and Snowflake credentials, enhancing security and management of third-party secrets.
+2. Outcome (impact):  
+This update allows for seamless credential rotation, reducing the risk of credential exposure and simplifying secret management for Datadog and Snowflake users.
+3. Where to use (use case):  
+Ideal for organizations using Datadog for monitoring and Snowflake for data warehousing, ensuring secure and automated management of their credentials.</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9982,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 06:54:38</t>
+          <t>2026-05-23 06:16:50</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9993,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -9707,7 +10003,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3527</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="7">
@@ -9717,7 +10013,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1160</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8">
@@ -9727,7 +10023,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00025</v>
+        <v>0.000182</v>
       </c>
     </row>
     <row r="9">
@@ -9737,7 +10033,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000329</v>
+        <v>0.00027</v>
       </c>
     </row>
     <row r="10">
@@ -9747,7 +10043,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00058</v>
+        <v>0.000451</v>
       </c>
     </row>
     <row r="11">
@@ -9757,7 +10053,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.015487</v>
+        <v>0.015938</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9917,6 +9917,43 @@
       <c r="F256" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>AWS Transform now modernizes networks during migrations</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-transform-network-modernization</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 14:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform now automates network modernization during migrations, optimizing designs and resolving conflicts before deployment.
+2. Outcome (impact):
+Reduces manual review time from days to instant, minimizes deployment conflicts, and accelerates migration timelines.
+3. Where to use (use case):
+Ideal for organizations migrating to AWS, needing to modernize and optimize their network infrastructure efficiently.</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -9982,7 +10019,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23 06:16:50</t>
+          <t>2026-05-26 06:52:20</t>
         </is>
       </c>
     </row>
@@ -9993,7 +10030,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -10003,7 +10040,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2563</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7">
@@ -10013,7 +10050,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>949</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -10023,7 +10060,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000182</v>
+        <v>3e-05</v>
       </c>
     </row>
     <row r="9">
@@ -10033,7 +10070,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00027</v>
+        <v>2.7e-05</v>
       </c>
     </row>
     <row r="10">
@@ -10043,7 +10080,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000451</v>
+        <v>5.7e-05</v>
       </c>
     </row>
     <row r="11">
@@ -10053,7 +10090,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.015938</v>
+        <v>0.015995</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9954,6 +9954,302 @@
       <c r="F257" t="inlineStr">
         <is>
           <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports ENA Express for Multi-AZ replication</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-rds-ena-express-multiAZ/</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS now supports ENA Express for Multi-AZ replication, enhancing network performance and reducing latency for write-intensive workloads.
+2. Outcome (impact):  
+Improved write throughput and lower write latencies for Multi-AZ RDS deployments, leading to better performance for database applications.
+3. Where to use (use case):  
+Ideal for write-intensive database workloads requiring high availability and low-latency replication across Availability Zones.</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8i and M8i-flex instances are now available in AWS GovCloud (US-East) Region</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-m8i-m8i-flex-govcloud-east/</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 M8i and M8i-flex instances are now available in AWS GovCloud (US-East) with enhanced performance and price-performance.
+2. Outcome (Impact):
+These instances provide up to 20% better performance, 15% better price-performance, and up to 60% faster NGINX web applications compared to previous generations.
+3. Where to Use (Use Case):
+Ideal for web and application servers, microservices, data stores, virtual desktops, enterprise applications, and large-scale databases like PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8i and R8i-flex instances are now available in AWS GovCloud (US-East) Region</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ec2-r8i-r8i-flex-govcloud-east/</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces R8i and R8i-flex instances in AWS GovCloud (US-East), powered by custom Intel Xeon 6 processors, offering enhanced performance and memory bandwidth.
+2. Outcome (impact):
+   Users can achieve up to 15% better price-performance and up to 60% faster performance for specific workloads compared to previous generations, enhancing efficiency and speed for critical applications.
+3. Where to use (use case):
+   Ideal for memory-intensive workloads such as SAP applications, PostgreSQL databases, NGINX web applications, and AI deep learning models.</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Amazon Elastic Compute Cloud (Amazon EC2)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Amazon VPC IPAM now supports tags on IPAM pool allocations</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-vpc-ipam-tags/</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon VPC IPAM now supports tags on IPAM pool allocations, enhancing IP address management and governance.
+2. Outcome (impact):
+   Improved organization, governance, and access control for IP address allocations across AWS environments.
+3. Where to use (use case):
+   Ideal for network administrators managing IP addresses in large, multi-account environments, ensuring compliance and security.</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Amazon VPC IPAM</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty Malware Protection for AWS Backup supports Amazon S3 continuous backups</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-guardduty-aws-backup-s3-continuous/</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GuardDuty now scans S3 continuous backups for malware, enabling safe recovery points.
+2. Outcome (impact):
+Enhanced security for S3 backups by identifying malware and ensuring clean recovery points.
+3. Where to use (use case):
+Ideal for organizations needing to ensure the integrity of their S3 backups before restoration.</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio adds interactive interface for managing Feature Store in IAM Domains</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/sagemaker-feature-store/</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 20:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker Unified Studio now offers an interactive interface for managing SageMaker Feature Store within IAM domains, streamlining feature management tasks.
+2. Outcome (impact):  
+This update enhances accessibility and efficiency for data scientists, ML engineers, and business analysts by enabling them to manage features without coding, fostering collaboration and accelerating ML workflows.
+3. Where to use (use case):  
+Ideal for managing features in ML projects, such as personalizing music recommendations by handling features like song ratings and listening durations.</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams launches Generation 6e stream classes for high-fidelity game streaming</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/amazon-gamelift-streams-g6e-stream-class/</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 16:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GameLift Streams has introduced Generation 6e stream classes, offering enhanced GPU performance for high-fidelity game streaming.
+2. Outcome (impact):
+   These new G6e stream classes provide up to 2.9x faster GPU memory bandwidth and 2x the GPU memory, enabling smoother and more detailed game streaming experiences.
+3. Where to use (use case):
+   Ideal for streaming AAA-quality games and GPU-intensive applications requiring high frame rates and resolutions.</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now supports browsing job attachments in the monitor</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-deadline-cloud/</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 20:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Deadline Cloud now allows users to browse job attachment files directly in the monitor, simplifying file management for rendering tasks.
+2. Outcome (impact):
+This update enhances efficiency by enabling users to easily view, organize, and download specific input and output files for render jobs, reducing time spent on file management.
+3. Where to use (use case):
+Ideal for teams involved in computer-generated graphics and visual effects for films, television, broadcasting, web content, and design.</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10315,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26 06:52:20</t>
+          <t>2026-05-27 07:09:28</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10326,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -10040,7 +10336,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>416</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="7">
@@ -10050,7 +10346,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8">
@@ -10060,7 +10356,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3e-05</v>
+        <v>0.000217</v>
       </c>
     </row>
     <row r="9">
@@ -10070,7 +10366,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7e-05</v>
+        <v>0.000277</v>
       </c>
     </row>
     <row r="10">
@@ -10080,7 +10376,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7e-05</v>
+        <v>0.000494</v>
       </c>
     </row>
     <row r="11">
@@ -10090,7 +10386,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.015995</v>
+        <v>0.016489</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -10248,6 +10248,413 @@
         </is>
       </c>
       <c r="F265" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of P6-B200 instances on SageMaker Notebook Instances</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/p6-b200-region-expansion-sagemaker-notebook-instances/</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 23:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched P6-B200 instances in US East (N. Virginia) for SageMaker, featuring 8 NVIDIA Blackwell GPUs and 1440 GB of GPU memory, enhancing AI training performance.
+2. Outcome (impact):
+   Users can achieve up to 2x better performance for AI training tasks, enabling efficient development and fine-tuning of large foundation models.
+3. Where to use (use case):
+   Ideal for developing and fine-tuning large language models (LLMs), mixture of experts models, and multi-modal reasoning models for generative AI applications.</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock expands support for Service Quotas</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/5/amazon-bedrock-service-quotas/</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 21:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock now supports Service Quotas for the bedrock-mantle endpoint, providing visibility and management of inference limits.
+2. Outcome (Impact):
+Customers can now monitor and manage their usage limits for the bedrock-mantle endpoint, ensuring they can scale their generative AI applications effectively.
+3. Where to Use (Use Case):
+Ideal for developers building and scaling generative AI applications using foundation models from leading AI companies like OpenAI and Anthropic.</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SageMaker Notebook Instances now support P5.4xl instance types</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/03/p5-4xl-new-instance-launch-sagemaker-notebook-instances/</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 20:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker notebook instances now support P5.4xl instances with H100 GPUs, enhancing performance and reducing costs for ML and HPC applications.
+2. Outcome (impact):
+   Accelerates deep learning and HPC tasks by up to 4x and reduces training costs by up to 40%.
+3. Where to use (use case):
+   Ideal for training and deploying complex models in generative AI applications like question answering, code generation, and image/video generation.</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SageMaker Notebook Instances now support P5en.48xl instance types</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/02/p5en-new-instance-launch-sagemaker-notebook-instances/</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 20:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker notebook instances now support P5en.48xl instances, featuring 8 H200 GPUs and enhanced CPU-GPU bandwidth.
+2. Outcome (Impact):
+   Improved AI training and inference performance with up to 35% lower latency for distributed training workloads.
+3. Where to Use (Use Case):
+   Ideal for deep learning, generative AI, real-time data processing, and high-performance computing (HPC) applications.</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Service: Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Amazon EMR now supports Apache Spark 4.0.2 in general availability</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-emr-apache-spark/</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 20:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR now supports Apache Spark 4.0.2, enhancing data pipeline management, security, and real-time application deployment.
+2. Outcome (impact):
+Easier data pipeline creation, improved security with fine-grained access control, better compliance with Apache Iceberg v3, and faster real-time application deployment.
+3. Where to use (use case):
+Data engineering, real-time analytics, fraud detection, personalization, and other time-sensitive applications.</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Amazon EMR</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>AWS Glue large and memory optimized workers now available in Europe (Spain) Region</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-glue-larger-memory-intensive-workers-spain</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 20:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Glue now provides large and memory-optimized workers in the Europe (Spain) Region, enhancing data processing capabilities for complex workloads.
+2. Outcome (impact):
+   Customers can now handle more demanding data processing tasks efficiently, with improved performance for complex transforms, aggregations, joins, and queries.
+3. Where to use (use case):
+   Ideal for data engineers and analysts needing to process large volumes of data with intensive compute or memory requirements, such as ETL jobs, data transformations, and analytics.</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now uses generative AI to automatically evaluate self-service interactions</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-customer-gen-AI-evaluations-self-service</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now leverages generative AI to automatically evaluate self-service interactions, providing managers with insights to enhance customer experience.
+2. Outcome (impact):
+   Managers can efficiently assess the quality of self-service interactions using custom evaluation criteria, leading to improved AI agent performance and better customer satisfaction.
+3. Where to use (use case):
+   This feature is ideal for customer service managers who need to evaluate and improve the performance of AI agents handling self-service interactions.</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod Slurm clusters now support specifying minimum capacity requirements with continuous provisioning</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-hyperpod-mincount/</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 15:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker HyperPod now allows users to set a minimum capacity requirement for Slurm clusters, ensuring a guaranteed number of nodes are provisioned before job scheduling begins.
+2. Outcome (impact):
+   This feature provides better control over cluster availability, ensuring that distributed training workloads start efficiently and correctly, and helps teams meet SLA or cost-efficiency targets.
+3. Where to use (use case):
+   Ideal for distributed training workloads using frameworks like PyTorch FSDP, Megatron-LM, or NVIDIA NeMo, where a fixed number of nodes is necessary for effective job execution.</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Amazon Aurora MySQL now supports integration with Kiro Powers</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-aurora-mysql-kiro-powers/</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS integrates Amazon Aurora MySQL with Kiro Powers, enabling faster application development through AI-assisted database operations.
+2. Outcome (Impact):
+Developers can now build and manage Aurora MySQL-backed applications more efficiently using natural language commands, reducing complexity and speeding up deployment.
+3. Where to Use (Use Case):
+Ideal for developers looking to streamline database operations and schema design in Aurora MySQL-backed applications.</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Amazon Aurora MySQL</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>AWS Backup adds OTP verification for Multi-party approval on logically air-gapped vaults</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-backup-otp-multi-party-approval-lag/</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Backup now mandates OTP verification for multi-party approval on logically air-gapped vaults, enhancing security for vault operations.
+2. Outcome (impact):
+Increased security for vault operations by ensuring only verified approvers can authorize actions, reducing the risk of unauthorized access.
+3. Where to use (use case):
+Ideal for environments requiring stringent security measures for data protection, such as financial institutions, healthcare providers, and government agencies.</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Amazon EC2 X8i instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/02/amazon-ec2-x8i-instances-SIN-SYD-PDT-region/</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 21:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 X8i instances are now available in Singapore, Sydney, and AWS GovCloud (US-West), offering enhanced performance and memory capacity.
+2. Outcome (impact):
+   Users can leverage up to 43% higher performance, 1.5x more memory, and 3.3x more memory bandwidth for memory-intensive workloads.
+3. Where to use (use case):
+   Ideal for SAP HANA, large databases, data analytics, and Electronic Design Automation (EDA).</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -10315,7 +10722,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27 07:09:28</t>
+          <t>2026-05-28 06:59:58</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10733,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -10336,7 +10743,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3051</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="7">
@@ -10346,7 +10753,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>975</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="8">
@@ -10356,7 +10763,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000217</v>
+        <v>0.000293</v>
       </c>
     </row>
     <row r="9">
@@ -10366,7 +10773,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000277</v>
+        <v>0.000396</v>
       </c>
     </row>
     <row r="10">
@@ -10376,7 +10783,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000494</v>
+        <v>0.0006890000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -10386,7 +10793,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.016489</v>
+        <v>0.017178</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -10657,6 +10657,595 @@
       <c r="F276" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Monitor AWS Budgets directly in Billing and Cost Management Dashboards with new Budgets widget</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/monitor-aws-budgets-using-dashboards</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 20:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS now allows you to monitor AWS Budgets directly within the Billing and Cost Management Dashboards using new Budgets widgets, enhancing cost management efficiency.
+2. Outcome (impact):
+   This update enables finance teams and cloud administrators to monitor budget performance more efficiently by integrating budget data directly into their dashboards, reducing time spent navigating between different console pages.
+3. Where to use (use case):
+   Ideal for organizations looking to streamline their cost management processes, allowing for real-time budget monitoring and better alignment of financial data within their existing dashboards.</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Billing and Cost Management (BCM)</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>AWS IoT Core adds APIs for MQTT connection management</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-iot-core-apis-mqtt/</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 20:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IoT Core introduces new MQTT connection management APIs, GetConnection and ListSubscriptions, to enhance visibility and control over IoT device connections and subscriptions.
+2. Outcome (impact):
+These APIs improve the ability to troubleshoot, monitor, and audit IoT device connections, leading to better performance and security of IoT solutions.
+3. Where to use (use case):
+Use these APIs to manage and troubleshoot IoT device connections, monitor client behavior, and optimize subscription patterns in IoT applications.</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>AWS IoT Core</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>AWS Organizations emits CloudTrail events for account membership changes</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-organizations-cloudtrail/</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Organizations now emits CloudTrail events for account membership changes, enhancing visibility and security monitoring.
+2. Outcome (impact):  
+Improved detection of unauthorized activities and potential security incidents within your organization.
+3. Where to use (use case):  
+Fraud detection, compliance auditing, security monitoring, and incident investigation.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>AWS Organizations</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>AWS announces general availability of the next generation of AWS Resilience Hub</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-announces-next-gen-aws-resilience-hub/</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>1. Short Summary: AWS launches the next-gen Resilience Hub for improved resilience assessment and management of critical workloads.
+2. Outcome (impact): Enhanced visibility, proactive failure mode analysis, and organization-wide resilience policy management.
+3. Where to use (use case): Ideal for platform engineering and site reliability teams managing critical applications on AWS.</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>AWS Resilience Hub</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer expands generative AI-powered post-contact summaries to eight new languages</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-summary-languages/</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 15:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers generative AI-powered post-contact summaries in eight new languages and non-US English variations.
+2. Outcome (impact):
+This expansion enables faster after-contact work for agents and better multilingual oversight for managers, enhancing global customer service efficiency.
+3. Where to use (use case):
+Ideal for global support organizations to generate and review summaries in multiple languages, ensuring consistent service quality across regions.</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8 is now available on AWS</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/claude-opus-4.8-aws/</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 15:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now offers Anthropic's latest AI model, Claude Opus 4.8, enhancing capabilities in coding, agentic tasks, and knowledge work for developers and enterprises.
+2. Outcome (impact):
+Improved autonomous task performance, deeper reasoning, and consistency in production AI applications, making it more reliable for complex, long-running tasks.
+3. Where to use (use case):
+Ideal for developers and enterprises building production AI applications requiring advanced coding assistance, autonomous task execution, and professional knowledge work.</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>DynamoDB Streams now supports AWS PrivateLink for FIPS endpoints in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-dynamodb-streams-privatelink-fips-govcloud/</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   DynamoDB Streams now supports AWS PrivateLink for FIPS endpoints in AWS GovCloud, enhancing security for federal compliance.
+2. Outcome (impact):
+   Government agencies can securely process real-time data streams within AWS network infrastructure, meeting strict federal compliance and regulatory requirements.
+3. Where to use (use case):
+   Ideal for government agencies and organizations needing to implement compliant change data capture (CDC) solutions and event-driven architectures in AWS GovCloud regions.</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>DynamoDB Streams</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications adds support for Windows Desktop OS</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-workspaces-applications-windows-desktop-OS/</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon WorkSpaces Applications now supports Windows Desktop OS with Bring Your Own License (BYOL), allowing customers to use their existing licenses for a seamless experience.
+2. Outcome (impact):  
+Customers can reduce costs by avoiding OS fees, maintain consistent workflows, and minimize onboarding time when transitioning between local and remote work environments.
+3. Where to use (use case):  
+Ideal for organizations needing to stream Windows desktop applications and full desktop experiences at scale while leveraging existing Windows Desktop licenses.</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>WorkSpaces Applications</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>The next generation of Amazon OpenSearch Serverless is now generally available</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-opensearch-serverless-next-generation-generally-available/</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the next generation of Amazon OpenSearch Serverless, offering faster scaling, cost savings, and new integrations for building agents.
+2. Outcome (impact):
+Customers can achieve up to 60% cost savings, faster scaling, and improved resource management with auto scaling and pay-per-usage pricing.
+3. Where to use (use case):
+Ideal for developers building intelligent agents and applications requiring scalable search and vector capabilities.</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>AWS IoT Core now supports direct messaging for point-to-point communication</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-iot-core-direct-messaging/</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 14:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IoT Core now supports direct messaging for point-to-point communication, enhancing message delivery visibility and reducing costs.
+2. Outcome (impact):
+Improved visibility into message delivery and reduced messaging costs by enabling direct communication with connected devices.
+3. Where to use (use case):
+Use cases include remote device management, real-time monitoring, and automated responses in IoT applications.</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>AWS IoT Core</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>AWS Partner Central now supports deal sizing using total contract value (TCV)</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-partner-central-opportunity-deal-sizing-tcv/</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Central now supports deal sizing using total contract value (TCV) to convert it into forecasted monthly recurring revenue (MRR) for faster and more accurate opportunity submissions.
+2. Outcome (impact):
+Partners can now submit opportunities faster and with improved accuracy by leveraging TCV to automatically estimate MRR, enhancing pipeline accuracy and accelerating deal velocity.
+3. Where to use (use case):
+This feature is ideal for AWS Partners managing their sales opportunities, allowing them to quickly and accurately forecast MRR based on TCV, thereby improving their sales process efficiency.</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of P5.48xl instances on SageMaker Notebook Instances</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/p5-48xl-region-expansion-sagemaker-notebook-instances/</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 23:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS has launched P5.48xl instances in Asia Pacific (Tokyo) for SageMaker, powered by H100 GPUs, enhancing deep learning and HPC performance.
+2. Outcome (impact):  
+   Users can accelerate ML model training by up to 4x and reduce costs by up to 40%, enabling faster deployment of generative AI applications.
+3. Where to use (use case):  
+   Ideal for training and deploying large language models, question answering, code generation, video/image generation, and speech recognition.</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Announcing Region Expansion of P4de instances on SageMaker Notebook Instances</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/04/p4de-region-expansion-sagemaker-notebook-instances/</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 23:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched P4de instances in Asia Pacific (Tokyo) for SageMaker, featuring 8 A100 GPUs with 640GB memory, offering 60% better training performance and 20% lower cost.
+2. Outcome (impact):
+Customers can now achieve faster model training times and reduced costs, accelerating their time to market for machine learning projects.
+3. Where to use (use case):
+Ideal for ML training on large datasets and high-resolution data, such as computer vision and natural language processing tasks.</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>AWS Elemental Inference now supports Smart Subtitles for automated live captioning</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/elemental-inference-subtitles</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental Inference now offers Smart Subtitles, an AI-powered feature that automatically generates real-time subtitles for live video streams in multiple languages.
+2. Outcome (impact):
+Broadcasters and streamers can now provide accessible content with real-time subtitles without manual captioning workflows or third-party services, enhancing viewer experience.
+3. Where to use (use case):
+Ideal for live broadcasts, sports events, webinars, and any live streaming content requiring multilingual, real-time subtitles.</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>AWS Elemental Inference</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches granular access controls for the agent login/logout report</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-customer/</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 21:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers tag-based access controls for the agent login/logout report, enhancing compliance and data security.
+2. Outcome (impact):
+This update allows contact center administrators to enforce granular access controls, ensuring that only authorized personnel can view sensitive login/logout information, thus meeting compliance and regulatory requirements.
+3. Where to use (use case):
+Use this feature to manage access to agent login/logout reports in contact centers, ensuring that only relevant team managers can view specific data, such as the Customer Service team manager seeing only Customer Service agents' data.</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>AWS Neuron 2.30.0 now available with NKI 0.4.0 and 22 new NKI Library kernels</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-announce-neuron-2-30-0</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Tue, 26 May 2026 20:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Neuron 2.30.0 is now available with NKI 0.4.0, new hardware capabilities, 22 new NKI Library kernels, and enhanced model porting tools.
+2. Outcome (impact):  
+   This release enhances ML development on AWS Trainium and Inferentia by improving kernel development, optimizing workloads, and simplifying model porting and validation.
+3. Where to use (use case):  
+   Ideal for ML developers optimizing training and inference on AWS Trainium and Inferentia instances, and those porting models to AWS infrastructure.</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>AWS Neuron</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -10722,7 +11311,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28 06:59:58</t>
+          <t>2026-05-29 06:59:53</t>
         </is>
       </c>
     </row>
@@ -10733,7 +11322,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -10743,7 +11332,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4133</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="7">
@@ -10753,7 +11342,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1394</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="8">
@@ -10763,7 +11352,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000293</v>
+        <v>0.000421</v>
       </c>
     </row>
     <row r="9">
@@ -10773,7 +11362,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000396</v>
+        <v>0.00056</v>
       </c>
     </row>
     <row r="10">
@@ -10783,7 +11372,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0006890000000000001</v>
+        <v>0.0009810000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -10793,7 +11382,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.017178</v>
+        <v>0.018159</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F292"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11246,6 +11246,339 @@
       <c r="F292" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Amazon SES now offers inbox placement metrics and blocklist monitoring</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-ses-global-deliverability/</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 21:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SES now provides inbox placement metrics and blocklist monitoring to help improve email deliverability and sender reputation.
+2. Outcome (Impact):
+Customers can now better understand and optimize their email deliverability, reduce spam placements, and maintain a good sender reputation by monitoring inbox placement rates and blocklist activity.
+3. Where to Use (Use Case):
+Marketing teams, customer engagement platforms, and businesses that rely heavily on email communication can use these features to ensure their emails reach the inbox rather than the spam folder.</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Amazon Simple Email Service (SES)</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging RCS for Business now available in 20 additional countries</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-rcs-countries/</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 20:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS End User Messaging now supports RCS for Business in 20 new countries, expanding its reach to 22 countries.
+2. Outcome (impact):  
+Businesses can now send verified, branded RCS messages globally, enhancing customer engagement and communication reliability.
+3. Where to use (use case):  
+Ideal for businesses needing to send high-fidelity, interactive messages to customers in multiple countries.</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports scheduling tasks up to 90 days in advance</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connect-customer-tasks-90day-schedule</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now allows scheduling tasks up to 90 days in advance, aiding in long-term planning and follow-up work.
+2. Outcome (impact):
+Organizations can better manage and route long-term tasks, improving efficiency and ensuring timely follow-ups.
+3. Where to use (use case):
+Ideal for industries like insurance, where managing tasks such as adjuster visits, parts checks, and repair follow-ups over an extended period is crucial.</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>AWS Shield Advanced introduces DDoS attack flow logs</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-shield-ddos/</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Shield Advanced now offers DDoS attack flow logs, providing detailed packet-level visibility into DDoS attacks on protected resources.
+2. Outcome (impact):  
+Enhances security by offering forensic analysis and compliance capabilities, allowing for better post-incident investigation and threat intelligence.
+3. Where to use (use case):  
+Ideal for organizations needing detailed insights into DDoS attacks to improve their security posture and ensure compliance.</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>AWS Shield Advanced</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Amazon Redshift Serverless now offers 4-RPU Minimum Capacity in 7 additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-redshift-serverless-4-rpu-seven-regions/</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Redshift Serverless now supports a minimum of 4 RPUs in 7 new regions, enabling cost-effective data warehousing with lower resource requirements.
+2. Outcome (impact):
+   This update allows users to start with a lower compute capacity, making it more accessible for small to medium workloads and reducing initial costs.
+3. Where to use (use case):
+   Ideal for development environments, small businesses, and startups that need to run analytics without managing clusters and require minimal compute and memory resources.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Amazon Redshift Serverless</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>AWS Interconnect - multicloud now offers a free 500 Mbps tier</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-interconnect-multicloud-offers-free-500-mbps-tier</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced a free 500 Mbps multicloud Interconnect, enabling private connections between AWS and other public clouds at no charge from AWS.
+2. Outcome (Impact):
+This offering simplifies multicloud connectivity, reduces costs for initial multicloud setups, and supports significant data transfer needs without incurring AWS Interconnect charges.
+3. Where to Use (Use Case):
+Ideal for customers adopting multicloud strategies, migrating applications to the cloud, and requiring private, resilient connectivity between AWS and other CSPs for workloads, data replication, or hybrid architectures.</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now supports April 2026 Release Update and Supplemental Patch Bundle</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-rds-oracle-supports-april-2026-release-update-supplemental-patch-bundle</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 07:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for Oracle now supports the April 2026 Release Update and Supplemental Patch Bundle, including security updates and additional patches for specific use cases.
+2. Outcome (impact):  
+Enhanced security and performance for Oracle databases hosted on Amazon RDS, ensuring compliance with the latest Oracle patches and recommendations.
+3. Where to use (use case):  
+Ideal for production and non-production environments where security and performance are critical, such as enterprise applications, data warehousing, and spatial data management.</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Oracle Database@AWS is now available in twenty AWS Regions</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/oracle-database-aws-available-twenty-regions/</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Oracle Database@AWS is now available in eight new regions, expanding its global footprint to twenty regions.
+2. Outcome (impact):  
+   This expansion enables customers in Europe, South America, and Asia Pacific to meet in-region data residency requirements by migrating on-premises Oracle Exadata and RAC applications to AWS.
+3. Where to use (use case):  
+   Ideal for businesses needing to comply with data residency laws in multiple regions while leveraging Oracle's managed Exadata systems on AWS.</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Oracle Database@AWS</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Amazon S3 Tables are now available in two additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-s3-tables-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Tables are now available in the Asia Pacific (Taipei) and Asia Pacific (New Zealand) Regions, offering built-in Apache Iceberg support for efficient tabular data storage.
+2. Outcome (impact):
+This expansion enhances data management capabilities, providing optimized query efficiency and cost management for data lakes in these regions.
+3. Where to use (use case):
+Ideal for organizations managing large-scale data lakes in the Asia Pacific region, requiring efficient and cost-effective tabular data storage and querying.</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29 06:59:53</t>
+          <t>2026-05-30 06:28:12</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11655,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -11332,7 +11665,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5927</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="7">
@@ -11342,7 +11675,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1971</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8">
@@ -11352,7 +11685,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000421</v>
+        <v>0.000237</v>
       </c>
     </row>
     <row r="9">
@@ -11362,7 +11695,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00056</v>
+        <v>0.000318</v>
       </c>
     </row>
     <row r="10">
@@ -11372,7 +11705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0009810000000000001</v>
+        <v>0.000555</v>
       </c>
     </row>
     <row r="11">
@@ -11382,7 +11715,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.018159</v>
+        <v>0.018714</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F301"/>
+  <dimension ref="A1:F318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11579,6 +11579,635 @@
       <c r="F301" t="inlineStr">
         <is>
           <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports Nextflow version pinning at run time</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-healthomics-nextflow-version-pinning-at-runtime/</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS HealthOmics now allows runtime pinning of Nextflow engine versions via the StartRun API, enabling controlled migration and testing.
+2. Outcome (impact):  
+Customers can maintain production stability while testing new Nextflow versions, reducing upgrade risks in regulated environments.
+3. Where to use (use case):  
+Ideal for healthcare and life sciences organizations needing to validate bioinformatics workflows before upgrading to new Nextflow versions.</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports Nextflow version 26.04</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-healthomics-nextflow-version-26-04/</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now supports Nextflow version 26.04, introducing features like record types, strict syntax parser, workflow output summaries, and agent logging mode.
+2. Outcome (impact):
+Customers can save compute time and costs, improve workflow readability and error reduction, and enhance integration and debugging capabilities.
+3. Where to use (use case):
+Ideal for healthcare and life sciences organizations needing scalable, efficient, and accurate bioinformatics workflows.</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Quick Research now supports customer managed keys</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-quick-research-cm-keys</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 18:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick Research now supports encryption with customer-managed keys (CMK) via AWS KMS, enhancing security and compliance for sensitive data.
+2. Outcome (impact):
+   Organizations can now manage their own encryption keys, providing greater security control, audit capabilities, and flexibility over their sensitive data.
+3. Where to use (use case):
+   Ideal for businesses with strict security and compliance requirements, needing to encrypt sensitive business intelligence data.</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Amazon Quick Research</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports VPC connectivity for MCP connections</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-quick-vpc-mcp/</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 17:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now supports VPC connectivity for privately hosted Model Context Protocol (MCP) servers, enabling secure access through private networks.
+2. Outcome (impact):
+Organizations can now securely connect their proprietary applications, custom data sources, and internal tools to Quick without exposing them to the internet.
+3. Where to use (use case):
+Ideal for enterprises that require secure, private connections for their AI workflows, ensuring data privacy and compliance with internal security policies.</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker adds permissions boundaries for SCP compliance</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-scp/</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now supports IAM permissions boundaries, ensuring compliance with SCP requirements without altering security posture.
+2. Outcome (impact):
+   Organizations can adopt SageMaker Unified Studio without modifying their security policies, ensuring that all IAM roles created within projects adhere to predefined permissions boundaries.
+3. Where to use (use case):
+   Ideal for organizations that enforce strict Service Control Policies (SCPs) and need to ensure that all IAM roles created within SageMaker projects comply with these policies automatically.</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Identity now allows you to bring your own secrets with AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/agentcore-identity-secrets-manager/</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Identity now supports bringing your own secrets via AWS Secrets Manager, allowing for enhanced governance and compliance.
+2. Outcome (impact):
+Customers can now manage their secrets with their own policies, including custom CMKs and tagging, reducing friction and improving compliance.
+3. Where to use (use case):
+This feature is ideal for organizations with strict governance requirements that need to manage secrets according to their own policies and compliance standards.</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8i and M8i-flex instances are now available in Asia Pacific (New Zealand) Region</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-m8i-m8i-flex-new-zealand/</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 M8i and M8i-flex instances are now available in Asia Pacific (New Zealand) Region, offering enhanced performance and price-performance.
+2. Outcome (Impact):
+   Users can leverage up to 20% better performance, 15% better price-performance, and significantly higher memory bandwidth for various workloads.
+3. Where to Use (Use Case):
+   Ideal for web and application servers, microservices, data stores, virtual desktops, enterprise applications, and large-scale database and AI workloads.</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8azn instances are now available in Europe (Ireland) Region</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-m8azn-europe-ireland/</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 M8azn instances, powered by 5th gen AMD EPYC processors, are now available in Europe (Ireland) with enhanced performance and networking capabilities.
+2. Outcome (impact):
+   Users can leverage up to 2x compute performance, higher memory bandwidth, and improved networking throughput for latency-sensitive and compute-intensive workloads.
+3. Where to use (use case):
+   Ideal for real-time financial analytics, high-performance computing, HFT, CI/CD, intensive gaming, and simulation modeling in various industries.</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports EFA-only network interfaces</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-hyperpod-efa-only/</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker HyperPod now supports EFA-only network interfaces, allowing dedicated EFA devices without traditional ENA for IP networking, enhancing scalability and performance for large-scale AI/ML workloads.
+2. Outcome (impact):
+This update enables users to scale AI/ML clusters larger without IP address exhaustion, improving the efficiency and performance of inter-node communication in distributed training jobs.
+3. Where to use (use case):
+Ideal for large-scale distributed training workloads in AI/ML where high-throughput, low-latency inter-node communication is critical, and IP networking is not required on every interface.</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now offers troubleshooting skills for AI coding assistants</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-hyperpod-troubleshooting-skills/</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker HyperPod now integrates expert-level AI/ML cluster diagnostics into coding assistants, enhancing troubleshooting efficiency.
+2. Outcome (impact):
+Reduces time and expertise needed to troubleshoot distributed AI/ML infrastructure, leading to faster issue resolution and improved cluster performance.
+3. Where to use (use case):
+Ideal for managing large-scale AI/ML workloads, particularly in environments requiring frequent cluster diagnostics and maintenance.</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect now supports VIF Rate Limiters to help prevent network congestion</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-direct-connect-now-supports-vif-rate-limiters/</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Direct Connect now offers VIF Rate Limiters to manage bandwidth and prevent congestion on dedicated connections.
+2. Outcome (impact):  
+Prevents network congestion by limiting bandwidth usage on individual VIFs, ensuring fair bandwidth distribution among multiple VIFs on the same connection.
+3. Where to use (use case):  
+Ideal for environments with multiple VIFs on a single connection where it's crucial to manage bandwidth effectively to avoid overconsumption by a single VIF.</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock adds Amazon CloudWatch metrics for OpenAI- and Anthropic-compatible APIs</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-supports-cloudwatch-metrics-bedrock-mantle-endpoint/</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 13:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock now offers Amazon CloudWatch metrics for its mantle endpoint, supporting OpenAI and Anthropic APIs, enabling better monitoring and management of inference traffic.
+2. Outcome (impact):
+Customers can now effectively monitor and manage their generative AI application performance, set up alarms for anomalies, and plan capacity more efficiently using detailed metrics.
+3. Where to use (use case):
+Ideal for developers and enterprises building and scaling generative AI applications using Amazon Bedrock, ensuring optimal performance and cost management.</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>GPT-5.5, GPT-5.4, and Codex from OpenAI are now generally available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-openai-models-codex-generally-available/</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Bedrock now offers GPT-5.5, GPT-5.4, and Codex for production use with enhanced security and operational controls.
+2. Outcome (impact):
+Developers can leverage advanced AI models for agentic coding, data analysis, and multi-step tasks, improving productivity and efficiency in software development.
+3. Where to use (use case):
+Ideal for software development, data analysis, and complex autonomous tasks in production environments.</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Amazon SES now supports tenant-level suppression lists</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ses-tenant-level-suppression-lists/</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SES now allows each tenant to maintain separate suppression lists, preventing cross-tenant email suppression issues.
+2. Outcome (impact):
+   This update ensures that bounces and complaints for one tenant do not affect other tenants within the same SES account, enhancing email deliverability and management.
+3. Where to use (use case):
+   Ideal for SaaS providers, enterprises, agencies, and any application managing distinct email streams from a single SES account.</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Amazon Inspector launches improved agent-based scanning for EC2</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-inspector-ec2-agent-scanning-improvements</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Sun, 31 May 2026 14:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Inspector introduces the Inspector VM Scanner for enhanced agent-based EC2 scanning, offering broader vulnerability detection with lower CPU usage.
+2. Outcome (impact):
+Security teams can now detect more vulnerabilities across various software and applications with reduced impact on EC2 instance performance.
+3. Where to use (use case):
+Ideal for organizations needing comprehensive vulnerability assessments on their EC2 instances without compromising production workloads.</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Amazon Inspector</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Amazon Connect’s AI assistant is now available in the UI builder</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-connects-ai-assistant-now-available-ui-builder</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 13:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect's AI assistant is now available in the UI builder, allowing managers to create and modify views using natural language.
+2. Outcome (impact):  
+Reduces the time and expertise needed to build Views by up to 70%.
+3. Where to use (use case):  
+Ideal for contact center managers who need to quickly create and modify UI components for Step-by-Step Guides and Workspace pages.</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Quick Research now supports customer managed keys</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-quick-research-cmk</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Thu, 21 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick Research now supports encryption with customer-managed keys (CMK) via AWS KMS, enhancing security and compliance for sensitive data.
+2. Outcome (impact):
+Organizations can now manage their own encryption keys, providing enhanced security control and comprehensive auditing capabilities, crucial for meeting strict security and compliance requirements.
+3. Where to use (use case):
+Ideal for businesses that require granular control over their sensitive data encryption, particularly those in highly regulated industries needing robust security measures.</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Amazon Quick Research</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -11644,7 +12273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30 06:28:12</t>
+          <t>2026-06-02 08:01:50</t>
         </is>
       </c>
     </row>
@@ -11655,7 +12284,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -11665,7 +12294,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3345</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="7">
@@ -11675,7 +12304,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1118</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="8">
@@ -11685,7 +12314,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000237</v>
+        <v>0.000452</v>
       </c>
     </row>
     <row r="9">
@@ -11695,7 +12324,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000318</v>
+        <v>0.000589</v>
       </c>
     </row>
     <row r="10">
@@ -11705,7 +12334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000555</v>
+        <v>0.001041</v>
       </c>
     </row>
     <row r="11">
@@ -11715,7 +12344,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.018714</v>
+        <v>0.019755</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F318"/>
+  <dimension ref="A1:F328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12208,6 +12208,376 @@
       <c r="F318" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Amazon EKS and Amazon EKS Distro now supports Kubernetes version 1.36</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-eks-distro-kubernetes-version-1-36</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 21:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS EKS and EKS Distro now support Kubernetes version 1.36, introducing new features like User Namespaces and Pod-Level Scaling.
+2. Outcome (impact):
+   Enhanced security with User Namespaces, improved resource management with Pod-Level Scaling, and better hardware health monitoring.
+3. Where to use (use case):
+   Ideal for deploying secure, scalable, and efficient containerized applications across various AWS regions.</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>AWS Config now supports internal service linked rules</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-config-supports-internal-service-linked-rules</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Config now supports internal service linked rules, enabling AWS services to evaluate resource configurations using managed rules without affecting customer setups.
+2. Outcome (impact):
+   This feature allows AWS services to provide integrated security and compliance capabilities using AWS Config managed rules, enhancing service-specific evaluations while customers can continue to use AWS Config for their governance needs.
+3. Where to use (use case):
+   Use this feature to leverage integrated security and compliance evaluations provided by AWS services like AWS Security Hub CSPM, without impacting your existing AWS Config setup.</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>AWS Config</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now supports persistent storage for Service Managed Fleets</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/deadline-cloud/persistent-storage</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Deadline Cloud now offers persistent storage for Service-Managed Fleets, enabling data retention across worker lifecycle events.
+2. Outcome (impact):
+Reduces worker startup time and improves job completion speed by preserving Conda environments, Perforce workspaces, shader caches, and asset collections.
+3. Where to use (use case):
+Ideal for teams running compute-intensive workloads in visual effects, animation, product design, simulation, and gaming.</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio now sets up in seconds with model customization ready from the start</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/quick-setup-model-customization-sagemaker-studio/</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 16:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Studio now sets up in seconds with automatic model customization permissions, speeding up the development process.
+2. Outcome (impact):
+   Users can start building, exploring, and fine-tuning models almost instantly, reducing setup time from minutes to seconds and simplifying permissions management.
+3. Where to use (use case):
+   Ideal for ML practitioners, data scientists, and developers who need a quick and efficient environment to build and deploy machine learning models.</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache for Valkey now supports durability</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/durability-amazon-elasticache</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS ElastiCache for Valkey now supports durability with synchronous and asynchronous write options, ensuring data protection across multiple Availability Zones.
+2. Outcome (impact):
+Enables use of ElastiCache for critical applications requiring low latency and data integrity, expanding its use cases to include AI agent memory, payment tokenization, and more.
+3. Where to use (use case):
+Ideal for AI agent long-term memory, AI agent workflow state, knowledge bases for RAG applications, payment tokenization, and real-time inventory management.</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Amazon Location Service announces public transit and intermodal routing</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-location-service/amazon-location-new-public-transit-intermodal-routing</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 14:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Location Service now supports public transit and intermodal routing, enabling developers to plan multi-modal journeys combining various transport types.
+2. Outcome (impact):
+This enhancement allows applications to provide more accurate and versatile route planning, improving user experience in mobility, logistics, and urban planning.
+3. Where to use (use case):
+Use cases include mobility apps, logistics management, employee commute planning, and urban planning applications that require multi-modal route calculations.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Amazon Location Service</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>AWS Cost and Usage Report 2.0 now supports Athena and Redshift integration</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-cur2.0-athena-redshift/</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 13:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CUR 2.0 now integrates with Athena and Redshift, enabling cost data analysis via SQL without custom data warehousing.
+2. Outcome (impact):
+   Simplifies cost data analysis, reduces manual configuration, and provides automatic updates to cost data in query engines.
+3. Where to use (use case):
+   Ideal for organizations needing detailed, automated cost analysis and reporting without managing complex data infrastructure.</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>AWS Cost and Usage Report</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server supports Bring Your Own Media</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/rds-sqlserver-supports-bring-your-own-media/</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for SQL Server now supports Bring Your Own Media (BYOM), allowing customers to reuse their existing Microsoft SQL Server licenses on AWS.
+2. Outcome (Impact):
+   Customers can now migrate SQL Server applications to AWS RDS without additional licensing costs, reducing overall operating expenses and simplifying license management.
+3. Where to Use (Use Case):
+   Ideal for businesses migrating SQL Server databases from on-premises, other cloud providers, or self-managed EC2 instances to AWS RDS, aiming to leverage managed services while maintaining license compliance.</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>AWS PCS now provides a production-ready Deep Learning AMI</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-pcs-deep-learning-ami/</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 16:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS PCS now offers a production-ready Deep Learning AMI, pre-installed with essential tools for AI/ML and HPC, simplifying cluster management and maintenance.
+2. Outcome (impact):
+This new AMI streamlines the setup of high-performance computing environments, reducing infrastructure management overhead and allowing researchers to focus on innovation.
+3. Where to use (use case):
+Ideal for AI/ML training and HPC workloads, particularly for users leveraging AWS PCS to build scalable, efficient compute environments.</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>AWS ParallelCluster</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>AWS HealthLake now supports CMS Interoperability and Prior Authorization Final Rule (CMS-0057-F) requirements</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-healthlake-cms-cms-0057-f/</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthLake now supports CMS Interoperability and Prior Authorization Final Rule requirements, enabling healthcare payers to comply with new FHIR-based API standards.
+2. Outcome (impact):
+Healthcare payers can now easily implement standardized APIs to meet CMS regulations, improving interoperability and patient data access while ensuring compliance by the 2027 deadline.
+3. Where to use (use case):
+Healthcare payers, including Medicare Advantage organizations, Medicaid managed care plans, CHIP managed care entities, and QHP issuers, can use AWS HealthLake to implement the required APIs for patient and provider data exchange.</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>AWS HealthLake</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -12273,7 +12643,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02 08:01:50</t>
+          <t>2026-06-03 08:24:23</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12654,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12664,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6364</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="7">
@@ -12304,7 +12674,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2074</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="8">
@@ -12314,7 +12684,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000452</v>
+        <v>0.000281</v>
       </c>
     </row>
     <row r="9">
@@ -12324,7 +12694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000589</v>
+        <v>0.000356</v>
       </c>
     </row>
     <row r="10">
@@ -12334,7 +12704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001041</v>
+        <v>0.000637</v>
       </c>
     </row>
     <row r="11">
@@ -12344,7 +12714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.019755</v>
+        <v>0.020392</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F328"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12578,6 +12578,709 @@
       <c r="F328" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>AWS IoT Device Management adds MQTT session data to connectivity status API</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-iot-device-management-mqtt/</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 21:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS IoT Device Management now includes MQTT session data in its connectivity status API, enhancing troubleshooting and auditing capabilities for IoT device fleets.
+2. Outcome (impact):  
+This update allows users to retrieve detailed connection and MQTT session information indefinitely, improving the ability to troubleshoot connectivity issues and audit connection patterns even after devices go offline.
+3. Where to use (use case):  
+Ideal for IoT fleet management where continuous monitoring and long-term troubleshooting of device connectivity issues are crucial, such as in smart manufacturing, logistics, and environmental monitoring.</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>AWS IoT Device Management</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Data Agent now supports conversation history</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-data-agent/</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 20:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Data Agent now supports conversation history, allowing data practitioners to maintain continuity and efficiency across analytical sessions.
+2. Outcome (impact):
+Data analysts and data scientists can save time, avoid rework, and focus more on insights by seamlessly resuming analyses and referencing past interactions.
+3. Where to use (use case):
+Ideal for data teams working in SageMaker Unified Studio, particularly for multi-step analyses, code reuse, and troubleshooting in notebooks and Query Editor workflows.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Data Agent</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports notebook scheduling</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-unified-studio/</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 20:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now allows scheduling, parameterizing, and orchestrating notebook runs directly from the interface, simplifying the transition from experimentation to production.
+2. Outcome (impact):
+   This feature automates recurring workloads, reduces manual effort, and accelerates troubleshooting, making it easier for users to manage and scale their data science projects.
+3. Where to use (use case):
+   Ideal for tasks like generating daily reports, performing data quality checks, retraining models, and creating performance reports for multiple entities.</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>AWS Step Functions adds AgentCore-powered agentic reasoning step</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-step-functions-agentcore/</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Step Functions now integrates with AgentCore in Amazon Bedrock, enabling AI agent reasoning steps in workflows for tasks like document classification and form extraction.
+2. Outcome (Impact):
+This integration allows for automated reasoning tasks within workflows, enhancing efficiency and accuracy in processing documents and forms, with detailed traceability and audit capabilities.
+3. Where to Use (Use Case):
+Ideal for automating complex workflows that require intelligent decision-making, such as processing customer documents, managing insurance claims, or extracting data from various forms.</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>AWS Step Functions</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-5.4 generally available on Amazon Bedrock in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/GPT54-available-in-aws-govcloud-us-west/</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 19:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock now offers GPT-5.4 from OpenAI in AWS GovCloud (US-West), providing secure, high-performance AI capabilities for government and regulated industries.
+2. Outcome (impact):
+Government and regulated industry customers can leverage advanced AI models for professional tasks while ensuring compliance and data security.
+3. Where to use (use case):
+Ideal for government agencies, defense contractors, and regulated industries requiring secure, high-performance AI for tasks like coding, document analysis, and multi-step agentic operations.</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>AWS Compute Optimizer now supports 32-day lookback for EBS volume and ECS service rightsizing recommendations</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-compute-optimizer-ebs-ecs-32-day-lookback/</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Compute Optimizer now offers a 32-day lookback period for EBS volume and ECS service rightsizing recommendations, improving cost and performance optimization.
+2. Outcome (impact):
+Enables better optimization decisions by accounting for monthly utilization patterns, leading to improved cost savings and performance.
+3. Where to use (use case):
+Ideal for workloads with significant month-end processing or varying utilization patterns, ensuring more accurate rightsizing recommendations.</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Compute Optimizer</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>ARC Region switch adds Amazon Aurora scaling and Amazon Neptune global database failover</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/region-switch-aurora-scaling-neptune-failover/</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 17:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Application Recovery Controller (ARC) now supports automated scaling and failover for Amazon Aurora and Amazon Neptune databases across regions.
+2. Outcome (impact):
+   Reduces recovery time objectives (RTO) by automating the scaling and failover processes for multi-region database workloads, minimizing manual intervention during critical failover scenarios.
+3. Where to use (use case):
+   Ideal for organizations running multi-region applications that require rapid recovery and minimal downtime in the event of regional outages, particularly those using Amazon Aurora and Amazon Neptune.</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Amazon Application Recovery Controller (ARC)</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces (for Apache Cassandra) now provides CDC iterator position</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/keyspaces-cdc-iterator-position/</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Keyspaces now provides CDC iterator positions to optimize data stream consumption and reduce costs.
+2. Outcome (impact):
+Customers can now efficiently poll CDC streams, lowering unnecessary consumption costs and improving data processing timeliness.
+3. Where to use (use case):
+Ideal for integrating with analytics, replication, and event-driven applications that require real-time data processing.</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports a localized experience in twelve languages</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/sagemaker-localization</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 15:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now offers a localized experience in twelve languages, enhancing global accessibility for users.
+2. Outcome (impact):
+   This update reduces language barriers, improves productivity, and facilitates better collaboration among global teams by allowing them to use the interface in their preferred language.
+3. Where to use (use case):
+   Ideal for data engineers, analysts, and data scientists working in multinational teams, enabling them to navigate, build, and collaborate more effectively.</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI launches multi-turn reinforcement learning for AI agent model customization</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/multi-turn-reinforcement-learning-on-sagemaker-ai/</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker AI introduces multi-turn reinforcement learning for customizing AI agents, enabling fine-tuning on complex tasks without managing infrastructure.
+2. Outcome (impact):
+This new feature simplifies the training of AI agents for multi-step tasks, reducing the time and complexity involved, and allowing for cost-effective model customization.
+3. Where to use (use case):
+Ideal for developing sophisticated AI agents in customer service, gaming, robotics, and other applications requiring decision-making over multiple steps.</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Amazon ECS Managed Instances now supports AWS Trainium and AWS Inferentia</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ecs-managed-instances-neuron</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS Managed Instances now supports AWS Trainium and AWS Inferentia, purpose-built AI accelerators for scalable AI workloads.
+2. Outcome (impact):
+This integration allows users to leverage AWS's specialized AI hardware for training and inference tasks, enhancing performance and cost efficiency.
+3. Where to use (use case):
+Ideal for deploying generative AI workloads, machine learning model training, and inference tasks requiring high-performance computing.</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>AWS Config now supports 9 new resource types</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-config-new-resource-types</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>1. Short Summary  
+AWS Config now supports 9 new resource types, enhancing monitoring and compliance across Amazon Bedrock and SageMaker services.
+2. Outcome (impact)  
+This update allows for improved visibility and management of AWS resources, enabling better auditing and compliance across expanded service types.
+3. Where to use (use case)  
+Use AWS Config to monitor and manage resources like Bedrock flow aliases and SageMaker endpoints, ensuring they adhere to organizational policies and best practices.</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>AWS Config</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Db2 launches support for IBM Db2 v12.1 and Db2 Community Edition</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-rds-db2-v12-community-edition</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 07:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for Db2 now supports IBM Db2 v12.1, including Standard, Advanced, and Community Editions, with no commercial licensing for development and testing.
+2. Outcome (impact):
+Developers can now easily start developing and testing Db2 applications on AWS without worrying about software licensing fees, enhancing flexibility and reducing costs.
+3. Where to use (use case):
+Ideal for development and testing environments, allowing teams to leverage a fully managed database service without incurring commercial software licensing charges.</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>AWS IoT Core adds new logs to troubleshoot connectivity and authentication</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-iot-core-ping-auth-logs/</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IoT Core introduces new CloudWatch logs for troubleshooting device connectivity and authentication issues, enhancing fleet management.
+2. Outcome (impact):
+These new logs enable quicker identification and resolution of connectivity and authentication problems, improving device fleet reliability and security.
+3. Where to use (use case):
+Use these logs to monitor and troubleshoot IoT devices' connectivity and authentication issues, ensuring smooth operation and security of your IoT fleet.</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>AWS IoT Core</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now optimizes placement of ad-hoc activities in agent schedules</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect-customer-activity-optimization/</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 18:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect Customer now optimizes scheduling of non-productive activities, minimizing impact on service levels.
+2. Outcome (impact):  
+Improves supervisor productivity and ensures consistent service levels by automatically finding optimal times for scheduling events.
+3. Where to use (use case):  
+Useful for scheduling training sessions, meetings, or other non-productive activities for agents.</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports up to 5,000 agents per schedule</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect-customer-5000-agents/</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 18:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now supports up to 5,000 agents per schedule, simplifying large-scale workforce management.
+2. Outcome (impact):
+   This update reduces operational complexity and enhances schedule optimization for larger and shared agent pools.
+3. Where to use (use case):
+   Ideal for businesses needing to manage large teams or multi-skilled agents within a single schedule, such as contact centers with extensive staffing needs.</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now provides schedule update notifications</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect-customer-scheduling-notifications/</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 18:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers automated schedule update notifications via email or text, improving communication efficiency for agents and schedulers.
+2. Outcome (impact):
+Eliminates manual notification efforts, enhances productivity for schedulers and agents by keeping them informed about schedule changes and leave request statuses.
+3. Where to use (use case):
+Ideal for contact centers and customer service teams that rely on Amazon Connect Customer for workforce management and scheduling.</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch now supports querying metrics data up to two weeks old</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-mi-extended-retention-region-expansion</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 02:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch now enables querying metrics data up to two weeks old using Metrics Insights, extending the previous 3-hour limit.
+2. Outcome (impact):
+   This enhancement allows teams to better identify trends and investigate impacts over a longer period, improving operational health and ensuring no issues are missed.
+3. Where to use (use case):
+   Ideal for monitoring dynamic groups of metrics over resources and applications, creating dashboards, and setting alarms for extended trend analysis and post-event investigations.</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Catalog Client for Apache Hive Metastore now supports Hive 3 and discovery of multiple catalogs</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/aws-glue-data-catalog-apache-hive3/</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Sat, 23 May 2026 00:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Data Catalog Client for Apache Hive Metastore now supports Hive 3, enabling the discovery of multiple catalogs.
+2. Outcome (impact):
+This update allows Hive-compatible clients to list and read multiple catalogs within the Glue Data Catalog, enhancing flexibility and integration capabilities.
+3. Where to use (use case):
+Ideal for organizations using Apache Hive who want to leverage AWS Glue Data Catalog for managing metadata across multiple catalogs.</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -12643,7 +13346,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03 08:24:23</t>
+          <t>2026-06-04 07:57:09</t>
         </is>
       </c>
     </row>
@@ -12654,7 +13357,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -12664,7 +13367,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3961</v>
+        <v>6472</v>
       </c>
     </row>
     <row r="7">
@@ -12674,7 +13377,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1254</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="8">
@@ -12684,7 +13387,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000281</v>
+        <v>0.00046</v>
       </c>
     </row>
     <row r="9">
@@ -12694,7 +13397,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000356</v>
+        <v>0.000646</v>
       </c>
     </row>
     <row r="10">
@@ -12704,7 +13407,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000637</v>
+        <v>0.001106</v>
       </c>
     </row>
     <row r="11">
@@ -12714,7 +13417,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.020392</v>
+        <v>0.021498</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -13281,6 +13281,230 @@
       <c r="F347" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Data Agent integrates business context into conversations</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-data-agent-bdc/</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 21:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Data Agent now integrates with SageMaker Catalog to enhance data discovery and code generation using business terminology.
+2. Outcome (impact):
+Data practitioners can generate accurate SQL and Python code faster by leveraging business context, reducing time-to-insight and enabling work in business language.
+3. Where to use (use case):
+Use in SageMaker Unified Studio notebooks and Query Editor to improve data discovery and code generation accuracy.</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Data Agent</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Amazon Cognito now supports multi-Region replication</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cognito-multi-region/</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Cognito now offers multi-Region replication to synchronize user and machine identity data to a standby Region in near real-time, enhancing authentication system resilience.
+2. Outcome (impact):  
+Improves the resilience of authentication systems by providing a standby replica that can handle traffic during regional service disruptions, ensuring continuous access for users without re-authentication.
+3. Where to use (use case):  
+Ideal for applications requiring high availability and disaster recovery for user authentication, such as web and mobile applications needing robust user identity management.</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Amazon Cognito</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>AWS Databases on Vercel now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-databases-vercel-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Vercel now offers AWS databases like Aurora PostgreSQL, Aurora DSQL, and DynamoDB in additional regions, enabling seamless integration and deployment.
+2. Outcome (impact):  
+   Developers can now build and deploy applications with AWS databases in more regions, enhancing flexibility and reducing setup time.
+3. Where to use (use case):  
+   Ideal for developers looking to quickly prototype or deploy applications using Vercel and AWS databases without manual provisioning.
+   Amazon Aurora DSQL | Category: Database  
+   Amazon DynamoDB | Category: Database</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Amazon Aurora PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Amazon EKS Capabilities now supports Amazon CloudWatch Vended Logs</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-eks-capabilities-logging</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EKS now supports log delivery to Amazon CloudWatch Vended Logs for monitoring EKS Capabilities, including Argo CD, ACK, and kro.
+2. Outcome (impact):
+This feature enhances monitoring and troubleshooting capabilities for EKS managed controllers, providing reliable and secure log delivery.
+3. Where to use (use case):
+Ideal for DevOps teams and Kubernetes administrators who need to monitor and troubleshoot EKS managed controllers for better operational insights.</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Amazon MQ is now available in the AWS European Sovereign Cloud (Germany) Region</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-mq-eur-sov-cloud</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 08:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MQ for RabbitMQ is now available in the AWS European Sovereign Cloud (Germany) Region, enabling regulated industries to meet sovereignty requirements.
+2. Outcome (impact):
+Customers in regulated industries and public sector organizations can now deploy RabbitMQ message brokers in a cloud environment entirely within the EU, ensuring compliance with data sovereignty regulations.
+3. Where to use (use case):
+Ideal for financial services, healthcare, and public sector organizations that require data to remain within EU borders to meet regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Amazon MQ</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Messaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock launches a redesigned console optimized for OpenAI- and Anthropic-compatible APIs</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-redesigned-console-optimized-openai-anthropic-compatible-apis/</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon Bedrock introduces a redesigned console optimized for using foundation models compatible with OpenAI and Anthropic APIs, enhancing the workflow for building generative AI applications.
+2. Outcome (impact)
+The new console experience simplifies model selection and accelerates the transition from evaluation to production, allowing developers to quickly integrate models into their applications with prefilled code snippets and streamlined workflows.
+3. Where to use (use case)
+This service is ideal for developers and enterprises looking to build, scale, and manage generative AI applications using high-performing foundation models from leading AI companies.</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -13346,7 +13570,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04 07:57:09</t>
+          <t>2026-06-05 07:14:18</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13581,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -13367,7 +13591,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6472</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="7">
@@ -13377,7 +13601,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2275</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8">
@@ -13387,7 +13611,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00046</v>
+        <v>0.000166</v>
       </c>
     </row>
     <row r="9">
@@ -13397,7 +13621,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000646</v>
+        <v>0.000215</v>
       </c>
     </row>
     <row r="10">
@@ -13407,7 +13631,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001106</v>
+        <v>0.000381</v>
       </c>
     </row>
     <row r="11">
@@ -13417,7 +13641,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.021498</v>
+        <v>0.021879</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F353"/>
+  <dimension ref="A1:F359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -13505,6 +13505,228 @@
       <c r="F353" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Runtime introduces interactive shells for terminal access into agent sessions</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-agentcore-runtime/</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 22:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Bedrock AgentCore Runtime now offers interactive shells via a new API, providing a full terminal experience within isolated microVMs for coding agents.
+2. Outcome (impact):
+   Developers can now interactively manage and debug their coding agents in real-time, enhancing productivity and debugging efficiency.
+3. Where to use (use case):
+   Ideal for developers working with coding agents like Amazon Kiro, allowing them to inspect, run commands, and debug within a persistent terminal session.</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Simplified permissions for Amazon S3 Tables and Iceberg materialized views are now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/gdc-s3tables-simplified-permissions-in-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 21:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Data Catalog now supports IAM-based authorization for Amazon S3 Tables and Iceberg materialized views in AWS GovCloud (US) Regions, simplifying permissions management.
+2. Outcome (impact):
+This update streamlines permission management by allowing users to define all necessary permissions in a single IAM policy, enhancing integration with AWS Analytics services and simplifying access control.
+3. Where to use (use case):
+Use this feature to simplify permissions for Amazon S3 Tables and Iceberg materialized views when integrating with AWS Analytics services like Amazon Athena, Amazon EMR, Amazon Redshift, and AWS Glue, especially in environments requiring strict compliance such as government sectors.</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch UI is now available in GovCloud regions</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/opensearch-ui-govcloud-region</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 20:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Service now offers its modernized UI in AWS GovCloud regions, enhancing collaboration and data exploration capabilities.
+2. Outcome (impact):
+   Users in GovCloud regions can now access the latest UI features for better data insights and collaboration, ensuring compliance and improved operational efficiency.
+3. Where to use (use case):
+   Ideal for government and regulated industries needing secure, compliant data analytics and collaboration tools within the AWS GovCloud environment.</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Amazon ECS with AWS Fargate now supports 32vCPU compute configurations</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ecs-fargate-32vcpu</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECS with AWS Fargate now supports 32vCPU tasks, enabling high-performance computing and large-scale data processing.
+2. Outcome (impact):
+   This update allows customers to run more demanding applications with greater flexibility and performance, scaling applications beyond previous limits.
+3. Where to use (use case):
+   Ideal for high-performance computing, large-scale data processing, AI inference, and other compute-intensive workloads.</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>The AWS MCP Server now supports cross-account and cross-role access</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-mcp-server/</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS MCP Server now supports seamless cross-account and cross-role access for AI coding agents, eliminating the need to restart sessions for profile changes.
+2. Outcome (impact):
+   This feature accelerates development workflows in multi-account environments, allowing developers to switch between accounts and roles without interruptions, enhancing productivity and efficiency.
+3. Where to use (use case):
+   DevOps engineers can diagnose performance issues by querying CloudWatch logs across different accounts, and application developers can manage resources like Lambda configurations and S3 bucket policies across accounts within a single session.</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>AWS Model Context Protocol (MCP) Server</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now supports plugin sync for service-managed fleets</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/deadline-cloud/plugin-sync</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 16:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Deadline Cloud now simplifies plugin delivery to cloud workers in service-managed fleets by automatically syncing plugins from an S3 bucket to workers.
+2. Outcome (impact):
+This feature reduces manual configuration, minimizes setup errors, and ensures jobs start with the correct plugins, enhancing efficiency and reliability for visual effects, animation, and gaming teams.
+3. Where to use (use case):
+Ideal for teams using compute-intensive workloads in visual effects, animation, product design, simulation, and gaming that require consistent plugin availability across multiple cloud workers.</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13792,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05 07:14:18</t>
+          <t>2026-06-06 06:35:00</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13813,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2335</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="7">
@@ -13601,7 +13823,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>758</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -13611,7 +13833,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000166</v>
+        <v>0.000157</v>
       </c>
     </row>
     <row r="9">
@@ -13621,7 +13843,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000215</v>
+        <v>0.000225</v>
       </c>
     </row>
     <row r="10">
@@ -13631,7 +13853,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000381</v>
+        <v>0.000383</v>
       </c>
     </row>
     <row r="11">
@@ -13641,7 +13863,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.021879</v>
+        <v>0.022262</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F359"/>
+  <dimension ref="A1:F374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -13725,6 +13725,561 @@
         </is>
       </c>
       <c r="F359" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>AWS Cost Explorer launches intelligent cost explanations powered by Amazon Q</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-cost-explorer-intelligent-cost-explanations</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 03:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Cost Explorer now offers 'Analyze with Amazon Q' to provide intelligent cost explanations and optimization insights with a single click.
+2. Outcome (impact):
+Reduces the time and effort required for manual cost analysis, enabling users to quickly identify cost trends, drivers, and optimization opportunities.
+3. Where to use (use case):
+Ideal for AWS users looking to efficiently manage and optimize their cloud spending by leveraging AI-driven insights.</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>AWS Cost Explorer</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>AWS Compute Optimizer now supports idle recommendations for six additional resource types</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-compute-optimizer-six-new-idle</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Compute Optimizer now identifies idle resources for six additional services, helping you find cost savings.
+2. Outcome (impact):
+Detect and optimize unused resources across more AWS services, leading to potential cost savings.
+3. Where to use (use case):
+Monitor and manage AWS resources to identify and optimize idle resources, reducing unnecessary costs.</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Compute Optimizer</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Amazon MSK Express Brokers now support automatic topic creation with Kafka Streams</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-msk-express-topic-support-kstreams/</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 19:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MSK Express Brokers now automatically create Kafka topics for Streams applications, simplifying deployment and reducing manual setup.
+2. Outcome (impact):
+   This update allows developers to deploy Kafka Streams applications more efficiently on MSK Express Brokers, saving time and reducing operational overhead.
+3. Where to use (use case):
+   Ideal for developers and operations teams deploying stateful applications using Kafka Streams on Amazon MSK, aiming to streamline the setup process and enhance productivity.</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Amazon MSK</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB now supports engine minor version starting with 5.0.1</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-documentdb-engine-minor-version-5-0-1/</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 18:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon DocumentDB now supports engine minor version 5.0.1, introducing new features and performance enhancements.
+2. Outcome (impact):  
+Users can benefit from enhanced aggregation capabilities, better monitoring, and improved performance metrics with the new minor version.
+3. Where to use (use case):  
+Ideal for applications requiring advanced MongoDB-compatible database features and better performance monitoring.</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs Insights adds 23 new query commands and functions</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-logs-insights-new/</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 17:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon CloudWatch Logs Insights has introduced 23 new query commands and functions, enhancing log querying, parsing, transformation, and analysis capabilities.
+2. Outcome (impact)
+These enhancements enable more sophisticated log analysis, including conditional processing, string manipulation, IP address handling, and complex statistical computations, improving log management efficiency and insights.
+3. Where to use (use case)
+Ideal for developers, system administrators, and security analysts who need to perform detailed log analysis, troubleshoot issues, monitor system performance, and ensure compliance.</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs Insights</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>AWS Savings Plans Purchase Analyzer now supports target coverage analysis</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-savings-plans-coverage/</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 17:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Savings Plans Purchase Analyzer now offers target coverage analysis, allowing users to set specific coverage targets for their On-Demand spend and receive recommendations based on historical usage.
+2. Outcome (impact):
+Users can better plan their Savings Plans purchases to achieve desired coverage levels, potentially leading to significant cost savings and improved budget management.
+3. Where to use (use case):
+Ideal for organizations aiming to maximize their AWS cost savings by strategically planning their Savings Plans purchases based on specific coverage targets.</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>AWS Billing and Cost Management</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>PostgreSQL 19 Beta 1 is now available in Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/postgresql-19-beta-1-amazon-rds-database-preview-environment/</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 17:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS now offers PostgreSQL 19 Beta 1 in the Database Preview Environment, featuring native graph query support and concurrent table repacking.
+2. Outcome (impact):
+   Users can now evaluate PostgreSQL 19's new features, including SQL Property Graph Queries and improved logical replication, with reduced downtime and enhanced database management.
+3. Where to use (use case):
+   Ideal for developers and DBAs looking to test new PostgreSQL 19 functionalities in a fully managed environment before full production deployment.</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>AWS Lambda Managed Instances expands to additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-lambda-managed-instances-region-expansion/</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Lambda Managed Instances (LMI) is now available in all commercial regions, offering managed EC2 instances for Lambda functions with enhanced compute configurations and cost optimization.
+2. Outcome (impact):  
+Customers can leverage specialized hardware, optimize costs using EC2 pricing models, and maintain operational simplicity while processing parallel requests efficiently.
+3. Where to use (use case):  
+Ideal for workloads requiring specialized hardware configurations, steady-state or predictable workloads, and those seeking to maximize resource utilization and optimize costs.</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>AWS Application Migration Service is now AWS Transform MGN</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-transform-mgn-rebrand/</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Application Migration Service (MGN) has been rebranded as AWS Transform MGN, enhancing its integration with AWS Transform for streamlined migrations.
+2. Outcome (impact):
+This rebranding aims to clarify MGN's role in AWS Transform, offering users a choice between manual control and fully automated migration workflows.
+3. Where to use (use case):
+Ideal for enterprises looking to migrate applications to AWS, providing options for both manual and agentic migration processes.</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>AWS Transform MGN</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL now supports the JSONB data type with compression</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-aurora-dsql-supports-jsonb/</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Aurora DSQL now supports PostgreSQL's JSONB data type with optional compression, enhancing storage efficiency for semi-structured data.
+2. Outcome (impact):
+   This update allows users to store semi-structured data more efficiently, reducing storage costs and enabling seamless integration with PostgreSQL-dependent applications.
+3. Where to use (use case):
+   Ideal for storing semi-structured data such as system configuration metadata, API parameters, and event logs alongside relational data.</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>AWS now provides AI-powered cost investigations for cost anomalies</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-ai-powered-cost-investigations/</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 16:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Cost Anomaly Detection now offers AI-powered investigations via Amazon Q, providing quick, plain-language explanations for cost anomalies.
+2. Outcome (impact):
+FinOps teams and engineers can swiftly identify and address cost anomalies, reducing the time from alert to action from hours to minutes.
+3. Where to use (use case):
+Ideal for organizations looking to efficiently manage and optimize cloud spending by quickly understanding the root causes of unexpected cost changes.</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>AWS Cost Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now offers AI agent trace details for self-service voice interactions</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect-ai-agent-traces/</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 16:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now offers AI agent trace details for self-service voice interactions, providing visibility into AI agent reasoning and actions.
+2. Outcome (impact):
+   Enhanced ability to diagnose issues, validate AI agent behavior, and confidently deploy AI-driven customer experiences by understanding how AI agents handle interactions.
+3. Where to use (use case):
+   Useful for customer service teams to troubleshoot and improve AI agent performance in handling customer requests, ensuring better customer satisfaction and support.</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Amazon Redshift reduces manual snapshot cost for Serverless and RG instances</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-redshift-incremental-manual-snapshots/</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift introduces a new billing model for manual snapshots, reducing costs by charging based on unique data blocks instead of total snapshot size.
+2. Outcome (impact):
+Customers will experience lower manual snapshot costs, especially those maintaining multiple snapshots for disaster recovery, testing, or long-term retention. This allows for more frequent snapshots without increased costs.
+3. Where to use (use case):
+Ideal for disaster recovery, testing environments, and long-term data retention strategies where multiple snapshots are necessary.</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server migration cost assessment capabilities now available in AWS Transform</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-rds-sql-server-cost-assessment-aws-transform/</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Mon, 08 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform now offers cost assessment for migrating SQL Server databases to Amazon RDS for SQL Server, using AI-powered analysis and what-if scenarios.
+2. Outcome (impact):
+Customers can estimate migration costs, optimize expenses, and choose the best instance types for their workloads, potentially saving up to 20% with Database Savings Plans.
+3. Where to use (use case):
+Ideal for organizations planning to migrate on-premises SQL Server databases to AWS, aiming to reduce costs and optimize resource utilization.</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8in instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-c8in-asia-pacific-europe/</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8in instances are now available in additional regions, offering enhanced performance and network capabilities.
+2. Outcome (impact):
+   Users can leverage higher performance and network bandwidth for demanding workloads in new regions.
+3. Where to use (use case):
+   Ideal for network-intensive workloads such as distributed compute and large-scale data analytics.</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -13792,7 +14347,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 06:35:00</t>
+          <t>2026-06-09 06:55:11</t>
         </is>
       </c>
     </row>
@@ -13803,7 +14358,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -13813,7 +14368,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2216</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="7">
@@ -13823,7 +14378,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>794</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="8">
@@ -13833,7 +14388,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000157</v>
+        <v>0.000368</v>
       </c>
     </row>
     <row r="9">
@@ -13843,7 +14398,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000225</v>
+        <v>0.000506</v>
       </c>
     </row>
     <row r="10">
@@ -13853,7 +14408,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000383</v>
+        <v>0.000873</v>
       </c>
     </row>
     <row r="11">
@@ -13863,7 +14418,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.022262</v>
+        <v>0.023135</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F374"/>
+  <dimension ref="A1:F382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -14282,6 +14282,302 @@
       <c r="F374" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio Notebooks now support EMR Serverless</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-unified-studio-emr/</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 18:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon SageMaker Unified Studio Notebooks now support Amazon EMR Serverless with Apache Spark Connect, enhancing flexibility for interactive analytics and data engineering.
+2. Outcome (Impact)
+Data engineers and analysts can now choose between Amazon Athena Spark and EMR Serverless as their Spark runtime, optimizing their workloads based on specific requirements.
+3. Where to Use (Use Case)
+Ideal for running PySpark and Spark SQL on EMR Serverless Spark Applications in Notebook cells, suitable for interactive analytics, data engineering, and accelerated Spark development workflows.</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Amazon S3 Access Grants are now available in the AWS European Sovereign Cloud (Germany) Region</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-s3-access-grants-european-sovereign-cloud-germany-region</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 17:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Access Grants are now available in the AWS European Sovereign Cloud (Germany) Region, enabling identity-based access to S3 data.
+2. Outcome (impact):
+Facilitates scalable data permission management by automatically granting S3 access based on corporate identities.
+3. Where to use (use case):
+Use case: Managing data access for enterprise users based on their directory identities, ensuring secure and scalable data permissions.</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>AWS FinOps Agent is now available in preview</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-finops-agent-preview/</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 15:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the FinOps Agent in preview, a tool for cost management that answers cost questions, identifies optimization opportunities, and automates anomaly investigations.
+2. Outcome (impact):
+The FinOps Agent enhances cost management by providing actionable insights, automating routine tasks, and improving collaboration between finance and engineering teams through real-time notifications and reports.
+3. Where to use (use case):
+Ideal for FinOps practitioners and engineering teams looking to optimize AWS costs, automate cost anomaly investigations, and streamline cost reporting and optimization workflows.</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>AWS FinOps Agent</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>AWS announces Claude Fable 5, the first generally available Mythos-class model</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/claude-fable-5-aws/</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 14:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS launches Claude Fable 5, a Mythos-class AI model with enhanced safety features, available generally to all customers via Amazon Bedrock and directly through Anthropic's platform.
+2. Outcome (impact):  
+Enables more autonomous and complex knowledge work and coding tasks, significantly advancing AI capabilities for professional sectors like finance, legal, and engineering.
+3. Where to use (use case):  
+Ideal for professional tasks in finance, legal, marketing, sales, data, and engineering sectors, facilitating advanced autonomous AI applications.</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>AWS Backup support for Amazon EKS is now available in the AWS European Sovereign Cloud (Germany) Region</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-backup-amazon-eks-aws-european-sovereign-cloud/</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Backup now supports Amazon EKS in the AWS European Sovereign Cloud (Germany) Region, offering managed data protection and recovery.
+2. Outcome (impact):  
+   Provides fully-managed, policy-based data protection and recovery for EKS clusters, enhancing disaster recovery, compliance, and upgrade safety.
+3. Where to use (use case):  
+   Ideal for protecting EKS clusters, namespaces, or persistent volumes in the AWS European Sovereign Cloud (Germany) Region.</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Run Interactive Workloads on Amazon EMR Serverless with Spark Connect</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-emr-serverless-spark-connect</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR Serverless now supports interactive Spark sessions with Spark Connect, allowing seamless integration with managed notebooks and IDEs for efficient data processing.
+2. Outcome (impact):
+Enables developers to interactively develop, debug, and deploy Apache Spark applications with persistent Spark contexts, enhancing productivity and workflow efficiency.
+3. Where to use (use case):
+Ideal for data scientists and engineers who need to perform ad hoc data exploration, iterative debugging, and incremental development of PySpark jobs within a managed environment.</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>The AWS Command Line Interface (CLI) now supports the Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-cli-agent-toolkit/</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CLI now supports the Agent Toolkit for AWS, enabling easy installation and management of coding agents with expert guidance.
+2. Outcome (Impact):
+This update streamlines the process of equipping coding agents with AWS expertise, enhancing productivity and efficiency for developers.
+3. Where to Use (Use Case):
+Ideal for developers and DevOps teams looking to integrate AWS services into their coding agents for better task automation and management.</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>AWS CLI</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches real-time dashboard alerts from conversational analytics</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect-customer/</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Wed, 03 Jun 2026 03:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect Customer introduces real-time dashboard alerts for supervisors based on conversational analytics, improving response times and customer outcomes.
+2. Outcome (impact):  
+Supervisors can intervene faster and coach agents in real-time, potentially reducing customer churn and enhancing overall customer satisfaction.
+3. Where to use (use case):  
+Ideal for contact centers aiming to monitor live calls and chats, enabling proactive management of customer interactions.</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -14347,7 +14643,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09 06:55:11</t>
+          <t>2026-06-10 07:14:14</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14654,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -14368,7 +14664,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5181</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="7">
@@ -14378,7 +14674,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1780</v>
+        <v>973</v>
       </c>
     </row>
     <row r="8">
@@ -14388,7 +14684,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000368</v>
+        <v>0.000195</v>
       </c>
     </row>
     <row r="9">
@@ -14398,7 +14694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000506</v>
+        <v>0.000276</v>
       </c>
     </row>
     <row r="10">
@@ -14408,7 +14704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000873</v>
+        <v>0.000471</v>
       </c>
     </row>
     <row r="11">
@@ -14418,7 +14714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.023135</v>
+        <v>0.023606</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F382"/>
+  <dimension ref="A1:F390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -14578,6 +14578,306 @@
       <c r="F382" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-5.4 and GPT-5.5 models now available in US East (N. Virginia) on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/openai-gpt-us-east-virginia-amazon/</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 00:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has expanded the availability of OpenAI's GPT-5.4 and GPT-5.5 models in the US East (N. Virginia) region on Amazon Bedrock.
+2. Outcome (impact):  
+Developers can now leverage advanced generative AI capabilities for a variety of tasks, including reasoning, coding, document workflows, and long-running agentic tasks.
+3. Where to use (use case):  
+These models are ideal for building applications that require advanced AI capabilities such as complex reasoning, coding assistance, document automation, and long-running tasks.</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service launches MCP Apps for agentic observability</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/opensearch-agentic-observability-mcp-app</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 22:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Service integrates MCP Apps for enhanced observability within IDEs, enabling AI agents to investigate incidents using logs, traces, metrics, and alerts.
+2. Outcome (impact):
+   This integration streamlines incident investigation and root cause analysis, allowing teams to work more efficiently within their local development environments.
+3. Where to use (use case):
+   Ideal for developers and DevOps teams needing to analyze and troubleshoot issues in real-time using integrated tools within their IDE.</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Amazon ECS Managed Daemons now support inter-task visibility and communication</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ecs-managed-daemons-pid-ipc-modes/</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECS now supports inter-task visibility and communication for managed daemons, enabling process-aware and IPC-dependent agents to run as daemons.
+2. Outcome (impact):
+   This feature allows for better deployment and management of tracing, profiling, and security agents, improving observability and security across ECS workloads.
+3. Where to use (use case):
+   Ideal for deploying agents that need access to application processes and shared IPC resources, such as monitoring, security, and profiling tools.</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M9g and M9gd general purpose instances are now available</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ec2-m9g-m9gd-instances-graviton5-processors-available</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 M9g and M9gd instances, powered by AWS Graviton5 processors, are now available, offering enhanced performance and security for general-purpose workloads.
+2. Outcome (impact):
+- Up to 25% better compute performance compared to previous generations.
+- Up to 30% faster for databases, 35% faster for web apps and machine learning.
+- Enhanced security with the Nitro Isolation Engine.
+3. Where to use (use case):
+- General-purpose workloads (application servers, microservices, gaming, caching, containers).
+- AI use cases (real-time reasoning, code generation, multi-step orchestration).
+- High-speed, low-latency storage needs (media processing, batch and log processing).</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B200 instances are now available in the AWS GovCloud (US-East) Region</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-p6-b200-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 14:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 P6-B200 instances with enhanced AI capabilities are now available in AWS GovCloud (US-East).
+2. Outcome (impact):
+These instances offer up to 2x performance improvement for AI training and inference, making them ideal for demanding AI workloads.
+3. Where to use (use case):
+Ideal for AI training and inference tasks, especially in government and regulated industries requiring high-performance computing.</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>AWS Cost and Usage Report 2.0 now supports table configurations update</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-cost-usage-report/</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 13:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CUR 2.0 now allows updates to data table configurations without deleting existing exports.
+2. Outcome (impact):
+   Customers can now adopt new CUR 2.0 features, such as additional columns and finer granularity, without disrupting their existing ETL jobs.
+3. Where to use (use case):
+   Ideal for businesses needing to integrate new AWS billing data features without reconfiguring their entire data pipeline.</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>AWS Cost and Usage Report</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Amazon FSx for OpenZFS Intelligent-Tiering storage class is now available in 8 additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-fsx-openzfs/</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 20:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon FSx for OpenZFS now supports Intelligent-Tiering storage in 8 new regions, offering cost-effective, high-performance storage for various file workloads.
+2. Outcome (impact):
+Users can achieve significant cost savings (up to 85% compared to FSx SSD) while maintaining high performance for active data, making it ideal for large-scale file storage needs.
+3. Where to use (use case):
+Ideal for general-purpose file workloads such as file shares, archives, media libraries, and on-premises HDD storage migrations.</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Amazon FSx for OpenZFS</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Announcing metal-48xl and metal-96xl for Amazon EC2 network/EBS instances</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-metal-sizes-network-EBS/</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces metal-48xl and metal-96xl instances for EC2, featuring enhanced compute performance and network/EBS bandwidth.
+2. Outcome (impact):
+These instances offer up to 43% better compute performance per vCPU and significantly higher network/EBS bandwidth, improving efficiency for high-demand workloads.
+3. Where to use (use case):
+Ideal for real-time big data analytics, AI/ML clusters, high-performance file systems, large commercial databases, and network-intensive applications.</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14943,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10 07:14:14</t>
+          <t>2026-06-11 08:09:29</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14964,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2740</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="7">
@@ -14674,7 +14974,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>973</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8">
@@ -14684,7 +14984,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000195</v>
+        <v>0.000238</v>
       </c>
     </row>
     <row r="9">
@@ -14694,7 +14994,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000276</v>
+        <v>0.000306</v>
       </c>
     </row>
     <row r="10">
@@ -14704,7 +15004,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000471</v>
+        <v>0.000543</v>
       </c>
     </row>
     <row r="11">
@@ -14714,7 +15014,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.023606</v>
+        <v>0.024149</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F390"/>
+  <dimension ref="A1:F399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -14878,6 +14878,339 @@
       <c r="F390" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Application Signals now supports infrastructure, logs, and traces context for faster troubleshooting</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/cloudwatch-application-signals-supports infrastructure-logs-traces-context-for-faster troubleshooting/</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 20:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch Application Signals now integrates infrastructure, logs, and traces for faster troubleshooting, ranking services by health and providing detailed insights without switching tools.
+2. Outcome (impact):
+   Operators can quickly identify and resolve issues by viewing compute environment, log snippets, and trace details in one place, reducing troubleshooting time from hours to minutes.
+3. Where to use (use case):
+   Ideal for monitoring and troubleshooting distributed applications running on Amazon EKS, Amazon ECS, AWS Lambda, and Amazon EC2.</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Application Signals</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Amazon Aurora now supports PostgreSQL major version 18</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-aurora-postgresql-major-version-18/</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 18:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora now supports PostgreSQL major version 18, enhancing query performance and introducing new database management features.
+2. Outcome (impact):
+Improved query performance, reduced index storage and maintenance overhead, faster large transaction replication, and efficient set operations directly in the database.
+3. Where to use (use case):
+Audience segmentation, tag-based filtering, permission checks, and any application requiring fast, memory-efficient set operations on large collections of integers.</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>AWS Elastic Beanstalk console now integrates CloudWatch Logs in the Logs tab</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/elastic-beanstalk-cloudwatch-logs/</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elastic Beanstalk now integrates CloudWatch Logs directly in the console, allowing users to view logs without navigating to the CloudWatch console.
+2. Outcome (impact):  
+This integration streamlines log management by providing direct access to CloudWatch logs within the Elastic Beanstalk console, saving time and improving efficiency.
+3. Where to use (use case):  
+Ideal for developers and DevOps teams managing applications on AWS Elastic Beanstalk, enabling easier log monitoring and troubleshooting.</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Elastic Beanstalk</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Amazon MWAA Serverless now supports Amazon EventBridge notifications</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-mwaa-serverless-eventbridge/</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MWAA Serverless now integrates with Amazon EventBridge to notify on workflow and task state changes.
+2. Outcome (impact):
+This integration allows for automated event-driven workflows, improving monitoring and operational efficiency.
+3. Where to use (use case):
+Automate alerts, restart dependent pipelines, and log state transitions for compliance and auditing in data engineering workflows.</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow (MWAA)</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus now supports Native Histograms</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-managed-service-prometheus-native-histograms/</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Managed Service for Prometheus now supports Prometheus native histograms, allowing for precise metric distribution monitoring with reduced cardinality and cost.
+2. Outcome (impact):
+DevOps engineers can achieve more accurate percentile calculations and monitor latency and request durations more effectively, with lower resource consumption and cost.
+3. Where to use (use case):
+Monitoring application performance metrics such as latency, request durations, and other distribution metrics in production environments.</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus now supports out of order sample ingestion</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-managed-service-prometheus-outoforder-ingestion/</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Managed Service for Prometheus now supports out-of-order sample ingestion and workspace-level rule query offset to enhance data completeness and alerting accuracy.
+2. Outcome (Impact):
+   Reduces data loss and improves alerting accuracy for workloads with distributed collectors, batched exports, or variable network latency by ensuring late-arriving samples are ingested and evaluated correctly.
+3. Where to Use (Use Case):
+   Ideal for monitoring and alerting systems where data collection and network latency can cause out-of-order sample ingestion, ensuring more reliable metrics and alerts.</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>AWS announces AWS Workload Credentials Provider</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-workload-credentials-provider/</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces the Workload Credentials Provider, a tool automating certificate deployment from ACM and caching secrets from Secrets Manager, simplifying certificate management and secret access.
+2. Outcome (impact):
+   This tool reduces the complexity of managing certificate renewals and secret access, ensuring smooth operation and reducing the risk of expiry-related failures across AWS and non-AWS environments.
+3. Where to use (use case):
+   Ideal for organizations running both AWS and non-AWS workloads that require secure and automated management of certificates and secrets, particularly for web servers using Apache or NGINX.</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>AWS Workload Credentials Provider</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Gemma 4 models now available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/gemma-4-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 19:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces Gemma 4 models on Amazon Bedrock, offering open-weight models for generative AI applications across various workflows.
+2. Outcome (impact):
+Enables developers to build advanced generative AI applications with improved reasoning, multimodal understanding, and support for multiple languages and media types.
+3. Where to use (use case):
+Ideal for reasoning-heavy tasks, coding assistance, cost-effective solutions, and low-latency interactive applications.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Amazon Virtual Private Cloud (VPC) Flow Logs introduces additional metadata</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-flow-logs-metadata</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 16:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon VPC Flow Logs now include EC2 resource tags and next-hop interface metadata, enhancing network monitoring and troubleshooting by integrating metadata directly into flow logs.
+2. Outcome (impact):
+This update simplifies the process of correlating flow log data with resource metadata, reducing manual effort and improving the efficiency of network traffic analysis and troubleshooting.
+3. Where to use (use case):
+Ideal for network administrators and security teams who need to monitor and troubleshoot network traffic, ensuring better visibility into how traffic flows through their VPC, especially across complex network architectures.</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>VPC Flow Logs</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -14943,7 +15276,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11 08:09:29</t>
+          <t>2026-06-12 07:27:43</t>
         </is>
       </c>
     </row>
@@ -14954,7 +15287,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -14964,7 +15297,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3348</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="7">
@@ -14974,7 +15307,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1076</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +15317,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000238</v>
+        <v>0.000251</v>
       </c>
     </row>
     <row r="9">
@@ -14994,7 +15327,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000306</v>
+        <v>0.000321</v>
       </c>
     </row>
     <row r="10">
@@ -15004,7 +15337,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000543</v>
+        <v>0.000572</v>
       </c>
     </row>
     <row r="11">
@@ -15014,7 +15347,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.024149</v>
+        <v>0.024721</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F399"/>
+  <dimension ref="A1:F407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -15211,6 +15211,302 @@
       <c r="F399" t="inlineStr">
         <is>
           <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Amazon Lightsail is now available in three additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-lightsail-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Fri, 12 Jun 2026 20:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Lightsail is now available in Asia Pacific (Hong Kong), South America (São Paulo), and Europe (Spain), enhancing global accessibility and performance.
+2. Outcome (Impact):
+Customers in these regions can benefit from lower latency, better performance, and compliance with local data residency requirements, facilitating efficient application deployment.
+3. Where to Use (Use Case):
+Ideal for startups, small businesses, and developers needing to run applications closer to their end users with reduced latency and predictable pricing.</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Amazon Lightsail</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>SageMaker AI now supports serverless fine-tuning for NVIDIA Nemotron models</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-sagemaker-ft-nemotron-3/</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Fri, 12 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker AI now supports serverless fine-tuning for the NVIDIA Nemotron 3 Nano model, enabling domain-specific customization without managing infrastructure.
+2. Outcome (impact):
+This update allows users to efficiently adapt the powerful 30B parameter Nemotron model to their specific needs, improving accuracy and performance on proprietary tasks while reducing operational overhead.
+3. Where to use (use case):
+Ideal for organizations needing to fine-tune large language models for specific applications, such as enhancing customer service chatbots, industry-specific content generation, or compliance-driven text processing.</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I7i instances now available in AWS Europe (Paris) Region</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-i7i-instances-europe-paris-region/</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Fri, 12 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces high-performance I7i instances in Europe (Paris) with enhanced compute and storage capabilities.
+2. Outcome (impact):  
+Improved compute performance by up to 23% and storage performance by up to 50% with lower latency and variability.
+3. Where to use (use case):  
+Ideal for I/O intensive and latency-sensitive workloads such as databases requiring high random IOPS.</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Capacity Blocks for ML is now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-capacity-blocks-ml-govcloud/</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Fri, 12 Jun 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 Capacity Blocks for ML is now available in AWS GovCloud (US) Regions, allowing government and regulated-industry customers to reserve GPU capacity for machine learning workloads.
+2. Outcome (impact):
+This update enables government and regulated-industry customers to secure GPU instances for machine learning tasks, ensuring low-latency and high-throughput connectivity for pre-training, fine-tuning, prototyping, and handling demand surges.
+3. Where to use (use case):
+Use this service for government and regulated industries needing to reserve GPU capacity for machine learning workloads, ensuring continuous access to accelerated compute for various ML tasks.</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7i-8TB instances now available in AWS Europe (Paris) region</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-u7i-8tb-europe-paris/</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has launched U7i-8TB instances in the Europe (Paris) region, offering 8 TiB of DDR5 memory and 448 vCPUs for high-memory workloads.
+2. Outcome (impact):
+Customers can now achieve up to 45% better price performance for memory-intensive applications in the Europe (Paris) region.
+3. Where to use (use case):
+Ideal for mission-critical in-memory databases such as SAP HANA, Oracle, and SQL Server.</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Amazon Quick now integrates with Snowflake Cortex AI</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-quick-snowflake-cortex-ai/</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 22:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick integrates with Snowflake Cortex AI, allowing teams to query data and documents using natural language and automate workflows within Quick.
+2. Outcome (impact):
+This integration enables teams to efficiently manage multi-step processes involving both structured and unstructured data, enhancing productivity and decision-making.
+3. Where to use (use case):
+Ideal for businesses needing to automate workflows that span across structured databases and unstructured documents, such as data analysis, customer support, and compliance tasks.</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports local clusters on AWS Outposts with Amazon EC2 instance store</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-eks-aws-outposts-ec2-instance-store/</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 20:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS EKS now supports local clusters on Outposts with EC2 instance store, enhancing data residency and network resilience.
+2. Outcome (impact):  
+   This update provides advanced data residency, minimizes network dependency risks, and offers feature parity with cloud-based EKS clusters.
+3. Where to use (use case):  
+   Ideal for organizations requiring strict data residency, reduced latency, and operational continuity in hybrid environments.</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>AWS Lake Formation extends table permissions to access underlying data in Amazon S3</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-lake-formation-access-data-amazon-s3</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lake Formation now allows table permissions to access underlying data in Amazon S3, integrating SQL queries and direct file access.
+2. Outcome (impact):
+This update streamlines data access management, providing unified permissions and audit trails for both SQL and file-based operations.
+3. Where to use (use case):
+Ideal for data scientists and analysts needing direct file access for tasks like model training, feature engineering, and debugging within Amazon EMR, Apache Spark, or Trino applications.</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>AWS Lake Formation</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15572,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12 07:27:43</t>
+          <t>2026-06-13 07:03:03</t>
         </is>
       </c>
     </row>
@@ -15287,7 +15583,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -15297,7 +15593,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3540</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="7">
@@ -15307,7 +15603,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1130</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="8">
@@ -15317,7 +15613,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000251</v>
+        <v>0.000211</v>
       </c>
     </row>
     <row r="9">
@@ -15327,7 +15623,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000321</v>
+        <v>0.000288</v>
       </c>
     </row>
     <row r="10">
@@ -15337,7 +15633,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000572</v>
+        <v>0.000499</v>
       </c>
     </row>
     <row r="11">
@@ -15347,7 +15643,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.024721</v>
+        <v>0.02522</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F407"/>
+  <dimension ref="A1:F427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -15507,6 +15507,746 @@
       <c r="F407" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>AWS Management Console Private Access now works without internet connectivity</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-management-console-private/</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Management Console Private Access now allows VPC users to access the console without internet connectivity, enhancing security for sensitive environments.
+2. Outcome (impact):
+   Enterprises can now manage their AWS infrastructure securely in air-gapped environments, complying with strict network security controls.
+3. Where to use (use case):
+   Ideal for regulated industries like financial services, government, defense, and healthcare, as well as enterprises with stringent security requirements.</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>AWS PrivateLink</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Grok 4.3 from xAI now available in Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/grok-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 20:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched xAI's Grok 4.3 model on Amazon Bedrock, enhancing generative AI capabilities with improved reasoning and tool use.
+2. Outcome (impact):
+This launch provides users with a more consistent and efficient reasoning model, suitable for high-volume inference and enterprise workloads, reducing costs and improving performance.
+3. Where to use (use case):
+Grok 4.3 is ideal for enterprise applications like contract review, case law research, credit agreement analysis, and financial document Q&amp;A.</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory now supports strictly consistent metadata for long-term memory</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/agentcore-memory-scmetadata</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Memory now allows direct attachment of metadata values from applications, ensuring they remain unchanged in long-term memory records.
+2. Outcome (impact):
+This update enhances data organization, filtering, and retrieval by providing precise metadata control, enabling better compliance and data isolation.
+3. Where to use (use case):
+Ideal for scenarios requiring strict data boundaries, such as department-specific data management, regulatory compliance, and multi-tenant environments.</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Amazon FSx for OpenZFS now supports on-demand data replication across AWS opt-in Regions</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/on-demand-cross-region-replication/</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon FSx for OpenZFS now supports on-demand data replication to opt-in AWS Regions, enhancing disaster recovery and data distribution capabilities.
+2. Outcome (impact):
+This update allows users to replicate data to additional AWS Regions, improving resilience and enabling lower latency access for global applications.
+3. Where to use (use case):
+Ideal for disaster recovery, replicating production data across different regions or accounts, and providing global customer access with lower latency.</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Amazon FSx for OpenZFS</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch introduces Log Analytics for unified log analysis</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-log-analytics/</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch has launched Log Analytics, a unified console for querying, real-time streaming, and analyzing logs, integrating Logs Insights, Live Tail, and Contributor Insights.
+2. Outcome (impact):
+Log Analytics streamlines log management and analysis, enhancing efficiency and providing deeper insights into log data with a consolidated interface.
+3. Where to use (use case):
+Ideal for operational teams needing to monitor, troubleshoot, and analyze application and system logs in real-time across multiple AWS services.</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Resolver DNS Firewall now supports Palo Alto Networks Advanced DNS Security (Preview)</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-route-53-resolver-dns/</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 17:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces a preview of Palo Alto Networks Advanced DNS Security integrated with Route 53 Resolver DNS Firewall, enhancing DNS threat protection without additional infrastructure.
+2. Outcome (impact):  
+This integration simplifies DNS security management, providing unified threat protection across AWS and on-premises environments, and reduces the need for separate firewall deployments.
+3. Where to use (use case):  
+Ideal for organizations looking to enhance DNS security with advanced threat detection and protection, particularly those managing hybrid-cloud environments.</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Resolver DNS Firewall</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Amazon ECS Express Mode is now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ecs-express-mode-govcloud/</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS Express Mode is now available in AWS GovCloud (US) Regions, enabling rapid deployment of containerized applications with auto-provisioned domains and integrated load balancing.
+2. Outcome (impact):
+Developers can quickly launch and manage containerized applications in a secure, compliant environment, benefiting from AWS operational best practices and simplified infrastructure management.
+3. Where to use (use case):
+Ideal for government agencies and organizations needing to deploy secure, scalable web applications and APIs in compliance with US federal regulations.</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>AWS launches Cost Explorer historical data retention for accounts in billing groups</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-cost-explorer/</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 16:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has extended Cost Explorer's historical data retention to accounts in billing groups, allowing access to past billing data at original rates.
+2. Outcome (impact):
+Customers can now maintain reporting continuity and access historical billing data for accounts in billing groups, enhancing cost management and analysis.
+3. Where to use (use case):
+Ideal for organizations using AWS Billing Conductor and Billing Transfer to manage multi-account billing and cost management, ensuring uninterrupted access to historical billing data.</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>AWS Billing Conductor</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>AWS Lambda Managed Instances now supports Tag Propagation for Managed Resources</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-lambda-managed-instances-tag-propagation/</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 15:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda Managed Instances now supports tag propagation, automatically applying specified tags to managed resources like EC2 instances and EBS volumes.
+2. Outcome (impact):
+   This feature simplifies cost tracking, enforces service control policies, and ensures compliance by consistently tagging all managed resources without manual intervention.
+3. Where to use (use case):
+   Ideal for organizations that rely on resource tagging for cost management, governance, and compliance, ensuring all provisioned resources meet required tagging standards.</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>AWS Lambda Managed Instances</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>AWS DevOps Agent expands with custom SRE agents and MCP/A2A protocols</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-devops-agent-custom-agents/</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 15:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS DevOps Agent now supports custom SRE agents, headless access via MCP/A2A protocols, and integration with third-party tools for enhanced automation and monitoring.
+2. Outcome (impact):
+Teams can automate SRE workflows, extend DevOps Agent capabilities, and access its features from existing tools, improving efficiency and reducing manual tasks.
+3. Where to use (use case):
+Automate recurring SRE tasks, integrate with IDEs and coding assistants, and monitor production health without switching contexts.</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>AWS DevOps Agent</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8i instances are now available in Europe (Stockholm) region</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-c8i-instances-europe-stockholm-region/</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched C8i instances in the Europe (Stockholm) region, offering enhanced performance and price-performance for memory-intensive workloads.
+2. Outcome (impact):
+   Users can achieve up to 20% higher performance and up to 15% better price-performance with these new instances, making them ideal for demanding applications.
+3. Where to use (use case):
+   Best suited for memory-intensive workloads such as NGINX web applications, AI deep learning models, and Memcached stores.</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C7i instances are now available in the Israel (Tel Aviv) region</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-c7i-instances-israel-tel-aviv-region/</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C7i instances with custom 4th Gen Intel Xeon processors are now available in the Israel (Tel Aviv) region, offering enhanced performance and scalability.
+2. Outcome (impact):
+C7i instances provide up to 15% better price-performance compared to C6i instances, making them ideal for compute-intensive tasks with improved data processing capabilities.
+3. Where to use (use case):
+Ideal for workloads such as batch processing, distributed analytics, ad-serving, video encoding, and CPU-based machine learning applications.</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>AWS WAF announces AI traffic monetization</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-waf-ai-traffic-monetization/</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS WAF introduces AI traffic monetization, enabling content owners to charge AI bots for accessing their resources and accept payments via third-party providers.
+2. Outcome (impact):  
+   Content owners and publishers can now monetize AI traffic accessing their content and APIs, allowing for differentiated pricing based on agent identity and verification status.
+3. Where to use (use case):  
+   Ideal for content owners and publishers who want to monetize access to their articles, data feeds, and licensed archives by AI bots and agents.</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>AWS WAF</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch now supports cross-account metrics centralization</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cross-account-metrics-centralization</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CloudWatch now allows cross-account and cross-region metrics centralization into a single destination account, enhancing visibility and management for multi-account setups.
+2. Outcome (impact):
+   This feature enables enterprise teams to achieve a unified view of their operational health, simplifying querying, alarming, compliance, and governance across their entire infrastructure.
+3. Where to use (use case):
+   Ideal for organizations with complex multi-account, multi-region deployments who need centralized monitoring and management of their AWS resources.</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Query Studio is now generally available</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-query-studio-generally-available</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch Query Studio is now generally available, providing a unified querying and visualization experience for exploring metrics across AWS accounts and regions.
+2. Outcome (Impact):
+Enables teams to efficiently correlate and analyze performance metrics, improving observability and troubleshooting across their entire AWS environment.
+3. Where to Use (Use Case):
+Ideal for DevOps teams, SREs, and IT operations professionals who need to monitor and analyze performance metrics across multiple AWS accounts and regions.</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Query Studio</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Free Network Bandwidth Amazon GameLift Servers is Here!</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-gamelift-servers-free-network-bandwidth</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GameLift Servers now offers free network bandwidth for all instance types from generation 6 and later, eliminating unpredictable bandwidth costs for game studios.
+2. Outcome (impact):
+Game developers can now focus on game development without worrying about network bandwidth costs, potentially reducing overall operational expenses and increasing budget flexibility.
+3. Where to use (use case):
+Ideal for multiplayer game developers who need to host game servers globally and require continuous network traffic to connected players.</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Amazon GameLift</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MariaDB supports Long-Term Support version 12.3 in Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-rds-maria-db-innovation-release-12-3-rds-database-preview-environment/</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for MariaDB now supports MariaDB 12.3 in the Database Preview Environment, enabling users to test new features before general availability.
+2. Outcome (impact):  
+Users can evaluate and test new MariaDB 12.3 features, ensuring compatibility and performance of their applications with the latest LTS release.
+3. Where to use (use case):  
+Ideal for developers and database administrators who need to test new MariaDB features and capabilities in a controlled environment before deploying them in production.</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MariaDB</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL announces Extended Support minor version 5.7.44-RDS.20260521</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-rds-mysql-extended-support-minor-5744-rds/</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon RDS for MySQL now supports Extended Support minor version 5.7.44-RDS.20260521, offering up to three years of critical security and bug fixes beyond standard support.
+2. Outcome (impact)
+Users can extend the lifecycle of their MySQL databases, ensuring they receive critical updates and security patches for up to three years after the community end of support.
+3. Where to use (use case)
+Ideal for businesses needing extended security and bug fixes for MySQL databases, allowing them to delay major version upgrades without compromising on security.</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MariaDB now supports community MariaDB minor versions 10.6.27, 10.11.18, 11.4.12, and 11.8.8</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-rds-mariadb-community-versions/</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for MariaDB now supports minor versions 10.6.27, 10.11.18, 11.4.12, and 11.8.8, offering security fixes and new features.
+2. Outcome (impact):
+   Users can upgrade to the latest MariaDB versions to enhance security, performance, and functionality of their databases.
+3. Where to use (use case):
+   Ideal for applications requiring secure, scalable, and high-performance MariaDB databases in the cloud.</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MariaDB</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch introduces native OpenTelemetry metrics with PromQL querying and per-GB pricing</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-otel-metrics/</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Tue, 09 Jun 2026 12:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch now supports OpenTelemetry metrics with PromQL querying and per-GB pricing, enhancing observability for AWS users.
+2. Outcome (impact):
+   Users can now ingest and query custom and AWS service metrics using PromQL, facilitating better observability and cost management.
+3. Where to use (use case):
+   Ideal for developers and DevOps teams managing microservices and containerized applications, especially those already using OpenTelemetry and Prometheus.</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
         </is>
       </c>
     </row>
@@ -15572,7 +16312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13 07:03:03</t>
+          <t>2026-06-16 08:51:56</t>
         </is>
       </c>
     </row>
@@ -15583,7 +16323,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -15593,7 +16333,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2972</v>
+        <v>7626</v>
       </c>
     </row>
     <row r="7">
@@ -15603,7 +16343,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1013</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="8">
@@ -15613,7 +16353,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000211</v>
+        <v>0.000541</v>
       </c>
     </row>
     <row r="9">
@@ -15623,7 +16363,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000288</v>
+        <v>0.000724</v>
       </c>
     </row>
     <row r="10">
@@ -15633,7 +16373,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000499</v>
+        <v>0.001265</v>
       </c>
     </row>
     <row r="11">
@@ -15643,7 +16383,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02522</v>
+        <v>0.026485</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F427"/>
+  <dimension ref="A1:F450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -16247,6 +16247,857 @@
       <c r="F427" t="inlineStr">
         <is>
           <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Guardrails announces a new API targeting agentic AI workflows</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-guardrails-api-ai/</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 22:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock Guardrails introduces the InvokeGuardrailChecks API, enabling granular, per-request AI safeguards without creating resources, ideal for agentic AI workflows.
+2. Outcome (impact):
+This API allows developers to dynamically apply specific safeguards at each step of their AI applications, enhancing security and compliance by providing detailed control over risk management.
+3. Where to use (use case):
+Ideal for AI applications that require iterative processes, such as chatbots, recommendation systems, and automated customer service tools, where each step may have unique risk profiles.</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Guardrails</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>AWS Transform now supports model-to-model migration assessment for generative AI workloads</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-transform-model-to-model-assessments</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 21:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform now offers a custom transformation for migrating generative AI workloads from third-party providers to Amazon Bedrock, providing a comprehensive migration plan and cost comparisons.
+2. Outcome (impact):
+Organizations can consolidate their AI workloads on AWS, gaining enhanced security, operational tools, and cost optimizations while preserving their application architecture.
+3. Where to use (use case):
+Ideal for organizations currently using generative AI models from providers like OpenAI, Google Gemini, Anthropic, or open-source models, aiming to migrate to AWS Bedrock.</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors now supports up to 10,000 similarity search results per query</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/s3-vectors-supports-10000-search-results-per-query</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 21:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Vectors now supports up to 10,000 similarity search results per query, a significant increase from the previous limit.
+2. Outcome (impact):
+This enhancement allows for more comprehensive similarity searches, facilitating advanced multi-stage retrieval pipelines for applications requiring extensive result sets.
+3. Where to use (use case):
+Ideal for applications needing extensive similarity searches, such as recommendation systems, image and video search, and natural language processing tasks that benefit from large candidate pools.</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>AWS Transform for mainframe now delivers a traceable reimagine workflow</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-transform-mainframe-traceable-reimagine-workflow/</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 18:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform for mainframe now offers a seamless, traceable workflow for modernizing mainframe applications, from assessment to cloud-native code generation.
+2. Outcome (impact):
+This update significantly reduces the time and effort required to modernize mainframe applications, compressing years of manual work into months of automated, traceable processes.
+3. Where to use (use case):
+Ideal for enterprises looking to modernize their z/OS COBOL and PL/I workloads by streamlining the assessment, extraction, and code generation phases into a unified workflow.</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>AWS Transform for mainframe</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>AWS Sign-in now supports resource-based policies and resource control policies</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-sign-in/</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 16:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Sign-in now supports resource-based policies and resource control policies to restrict console access based on network and account.
+2. Outcome (impact):  
+Enhances security by allowing administrators to control which networks and accounts can access the AWS Management Console.
+3. Where to use (use case):  
+Ideal for organizations that need to enforce strict network access controls and ensure console access is limited to specific accounts and networks.</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>AWS Sign-in</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Amazon Redshift RG instances powered by AWS Graviton now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-redshift-rg-instances-3-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 16:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Redshift RG instances, powered by AWS Graviton processors, are now available in three new regions with enhanced performance and cost savings.
+2. Outcome (impact):
+   Customers can achieve up to 4.2X better price-performance, 2.4X faster workloads, and 30% lower costs per vCPU, along with additional savings on backup storage and Redshift Spectrum scanning.
+3. Where to use (use case):
+   Ideal for a range of workloads from small development environments to large-scale production data warehouse deployments in Cape Town, Bangkok, and Mexico Central.</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>AWS announces AWS Blocks, an open-source framework for composing application backends on AWS (Preview)</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-blocks-preview</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 15:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces AWS Blocks, an open-source TypeScript framework simplifying backend development on AWS without needing infrastructure expertise. It offers local testing and seamless production deployment on AWS services.
+2. Outcome (impact):
+   AWS Blocks accelerates backend development for SaaS applications by providing a unified framework for adding essential features like databases, authentication, and AI agents, while ensuring type safety and correct architecture.
+3. Where to use (use case):
+   Ideal for developers building SaaS applications who want to quickly prototype and deploy backend services on AWS without managing infrastructure, allowing them to focus on application logic.</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>AWS Blocks</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>AWS Partner Central agents now accelerate co-selling on every deal</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/accelerate-co-selling-with-agents/</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Partner Central agents now qualify co-sell opportunities in real time, accelerating deal progression and enhancing AWS engagement.
+2. Outcome (impact):
+   Partners can build a stronger pipeline and progress deals faster by eliminating manual review and receiving real-time recommendations.
+3. Where to use (use case):
+   This service is ideal for AWS Partners looking to enhance their sales processes and improve co-sell readiness.</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>AWS Marketplace announces AI-assisted product listing</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ai-assisted-product-listing/</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 12:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces an AI-assisted tool in Partner Assistant chat to help ISVs and Consulting Partners create optimized product listings on AWS Marketplace using existing digital assets.
+2. Outcome (impact):
+   This new capability reduces manual data entry and errors, ensuring listings meet AWS standards and are more discoverable by buyers, thereby improving the quality and visibility of product listings.
+3. Where to use (use case):
+   Ideal for ISVs and Consulting Partners looking to efficiently create and manage high-quality product listings on AWS Marketplace, enhancing their market presence and customer engagement.</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Partner Assistant</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>AWS Partner Central now validates Foundational Technical Review in minutes</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-partner-central-foundational-technical-review/</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+AWS Partner Central now expedites Foundational Technical Review (FTR) using AI-powered validation, accepting SOC 2 Type II or AWS Well-Architected Framework Reviews (WAFR) reports.
+2. Outcome (impact)
+Partners can quickly validate their solutions against AWS requirements, receive immediate feedback, and unlock benefits such as the qualified software badge and APN program eligibility.
+3. Where to use (use case)
+Use this streamlined FTR process for software solutions deployed on AWS, especially for partners seeking to comply with industry standards and accelerate their validation timelines.</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>AWS Partner Central launches new funding benefits for Business Value Realization</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-partner-business-value-realization/</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Central introduces Business Value Realization (BVR) funding benefits to support partners in driving customer adoption and outcomes with AWS services.
+2. Outcome (impact):
+Partners can now track customer progress, receive funding tied to value realization, and access AI-generated reports to optimize customer adoption.
+3. Where to use (use case):
+Ideal for consulting, system integrator, and managed services partners aiming to enhance customer engagement and achieve measurable business outcomes using AWS services.</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server now supports X2m instances</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/rds-sqlserver-supports-x2m/</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for SQL Server introduces X2m instances, offering significant cost savings and enhanced performance for memory-intensive workloads.
+2. Outcome (impact):
+Customers can reduce SQL Server software licensing costs by 50% or more while benefiting from up to 64 vCPUs, 4 TB memory, and 256K IOPS.
+3. Where to use (use case):
+Ideal for memory-intensive database workloads such as data warehousing, large-scale transactional databases, and high-performance analytics.</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors reduces query charges by up to 80% for large vector indexes</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/s3-vectors-reduces-query-charges-80-percent-large-indexes/</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Vectors now reduces query charges by up to 80% for large vector indexes, lowering costs for AI, RAG, and semantic search workloads.
+2. Outcome (impact):
+Customers will experience significant cost savings on query charges for vector indexes with over 10 million vectors, with no changes to their applications.
+3. Where to use (use case):
+Ideal for large-scale AI, Retrieval-Augmented Generation (RAG), and semantic search applications that require efficient similarity searches.</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>AWS Marketplace reduces listing fee for professional services to 0.5%</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/reduce-listing-fee-professional-services-aws-marketplace</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Marketplace has lowered the listing fee for professional services to 0.5%, down from 2.5%, enhancing cost-effectiveness for service providers.
+2. Outcome (impact):  
+This reduction simplifies and makes it more economical for consulting partners, systems integrators, managed services providers, and independent software vendors to offer their services on AWS Marketplace, while retaining procurement and billing benefits.
+3. Where to use (use case):  
+Ideal for professional service providers looking to list and transact their services on AWS Marketplace, leveraging its AI-powered discovery, multi-product solutions, and flexible billing models.</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>AWS Partners can now accelerate co-sell deals with express private offers</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-partners-express-private-offers</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partners can now expedite co-sell deals by automating pricing through express private offers, reducing negotiation time from weeks to minutes.
+2. Outcome (impact):
+Faster deal conversion, increased visibility in AWS-led sales motions, and enhanced engagement with customers who have shown purchase intent.
+3. Where to use (use case):
+Ideal for AWS Partners involved in co-selling, aiming to streamline the sales process and provide personalized pricing to customers swiftly.</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>AWS announces Amazon Connect Customer Services Competency</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-announces-amazon-connect-customer-services-competency</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces the Amazon Connect Customer Competency to help businesses find expert partners for enhancing customer experiences using Amazon Connect.
+2. Outcome (impact):
+   Businesses can confidently partner with AWS-validated experts to modernize their contact centers and integrate AI for seamless, personalized customer interactions.
+3. Where to use (use case):
+   Ideal for enterprises looking to upgrade their customer service operations with advanced AI capabilities across various communication channels.</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>AWS Marketplace Storefront is now generally available</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-marketplace-storefront/</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Marketplace Storefront is now available, allowing partners to create branded catalogs for their solutions and services with no coding required.
+2. Outcome (impact):
+Partners can easily manage their cloud marketplace business, simplify customer discovery and purchase processes, and maintain customer relationships with a fully branded storefront.
+3. Where to use (use case):
+Ideal for AWS Partners, Channel Partners, and Independent Software Vendors to present tailored catalogs of solutions to their customers, automate deal workflows, and manage their cloud marketplace business efficiently.</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>AWS Marketplace Storefront</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>AWS Transform now supports Amazon FSx for NetApp ONTAP (Public Preview)</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-transform-vmware-fsx-for-ontap-preview</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform now supports migrating block storage workloads to Amazon FSx for NetApp ONTAP, simplifying storage migrations during infrastructure modernization.
+2. Outcome (impact):  
+This new capability streamlines storage migrations by integrating them into the same migration process as compute and network, reducing complexity, cost, and risk.
+3. Where to use (use case):  
+Ideal for enterprises looking to migrate on-premises NetApp ONTAP or other storage workloads to AWS without changing their data management practices.</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>AWS Partner Central agents now guide new partners from registration to ready-to-sell</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-partner-central/</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Partner Central agents now provide guided onboarding for new partners, ensuring they meet all requirements to sell on AWS Marketplace.
+2. Outcome (impact):
+   New partners can quickly and efficiently complete their onboarding process with personalized guidance, reducing time and effort required to start selling on AWS.
+3. Where to use (use case):
+   Ideal for new AWS partners needing streamlined onboarding and compliance setup to start selling on AWS Marketplace.</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Amazon S3 adds annotations to provide AI agents and analytics tools with context for data discovery</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-s3-annotations-business-context</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 introduces annotations for attaching extensive custom metadata to objects, enhancing data discovery for AI and analytics.
+2. Outcome (impact):
+Enables AI agents and analytics tools to better discover and utilize data by providing rich, scalable context directly within S3 objects.
+3. Where to use (use case):
+Ideal for scenarios requiring extensive metadata for data discovery, such as large-scale data lakes, AI model training, and complex analytics workflows.</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B200 instances are now available in the Asia Pacific (Mumbai) Region</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-p6-b200-mumbai/</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 03:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 P6-B200 instances with enhanced AI capabilities are now available in the Asia Pacific (Mumbai) Region.
+2. Outcome (impact):
+These instances offer up to 2x performance improvement for AI training and inference, enabling faster and more efficient AI workloads.
+3. Where to use (use case):
+Ideal for AI training, machine learning inference, and any compute-intensive applications requiring high GPU memory and bandwidth.</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Amazon FSx for Lustre Intelligent-Tiering storage class is now available in 13 additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-fsx-lustre-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 16:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon FSx for Lustre now offers Intelligent-Tiering storage in 13 new regions, providing cost-effective, fully elastic storage for HPC and AI/ML workloads.
+2. Outcome (impact):
+Customers can achieve up to 34% better price-performance compared to on-premises storage and reduce costs for infrequently accessed data by up to 96%.
+3. Where to use (use case):
+Ideal for High-Performance Computing (HPC) and Artificial Intelligence/Machine Learning (AI/ML) workloads with mixed data access patterns.</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Amazon FSx for Lustre</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>AWS Partner Central now provides lead enrichment and prospecting</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/lead-enrichment-and-prospecting</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 15:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Partner Central now offers lead enrichment and prospecting features, providing AWS Partners with insights and recommendations to enhance their sales strategies.
+2. Outcome (impact):
+   AWS Partners can better target and engage potential customers by leveraging enriched lead data and propensity insights, potentially increasing conversion rates and sales efficiency.
+3. Where to use (use case):
+   This feature is ideal for AWS Partners looking to optimize their lead management and sales motions, ensuring they focus on high-potential leads.</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -16312,7 +17163,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16 08:51:56</t>
+          <t>2026-06-17 08:33:43</t>
         </is>
       </c>
     </row>
@@ -16323,7 +17174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -16333,7 +17184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7626</v>
+        <v>8519</v>
       </c>
     </row>
     <row r="7">
@@ -16343,7 +17194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2548</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="8">
@@ -16353,7 +17204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000541</v>
+        <v>0.000605</v>
       </c>
     </row>
     <row r="9">
@@ -16363,7 +17214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000724</v>
+        <v>0.000833</v>
       </c>
     </row>
     <row r="10">
@@ -16373,7 +17224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001265</v>
+        <v>0.001438</v>
       </c>
     </row>
     <row r="11">
@@ -16383,7 +17234,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.026485</v>
+        <v>0.027923</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F450"/>
+  <dimension ref="A1:F472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -17098,6 +17098,820 @@
       <c r="F450" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>AWS Glue Interactive Sessions now support Spark Connect for interactive workloads</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-glue-interactive-sessions-spark-connect-smus-notebooks</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 19:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Interactive Sessions now support Spark Connect, enabling interactive Spark applications to be developed and run from preferred environments on AWS's serverless infrastructure.
+2. Outcome (impact):
+This integration simplifies the development and debugging of Spark applications, enhances stability, and improves observability through real-time monitoring and history tracking.
+3. Where to use (use case):
+Ideal for data exploration, iterative debugging, and incremental development of PySpark jobs in environments like Amazon SageMaker, Jupyter, or Visual Studio Code.</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>AWS Glue Interactive Sessions</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now streams workflow engine logs to Amazon CloudWatch in real time</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-healthomics-real-time-engine-log-streaming/</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now streams workflow engine logs to Amazon CloudWatch in real time, enhancing monitoring and debugging capabilities for bioinformatics workflows.
+2. Outcome (impact):
+Real-time log streaming accelerates iterative workflow development and debugging, providing immediate access to execution details and enabling early detection of anomalies.
+3. Where to use (use case):
+Ideal for researchers, bioinformaticians, and workflow developers in healthcare and life sciences who need to monitor and debug bioinformatics workflows efficiently.</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>AWS DevOps Agent adds release management capability (preview)</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-devops-agent-release-management/</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS DevOps Agent now offers release management in preview, ensuring code changes are production-ready through automated testing and compliance checks.
+2. Outcome (impact):
+   Accelerates deployment, reduces Mean Time to Recovery (MTTR), and enhances operational excellence by ensuring code changes are safe and compliant before production.
+3. Where to use (use case):
+   Ideal for development teams aiming to safely and efficiently deploy code changes across AWS, multicloud, and on-premises environments.</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>AWS DevOps Agent</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL, MySQL, and MariaDB now supports M9g database instances</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-rds-postgresql-mysql-mariadb-m9g-instances/</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS now supports M9g instances for PostgreSQL, MySQL, and MariaDB, offering enhanced performance and cost efficiency.
+2. Outcome (impact):
+   Users can achieve up to 30% performance improvement and up to 23% better price/performance with the new Graviton5-based M9g instances.
+3. Where to use (use case):
+   Ideal for high-performance database workloads requiring significant vCPU and networking bandwidth, such as large-scale enterprise applications.</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Amazon Aurora and RDS for MySQL expand Extended Support for MySQL 5.7 through June 2029</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/rds-mysql-es-extension/</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS extends support for MySQL 5.7 on Amazon Aurora and RDS until June 2029, providing more time for upgrades with security patches.
+2. Outcome (impact):  
+Customers gain additional time to upgrade to newer MySQL versions, ensuring they receive critical security updates and bug fixes without incurring extra costs.
+3. Where to use (use case):  
+Ideal for businesses needing more time to transition from MySQL 5.7 to newer versions, ensuring ongoing security and operational stability.</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon RDS for MySQL</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>AWS Outposts racks now support bmn-cx3a instances, the first AMD-based instances with accelerated networking on Outposts</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-outposts-amd-bmn-cx3a/</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 14:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Outposts racks now support bmn-cx3a instances, featuring AMD processors and accelerated networking, ideal for high-throughput workloads.
+2. Outcome (impact):
+Enhanced performance and capabilities for high-throughput applications on-premises, leveraging AWS infrastructure.
+3. Where to use (use case):
+Real-time market data ingestion, market and risk analytics, telecom 5G core networks, and media distribution.</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>AWS Outposts</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Amazon Quick announces autonomous agents, multi-dataset analytics, and redesigned activity feed</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-quick/</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 13:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces Amazon Quick's new autonomous agents, multi-dataset analytics, and a redesigned activity feed to automate tasks and enhance data analysis.
+2. Outcome (impact):
+   These enhancements will significantly reduce manual repetitive work, streamline workflows, and provide unified analytics across multiple data sources, improving efficiency and productivity.
+3. Where to use (use case):
+   Ideal for businesses needing to automate routine tasks, analyze data from various sources, and improve collaboration across platforms.</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore introduces new optimization capabilities to continuously improve agents in production</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-agentcore-new-optimization-capabilities</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces AgentCore's new optimization capabilities to enhance agents by analyzing production traces, identifying silent failures, and suggesting targeted improvements.
+2. Outcome (impact):
+AgentCore's new features enable teams to proactively address agent failures, improve user experience, and reduce customer complaints by identifying and fixing issues before they impact users.
+3. Where to use (use case):
+Use AgentCore for customer-facing AI agents in customer service, support, and other interactive applications to ensure smooth operations and high user satisfaction.</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>AgentCore harness in now generally available</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-agentcore-harness-generally-available</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched the general availability of AgentCore harness in Amazon Bedrock, enabling rapid development and deployment of production-grade agents with a managed orchestration loop.
+2. Outcome (impact):
+   Teams can now quickly create and scale agents without extensive coding, reducing development time and effort while ensuring robust performance and flexibility.
+3. Where to use (use case):
+   Ideal for building customer service chatbots, automated workflow agents, and any application requiring intelligent, context-aware interactions.</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore now supports Bedrock Guardrails in policy</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-agentcore-policy-guardrails-generally-available</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces Bedrock Guardrails in policy for Amazon Bedrock AgentCore, enhancing AI agent safety and security with real-time risk detection and consistent enforcement.
+2. Outcome (impact):
+Enterprises can now scale AI agents in production with deeper safety and security controls, mitigating risks such as prompt injection attacks and sensitive data exposure.
+3. Where to use (use case):
+Ideal for enterprises deploying AI agents in production environments, ensuring secure and safe interactions with downstream systems.</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Catalog now supports business context and semantic search (Preview)</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-glue-data-catalog/</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Glue Data Catalog now offers business context and semantic search in preview, enabling users to discover and understand data by its semantic meaning.
+2. Outcome (impact):  
+This feature enhances data discoverability and understanding by allowing users to search data based on both technical metadata and business context, improving data governance and AI agent accuracy.
+3. Where to use (use case):  
+Use this feature for data discovery in data lakes, improving data governance, and enhancing AI agent capabilities by providing them with trusted definitions and context.</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Catalog</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Introducing AWS Continuum for security at machine speed</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-continuum/</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Continuum automates security risk discovery, prioritization, validation, and remediation at machine speed, integrating with existing tools and services.
+2. Outcome (impact):
+Shifts security teams from manual triage to strategic oversight, improving efficiency and effectiveness in managing software vulnerabilities.
+3. Where to use (use case):
+Ideal for organizations needing to manage and mitigate security risks in their software development lifecycle, particularly in environments with complex dependencies and high-velocity deployments.</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>AWS Continuum</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Oracle Database@AWS now supports Oracle Autonomous AI Database Serverless</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/oracle-database-aws-autonomous-database-serverless/</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Oracle Database@AWS now supports Oracle Autonomous AI Database Serverless, a fully managed service that automatically handles database operations and scales based on workload demand.
+2. Outcome (impact):
+This update enhances database management by reducing operational overhead and providing scalable, AI-driven database solutions.
+3. Where to use (use case):
+Ideal for AI Transaction Processing, AI Lakehouse, AI JSON Database, and Oracle APEX workloads requiring high availability and disaster recovery.</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Oracle Database@AWS</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager introduces safe secrets handling in the Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/safe-secrets-handling-in-agent-toolkit-for-aws/</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Secrets Manager now provides a secret safety skill in the Agent Toolkit for AWS, ensuring secrets are handled securely without exposing them to models or logs.
+2. Outcome (impact):
+   Developers can securely use secrets in AI coding agents without risking exposure of sensitive information, enhancing security and compliance.
+3. Where to use (use case):
+   Ideal for developers using AI coding agents who need to manage secrets securely within their workflows, such as in CI/CD pipelines or automated application deployments.</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base is now generally available</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-managed-knowledge-base/</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock Managed Knowledge Base is now available, offering a fully managed RAG service to build AI agents grounded in enterprise data without managing infrastructure.
+2. Outcome (impact):
+Teams can accelerate the development of production-ready AI agents by leveraging managed data ingestion, storage, and retrieval capabilities, reducing time from prototype to production.
+3. Where to use (use case):
+Power employee assistants, automate customer support, and build multimodal knowledge bases for various content types.</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>AWS Security Agent announces support for Threat Modeling</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-security-agent-threat-modeling/</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Security Agent now supports threat modeling using AI to analyze applications and generate threat models with recommended mitigations.
+2. Outcome (impact):  
+This feature simplifies and accelerates threat modeling, reducing the need for specialized expertise and manual effort, and helps identify potential threats early in the development process.
+3. Where to use (use case):  
+Developers can use it in IDEs for early design phase threat assessment, while security teams can use it for pre-deployment evaluations.</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>AWS Security Agent</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>AWS Security Agent adds Kiro Power, Claude Code, simulated validations and new integrations support</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-kiro-power-claude-code/</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Agent now supports Kiro and Claude Code, integrates with multiple platforms, and validates security findings through simulated exploits.
+2. Outcome (impact):
+This update enhances security by reducing false positives, providing actionable insights, and integrating seamlessly into developers' workflows.
+3. Where to use (use case):
+Ideal for development teams needing integrated security solutions within their IDEs and source control platforms to ensure secure coding practices.</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>AWS Security Agent</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Guardrails adds automated reasoning checks in Sydney</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-guardrails-sydney/</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 20:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock Guardrails introduces Automated Reasoning checks in Sydney, offering rigorous mathematical validation for AI model outputs to ensure accuracy and compliance.
+2. Outcome (impact):  
+This feature provides up to 99% accuracy in detecting correct responses from large language models, significantly reducing risks of AI hallucinations and policy violations, and enhancing trust in AI systems.
+3. Where to use (use case):  
+Ideal for regulated industries like finance, healthcare, and legal services, as well as any enterprise requiring unambiguous validation of AI outputs, such as ensuring compliance in enterprise applications and quality assurance in critical workflows.</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Announcing Web Search on Amazon Bedrock AgentCore for Agentic Web Retrieval</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-agentcore-web-search/</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces Web Search on Amazon Bedrock AgentCore, enabling AI agents to access current web knowledge securely within the AWS environment.
+2. Outcome (impact):
+Developers can now focus on building AI agents without the complexity of integrating external search providers, enhancing the accuracy and relevance of agent responses.
+3. Where to use (use case):
+Ideal for creating intelligent customer service bots, information retrieval systems, and any AI application requiring up-to-date web information.</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Amazon Quick expands integrations with new connectors for Adobe, Figma, WhatsApp, and more</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-quick-adobe-figma-whatsapp/</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 15:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick has expanded its integrations to include 16 new tools, enhancing its ability to connect productivity, design, analytics, and communication apps.
+2. Outcome (impact):
+Teams can now act on insights from their data and tools without switching contexts, improving efficiency and workflow integration.
+3. Where to use (use case):
+Ideal for revenue teams, data analysts, designers, and communication teams to streamline their workflows by integrating multiple tools within a single conversation.</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>AWS launches a new continuous modernization capability in AWS Transform that provides autonomous tech debt analysis and remediation at scale</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-transform-continuous-modernization/</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 21:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform introduces a new continuous modernization capability that autonomously detects and remediates tech debt across enterprise software portfolios.
+2. Outcome (impact):  
+This new feature simplifies managing software tech debt, enabling enterprises to transition from manual maintenance to automated codebase updates, enhancing efficiency and reducing manual effort.
+3. Where to use (use case):  
+Ideal for enterprises looking to modernize their software portfolios, improve codebase maintenance, and integrate AI readiness assessments and security vulnerability remediation.</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Future-dated Capacity Reservations Now Supports Cancellation</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-fcr-cancellation/</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 22:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 now allows users to cancel future-dated Capacity Reservations with potential charges, providing flexibility in capacity planning.
+2. Outcome (impact):
+   Users can better manage their capacity needs and avoid unnecessary costs by canceling reservations if plans change, with transparent charge details.
+3. Where to use (use case):
+   Ideal for businesses needing to reserve capacity for future events or projects but requiring the flexibility to cancel if circumstances change.</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17977,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17 08:33:43</t>
+          <t>2026-06-18 08:14:13</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17988,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -17184,7 +17998,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8519</v>
+        <v>8598</v>
       </c>
     </row>
     <row r="7">
@@ -17194,7 +18008,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2933</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="8">
@@ -17204,7 +18018,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000605</v>
+        <v>0.00061</v>
       </c>
     </row>
     <row r="9">
@@ -17214,7 +18028,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000833</v>
+        <v>0.000768</v>
       </c>
     </row>
     <row r="10">
@@ -17224,7 +18038,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001438</v>
+        <v>0.001378</v>
       </c>
     </row>
     <row r="11">
@@ -17234,7 +18048,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.027923</v>
+        <v>0.029301</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F472"/>
+  <dimension ref="A1:F487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -17912,6 +17912,561 @@
       <c r="F472" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Announcing the general availability of a new AWS Local Zone in Hanoi, Vietnam</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-local-zones-hanoi-vietnam/</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Fri, 19 Jun 2026 01:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched a new Local Zone in Hanoi, Vietnam, offering low-latency access to compute, storage, and networking services, supporting data residency and AI/ML workloads.
+2. Outcome (impact):
+This new Local Zone enables businesses in Vietnam to achieve lower latency for end-user applications, meet local data residency requirements, and support AI/ML inference workloads with minimal latency.
+3. Where to use (use case):
+Ideal for applications requiring low-latency access, such as real-time analytics, AI/ML inference, content delivery, and other latency-sensitive workloads.</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Amazon Elastic Compute Cloud (Amazon EC2)</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Amazon MSK Express brokers now support Intelligent Rebalancing on existing clusters</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-msk-express-intelligent/</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 22:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MSK Express brokers now support Intelligent Rebalancing on all existing clusters, enhancing performance and efficiency at no extra cost.
+2. Outcome (impact):
+   Customers can now benefit from automatic partition balancing, leading to improved resource utilization and better performance in their Kafka clusters without manual intervention.
+3. Where to use (use case):
+   Ideal for managing large-scale Kafka clusters where automatic rebalancing can help maintain optimal performance and capacity utilization, especially when scaling operations.</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Amazon MSK</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Amazon ECS announces faster service auto scaling</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ecs-faster-autoscaling/</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now offers faster service auto scaling with support for high-resolution (20-second) metrics, reducing scale-out and provisioning times significantly.
+2. Outcome (impact):
+Faster scaling response times (76% faster scale-out, 72% faster provisioning) and the ability to lower baseline capacity, resulting in reduced compute costs while maintaining performance.
+3. Where to use (use case):
+Ideal for applications with fluctuating workloads requiring rapid scaling to meet demand, such as e-commerce platforms during sales events or dynamic web applications.</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Amazon EC2 G7 instances are now generally available</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-g7-generally-available</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 20:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched Amazon EC2 G7 instances with RTX PRO 4500 GPUs, offering enhanced AI and graphics performance.
+2. Outcome (impact):
+   Users can achieve up to 4.6x AI inference and 2.1x graphics performance improvements over previous generations.
+3. Where to use (use case):
+   Ideal for AI inference tasks (e.g., translation, video analysis), graphics rendering, game streaming, and large-scale data processing.</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Amazon MQ for RabbitMQ now supports private networking connectivity</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/amazon-mq-private-network-connectivity/</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 20:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MQ for RabbitMQ now supports private networking, allowing brokers to securely connect to private VPC resources without public exposure.
+2. Outcome (impact):
+Enhances security and compliance by enabling secure private connections for RabbitMQ brokers to private resources, eliminating the need for public exposure.
+3. Where to use (use case):
+Ideal for connecting RabbitMQ brokers to private identity providers, other RabbitMQ brokers, or self-hosted RabbitMQ instances within a VPC.</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Amazon MQ</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Nested virtualization is now available on additional Intel platforms and US Gov Cloud regions</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/nested-virtualization-intel-us-gov-cloud/</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 18:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Nested virtualization is now available on more Intel instances and US GovCloud regions, enabling running KVM or Hyper-V on EC2 instances.
+2. Outcome (impact):
+   Expands the flexibility and use cases for EC2 instances, allowing customers to run nested virtual environments for specialized applications.
+3. Where to use (use case):
+   Running emulators for mobile applications, simulating in-vehicle hardware, and using Windows Subsystem for Linux on Windows workstations.</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches the ability to interrupt an agent with an urgent contact</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect-interrupt-agent-with-urgent-contact/</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 18:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now allows urgent contacts to interrupt agents, overriding their current routing configuration for time-sensitive tasks.
+2. Outcome (impact):
+Enhances efficiency by ensuring agents can handle critical calls promptly, even if they are currently engaged in other tasks.
+3. Where to use (use case):
+Ideal for scenarios where agents need to manage both customer service calls and personal urgent callbacks, such as callbacks on personal extensions.</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L12-v2 for semantic search and sentence similarity is now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/all-minilm-l12-v2-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced the all-MiniLM-L12-v2 model in Amazon SageMaker JumpStart for enhanced semantic search and sentence similarity.
+2. Outcome (impact):
+This model enables efficient text representation and retrieval, improving the accuracy and speed of semantic search, text clustering, and sentence similarity applications.
+3. Where to use (use case):
+Ideal for information retrieval, semantic search systems, document clustering, duplicate detection, and paraphrase identification.</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>AWS Compute Optimizer enhances EBS volume recommendations with additional performance metrics</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-compute-optimizer-enhances-ebs-recommendations/</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Compute Optimizer now offers enhanced EBS volume recommendations by analyzing additional performance metrics, helping balance cost and performance.
+2. Outcome (impact):
+Users can make more informed rightsizing decisions for EBS volumes experiencing high IOPS or throughput spikes, optimizing both cost and performance.
+3. Where to use (use case):
+Ideal for workloads with unpredictable performance spikes, ensuring EBS volumes are appropriately sized to handle bursts without over-provisioning.</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>AWS Compute Optimizer</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Ministral-3-14B-Instruct for multimodal reasoning and agentic AI is now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ministral-3-14b-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced Ministral-3-14B-Instruct, a powerful multimodal model in SageMaker JumpStart, enhancing AI capabilities with advanced vision and multilingual support.
+2. Outcome (impact):
+This model enables the creation of sophisticated AI assistants and agentic systems, improving efficiency and accuracy in processing visual and textual data across multiple languages.
+3. Where to use (use case):
+Ideal for developing AI applications that require multimodal input, such as customer service chatbots, image analysis tools, and multilingual support systems.</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports customer-routed control plane egress</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-eks-customer-routed-control-plane-egress</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EKS now allows routing Kubernetes API server traffic through your VPC, enhancing control over security and routing.
+2. Outcome (impact):
+Organizations can better enforce data perimeters, comply with regulations, and integrate with private network infrastructures.
+3. Where to use (use case):
+Ideal for organizations needing to route control plane traffic through their own VPC for security, compliance, or integration with private services.</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI Announces New observability capability For Inference Endpoints</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-ai-inference/</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 15:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker introduces enhanced observability for inference endpoints, offering real-time metrics and insights to optimize AI performance and reliability.
+2. Outcome (impact):
+This new capability enables faster issue resolution, improved AI workload performance, and better resource utilization by providing comprehensive visibility into inference operations.
+3. Where to use (use case):
+Ideal for managing and optimizing production generative AI applications, ensuring high availability, and quickly diagnosing performance issues.</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Amazon SNS now supports sending SMS in the Asia Pacific (Seoul) Region</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sns-supports-sending-sms-seoul-region/</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SNS now supports sending SMS in the Asia Pacific (Seoul) Region, enabling subscribers to receive text messages in over 200 countries and territories.
+2. Outcome (impact):
+Customers in the Asia Pacific (Seoul) Region can now leverage Amazon SNS to send SMS notifications globally, enhancing communication capabilities for mobile applications and services.
+3. Where to use (use case):
+Ideal for mobile applications, customer notifications, alert systems, and any use case requiring SMS communication within the Asia Pacific (Seoul) Region.</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Amazon Simple Notification Service (Amazon SNS)</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers adds new container fleet improvements</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-gamelift-servers-container-fleet-improvements</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GameLift Servers introduces enhanced container flexibility and inter-container communication for game server deployments.
+2. Outcome (impact):
+   Developers gain better control over container permissions and can easily discover co-located containers, improving service discovery and inter-container communication.
+3. Where to use (use case):
+   Ideal for game developers using containerized architectures who need specialized capabilities and seamless communication between game servers and auxiliary services.</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Amazon GameLift</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server increases the maximum size and provisioned performance of General Purpose (gp3) volumes</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/rds-sqlserver-increases-gp3-limits/</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for SQL Server now supports larger General Purpose (gp3) volumes, with increased size, IOPS, and throughput limits.
+2. Outcome (impact):
+Customers can now run larger and more demanding SQL Server databases with improved performance and simplified storage management.
+3. Where to use (use case):
+Ideal for high-throughput OLTP systems, large-scale analytical workloads, and mission-critical SQL Server databases.</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -17977,7 +18532,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18 08:14:13</t>
+          <t>2026-06-19 08:36:58</t>
         </is>
       </c>
     </row>
@@ -17988,7 +18543,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -17998,7 +18553,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8598</v>
+        <v>5437</v>
       </c>
     </row>
     <row r="7">
@@ -18008,7 +18563,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2704</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="8">
@@ -18018,7 +18573,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00061</v>
+        <v>0.000386</v>
       </c>
     </row>
     <row r="9">
@@ -18028,7 +18583,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000768</v>
+        <v>0.000521</v>
       </c>
     </row>
     <row r="10">
@@ -18038,7 +18593,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001378</v>
+        <v>0.000907</v>
       </c>
     </row>
     <row r="11">
@@ -18048,7 +18603,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.029301</v>
+        <v>0.030208</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F487"/>
+  <dimension ref="A1:F489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -18467,6 +18467,80 @@
       <c r="F487" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Synthetics now supports multilocation canaries</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-synthetics-multilocation/</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 22:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon CloudWatch Synthetics now supports multilocation canaries, enabling simultaneous monitoring across multiple AWS Regions from a single point of management.
+2. Outcome (impact):  
+   Reduces operational overhead, minimizes configuration drift, and enhances monitoring consistency and reliability for global applications.
+3. Where to use (use case):  
+   Ideal for developers and site reliability engineers who need to monitor application availability and performance across different geographic locations.</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Synthetics</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Personal Supports Ubuntu 24.04</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ubuntu-china-zhy/</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces Ubuntu 24.04 LTS bundles for Amazon WorkSpaces Personal in China, enhancing software ecosystem and security.
+2. Outcome (impact):
+   Customers in China can now leverage the latest Linux packages, improved security, and extended support lifecycle with Ubuntu 24.04 on WorkSpaces.
+3. Where to use (use case):
+   Ideal for developers and IT professionals in China needing up-to-date software and security features on their virtual desktops.</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -18532,7 +18606,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19 08:36:58</t>
+          <t>2026-06-20 07:04:57</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18617,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -18553,7 +18627,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5437</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7">
@@ -18563,7 +18637,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1836</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
@@ -18573,7 +18647,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000386</v>
+        <v>4.9e-05</v>
       </c>
     </row>
     <row r="9">
@@ -18583,7 +18657,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000521</v>
+        <v>6.8e-05</v>
       </c>
     </row>
     <row r="10">
@@ -18593,7 +18667,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000907</v>
+        <v>0.000117</v>
       </c>
     </row>
     <row r="11">
@@ -18603,7 +18677,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.030208</v>
+        <v>0.030325</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F489"/>
+  <dimension ref="A1:F497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -18539,6 +18539,302 @@
         </is>
       </c>
       <c r="F489" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports Nextflow profiles</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-healthomics-nextflow-profiles/</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now supports Nextflow profiles, allowing users to easily switch between execution settings without modifying workflow source code.
+2. Outcome (impact):
+This feature reduces manual errors, accelerates workflow portability, and saves time when transitioning from development to production.
+3. Where to use (use case):
+Healthcare and life sciences customers can use this feature to manage bioinformatics workflows more efficiently, especially when scaling from development to production environments.</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>HealthOmics</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>AWS introduces Lambda MicroVMs for isolated execution of user and AI-generated code</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-lambda-microvms/</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces Lambda MicroVMs, offering VM-level isolation, fast launch speeds, and state retention for secure, isolated code execution.
+2. Outcome (impact):
+   Developers can securely run user or AI-generated code in isolated environments without managing infrastructure, balancing isolation, speed, and state retention.
+3. Where to use (use case):
+   Ideal for multi-tenant applications like interactive coding environments, data analytics platforms, coding assistants, and vulnerability scanning platforms.</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall updates default drop action for improved connection reliability</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-network-firewall-updates-default-drop-action</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Network Firewall has updated its default drop action to improve connection reliability by preventing silent drops of legitimate packets.
+2. Outcome (impact):
+   This change reduces the likelihood of intermittent connection failures caused by the previous default setting, making network connections more reliable.
+3. Where to use (use case):
+   Ideal for environments where maintaining stable and reliable network connections is critical, such as web servers, application servers, and any service where dropped packets could lead to service disruptions.</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>AWS Batch now supports customer-ordered instance allocation strategies</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/batch-ordered-allocation-strategies/</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Batch now allows users to define custom instance allocation strategies with BFPO and SCOP, providing better control over instance type prioritization.
+2. Outcome (impact):
+   Users can optimize compute costs and performance by manually ordering instance types based on specific workload needs, leading to more efficient resource utilization.
+3. Where to use (use case):
+   Ideal for workloads with specific performance requirements, such as high-performance computing (HPC), machine learning training, and data processing tasks that benefit from custom instance type ordering.</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>AWS Batch</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center now supports separate quotas for AWS accounts and applications</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-identity-center-separate-quotas/</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 16:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS IAM Identity Center now allows separate quotas for AWS accounts and applications, enabling independent management of up to 7,000 each.
+2. Outcome (impact):
+   Organizations can manage thousands of AWS accounts and applications without consuming each other's quota capacity, facilitating easier onboarding of applications.
+3. Where to use (use case):
+   Ideal for large enterprises managing numerous AWS accounts and applications, ensuring efficient resource allocation and management.</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Amazon MSK now offers AI Agent Skills to help developers operate MSK efficiently and accelerate migrations to MSK</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-msk-ai-agent-skills</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MSK introduces AI Agent Skills to simplify operations and migrations, offering expert guidance for tasks like troubleshooting and sizing.
+2. Outcome (impact):
+Developers can efficiently manage and migrate Kafka clusters to MSK Express, achieving higher throughput, faster scaling, and reduced recovery times.
+3. Where to use (use case):
+Ideal for teams managing Kafka clusters who need to optimize performance, troubleshoot issues, and migrate workloads to MSK Express.</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Amazon Managed Streaming for Apache Kafka (MSK)</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Introducing self-service lifecycle management capabilities for AWS Outposts</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-outposts-self-service-lifecycle-management</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Outposts now offers self-service lifecycle management, enabling customers to configure, quote, order, renew, and decommission directly from the console, CLI, or API.
+2. Outcome (impact):
+   This update empowers customers to manage their Outposts lifecycle independently, reducing dependency on AWS support teams and streamlining the process from evaluation to decommissioning.
+3. Where to use (use case):
+   Ideal for enterprises that need to efficiently manage their on-premises AWS infrastructure, allowing for quick adjustments to capacity and cost without lengthy support interactions.</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>AWS Outposts</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service supports P6e-GB200 and P6e-GB300 UltraServers</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-parallel-computing-service/</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Parallel Computing Service now supports P6e-GB200 and P6e-GB300 UltraServers, enabling large-scale GPU workloads with advanced compute capabilities.
+2. Outcome (impact):
+This update allows customers to leverage powerful GPU instances for high-performance computing tasks, enhancing the scalability and efficiency of their HPC workloads.
+3. Where to use (use case):
+Ideal for large-scale machine learning, scientific simulations, and data analytics requiring significant GPU power and memory.</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service (PCS)</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -18606,7 +18902,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20 07:04:57</t>
+          <t>2026-06-23 06:56:05</t>
         </is>
       </c>
     </row>
@@ -18617,7 +18913,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -18627,7 +18923,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>688</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="7">
@@ -18637,7 +18933,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>240</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8">
@@ -18647,7 +18943,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.9e-05</v>
+        <v>0.000201</v>
       </c>
     </row>
     <row r="9">
@@ -18657,7 +18953,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.8e-05</v>
+        <v>0.000281</v>
       </c>
     </row>
     <row r="10">
@@ -18667,7 +18963,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000117</v>
+        <v>0.000483</v>
       </c>
     </row>
     <row r="11">
@@ -18677,7 +18973,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.030325</v>
+        <v>0.030808</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F497"/>
+  <dimension ref="A1:F509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -18835,6 +18835,450 @@
         </is>
       </c>
       <c r="F497" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs supports managed syslog ingestion</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-syslog-ingestion/</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 20:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch Logs now supports managed syslog ingestion, allowing direct syslog message collection from various devices into CloudWatch without agents.
+2. Outcome (impact):
+   This feature centralizes log visibility, simplifies operational workflows, and reduces the need for managing log collection agents across environments.
+3. Where to use (use case):
+   Ideal for ingesting syslogs from firewalls, routers, switches, and Linux servers to monitor security events and troubleshoot issues.</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>SageMaker Notebook Instances now support G6e instance types</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/03/g6e-new-launch-sagemaker-notebook-instances/</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 18:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker notebook instances now support G6e instances, offering enhanced GPU performance for AI/ML workloads.
+2. Outcome (impact):
+   Users can achieve up to 2.5x better performance for tasks like model training and deployment, particularly for generative AI and large language models.
+3. Where to use (use case):
+   Ideal for interactive model training and deployment, especially for generative AI fine-tuning, large language models, and diffusion models for multimedia generation.</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory now supports cross-account access</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/agentcore-memory-cross-account-access</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 17:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Memory now supports cross-account access, enabling memory resources and agents to span multiple AWS accounts.
+2. Outcome (impact):
+Facilitates the creation of multi-account architectures, allowing seamless data sharing and event delivery across different AWS accounts.
+3. Where to use (use case):
+Ideal for organizations with multiple AWS accounts needing to share memory resources and events, such as enterprise applications requiring centralized data management.</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports ephemeral storage for private workflows</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/healthomics-scratch-storage/</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 17:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS HealthOmics now offers ephemeral storage for private workflows, enhancing performance and reducing costs for bioinformatics tasks.
+2. Outcome (impact):  
+Bioinformatics workloads, such as genomic sequence alignment and variant calling, will experience faster run times and more consistent performance due to dedicated scratch space.
+3. Where to use (use case):  
+Use cases include genomic data processing, sequence alignment, BAM sorting, and variant calling in healthcare and life sciences.</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Amazon Cognito now supports customer managed key for encryption at rest</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cognito-customer-managed-key</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 17:00:46 GMT</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Cognito now supports customer managed keys in AWS KMS for encrypting user pool data at rest, providing enhanced data governance and control.
+2. Outcome (impact):
+Customers can achieve better data governance by managing their own encryption keys, ensuring compliance with organizational policies and enhancing security.
+3. Where to use (use case):
+Use case for securing sensitive user data in Amazon Cognito user pools, particularly in environments requiring strict data control and compliance.</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Amazon Cognito</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Automated Reasoning checks in Amazon Bedrock Guardrails add new policy refinement workflows</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-guardrails/</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 16:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces automated refinement workflows for Automated Reasoning checks in Amazon Bedrock Guardrails, enhancing policy accuracy and reliability.
+2. Outcome (impact):
+   These workflows reduce manual effort in policy refinement, leading to more accurate validation of generative AI responses and fewer hallucinations.
+3. Where to use (use case):
+   Ideal for organizations utilizing Amazon Bedrock Guardrails to ensure their generative AI models adhere to defined policies, particularly in sectors requiring high accuracy and reliability, such as finance and healthcare.</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch launches OTel Container Insights for Amazon EKS</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-otel-amazon-eks/</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 15:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch introduces OTel Container Insights for Amazon EKS, offering detailed metrics collection and pre-built dashboards for cluster health and resource usage.
+2. Outcome (impact):
+   This service enhances observability for Amazon EKS clusters, providing deeper insights into node and pod performance, and simplifying correlation of metrics across different resources.
+3. Where to use (use case):
+   Ideal for Kubernetes cluster administrators and DevOps teams looking to monitor and optimize the performance of their Amazon EKS workloads.</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Claude Tag is now available in beta via Claude Enterprise in AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/claude-tag-aws-marketplace/</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Anthropic has launched Claude Tag in beta, integrating with Slack for teams using AWS Marketplace's Claude Enterprise, allowing collaborative task delegation and context retention.
+2. Outcome (impact):
+Teams can enhance productivity by delegating tasks to Claude Tag in Slack, leveraging its ability to remember context and plan tasks, while maintaining security and governance through scoped identities and default settings.
+3. Where to use (use case):
+Ideal for collaborative environments within Slack where teams need an AI assistant to manage tasks, retain context, and integrate with various tools and data sources.</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service now offers AI-assisted migrations</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-opensearch-service-ai-migrations</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 03:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Service now offers an AI-assisted migration experience to simplify moving self-managed Solr, Elasticsearch, or OpenSearch deployments to OpenSearch Serverless or Managed Clusters.
+2. Outcome (impact):
+This new AI-assisted feature reduces the complexity and time required for migrations, minimizes errors, and provides a more reliable migration process.
+3. Where to use (use case):
+Ideal for organizations looking to transition from self-managed search and analytics solutions to AWS-managed OpenSearch services without extensive manual intervention.</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio notebooks now support G7e instance types</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/02/g7e-new-launch-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 01:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Studio now supports G7e instances, featuring powerful GPUs and CPUs for enhanced AI and graphics processing.
+2. Outcome (impact):
+   Users can leverage high-performance computing for large language models, multimodal AI, and spatial computing workloads with improved efficiency and reduced latency.
+3. Where to use (use case):
+   Ideal for deploying large language models, agentic AI, multimodal generative AI, physical AI models, and spatial computing applications.</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>AWS Transform for migrations now supports all AWS commercial regions as migration targets</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-transform-migrations-region-expansion/</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 17:30:40 GMT</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform for migrations now supports migrations to all commercial regions, enabling easier compliance with data residency requirements.
+2. Outcome (impact):
+Customers can now deploy workloads in any commercial region, enhancing flexibility and meeting regulatory demands more effectively.
+3. Where to use (use case):
+Use this feature to migrate workloads to specific regions where data residency and compliance requirements must be met.</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>AWS Transform for migrations</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>MSK Replicator now supports mutual TLS (mTLS) authentication for replication from external Apache Kafka clusters to MSK Express brokers</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-msk-replicator-mtls-support</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon MSK Replicator now supports mutual TLS authentication for replicating data from external Kafka clusters to MSK Express brokers.
+2. Outcome (impact):  
+This enhancement allows secure data replication from external Kafka clusters to MSK Express, enabling easier migration, disaster recovery, and hybrid cloud data distribution.
+3. Where to use (use case):  
+Use this feature to migrate workloads to MSK Express, set up disaster recovery with MSK Express as a backup, and distribute data across hybrid and multi-cloud environments securely.</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Amazon Managed Streaming for Apache Kafka (MSK)</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -18902,7 +19346,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23 06:56:05</t>
+          <t>2026-06-24 06:53:47</t>
         </is>
       </c>
     </row>
@@ -18913,7 +19357,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -18923,7 +19367,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2838</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="7">
@@ -18933,7 +19377,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>990</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="8">
@@ -18943,7 +19387,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000201</v>
+        <v>0.000298</v>
       </c>
     </row>
     <row r="9">
@@ -18953,7 +19397,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000281</v>
+        <v>0.000423</v>
       </c>
     </row>
     <row r="10">
@@ -18963,7 +19407,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000483</v>
+        <v>0.000721</v>
       </c>
     </row>
     <row r="11">
@@ -18973,7 +19417,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.030808</v>
+        <v>0.031529</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F509"/>
+  <dimension ref="A1:F516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -19281,6 +19281,265 @@
       <c r="F509" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Amazon EC2 announces AMI Watermarks for improved AMI governance</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ec2-image-watermarks-allowed-images</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 introduces AMI watermarks to embed custom identifiers in private AMIs, ensuring traceability and governance across instances and accounts.
+2. Outcome (impact):
+AMI watermarks help organizations identify trusted AMIs, track their provenance, and enforce governance policies by embedding metadata that persists through AMI copies and new creations.
+3. Where to use (use case):
+Use AMI watermarks to manage and govern AMI usage across multiple accounts and regions, ensuring compliance and security by restricting instance launches to approved AMIs.</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless now supports live configuration updates without application restarts</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-emr-serverless/</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 19:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EMR Serverless now allows live configuration updates without restarting applications, enhancing operational efficiency.
+2. Outcome (impact):  
+This update minimizes downtime and operational overhead by enabling immediate configuration changes, ensuring continuous job execution.
+3. Where to use (use case):  
+Ideal for scenarios requiring frequent scaling adjustments or custom image updates, such as dynamic data processing workloads.</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>AWS IoT Device SDK for Swift is now generally available</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-iot-device-sdk-swift/</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 18:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has released the IoT Device SDK for Swift, enabling secure and scalable IoT application development on Apple platforms and Linux.
+2. Outcome (impact):
+Swift developers can now build robust IoT applications with native support for AWS IoT services, enhancing security and scalability across Apple devices and Linux.
+3. Where to use (use case):
+Ideal for managing IoT device fleets, synchronizing device states, automating device onboarding, and ensuring secure communication in applications on macOS, iOS, tvOS, and Linux.</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>AWS IoT Device SDK</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Amazon Neptune now supports AWS CloudFormation for global databases</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-neptune-aws-cloudformation/</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Neptune now supports AWS CloudFormation for managing Neptune global databases, enabling automated deployment and configuration management.
+2. Outcome (impact):  
+   Simplifies provisioning and management of multi-region graph databases, enhancing deployment automation, version control, and integration with CI/CD pipelines.
+3. Where to use (use case):  
+   Ideal for applications requiring low-latency read access, disaster recovery, data residency compliance, and high-availability graph deployments.</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Amazon Neptune</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch now supports tags on dashboards</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-tags-on-dashboards</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch now allows tagging for dashboards, enabling better organization, categorization, and access control through key-value pairs.
+2. Outcome (impact):
+This feature enhances the management of CloudWatch dashboards by allowing users to group, filter, and control access based on tags, improving resource organization and security.
+3. Where to use (use case):
+Use tagging for CloudWatch dashboards to organize dashboards by team, project, or environment, implement attribute-based access control, and filter dashboards in AWS Resource Explorer.</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7in-24TB instances now available in AWS Asia Pacific (Seoul) region</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-u7in-24tb-aws-seoul/</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 01:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS introduces U7in-24TB instances in Asia Pacific (Seoul) with 24 TiB DDR5 memory, 896 vCPUs, and 100 Gbps EBS bandwidth.
+2. Outcome (impact):  
+   Enhanced transaction processing and scalability for mission-critical in-memory databases in fast-growing data environments.
+3. Where to use (use case):  
+   Ideal for running in-memory databases like SAP HANA, Oracle, and SQL Server.</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty AI-powered investigations accelerate threat response (Preview)</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-guardduty/</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 19:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces AI-powered investigations in Amazon GuardDuty, automating threat analysis to expedite threat response and reduce alert fatigue.
+2. Outcome (impact):  
+This feature accelerates incident response by quickly distinguishing true threats from benign findings, enabling security teams to focus on genuine threats and reduce mean time to resolution.
+3. Where to use (use case):  
+Ideal for security operations centers and cloud security analysts managing multiple AWS accounts or entire AWS Organizations, to efficiently handle security alerts.</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19605,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24 06:53:47</t>
+          <t>2026-06-25 06:53:15</t>
         </is>
       </c>
     </row>
@@ -19357,7 +19616,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -19367,7 +19626,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4201</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="7">
@@ -19377,7 +19636,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1489</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8">
@@ -19387,7 +19646,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000298</v>
+        <v>0.000162</v>
       </c>
     </row>
     <row r="9">
@@ -19397,7 +19656,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000423</v>
+        <v>0.000241</v>
       </c>
     </row>
     <row r="10">
@@ -19407,7 +19666,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000721</v>
+        <v>0.000403</v>
       </c>
     </row>
     <row r="11">
@@ -19417,7 +19676,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.031529</v>
+        <v>0.031932</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F516"/>
+  <dimension ref="A1:F528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -19540,6 +19540,450 @@
       <c r="F516" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C7a instances are now available in the Asia Pacific (Singapore) Region</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-c7a-instances-asia-pacific-singapore-region/</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 22:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C7a instances, powered by 4th Gen AMD EPYC processors, are now available in the Asia Pacific (Singapore) Region, offering up to 50% higher performance than C6a instances.
+2. Outcome (impact):
+Enhanced performance and memory bandwidth for compute-intensive workloads, with support for up to 128 EBS volumes per instance.
+3. Where to use (use case):
+Ideal for high-performance, compute-intensive workloads such as batch processing, distributed analytics, HPC, ad serving, gaming, and video encoding.</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8a instances now available in the Asia Pacific (Mumbai) region</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-m8a-instances-asia-pacific-mumbai-region/</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 22:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 M8a instances, powered by 5th Gen AMD EPYC processors, are now available in the Asia Pacific (Mumbai) region, offering higher performance and better price-performance.
+2. Outcome (impact):
+   Customers can achieve up to 30% higher performance and 19% better price-performance, making these instances ideal for latency-sensitive workloads and specific applications.
+3. Where to use (use case):
+   Suitable for financial applications, gaming, rendering, application servers, simulation modeling, mid-size data stores, application development environments, and caching fleets.</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>OpenAI GPT, OpenAI GPT OSS, and NVIDIA Nemotron models on Amazon Bedrock receive FedRAMP High and DoD IL-4/5 approval in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/addl-bedrock-model-fedramp-il-5-govcloud</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS GovCloud (US) now supports FedRAMP High and DoD IL-4/5 compliant versions of OpenAI GPT, OSS, and NVIDIA Nemotron models on Amazon Bedrock.
+2. Outcome (Impact):  
+Federal agencies and organizations with stringent security requirements can now confidently build and scale generative AI applications using these models.
+3. Where to Use (Use Case):  
+Ideal for government workloads, public sector projects, and enterprises needing high compliance standards in AI applications.</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall now supports managed threat intelligence rules from VisionHeight</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/network-firewall-visionheight-managed-rules</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 20:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Network Firewall now integrates managed threat intelligence rules from VisionHeight, including Zero-Day Threat Protection and Noisy Scanners and Tor Protection.
+2. Outcome (impact):
+Enhances security by proactively blocking emerging threats and reducing unnecessary log noise, thereby improving SOC efficiency and lowering SIEM costs.
+3. Where to use (use case):
+Ideal for organizations looking to strengthen their network defenses against targeted attacks and unwanted traffic, such as Tor exit nodes and high-volume scanning sources.</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Kiro achieves FedRAMP High and DoD IL-4/5 authorization in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/kiro-fedramp-high-dod-il-4-5-govcloud-us/</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Kiro is now authorized for FedRAMP High and DoD IL-4/5 in AWS GovCloud (US), enabling secure application development for federal agencies and enterprises.
+2. Outcome (impact):
+Federal agencies and organizations with stringent security requirements can now confidently use Kiro for sensitive workloads, ensuring compliance with FedRAMP High and DoD CC SRG IL-4/5 standards.
+3. Where to use (use case):
+Ideal for federal agencies, public sector organizations, and enterprises needing to develop secure applications that meet high compliance standards.</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Kiro</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Amazon Redshift adds Reserved Instance upfront pricing options for RG instances</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-redshift-ri-upfront-pricing-rg-instances</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 16:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift introduces All Upfront and Partial Upfront payment options for RG reserved instances, offering significant savings over on-demand rates and greater financial flexibility.
+2. Outcome (impact):
+Customers can now optimize their compute costs more effectively by choosing between upfront, partial upfront, or no upfront payment options, leading to potential cost savings.
+3. Where to use (use case):
+Ideal for organizations with predictable workloads that can commit to longer-term reservations to achieve maximum cost savings.</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>AWS GovCloud (US) now offers US-based, US citizen 24/7 technical support for all customers by default</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/default-govcloud-us-based-support/</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS GovCloud (US) now provides 24/7 US-based, US-citizen technical support by default, ensuring compliance and faster issue resolution.
+2. Outcome (impact):  
+This update enhances security and compliance for AWS GovCloud (US) customers by ensuring all technical support is handled by US citizens within the US, reducing latency and improving response times.
+3. Where to use (use case):  
+Ideal for government agencies and contractors requiring high levels of data security and compliance with ITAR regulations.</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>AWS Backup enhances Amazon S3 backup copy performance</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-backup-amazon-s3-copy-enhancement/</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Backup now offers up to 8x faster S3 backup copy operations for large buckets with minimal changes, using enhanced change tracking.
+2. Outcome (impact):
+Reduces time for cross-account and cross-Region S3 backup copies, improving efficiency and lowering costs.
+3. Where to use (use case):
+Ideal for organizations with large S3 buckets that require frequent cross-account or cross-Region backups.</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom now supports the latest CU and GDR updates for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-rds-custom-supports-latest-cu-gdr-updates-microsoft-sql-server</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 07:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS Custom for SQL Server now supports the latest CU and GDR updates, including SQL Server 2019 CU32+GDR and SQL Server 2022 CU25, enhancing security and performance.
+2. Outcome (impact):
+This update ensures that RDS Custom for SQL Server instances are protected against vulnerabilities and benefit from the latest improvements and fixes provided by Microsoft.
+3. Where to use (use case):
+Ideal for businesses requiring the latest SQL Server updates for compliance, security, and performance enhancements in their database management.</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports the latest GDR updates for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-rds-supports-latest-gdr-updates-microsoft-sql-server</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 07:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for SQL Server now supports the latest GDR updates for SQL Server 2016, 2017, 2019, and 2022, addressing critical vulnerabilities.
+2. Outcome (impact):
+Enhanced security and stability for RDS SQL Server instances by applying the latest GDR updates, mitigating vulnerabilities CVE-2026-32167 and CVE-2026-32176.
+3. Where to use (use case):
+Ideal for environments requiring up-to-date security patches and compliance with the latest Microsoft SQL Server updates, such as financial services, healthcare, and enterprise applications.</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Ingestion now available in AWS Europe (Paris) Region</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/opensearch-ingestion-europe-paris-region-availability</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 01:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Ingestion is now available in the Europe (Paris) Region, enabling data ingestion into OpenSearch Service with no-code processing.
+2. Outcome (impact):
+Customers can now efficiently ingest, filter, and transform data for OpenSearch Service in the eu-west-3 region, enhancing data management capabilities.
+3. Where to use (use case):
+Ideal for organizations needing to process and route large volumes of data into OpenSearch Service for analytics, monitoring, or logging in the Paris region.</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Ingestion</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Amazon Route 53 Global Resolver now supports sharing DNS Views between AWS Accounts</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-route-53-global-resolver/</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 16:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Route 53 Global Resolver now allows sharing DNS views between AWS accounts using AWS RAM, enabling centralized resolution without transferring ownership.
+2. Outcome (impact):
+   Teams can manage their private hosted zones independently while leveraging a centralized global resolver for resolution across all AWS regions, improving efficiency and collaboration.
+3. Where to use (use case):
+   Ideal for organizations with multiple AWS accounts needing to resolve private DNS records centrally without changing ownership or management of their hosted zones.</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Amazon Route 53</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -19605,7 +20049,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25 06:53:15</t>
+          <t>2026-06-26 06:59:36</t>
         </is>
       </c>
     </row>
@@ -19616,7 +20060,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -19626,7 +20070,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2282</v>
+        <v>4384</v>
       </c>
     </row>
     <row r="7">
@@ -19636,7 +20080,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>847</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="8">
@@ -19646,7 +20090,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000162</v>
+        <v>0.000311</v>
       </c>
     </row>
     <row r="9">
@@ -19656,7 +20100,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000241</v>
+        <v>0.000453</v>
       </c>
     </row>
     <row r="10">
@@ -19666,7 +20110,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000403</v>
+        <v>0.000764</v>
       </c>
     </row>
     <row r="11">
@@ -19676,7 +20120,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.031932</v>
+        <v>0.032696</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F528"/>
+  <dimension ref="A1:F531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -19984,6 +19984,117 @@
       <c r="F528" t="inlineStr">
         <is>
           <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8g instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-r8g-instances-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Fri, 26 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EC2 R8g instances, powered by AWS Graviton4 processors, are now available in new regions with up to 30% better performance.
+2. Outcome (impact):  
+Enhanced performance for memory-intensive workloads, up to 30% faster for databases and large Java applications.
+3. Where to use (use case):  
+Ideal for databases, in-memory caches, real-time big data analytics, and other memory-intensive applications.</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8in instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-ec2-c8in-ireland-ohio/</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C8in instances, powered by sixth-generation Intel Xeon Scalable processors, are now available in additional regions with enhanced performance and network bandwidth.
+2. Outcome (Impact):
+Users can leverage higher performance and network capabilities for network-intensive workloads, improving efficiency and scalability for applications like distributed compute and large-scale data analytics.
+3. Where to Use (Use Case):
+Ideal for network-intensive workloads such as distributed computing, large-scale data analytics, and high-performance computing applications.</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches Agentic CX designer (NLX) in preview</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect-customer-agentic-cx-preview/</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 16:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer introduces Agentic CX designer (NLX) in preview, a no-code tool for creating AI-driven self-service experiences, enhancing customer interactions through real-time web/mobile app integration.
+2. Outcome (impact):
+Businesses can rapidly design, test, and deploy AI-powered customer experiences, improving service efficiency and customer satisfaction by enabling seamless voice and digital interactions.
+3. Where to use (use case):
+Ideal for customer service operations in banking, e-commerce, and healthcare, where guided customer interactions and real-time application completion are crucial.</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -20049,7 +20160,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26 06:59:36</t>
+          <t>2026-06-27 06:33:43</t>
         </is>
       </c>
     </row>
@@ -20060,7 +20171,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -20070,7 +20181,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4384</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7">
@@ -20080,7 +20191,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1594</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8">
@@ -20090,7 +20201,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000311</v>
+        <v>8.7e-05</v>
       </c>
     </row>
     <row r="9">
@@ -20100,7 +20211,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000453</v>
+        <v>0.000112</v>
       </c>
     </row>
     <row r="10">
@@ -20110,7 +20221,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000764</v>
+        <v>0.000199</v>
       </c>
     </row>
     <row r="11">
@@ -20120,7 +20231,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.032696</v>
+        <v>0.032895</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F531"/>
+  <dimension ref="A1:F535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -20095,6 +20095,154 @@
       <c r="F531" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>AWS WAF adds support for Amazon Bedrock AgentCore Gateway</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-waf-amazon-bedrock-agentcore/</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Mon, 29 Jun 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS WAF now protects Amazon Bedrock AgentCore Gateway from web exploits, offering IP-based controls, rate-based rules, and managed rule groups.
+2. Outcome (impact):
+Enterprises can safeguard their agentic AI workloads against common web threats with consistent, customizable protections at the Gateway layer.
+3. Where to use (use case):
+Ideal for securing agentic AI applications as they transition from prototype to production, ensuring robust defenses against web-based attacks.</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>AWS WAF</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Amazon MWAA Serverless now supports shared VPC configurations</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-mwaa-serverless-vpc/</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Mon, 29 Jun 2026 17:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon MWAA Serverless now validates shared VPC subnets, enabling workflows in multi-account setups.
+2. Outcome (impact):  
+Organizations can now deploy MWAA Serverless workflows in member accounts using shared subnets without workarounds.
+3. Where to use (use case):  
+Ideal for multi-account landing zone architectures where networking is centrally managed.</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Amazon MWAA Serverless</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Amazon S3 server access logs now deliver to Amazon CloudWatch Logs and Amazon S3 Tables</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-s3-cloudwatch-logs-tables/</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Mon, 29 Jun 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon S3 now delivers server access logs to Amazon CloudWatch Logs and S3 Tables, enhancing monitoring and analysis capabilities.
+2. Outcome (impact):  
+Improved monitoring, instant querying, cross-account/Region aggregation, and SQL querying capabilities for S3 access logs.
+3. Where to use (use case):  
+Monitoring and analyzing S3 access patterns, setting alarms for anomalies, auditing access, and identifying cost drivers.</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache now supports Valkey 9.1</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-elasticache-valkey-9-1/</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 17:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon ElastiCache now supports Valkey 9.1, offering higher throughput, better memory efficiency, and enhanced access control for multi-tenant applications.
+2. Outcome (impact):  
+   Improved performance and operational visibility, enabling higher throughput and reduced memory usage, while simplifying application workflows with new commands.
+3. Where to use (use case):  
+   Ideal for applications requiring high-performance caching, multi-tenant environments, and simplified key management operations.</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>ElastiCache</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -20160,7 +20308,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27 06:33:43</t>
+          <t>2026-06-30 07:00:08</t>
         </is>
       </c>
     </row>
@@ -20171,7 +20319,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -20181,7 +20329,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1219</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="7">
@@ -20191,7 +20339,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>395</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -20201,7 +20349,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.7e-05</v>
+        <v>9.399999999999999e-05</v>
       </c>
     </row>
     <row r="9">
@@ -20211,7 +20359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000112</v>
+        <v>0.00013</v>
       </c>
     </row>
     <row r="10">
@@ -20221,7 +20369,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000199</v>
+        <v>0.000224</v>
       </c>
     </row>
     <row r="11">
@@ -20231,7 +20379,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.032895</v>
+        <v>0.033119</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F535"/>
+  <dimension ref="A1:F559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -20243,6 +20243,898 @@
       <c r="F535" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs enriches log events with AWS resource tags</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-cloudwatch-logs-resource-tags/</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 21:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon CloudWatch Logs now enriches log events with resource tags, simplifying log filtering and analysis by adding metadata directly at ingestion.
+2. Outcome (impact):  
+Easier log management and analysis by leveraging existing resource tags without modifying logging instrumentation, enhancing efficiency in log queries and incident investigations.
+3. Where to use (use case):  
+Use case: Quickly filter and analyze logs based on team ownership, environment, cost center, or application name during operational tasks or incident investigations.</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation and CDK accelerate development feedback loops with pre-deployment validation on all stack operations</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-cloudformation/</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CloudFormation now offers immediate pre-deployment validation on all stack operations, catching errors before resource provisioning and speeding up development cycles.
+2. Outcome (impact):
+   Developers can identify and fix deployment errors faster, reducing the time spent on full provision-and-rollback cycles and enhancing overall development efficiency.
+3. Where to use (use case):
+   Ideal for CI/CD pipelines, manual iterations, and AI agents automating infrastructure provisioning, ensuring robust and error-free deployments.</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation and CDK express mode speeds up infrastructure deployments by up to 4x</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-cloudformation-cdk/</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CloudFormation and CDK express mode accelerates infrastructure deployment times by up to 4x, completing stack operations once resource configuration is applied.
+2. Outcome (impact):
+   Developers and AI agents can achieve faster iteration cycles, reducing wait times significantly during infrastructure development.
+3. Where to use (use case):
+   Ideal for development environments where rapid infrastructure changes and iterations are necessary, such as testing new configurations or features.</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>CloudFormation</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Amazon RDS Enhances IAM Database Authentication with Connection Rate Scaling</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-rds-iam/</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS now dynamically scales IAM database authentication connection rates based on instance resources, enhancing performance for high-volume workloads.
+2. Outcome (impact):
+This enhancement allows enterprise workloads to efficiently use IAM database authentication for high-connection scenarios, improving performance and reliability.
+3. Where to use (use case):
+Ideal for enterprise applications requiring robust IAM database authentication, such as high-traffic web applications, large-scale data processing systems, and critical business applications.</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service supports in-place Slurm major version upgrades</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-parallel-computing-service-upgrade/</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 19:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Parallel Computing Service now enables seamless in-place upgrades of Slurm major versions for existing clusters, ensuring uninterrupted job execution.
+2. Outcome (impact):
+This feature allows users to advance their Slurm versions with minimal downtime, facilitating easier management of HPC environments and ensuring continuity of operations.
+3. Where to use (use case):
+Ideal for high-performance computing (HPC) environments that require frequent updates to Slurm versions to leverage new features or security patches without disrupting ongoing computations.</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service (PCS)</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache T4g nodes now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-elasticache-t4g-additional-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ElastiCache now offers T4g nodes in five new regions, powered by AWS Graviton2 processors for burstable CPU performance.
+2. Outcome (impact):
+   Users can now deploy ElastiCache clusters in additional regions with cost-effective, burstable CPU performance suitable for variable workloads.
+3. Where to use (use case):
+   Ideal for applications with unpredictable workloads, such as web applications, microservices, and development/test environments.</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Amazon Neptune announces dual stack support with IPv6</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-neptune-ipv6/</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Neptune now supports dual-stack mode, allowing connections over IPv4, IPv6, or both, with options for private and public configurations.
+2. Outcome (impact):  
+Enables organizations to adopt IPv6 while maintaining compatibility with IPv4, facilitating smoother transitions to modern networking protocols.
+3. Where to use (use case):  
+Ideal for internal applications needing isolated IPv6 endpoints or internet-facing applications requiring hybrid network support.</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Amazon Neptune</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging RCS now supports rich media and interactive messaging</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-end-user-messaging-rcs/</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 18:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS End User Messaging now supports rich media and interactive RCS messaging across 22 countries, enabling rich cards, carousels, and interactive actions within messaging apps.
+2. Outcome (impact):
+Enhances user engagement and interaction by providing a seamless, in-app experience for users to perform actions like booking appointments, browsing products, and completing payments without leaving the messaging app.
+3. Where to use (use case):
+Ideal for customer service, e-commerce, appointment scheduling, payment processing, and AI-driven interactions within messaging platforms.</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>AWS End User Messaging</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Amazon Time Sync Service adds support for Microsecond accurate time on 26 additional EC2 instance types in all commercial regions</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ec2-time-sync-precision-time-placement-group</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Time Sync Service now offers microsecond accurate time on 26 additional EC2 instance types across all commercial regions, enhancing precision for distributed applications.
+2. Outcome (impact):
+This update allows developers to achieve higher accuracy in time-sensitive applications, improving event ordering, network latency measurements, and transaction speeds in distributed systems.
+3. Where to use (use case):
+Ideal for financial trading platforms, high-frequency trading systems, real-time analytics, and any application requiring precise time synchronization.</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Amazon Time Sync Service</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Announcing general availability of Amazon WorkSpaces for AI agents</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-workspaces-ai/</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 17:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon WorkSpaces for AI agents is now generally available, enabling AI agents to securely operate desktop applications in managed cloud environments without requiring modernization.
+2. Outcome (impact):
+   Enterprises can automate critical business processes on legacy desktop applications, ensuring compliance and governance while reducing costs and improving efficiency.
+3. Where to use (use case):
+   Ideal for automating workflows in industries such as finance (trade settlement), healthcare (patient record updates), and insurance (claims processing).</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Auto Scaling now supports reservations then balanced Availability Zone distribution</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ec2-auto-scaling-res-then-balanced/</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 17:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   Amazon EC2 Auto Scaling now supports a new AZ distribution strategy called "reservations-then-balanced" to maximize pre-purchased capacity utilization.
+2. Outcome (Impact)
+   This strategy ensures efficient use of On-Demand Capacity Reservations, Capacity Blocks, and Interruptible Capacity Reservations while maintaining operational simplicity and resilience.
+3. Where to Use (Use Case)
+   Ideal for organizations that have pre-purchased capacity and want to ensure it is utilized before distributing remaining capacity across AZs.</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Auto Scaling</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Announcing Capability Insights for AWS, an open-source solution for regional capabilities</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/capability-insights-aws/</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces Capability Insights, an open-source solution to deploy regional capabilities data within your VPC, ensuring data residency and compliance.
+2. Outcome (impact):
+Facilitates quick multi-Region gap analysis, supports compliance and data residency, and provides full control over infrastructure hosting regional capabilities data.
+3. Where to use (use case):
+Ideal for organizations with data residency requirements, compliance teams, and those planning regional expansion or multi-Region recovery strategies.</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Amazon VPC</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI cuts generative AI inference scale-out time by up to half with automatic container image caching</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/sagemakerai-inf-scale-out-time</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 16:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   Amazon SageMaker Inference now speeds up scaling for generative AI models by caching container images, reducing cold-start latency.
+2. Outcome (impact)
+   This update reduces generative AI inference scale-out time by up to half, improving response times during scaling events.
+3. Where to use (use case)
+   Ideal for deploying large deep learning models in environments requiring rapid scaling, such as real-time recommendation systems and dynamic content generation.</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>AWS Security Hub CSPM launches AI Security Best Practices standard with 31 automated controls</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-security-hub-cspm-ai-security/</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 16:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Hub CSPM introduces an AI Security Best Practices standard with 31 automated controls to ensure AI resources adhere to security best practices.
+2. Outcome (impact):
+This standard helps organizations continuously evaluate and secure their AI workloads, reducing the risk of misconfigurations and enhancing overall security posture.
+3. Where to use (use case):
+Ideal for securing Amazon Bedrock, Bedrock AgentCore, and SageMaker workloads by automating the assessment of critical security domains.</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>AWS Security Hub CSPM</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>IAM Identity Center now enables programmatic AWS account access for customer managed applications</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-iam-identity-center-account-access-customer-managed-apps/</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   IAM Identity Center now allows customer managed applications to programmatically access AWS accounts using external identity providers, eliminating redundant sign-ins.
+2. Outcome (Impact):
+   This update streamlines user access to AWS accounts by enabling single sign-on (SSO) for customer managed applications, reducing the need for multiple authentication steps and enhancing user experience.
+3. Where to Use (Use Case):
+   Ideal for organizations using external identity providers to manage user access to multiple AWS accounts, ensuring seamless and secure access without repeated sign-ins.</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 is now available on AWS</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/claude-sonnet-5-now-available-on-aws</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS now offers Claude Sonnet 5, Anthropic's latest model, for coding, agents, and professional tasks at Sonnet pricing.
+2. Outcome (impact):
+   Enhanced performance in coding, agent tasks, and professional work with balanced capability, cost, and speed.
+3. Where to use (use case):
+   Coding, agentic tasks, professional document drafting, and data analysis.</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI now supports serverless model customization for Gemma 4 models</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-sagemaker-ai-gemma-4/</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker now supports serverless customization for Gemma 4 models, enabling domain-specific adaptations with supervised fine-tuning, direct preference optimization, and reinforcement fine-tuning.
+2. Outcome (impact):
+Users can now tailor Gemma 4 models to their specific needs without managing infrastructure, improving model accuracy and performance for domain-specific tasks.
+3. Where to use (use case):
+Adapting open models for specific organizational needs, such as improving task accuracy, aligning outputs with corporate tone, or enhancing performance on new tasks using proprietary data.</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C9g and C9gd compute optimized instances are now available</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/ec2-c9g-c9gd-instances-graviton5-processors-available/</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EC2 C9g and C9gd instances, powered by AWS Graviton5 processors, are now available, offering enhanced compute performance and security.
+2. Outcome (impact):  
+These instances provide up to 25% better compute performance, 30% faster databases, 35% faster web apps and ML, and feature the Nitro Isolation Engine for enhanced security.
+3. Where to use (use case):  
+Ideal for HPC, batch processing, gaming, video encoding, scientific modeling, distributed analytics, CPU-based ML inference, real-time analytics, and ad serving.</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8 is now available in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/claude-opus-4.8-aws-govcloud-us</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS GovCloud (US) now offers Anthropic's latest model, Claude Opus 4.8, enhancing agentic coding, professional knowledge work, and autonomous task management.
+2. Outcome (impact):  
+Developers and enterprises can leverage advanced AI capabilities for production applications, improving efficiency, error recovery, and consistency in long-running tasks.
+3. Where to use (use case):  
+Ideal for production AI applications in coding, agentic tasks, and professional knowledge work requiring deep reasoning and long-term context.</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-5.4 and NVIDIA Nemotron 3 Super 120B now available on Kiro in AWS GovCloud (US-West) Region</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/kiro-gpt-nemotron-launch-aws-govcloud-us/</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Two new AI models, OpenAI GPT-5.4 and NVIDIA Nemotron 3 Super 120B, are now available on Kiro in AWS GovCloud (US-West) for advanced AI applications.
+2. Outcome (impact):  
+   Developers can leverage these models for complex reasoning, coding, document analysis, and multi-step agentic workflows, enhancing productivity and efficiency in AI application development.
+3. Where to use (use case):  
+   Ideal for tasks requiring sophisticated AI capabilities, such as interpreting context, interacting with tools, operating software environments, and verifying outputs across multiple steps.</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Kiro</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers announces DDoS Protection client SDKs for C# and Unity</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-gamelift-servers-ddos-protection-unity</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GameLift Servers introduces DDoS Protection client SDKs for C# and Unity, enhancing game security against DDoS attacks with no extra cost.
+2. Outcome (impact):
+Game developers can now protect their session-based multiplayer games from denial-of-service attacks, ensuring smoother gameplay and better player experience.
+3. Where to use (use case):
+Ideal for developers of session-based multiplayer games who need to safeguard their games from DDoS attacks, ensuring uninterrupted gameplay for players.</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch pipelines now supports processing and enriching OpenTelemetry metrics</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/cloudwatch-pipelines-otel-metrics</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 07:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch pipelines now support processing and enriching OpenTelemetry metrics during ingestion, allowing for centralized transformations without modifying application instrumentation.
+2. Outcome (impact):
+   This update enables users to enrich and transform OpenTelemetry metrics centrally, reducing the need for custom processing layers and ensuring consistent naming conventions and reduced storage costs.
+3. Where to use (use case):
+   Ideal for organizations that need to add business context to their metrics, manage high-cardinality labels, and enforce naming conventions across their infrastructure.</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>AWS Service Availability Updates</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-service-availability/</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS is updating its service availability, moving certain services to maintenance and sunsetting others, affecting new customer access and operational support.
+2. Outcome (impact):
+New customers will not be able to access certain AWS services starting July 30, 2026, while existing customers can continue using them. Services will be fully sunset on specified dates, ending operations and support.
+3. Where to use (use case):
+These services are used in various scenarios such as AI/ML model management, user authentication, data search, IoT device security, mainframe modernization, and resource management.
+AWS Service: Amazon Cognito Sync | Category: Security
+AWS Service: Amazon Kendra | Category: Analytics
+AWS Service: AWS IoT Device Defender – Detect | Category: Security
+AWS Service: AWS Systems Manager – Application Manager | Category: Management</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Agents</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms now supports intermediate tables for SQL</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-clean-rooms-intermediate-tables</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Clean Rooms now supports intermediate tables for SQL, enhancing flexibility for multi-step analytical workflows within secure collaborations.
+2. Outcome (impact):
+This feature allows organizations to reuse complex SQL query results, enabling more efficient and cost-effective data analysis within privacy boundaries.
+3. Where to use (use case):
+Use case: Publishers and advertisers can build and reuse ID mapping tables for various analyses, optimizing performance and reducing costs.</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -20308,7 +21200,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30 07:00:08</t>
+          <t>2026-07-01 07:17:28</t>
         </is>
       </c>
     </row>
@@ -20319,7 +21211,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -20329,7 +21221,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1324</v>
+        <v>8915</v>
       </c>
     </row>
     <row r="7">
@@ -20339,7 +21231,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>459</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="8">
@@ -20349,7 +21241,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.399999999999999e-05</v>
+        <v>0.000633</v>
       </c>
     </row>
     <row r="9">
@@ -20359,7 +21251,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00013</v>
+        <v>0.000878</v>
       </c>
     </row>
     <row r="10">
@@ -20369,7 +21261,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000224</v>
+        <v>0.001511</v>
       </c>
     </row>
     <row r="11">
@@ -20379,7 +21271,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.033119</v>
+        <v>0.03463</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F559"/>
+  <dimension ref="A1:F578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -21135,6 +21135,717 @@
       <c r="F559" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore increases default runtime quota limits</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-bedrock-agentcore-increases-default-runtime-quota-limits/</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore has increased its default runtime quota limits, enabling higher scalability for agent-based workloads.
+2. Outcome (impact):
+Customers can now run more AI agents simultaneously, supporting up to 5,000 active concurrent sessions in select regions and 2,500 in others, with enhanced interaction and session creation rates.
+3. Where to use (use case):
+Ideal for applications requiring high-throughput AI agent interactions, such as customer service chatbots, automated trading systems, and real-time data processing.</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch supports creating alarms from log queries</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-cloudwatch-log-alarms/</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 21:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch now enables direct creation of alarms from log queries, allowing for streamlined monitoring and alerting based on log data.
+2. Outcome (impact):
+   This feature simplifies the monitoring process by eliminating the need for intermediate steps like creating metric filters or custom metrics, thereby reducing complexity and improving efficiency.
+3. Where to use (use case):
+   Use this feature to monitor log data for anomalies such as error rates by service, and receive immediate notifications when thresholds are breached, all within the log analysis workflow.</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>ECS Service Connect now supports Zone-Aware routing</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/ecs-service-connect-zone-aware/</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 21:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   ECS Service Connect now supports zone-aware routing to minimize cross-AZ costs and latency by prioritizing same-AZ traffic.
+2. Outcome (impact):
+   Reduces cross Availability Zone data transfer costs and latency, enhancing cost efficiency and performance for microservices architectures.
+3. Where to use (use case):
+   Ideal for applications distributed across multiple AZs for high availability, aiming to optimize service-to-service communication costs and speed.</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Amazon Elastic Container Service (ECS)</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Amazon ECS now provides real-time deployment observability in the AWS Management Console</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ecs-aws-management-console/</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 20:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now offers real-time deployment observability in the AWS Management Console, enabling users to monitor and troubleshoot deployments more effectively.
+2. Outcome (impact):
+Users can now track deployment progress, monitor health, and diagnose failures directly from the console, reducing troubleshooting time and improving deployment reliability.
+3. Where to use (use case):
+Ideal for developers and DevOps teams managing containerized applications on Amazon ECS, ensuring smoother and more reliable deployments.</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>AWS Artifact now includes Assurance Assistant for compliance inquiries</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-artifact-assurance-assistant/</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 20:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Artifact now offers Assurance Assistant, an AI-powered tool providing citation-backed compliance answers for security and compliance inquiries.
+2. Outcome (impact):  
+Assurance Assistant accelerates vendor assessments and DDQ completions, allowing third-party risk managers and auditors to quickly access verified AWS compliance information.
+3. Where to use (use case):  
+Ideal for third-party risk managers, compliance officers, security engineers, and auditors to efficiently complete vendor assessments and due diligence questionnaires.</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>AWS Artifact</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>AWS Partner Central now supports AWS Marketplace listings for co-selling</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-marketplace-co-selling-support/</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 19:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Central now allows partners to directly associate AWS Marketplace solutions and products with co-selling opportunities, streamlining the process and improving tracking.
+2. Outcome (impact):
+Partners can now more effectively manage and track their AWS Marketplace listings and co-selling opportunities in one place, reducing the need to maintain separate catalogs and simplifying the co-selling process.
+3. Where to use (use case):
+This feature is ideal for AWS partners who want to seamlessly integrate their AWS Marketplace offerings into their co-selling opportunities, ensuring better alignment and tracking of their sales efforts.</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Amazon RDS announces Cross-Region Automated Backups in four additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-cross-region-automated-backups-additional-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS now supports Cross-Region Automated Backup replication in four additional regions, enhancing disaster recovery capabilities.
+2. Outcome (impact):
+   Improved disaster recovery and business continuity by allowing automated backup replication across specified regions, ensuring data availability and minimal downtime.
+3. Where to use (use case):
+   Ideal for mission-critical applications requiring high availability and disaster recovery solutions across multiple regions.</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore now available in four additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-bedrock-agentcore-four-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore is now available in four new regions, enhancing agent deployment and performance for customers globally.
+2. Outcome (impact):
+Customers in Asia Pacific (Bangkok), Asia Pacific (Malaysia), Europe (Milan), and Europe (Spain) can now deploy agents with lower latency and improved performance.
+3. Where to use (use case):
+Use AgentCore to build, connect, and optimize agents for enterprise applications, enabling faster agent deployment and better performance near end users.</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Amazon ECS now supports configurable deployment circuit breaker settings</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ecs-circuit-breaker-settings/</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon ECS now allows customizable deployment circuit breaker settings to manage failed deployments and automatic rollbacks.
+2. Outcome (impact):  
+Users can now fine-tune deployment failure thresholds and rollback mechanisms to better suit their application's needs and environments.
+3. Where to use (use case):  
+Ideal for managing deployments in development, testing, and production environments with varying tolerance for task failures.</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty adds sensitive file modification threat detections</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-guardduty-sfm/</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 16:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon GuardDuty now detects sensitive file modifications on EC2, EKS, and ECS workloads, alerting security teams to potential post-compromise activities.
+2. Outcome (impact):  
+Enhances threat detection capabilities by identifying unauthorized modifications to critical system files, reducing false positives, and providing actionable intelligence.
+3. Where to use (use case):  
+Ideal for security teams, DevSecOps professionals, and cloud security architects managing AWS compute environments to ensure comprehensive threat visibility.</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>AWS AppConfig launches managed experimentation tools for A/B testing</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/6/aws-appconfig-experimentation/</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS AppConfig now offers managed experimentation tools for A/B testing, enabling robust feature experiments without separate infrastructure.
+2. Outcome (impact):
+Facilitates confident, data-driven decisions for feature rollouts, leveraging AI-driven guidance and Amazon's best practices.
+3. Where to use (use case):
+Ideal for running A/B tests and multivariate experiments across various application components, including UI changes, recommendation algorithms, and AI model selections.</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>AWS AppConfig</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Amazon ECS Express Mode now supports custom task definitions</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ecs-express-mode-custom-task-def/</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 16:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS Express Mode now supports custom task definitions, allowing for advanced configurations while maintaining simplified deployment.
+2. Outcome (impact):
+Users can leverage existing ECS task definitions and advanced customizations within Express Mode, enhancing flexibility and operational efficiency.
+3. Where to use (use case):
+Ideal for deploying containerized web applications and APIs with the need for custom configurations and existing CI/CD integration.</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports Kubernetes version rollback</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-eks-version-rollback</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EKS now supports Kubernetes version rollback, allowing users to revert to the previous minor version within 7 days post-upgrade.
+2. Outcome (impact):
+   This feature provides a safety net during upgrades, enabling users to validate new Kubernetes versions in production and rollback if issues arise.
+3. Where to use (use case):
+   Ideal for managing Kubernetes clusters in production environments where minimizing downtime and ensuring stability during upgrades is critical.</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus achieves FedRAMP High and DoD IL-4/5 authorization in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-managed-service-prometheus-fedramp-high/</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 15:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Managed Service for Prometheus now meets FedRAMP High and DoD IL-4/5 standards in AWS GovCloud (US), enabling secure monitoring for sensitive environments.
+2. Outcome (impact):  
+   Federal agencies and public sector organizations can confidently use Amazon Managed Service for Prometheus to monitor their workloads, ensuring compliance with stringent security and regulatory requirements.
+3. Where to use (use case):  
+   Ideal for federal agencies, public sector organizations, and enterprises needing to monitor and alert on operational metrics in compliance with FedRAMP High and DoD IL-4/5 standards.</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>AWS Security Agent now available in Asia Pacific (Mumbai), Asia Pacific (Singapore), and South America (São Paulo)</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-security-agent-asia-pacific/</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 15:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Agent is now available in Mumbai, Singapore, and São Paulo, offering threat modeling, code reviews, and penetration testing.
+2. Outcome (impact):
+Customers in these regions can now secure their applications early in the development lifecycle with advanced security tools.
+3. Where to use (use case):
+Ideal for developers and security teams looking to integrate security practices throughout the application development process.</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>AWS Security Agent</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Db2 now supports self-managed Active Directory</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-db2-supports-self-managed-active-directory</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 07:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for Db2 now directly supports self-managed Active Directory for domain joining and Kerberos authentication, simplifying user management and compliance.
+2. Outcome (impact):
+   Simplifies database user authentication and authorization by eliminating the need for AWS Managed Microsoft AD and trust relationships, reducing complexity and operational overhead.
+3. Where to use (use case):
+   Ideal for organizations that need to integrate their RDS for Db2 instances with existing on-premises or cloud-based Active Directory environments for streamlined access control and compliance.</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Db2</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service optimized for log analytics</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-opensearch-service-optimized-log-analytics</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Wed, 01 Jul 2026 02:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Service introduces a new engine optimized for log analytics, offering up to 4x better price-performance and 70% lower storage costs.
+2. Outcome (impact):
+- Up to 4x better price-performance on internal benchmarks.
+- Up to 70% lower storage costs with new columnar storage.
+- Up to 3x more data retention at the same cost.
+- Up to 2x higher ingestion throughput.
+- Up to 2x faster analytical queries.
+3. Where to use (use case):
+- Cloud-native architectures.
+- AI workloads.
+- Compliance needs.
+- Aggregations and trend analysis.
+- Incident investigations requiring precise text search.</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall now supports container attribute-based inspection for Amazon EKS and Amazon ECS</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-network-firewall-container-attributes-referencing</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Network Firewall now supports container attribute-based inspection for Amazon EKS and ECS, simplifying security for containerized workloads.
+2. Outcome (impact):  
+This feature simplifies container security management, reduces complexity, and ensures consistent protection as containers scale or restart.
+3. Where to use (use case):  
+Ideal for securing containerized applications, including generative AI workloads, on Amazon EKS and ECS by applying attribute-based rules.</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>AWS announces AWS Interconnect - last mile new partner with AT&amp;T in gated preview</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-announces-AWS-interconnect-last-mile-ATT-gated-preview/</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced AWS Interconnect - last mile, a managed service in collaboration with AT&amp;T, simplifying private, high-speed connections to AWS with automated network setup.
+2. Outcome (impact):
+This service reduces the complexity and time required to establish secure, high-speed connections to AWS, enhancing connectivity efficiency and reliability for businesses.
+3. Where to use (use case):
+Ideal for businesses needing to connect branch offices, data centers, and remote locations to AWS with minimal setup effort, ensuring high availability and reliability.</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>AWS Interconnect - last mile</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -21200,7 +21911,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:17:28</t>
+          <t>2026-07-02 06:47:05</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21922,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -21221,7 +21932,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8915</v>
+        <v>6914</v>
       </c>
     </row>
     <row r="7">
@@ -21231,7 +21942,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3090</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="8">
@@ -21241,7 +21952,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000633</v>
+        <v>0.000491</v>
       </c>
     </row>
     <row r="9">
@@ -21251,7 +21962,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000878</v>
+        <v>0.000673</v>
       </c>
     </row>
     <row r="10">
@@ -21261,7 +21972,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001511</v>
+        <v>0.001164</v>
       </c>
     </row>
     <row r="11">
@@ -21271,7 +21982,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03463</v>
+        <v>0.035794</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F578"/>
+  <dimension ref="A1:F585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -21846,6 +21846,265 @@
       <c r="F578" t="inlineStr">
         <is>
           <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports Terraform for provisioning</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-unified-studio-terraform/</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 21:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker Unified Studio now supports Terraform for provisioning, enabling infrastructure-as-code deployment of unified development environments.
+2. Outcome (impact):  
+This integration allows platform teams to maintain consistency across environments and streamline the deployment of SageMaker Unified Studio domains using version-controlled templates.
+3. Where to use (use case):  
+Ideal for data teams needing a consistent, version-controlled setup for development, staging, and production environments in SageMaker Unified Studio.</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Amazon EC2 X8i instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/02/amazon-ec2-x8i-instances-ICN-KUL-NRT-region/</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 20:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 X8i instances are now available in three new regions, offering enhanced performance and memory capacity for memory-intensive workloads.
+2. Outcome (impact):
+   Users can now leverage high-performance, memory-optimized instances in additional regions, improving the efficiency and speed of their memory-intensive applications.
+3. Where to use (use case):
+   Ideal for workloads such as SAP HANA, large databases, data analytics, and Electronic Design Automation (EDA).</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Dedicated Hosts now support AMD SEV-SNP</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/ec2-amd-sev-snp-dedicated-hosts</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 now supports AMD SEV-SNP on Dedicated Hosts, enabling secure, confidential computing workloads on fully dedicated physical servers.
+2. Outcome (impact):
+   Customers can now run sensitive applications with enhanced security, leveraging Dedicated Hosts for better control and consistency.
+3. Where to use (use case):
+   Ideal for industries requiring high security and compliance, such as finance, healthcare, and government.</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports AMI versioning and auto-patching</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-hyperpod-ami-version-auto-patch</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker HyperPod now supports AMI versioning and auto-patching to enhance security and operational efficiency.
+2. Outcome (impact):
+   Improved visibility and control over AMI versions, automated security patching, and reduced operational burden for cluster administrators.
+3. Where to use (use case):
+   Ideal for training and deploying foundation models at scale, ensuring clusters remain secure and consistent without disrupting workloads.</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>AWS Config now supports 8 new resource types</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-config-new-resource-types</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Config now supports 8 new resource types, enhancing monitoring and compliance across AWS services.
+2. Outcome (impact):
+This update allows for more comprehensive tracking, auditing, and remediation of AWS resources, improving overall environment management.
+3. Where to use (use case):
+Ideal for organizations needing detailed visibility and control over their AWS resources, ensuring compliance and security across expanded service types.</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>AWS Config</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports rule based redaction for agent screen recording</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/screen-recording-rule-based/</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 22:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect now offers rule-based redaction for agent screen recordings to protect sensitive information by automatically obscuring specific applications or URLs.
+2. Outcome (impact):
+This feature enhances data privacy and compliance by ensuring that sensitive information is not captured in agent screen recordings, which are used for supervision and coaching.
+3. Where to use (use case):
+Use this feature in customer service environments where agent screen recordings are utilized for training and quality assurance, ensuring compliance with data protection regulations.</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports assigning up to 7 security profiles with granular access controls per user</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/connect-7-security-profiles-user/</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 18:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now allows assigning up to 7 security profiles per user for enhanced access control.
+2. Outcome (Impact):
+   This update provides greater flexibility and security by enabling agents to have distinct permissions for multiple lines of business, ensuring least privilege access.
+3. Where to Use (Use Case):
+   Ideal for organizations with multiple business lines, such as financial services companies, where agents need specific access to resources related to different divisions.</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -21911,7 +22170,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02 06:47:05</t>
+          <t>2026-07-03 06:37:20</t>
         </is>
       </c>
     </row>
@@ -21922,7 +22181,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -21932,7 +22191,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6914</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="7">
@@ -21942,7 +22201,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2369</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8">
@@ -21952,7 +22211,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000491</v>
+        <v>0.000166</v>
       </c>
     </row>
     <row r="9">
@@ -21962,7 +22221,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000673</v>
+        <v>0.000227</v>
       </c>
     </row>
     <row r="10">
@@ -21972,7 +22231,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001164</v>
+        <v>0.000393</v>
       </c>
     </row>
     <row r="11">
@@ -21982,7 +22241,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.035794</v>
+        <v>0.036187</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F585"/>
+  <dimension ref="A1:F594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -22105,6 +22105,340 @@
       <c r="F585" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports disaggregated prefill and decode</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/7/amazon-sagemaker-hyperpod-dpd/</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 21:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker HyperPod now supports Disaggregated Prefill and Decode (DPD), optimizing large language model inference by separating prefill and decode phases onto dedicated GPU pools.
+2. Outcome (impact):  
+DPD enhances per-token latency consistency, improves throughput under strict latency constraints, and allows independent scaling of prefill and decode capacities, reducing the need for over-provisioning.
+3. Where to use (use case):  
+Ideal for production LLMs in applications like chat assistants, agentic pipelines, retrieval-augmented generation, and long-document analysis requiring stable performance under mixed traffic.</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon SageMaker  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Amazon Cognito now supports self-service provisioned API rate limits</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/cognito-provisioned-limits</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Cognito now enables users to self-adjust API rate limits on demand, allowing for more responsive scaling to application traffic.
+2. Outcome (impact):
+   This new feature allows developers to quickly match API rate limits to their application's traffic patterns without waiting for manual review, enhancing application performance and user experience.
+3. Where to use (use case):
+   Ideal for applications with variable traffic loads, such as e-commerce platforms during sales events, or any application that experiences unpredictable spikes in user activity.</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Amazon Cognito</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio now integrates with Hugging Face for one-click model deployment and customization</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/sagemaker-studio-hugging-face-integration/</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 20:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Studio now integrates with Hugging Face, enabling one-click model deployment and customization directly from model discovery.
+2. Outcome (impact):
+   Simplifies the process of deploying and customizing models by eliminating multiple steps and manual configurations, allowing users to start working with models faster.
+3. Where to use (use case):
+   Ideal for data scientists and ML practitioners who need to quickly deploy and fine-tune models using a pre-configured environment.</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Amazon EVS VCF 9.0 and 9.1 support</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-evs-vcf9</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 17:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EVS now supports VMware Cloud Foundation (VCF) 9.0 and 9.1, enabling full control over installation, operations, and management.
+2. Outcome (Impact):
+Users can manage their VCF environments using familiar tools and processes, either independently or with AWS partners, enhancing flexibility and control.
+3. Where to Use (Use Case):
+Ideal for enterprises looking to extend their on-premises VMware environments to the cloud while maintaining consistent management practices.</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Amazon Elastic VMware Service (EVS)</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>AWS Certificate Manager now supports the ACME protocol for public certificates</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-certificate-manager-acme/</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Certificate Manager now supports ACME protocol for issuing and renewing public TLS certificates automatically.
+2. Outcome (impact):  
+This update simplifies the automation of certificate issuance and renewal, reducing manual management efforts and ensuring compliance with CA/Browser Forum standards.
+3. Where to use (use case):  
+Ideal for developers and PKI administrators who need to manage public TLS certificates for their applications and services in a centralized and automated manner.</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>AWS Certificate Manager (ACM)</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>CloudWatch Application Signals now automatically captures errors, performance anomalies, and deployment events</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/cloudwatch-service-events/</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CloudWatch Application Signals now automatically captures errors, performance anomalies, and deployment events, providing deeper insights without additional code changes.
+2. Outcome (impact):
+   Customers can quickly identify deployment-related issues and performance anomalies, improving application reliability and performance monitoring.
+3. Where to use (use case):
+   Ideal for developers and DevOps teams managing instrumented applications in AWS, especially those using Java, Python, or JavaScript.</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>AWS CodePipeline now available in Asia Pacific (New Zealand) region</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-codepipeline-new-zealand/</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CodePipeline is now available in the Asia Pacific (New Zealand) region, enabling continuous delivery for software releases with enhanced governance and security.
+2. Outcome (impact):
+This expansion allows teams in New Zealand to leverage AWS CodePipeline for automated, secure, and compliant CI/CD pipelines, improving release efficiency and security.
+3. Where to use (use case):
+Ideal for organizations in New Zealand needing to automate the release process of their software, ensuring compliance and security throughout the software delivery lifecycle.</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>CodePipeline</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager adds managed external secrets support for Paddle and GitLab</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/secrets-manager-managed-external-secrets-paddle-gitlab/</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Secrets Manager now supports automatic rotation for Paddle API keys and GitLab access tokens, enhancing security through seamless integration.
+2. Outcome (impact):
+   This update allows for more secure and automated management of third-party credentials, reducing the risk of credential exposure and simplifying secret rotation processes.
+3. Where to use (use case):
+   Ideal for organizations using Paddle and GitLab services, enabling them to securely manage and automatically rotate API keys and access tokens without manual intervention.</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>CloudWatch Application Signals now supports Dynamic Instrumentation</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/cloudwatch-dynamic-instrumentation/</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS CloudWatch Application Signals now supports Dynamic Instrumentation, allowing developers to capture runtime state from live applications without restarts or redeployments.
+2. Outcome (impact):  
+Developers can now inspect variable values, method arguments, return values, and stack traces at specific code locations, making it easier to debug production issues that are difficult to replicate locally.
+3. Where to use (use case):  
+Ideal for debugging complex production issues in Java, Python, and JavaScript/TypeScript applications without the need for redeploying or adding logging statements.</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -22170,7 +22504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03 06:37:20</t>
+          <t>2026-07-07 06:51:59</t>
         </is>
       </c>
     </row>
@@ -22181,7 +22515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -22191,7 +22525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2337</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="7">
@@ -22201,7 +22535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>798</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="8">
@@ -22211,7 +22545,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000166</v>
+        <v>0.000241</v>
       </c>
     </row>
     <row r="9">
@@ -22221,7 +22555,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000227</v>
+        <v>0.000326</v>
       </c>
     </row>
     <row r="10">
@@ -22231,7 +22565,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000393</v>
+        <v>0.000567</v>
       </c>
     </row>
     <row r="11">
@@ -22241,7 +22575,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.036187</v>
+        <v>0.036754</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F594"/>
+  <dimension ref="A1:F608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -22439,6 +22439,524 @@
       <c r="F594" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams introduces secure terminal access for stream sessions</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-gamelift-streams-terminal-access/</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 21:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GameLift Streams now offers secure terminal access to stream sessions for real-time troubleshooting, without managing SSH keys or open ports.
+2. Outcome (impact):
+Developers can more efficiently troubleshoot and monitor their game servers in real-time, improving application reliability and performance.
+3. Where to use (use case):
+Ideal for game developers needing to debug and monitor live game server sessions without exposing their infrastructure to potential security risks.</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Amazon GameLift</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors is now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/s3-vectors-available-aws-govcloud-regions/</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Vectors, a purpose-built vector storage solution for AI applications, is now available in AWS GovCloud (US) Regions.
+2. Outcome (impact):
+This launch enhances the capability to handle large-scale vector data for AI agents, inference, RAG, and semantic search within secure, compliance-focused environments.
+3. Where to use (use case):
+Ideal for government agencies and organizations requiring secure, scalable vector storage for AI applications, ensuring compliance with stringent data protection regulations.</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>AWS Security Hub extends unified security management to Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-security-hub-supports-monitoring-microsoft-azure/</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 18:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Hub now integrates with Microsoft Azure, providing unified security management across both cloud platforms.
+2. Outcome (impact):
+Security teams can now manage and respond to security risks across AWS and Azure from a single console, improving efficiency and consistency in security operations.
+3. Where to use (use case):
+Organizations running hybrid workloads in both AWS and Azure can benefit from consolidated security management, reducing the complexity of maintaining separate security tools for each cloud.</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Amazon ECS Managed Instances reduces GPU management fees by up to 60%</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ecs-managed-instances-gpu-price/</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS Managed Instances now offers up to 60% reduction in GPU management fees starting July 1, 2026, with no customer action required.
+2. Outcome (impact):
+Customers running GPU workloads on ECS Managed Instances will benefit from significantly lower management fees, enhancing cost efficiency for their accelerated computing needs.
+3. Where to use (use case):
+Ideal for users running GPU-intensive applications such as deep learning, scientific simulations, and high-performance computing workloads.</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless now supports larger worker sizes to run more compute and memory intensive workloads</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-emr-serverless/</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 17:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR Serverless now supports larger worker sizes of up to 32 vCPUs and 244 GB of memory, enhancing performance for compute and memory-intensive workloads.
+2. Outcome (impact):
+Larger worker configurations improve runtime performance, reduce data transfer inefficiencies, and lower the risk of out-of-memory failures for shuffle-heavy and data-skewed jobs.
+3. Where to use (use case):
+Ideal for compute and memory-intensive Spark and Hive workloads, particularly those involving data shuffling, data skew, or extensive data caching.</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Amazon EMR Serverless</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8ine instances are now available in AWS Europe (Frankfurt) region</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-c8ine-aws-frankfurt/</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C8ine instances, powered by custom Intel Xeon Scalable processors, are now available in the AWS Europe (Frankfurt) region, offering enhanced performance and network capabilities.
+2. Outcome (impact):
+Users in the Europe (Frankfurt) region can now leverage improved performance and network throughput for security and network virtual appliances, enhancing their workloads' efficiency and effectiveness.
+3. Where to use (use case):
+Ideal for security and network virtual appliances such as virtual firewalls, load balancers, and Telco 5G UPF workloads.</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker now supports data lineage in IAM-based domains</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-data-lineage-iam-domain</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker now supports OpenLineage compatible data lineage in IAM-based domains, enhancing data tracking across various services.
+2. Outcome (impact):
+Improved data governance and traceability for data transformations and workflows across multiple AWS services.
+3. Where to use (use case):
+Data-intensive applications requiring detailed tracking of data movement and transformations, such as data engineering pipelines and ETL processes.</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Amazon Redshift RG instances now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-redshift-rg-instances-aws-govcloud</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift RG instances, powered by AWS Graviton processors, are now available in AWS GovCloud (US) Regions, offering up to 2.4x faster performance at 30% lower price per vCPU.
+2. Outcome (impact):
+Customers can now run data warehouse and data lake workloads significantly faster and more cost-effectively in secure, compliance-focused environments.
+3. Where to use (use case):
+Ideal for government agencies and organizations requiring high-performance analytics in secure, compliant environments.</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now supports Oracle Database 26ai</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-oracle-database-26ai/</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for Oracle now supports Oracle Database 26ai, featuring AI capabilities and Amazon Bedrock integration.
+2. Outcome (impact):
+Enhances productivity with AI-driven SQL generation, retrieval augmented generation, and in-database graph analytics.
+3. Where to use (use case):
+Ideal for developers and business users needing advanced AI features within their relational database.</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Amazon S3 Express One Zone is now available in the AWS Europe (Frankfurt) Region</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/s3-express-one-zone-europe-frankfurt/</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Express One Zone is now available in the Europe (Frankfurt) Region, offering high-performance, single-AZ storage with ultra-low latency.
+2. Outcome (Impact):
+Enables faster data access speeds (up to 10x) and lower costs (up to 80%) for latency-sensitive applications like machine learning and interactive analytics.
+3. Where to Use (Use Case):
+Ideal for machine learning training, interactive analytics, and key-value caching in AI search engines.</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Amazon S3 Express One Zone</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Amazon EKS Auto Mode reduces GPU management fees by up to 60%</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-eks-auto-mode-gpu-price</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EKS Auto Mode now offers up to 60% reduction in management fees for GPU instances starting July 1, 2026.
+2. Outcome (impact):
+Customers will experience significant cost savings on GPU workloads, making EKS Auto Mode more cost-effective for machine learning, rendering, and batch processing.
+3. Where to use (use case):
+Ideal for machine learning inference, fine-tuning, rendering, and batch processing workloads that require GPU acceleration.</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports importing existing MWAA environments</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-unified-studio-import-existing-mwaa-environments/</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 02:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now integrates existing MWAA environments, allowing seamless management of Airflow workflows within the same interface.
+2. Outcome (impact):
+   Data engineers and platform teams can now manage their Airflow workflows without recreating configurations or migrating DAGs, enhancing efficiency and reducing operational overhead.
+3. Where to use (use case):
+   Ideal for data engineering teams and platform engineers who use both SageMaker for ML tasks and MWAA for orchestrating workflows, enabling unified management and monitoring.</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>AWS Security Hub adds impact analysis for exposure findings</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/impact-analysis-aws-security-hub/</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 21:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Security Hub now offers impact analysis for exposure findings, providing deeper insights into potential attack paths and resource risks.
+2. Outcome (impact):
+   Security teams can better understand and prioritize risks by visualizing the full scope of potential compromises stemming from exposed resources.
+3. Where to use (use case):
+   Ideal for organizations seeking to enhance their security posture by identifying and mitigating risks associated with exposed resources and privilege escalation paths.</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>AWS introduces declarative controls for VPC Encryption Controls</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/vpc-encryption-controls-declarative-controls/</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Mon, 06 Jul 2026 18:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS now allows centralized management of VPC Encryption Controls through declarative policies, enabling consistent encryption enforcement across all VPCs.
+2. Outcome (impact):
+   This feature simplifies the management of encryption controls, enhances compliance with standards like HIPAA and FedRAMP, and provides centralized visibility and control over encryption settings.
+3. Where to use (use case):
+   Ideal for organizations that need to enforce consistent encryption policies across multiple VPCs to meet regulatory requirements and improve security posture.</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>AWS Organizations</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -22504,7 +23022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07 06:51:59</t>
+          <t>2026-07-08 05:57:38</t>
         </is>
       </c>
     </row>
@@ -22515,7 +23033,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -22525,7 +23043,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3389</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="7">
@@ -22535,7 +23053,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1148</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="8">
@@ -22545,7 +23063,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000241</v>
+        <v>0.000348</v>
       </c>
     </row>
     <row r="9">
@@ -22555,7 +23073,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000326</v>
+        <v>0.000489</v>
       </c>
     </row>
     <row r="10">
@@ -22565,7 +23083,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000567</v>
+        <v>0.000837</v>
       </c>
     </row>
     <row r="11">
@@ -22575,7 +23093,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.036754</v>
+        <v>0.037591</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F608"/>
+  <dimension ref="A1:F616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -22957,6 +22957,302 @@
       <c r="F608" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>AWS Builder Center Now Offers Free Sandbox Environments</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-builder-center-sandbox/</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 22:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Builder Center now offers free, time-limited sandbox environments for hands-on learning, eliminating the need for personal AWS accounts or credit cards.
+2. Outcome (impact):  
+Enables builders of all skill levels to gain practical AWS experience safely and without financial risk, enhancing accessibility and learning opportunities.
+3. Where to use (use case):  
+Ideal for learning and experimenting with AWS services, especially for beginners or those without an existing AWS account.</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>AWS Builder Center</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>AWS Security Hub now offers Network Scanning to identify publicly reachable resources</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-security-hub-network-scanning/</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Hub now offers Network Scanning to identify and confirm publicly reachable resources from the internet, providing actionable insights beyond configuration checks.
+2. Outcome (impact):
+Enhances visibility into actual internet exposure, helping to mitigate risks associated with publicly accessible resources by identifying and detailing actual reachability and running services.
+3. Where to use (use case):
+Ideal for organizations needing to secure their cloud environments by identifying and managing resources that are inadvertently exposed to the public internet, ensuring compliance and reducing potential attack surfaces.</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Amazon Redshift RG instances now available on the trailing track</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-redshift-graviton-rg-instances-trailing-track</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 18:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now offers Graviton-based RG instances on the trailing track, providing enhanced performance and cost savings for production workloads.
+2. Outcome (impact):
+Customers can achieve up to 2.4x faster query performance with RG instances at 30% lower price per vCPU, improving efficiency and reducing costs.
+3. Where to use (use case):
+Ideal for production workloads that require stability and validated performance, such as data warehousing and analytics.</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL change data capture (CDC) Is now generally available</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-aurora-dsql-cdc-ga/</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora DSQL CDC is now available, enabling real-time streaming of database changes to Kinesis Data Streams.
+2. Outcome (impact):
+Facilitates event-driven architectures and data integration workflows with zero performance impact on database workloads.
+3. Where to use (use case):
+Synchronize data across microservices, trigger Lambda functions, or deliver changes to S3, Redshift, and OpenSearch.</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports forecasting, planning, and scheduling for Tasks and Emails</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-connect-customer-agent-scheduling-tasks/</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now supports forecasting, planning, and scheduling for Tasks and Emails, optimizing workforce allocation across all interaction channels.
+2. Outcome (impact):
+   This enhancement allows organizations to create unified forecasts and schedules, ensuring efficient workforce management and consistent service levels across voice, chat, tasks, and emails.
+3. Where to use (use case):
+   Ideal for contact centers managing multiple customer interaction channels, enabling better resource allocation and improved service consistency.</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7i instances now available in AWS Europe (Zurich) region</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-u7i-aws-europe-zurich/</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 23:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 introduces High Memory U7i instances with 12TB of memory in the Europe (Zurich) region, powered by Intel Xeon Scalable Processors.
+2. Outcome (impact):
+Enables customers to scale transaction processing throughput in large data environments with enhanced memory and performance capabilities.
+3. Where to use (use case):
+Ideal for mission-critical in-memory databases like SAP HANA, Oracle, and SQL Server.</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>AWS Systems Manager simplifies Azure VM management and hybrid node pricing</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/aws-systems-manager-multicloud-vm/</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Systems Manager now allows seamless management of Azure VMs without manual agent installation and eliminates per-instance fees.
+2. Outcome (impact):
+Organizations can efficiently manage hybrid and multicloud environments, reducing costs and simplifying operations.
+3. Where to use (use case):
+Ideal for enterprises managing workloads across AWS and Azure, ensuring unified management and cost efficiency.</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>AWS Systems Manager</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>AWS CodeBuild now supports Amazon Linux 2023 for on-demand build hosts</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-codebuild-amazon-linux-2023/</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Fri, 03 Jul 2026 12:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CodeBuild now supports Amazon Linux 2023 for on-demand build hosts, offering an updated kernel and improved packages.
+2. Outcome (impact):
+   Developers can now leverage the latest features and security updates in Amazon Linux 2023 for their builds, enhancing performance and security.
+3. Where to use (use case):
+   Ideal for CI/CD pipelines requiring the latest Linux kernel and package updates to ensure optimal build environments.</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>AWS CodeBuild</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -23022,7 +23318,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08 05:57:38</t>
+          <t>2026-07-09 06:50:42</t>
         </is>
       </c>
     </row>
@@ -23033,7 +23329,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -23043,7 +23339,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4896</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="7">
@@ -23053,7 +23349,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1722</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -23063,7 +23359,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000348</v>
+        <v>0.000167</v>
       </c>
     </row>
     <row r="9">
@@ -23073,7 +23369,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000489</v>
+        <v>0.000264</v>
       </c>
     </row>
     <row r="10">
@@ -23083,7 +23379,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000837</v>
+        <v>0.00043</v>
       </c>
     </row>
     <row r="11">
@@ -23093,7 +23389,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.037591</v>
+        <v>0.038021</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F616"/>
+  <dimension ref="A1:F626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -23253,6 +23253,388 @@
       <c r="F616" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>OAuth support for the AWS MCP Server</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/oauth-aws-mcp-server/</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 23:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS MCP Server now supports OAuth for AI agent connections, enabling secure, industry-standard authentication without additional software.
+2. Outcome (impact):
+   Enhances security and simplifies the connection process for AI agents, leveraging existing AWS IAM policies and governance controls.
+3. Where to use (use case):
+   Ideal for developers integrating AI agents with AWS services, ensuring secure and streamlined authentication.</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>AWS Management and Governance</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB now publishes database state change events to Amazon EventBridge</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/timestream-influxdb-eventbridge/</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 17:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Timestream for InfluxDB now sends state change events to Amazon EventBridge, enabling automated responses to database operations.
+2. Outcome (impact):
+This feature allows for automated workflows, immediate alerts on failures, and audit trails without the need for constant API polling.
+3. Where to use (use case):
+DevOps teams can automate scaling operations, operations teams can quickly respond to failures, and compliance teams can maintain audit logs.</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>AWS Client VPN extends availability to four additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-client-vpn-four-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 17:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Client VPN is now available in four new regions: Calgary, Mexico Central, New Zealand, and Taipei, providing secure remote access to AWS and on-premises networks.
+2. Outcome (impact):
+This expansion enhances global accessibility, enabling organizations to securely connect remote users to AWS resources and on-premises networks without the need for hardware VPN appliances.
+3. Where to use (use case):
+Ideal for remote workforces needing secure access to AWS resources and on-premises networks, such as employees working from home, branch offices, or mobile teams.</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>AWS Client VPN</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio adds custom asset types to the catalog in IAM-based domains</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/smus-custom-asset-types-iam/</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 16:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now supports custom asset types in IAM-based domains, enabling cataloging of various asset formats for better discovery and management.
+2. Outcome (impact):
+   This update allows domain administrators to catalog diverse assets, improving asset discoverability and management within the studio, and enhancing collaboration across teams.
+3. Where to use (use case):
+   Ideal for data scientists, analysts, and researchers who need to manage and share a variety of asset types, such as medical imaging files, dashboards, and research reports, within a unified platform.</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports deep health checks for Slurm clusters with continuous provisioning</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/deep-health-check-continuous-slurm/</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker HyperPod now offers deep health checks for Slurm clusters with continuous provisioning, ensuring GPU health and preventing delays due to unhealthy nodes.
+2. Outcome (impact):
+   This feature helps prevent compute time waste and delays by proactively verifying GPU health, ensuring only healthy nodes are used for training jobs.
+3. Where to use (use case):
+   Ideal for high-performance computing (HPC) and machine learning (ML) workloads that require reliable GPU performance and quick scaling.</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Feature Store now supports batch feature writes and record listing</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amzn-sgm-feature-store-batch-write-list/</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 15:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Feature Store now supports batch feature writes and record listing, enhancing feature ingestion and management for AI models.
+2. Outcome (impact):
+Data scientists can now ingest features more efficiently, manage records better, and reduce the need for custom tooling, leading to faster model training and deployment.
+3. Where to use (use case):
+Ideal for data scientists working on machine learning projects requiring high-throughput feature ingestion and streamlined feature management.</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Feature Store</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Amazon MSK Replicator now supports replication from external Apache Kafka clusters to MSK Standard brokers</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-msk-replicator-external-kafka-standard-broker-support</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MSK Replicator now supports replicating data from external Kafka clusters to MSK Standard brokers, enhancing hybrid and multi-cloud data distribution.
+2. Outcome (impact):
+   This update enables seamless migration to MSK Standard brokers, supports disaster recovery, and facilitates data distribution across hybrid and multi-cloud environments.
+3. Where to use (use case):
+   Use this feature for migrating workloads to MSK Standard brokers, setting up disaster recovery, and enabling data distribution in hybrid and multi-cloud setups.</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Amazon MSK</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>AWS Config now supports 191 additional managed rules</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-config-additional-managed-rules</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Config now supports 191 additional managed rules to enhance governance across various services, including AI/ML, compute, and storage.
+2. Outcome (impact):
+This expansion improves compliance and operational best practices, ensuring better security, data protection, and resource management across AWS services.
+3. Where to use (use case):
+Deploy these rules to monitor and enforce best practices in resource configurations for encryption, logging, public access, and network security across your AWS environment.
+AWS Service: Amazon S3 | Category: Storage  
+AWS Service: Amazon RDS | Category: Database  
+AWS Service: Amazon EKS | Category: Compute  
+AWS Service: Amazon CloudTrail | Category: Security  
+AWS Service: Amazon SageMaker | Category: AI/ML  
+AWS Service: Amazon ECS | Category: Compute  
+AWS Service: Amazon Redshift | Category: Analytics  
+AWS Service: AWS Certificate Manager | Category: Security  
+AWS Service: Amazon API Gateway | Category: Networking  
+AWS Service: AWS AppSync | Category: Developer Tools  
+AWS Service: Amazon Athena | Category: Analytics  
+AWS Service: AWS CloudFormation | Category: Management</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio Workflows now supports operators for Amazon Bedrock, S3 Tables, S3 Vectors, and Glue Catalog</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/apache-airflow-operators-amazon-sagemaker-unified-studio-workflows/</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio Workflows now supports 19 new operators for Amazon Bedrock, S3 Tables, S3 Vectors, Glue Catalog, and MWAA Serverless, enabling visual orchestration without custom code.
+2. Outcome (impact):
+This update allows data workers and builders to manage AWS services more efficiently, reducing the need for multiple console switches and custom integration code, thus enhancing productivity and workflow management.
+3. Where to use (use case):
+Ideal for data scientists and ML engineers who need to integrate and manage multiple AWS services within a unified workflow, such as managing Bedrock guardrails, S3 resources, Glue Catalog tables, and MWAA Serverless workflows.</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>AWS Neuron 2.31.0 now available with NKI 0.5.0 and UltraServer Operator</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-announce-neuron-2-31-0</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 15:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Neuron 2.31.0 introduces NKI 0.5.0 enhancements and the Neuron UltraServer Operator for EKS, improving performance and simplifying device configuration.
+2. Outcome (impact):
+Enhanced performance and efficiency in training large-scale machine learning models, particularly beneficial for MoE training and attention mechanisms.
+3. Where to use (use case):
+Ideal for large-scale machine learning training workloads, especially those requiring efficient memory usage and performance optimization.</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>AWS Neuron</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23700,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09 06:50:42</t>
+          <t>2026-07-10 06:51:12</t>
         </is>
       </c>
     </row>
@@ -23329,7 +23711,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -23339,7 +23721,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2351</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="7">
@@ -23349,7 +23731,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>928</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="8">
@@ -23359,7 +23741,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000167</v>
+        <v>0.000268</v>
       </c>
     </row>
     <row r="9">
@@ -23369,7 +23751,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000264</v>
+        <v>0.000409</v>
       </c>
     </row>
     <row r="10">
@@ -23379,7 +23761,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00043</v>
+        <v>0.000677</v>
       </c>
     </row>
     <row r="11">
@@ -23389,7 +23771,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.038021</v>
+        <v>0.038698</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F626"/>
+  <dimension ref="A1:F638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -23635,6 +23635,450 @@
       <c r="F626" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Amazon EC2 network/EBS instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-r8in-r8ib-r8idn-r8idb</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 introduces new R8in, R8ib, R8idn, and R8idb instances in Tokyo and Frankfurt, featuring enhanced networking and EBS bandwidth.
+2. Outcome (impact):
+   These instances offer up to 43% better compute performance per vCPU and higher network/EBS bandwidth, improving efficiency for compute- and storage-intensive workloads.
+3. Where to use (use case):
+   Ideal for real-time analytics, AI/ML, high-performance databases, and network-intensive applications requiring high bandwidth and low-latency storage.</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Amazon EMR on EKS now supports Apache Spark troubleshooting agent</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-emr-eks-spark-troubleshooting/</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 18:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EMR on EKS now supports an Apache Spark troubleshooting agent that provides automated root cause analysis and PySpark code recommendations.
+2. Outcome (impact):  
+Data engineers can diagnose EMR on EKS job failures more efficiently, reducing manual effort and speeding up troubleshooting.
+3. Where to use (use case):  
+Ideal for diagnosing and resolving issues in Spark jobs running on Amazon EMR on EKS, improving job reliability and performance.</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Amazon EMR</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Amazon Location Service enhances Places APIs with new address and search options</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-location-service-enhanced-address-search</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 17:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Location Service has introduced new enhancements to its Places APIs, offering better address formatting, multilingual support, travel-optimized search, and drive-through data.
+2. Outcome (impact):
+These updates empower developers to create more accurate, relevant, and user-friendly location-based applications, improving user experience in navigation, logistics, and multilingual services.
+3. Where to use (use case):
+Ideal for navigation apps, logistics services, food delivery platforms, and any application requiring precise, multilingual, and context-aware location data.</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Amazon Location Service</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports AMI-based node lifecycle configuration for Slurm clusters using continuous provisioning</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2025/06/ami-configuration-continuous-slurm/</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker HyperPod now supports AMI-based configuration for Slurm clusters using continuous provisioning, eliminating the need for lifecycle scripts.
+2. Outcome (impact):  
+This update accelerates the availability of nodes in AI/ML training workloads by configuring nodes directly from the AMI, reducing setup time and complexity.
+3. Where to use (use case):  
+Ideal for AI/ML training environments requiring rapid scaling and configuration of compute resources without manual intervention.</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Amazon EC2 G7 instances are now available in the AWS US East (N. Virginia) Region</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-g7-available-North-Virginia</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 15:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 G7 instances, powered by RTX PRO 4500 GPUs, are now available in US East (N. Virginia) with enhanced AI and graphics performance.
+2. Outcome (impact):
+G7 instances offer up to 4.6x AI inference and 2.1x graphics performance compared to G6 instances, boosting productivity for AI, graphics, and data analytics workloads.
+3. Where to use (use case):
+Ideal for AI model deployment, video/image analysis, speech recognition, real-time graphics rendering, game streaming, video transcoding, and data analytics.</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>AWS DMS Schema Conversion now supports offline SQL Server conversion</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-dms-schema-conversion-offline-source/</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 15:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS DMS Schema Conversion now supports offline conversion for SQL Server, allowing schema and code conversion without direct database access.
+2. Outcome (impact):
+   This feature accelerates migration projects by bypassing security reviews, firewall changes, and VPN setup, while maintaining the same conversion quality.
+3. Where to use (use case):
+   Ideal for organizations with strict security policies that prevent direct access to production SQL Server databases, enabling secure and efficient schema conversion.</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>AWS Database Migration Service (DMS)</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I7ie instances now available in AWS Asia Pacific (Hyderabad) region</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-i7ie-instances-aws-hyd-region/</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 14:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched I7ie instances in the Asia Pacific (Hyderabad) region, offering enhanced compute and storage performance for I/O intensive workloads.
+2. Outcome (impact):
+Customers can now leverage high-performance compute and storage solutions in the Hyderabad region, improving efficiency and reducing latency for data-intensive applications.
+3. Where to use (use case):
+Ideal for large-scale data processing, analytics, high-performance computing, and other storage I/O intensive applications.</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB (with MongoDB compatibility) now supports R8g.24xlarge and R8g.48xlarge instances</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-documentdb-r8g-24xl-48xl/</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DocumentDB now supports R8g.24xlarge and R8g.48xlarge instances, powered by AWS Graviton4 processors for higher throughput and larger memory capacity.
+2. Outcome (impact):
+   Customers can now run more demanding workloads with improved performance and efficiency, supporting high-concurrency applications and large-scale document processing.
+3. Where to use (use case):
+   Ideal for high-concurrency transactional applications, large-scale document processing, and memory-intensive operational workloads.</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>AWS DMS Schema Conversion now supports AI agent automation</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-dms-sc-ai-agent-automation-mcp-server/</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   AWS DMS Schema Conversion now integrates AI agents like Kiro, Claude Code, and Cursor to automate migration workflows using natural language.
+2. Outcome (impact)
+   This integration reduces manual effort and errors in schema conversion, accelerates migration processes, and enhances productivity by leveraging AI for complex tasks.
+3. Where to use (use case)
+   Ideal for database administrators and migration teams looking to streamline and automate the conversion of database schemas during migrations to AWS.</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>AWS Database Migration Service (DMS)</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>AWS Organizations now applies account departure security controls by default for new organizations created via AWS Organizations console</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-organizations-security-controls-new-orgs-console</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Organizations now automatically applies security controls by default for new organizations, preventing member accounts from leaving or closing themselves.
+2. Outcome (impact):
+   This simplifies initial security configuration for new organizations, ensuring immediate protection against unintended account departures without requiring deep security expertise.
+3. Where to use (use case):
+   Ideal for enterprises migrating to AWS or starting new organizations, ensuring strong governance patterns from the outset.</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>AWS Organizations</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I8g instances now available in AWS GovCloud (US) regions</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-i8g-instances-aws-govcloud-us-regions/</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 18:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched I8g instances in AWS GovCloud (US) regions, offering enhanced storage performance for I/O intensive workloads.
+2. Outcome (impact):
+I8g instances provide up to 60% better compute performance and up to 65% better storage performance compared to previous generations, significantly improving efficiency for storage-intensive applications.
+3. Where to use (use case):
+Ideal for transactional databases, real-time analytics, data lakehouse, and AI LLM pre-processing tasks requiring rapid data access and low latency.</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Amazon EC2 now supports using an EBS volume for Replace Root Volume</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-replace-root-volume-ebs-volume/</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 18:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS now allows EC2 instances to replace their root volume using an existing EBS volume, streamlining patching for stateful workloads.
+2. Outcome (impact):
+   This new feature reduces operational overhead and speeds up the process of applying OS patches and configuration changes without stopping the instance.
+3. Where to use (use case):
+   Ideal for stateful workloads where specific metadata or software must be present on the root volume before the application boots, such as databases or custom-configured servers.</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -23700,7 +24144,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10 06:51:12</t>
+          <t>2026-07-11 05:45:54</t>
         </is>
       </c>
     </row>
@@ -23711,7 +24155,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -23721,7 +24165,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3776</v>
+        <v>4801</v>
       </c>
     </row>
     <row r="7">
@@ -23731,7 +24175,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1441</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="8">
@@ -23741,7 +24185,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000268</v>
+        <v>0.000341</v>
       </c>
     </row>
     <row r="9">
@@ -23751,7 +24195,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000409</v>
+        <v>0.000435</v>
       </c>
     </row>
     <row r="10">
@@ -23761,7 +24205,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000677</v>
+        <v>0.000775</v>
       </c>
     </row>
     <row r="11">
@@ -23771,7 +24215,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.038698</v>
+        <v>0.039473</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F638"/>
+  <dimension ref="A1:F649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -24079,6 +24079,414 @@
       <c r="F638" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-5.6 Sol, Terra, and Luna now generally available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/openai-gpt-sol-terra/</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 22:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+OpenAI's GPT-5.6 models (Sol, Terra, Luna) are now available on Amazon Bedrock, offering enhanced intelligence, efficiency, and cost-effectiveness.
+2. Outcome (impact):  
+Users can leverage advanced AI capabilities for tasks like autonomous coding, genomics analysis, and cybersecurity research with improved performance and reduced costs.
+3. Where to use (use case):  
+Ideal for developers and researchers needing high-performance AI for coding automation, biological research, and cybersecurity tasks.</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon Bedrock  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus is now available in Asia Pacific (New Zealand) Region</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-managed-service-prometheus-new-zealand/</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 21:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Managed Service for Prometheus is now available in the Asia Pacific (New Zealand) Region, offering a fully managed, Prometheus-compatible monitoring service.
+2. Outcome (Impact):
+This availability enhances global coverage, allowing customers in New Zealand to monitor and alert on operational metrics at scale with a fully managed service.
+3. Where to Use (Use Case):
+Ideal for organizations in New Zealand needing to monitor and manage their Prometheus metrics with a scalable, fully managed service.</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB (with MongoDB compatibility) now available as a skill in the Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-documentdb-agent-skill</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon DocumentDB (with MongoDB compatibility) is now a skill in the AWS Agent Toolkit, enabling AI coding agents to manage DocumentDB clusters efficiently.
+2. Outcome (impact)
+This skill reduces manual errors and accelerates development by automating best-practice workflows for provisioning, migration, optimization, and troubleshooting of DocumentDB clusters.
+3. Where to use (use case)
+Ideal for developers and DevOps teams managing MongoDB-compatible databases, facilitating easier cluster management, migration, and optimization.</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB (with MongoDB compatibility) adds support for 46 new MongoDB operators in version 8.0.1</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-documentdb-mongodb-8-0-1-mongo-api</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon DocumentDB now supports 46 new MongoDB operators in version 8.0.1, enhancing query API compatibility and easing migration from MongoDB.
+2. Outcome (impact):
+This update significantly reduces the need for application code changes when migrating MongoDB workloads to Amazon DocumentDB, improving developer efficiency and application performance.
+3. Where to use (use case):
+Ideal for migrating MongoDB databases to Amazon DocumentDB with minimal application changes, suitable for businesses needing robust, scalable database solutions.</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Gemma-4-E2B-it for is now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/gemma-4-e2b-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced the Gemma-4-E2B-it model in SageMaker JumpStart, a multimodal AI model optimized for efficient local execution, supporting text, image, and audio processing.
+2. Outcome (impact):
+This addition enhances AWS's AI capabilities, enabling customers to develop advanced AI applications with improved efficiency and multimodal functionality.
+3. Where to use (use case):
+Ideal for applications requiring complex AI tasks such as image understanding, document parsing, video comprehension, multilingual support, and code generation.</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>OpenAI privacy-filter for PII detection and masking is now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/privacy-filter-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces a privacy-filter model from OpenAI in SageMaker JumpStart for detecting and masking PII in text.
+2. Outcome (impact):  
+Enables fast, context-aware, and tunable data sanitization workflows to protect sensitive information in text data.
+3. Where to use (use case):  
+Ideal for data sanitization workflows in applications handling personal information, such as customer support, healthcare, and finance.</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Voxtral-Mini-4B-Realtime for real-time speech transcription is now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/voxtral-mini-realtime-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced Voxtral-Mini-4B-Realtime, a multilingual real-time speech-to-text model in SageMaker JumpStart, supporting 13 languages with configurable latency.
+2. Outcome (impact):
+This new model enables developers to create low-latency, multilingual speech applications efficiently, enhancing user experience in various real-time communication scenarios.
+3. Where to use (use case):
+Ideal for applications requiring real-time transcription services such as live subtitles, multilingual customer support, and real-time language translation in communication platforms.</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Qwen3 embedding and reranking models for retrieval are now available in Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/qwen3-search-retrieval-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced Qwen3-VL-Embedding-2B and Qwen3-Reranker-4B models in Amazon SageMaker JumpStart for enhanced information retrieval and cross-modal understanding.
+2. Outcome (Impact):
+These models enable efficient initial recall and precise re-ranking of search results, improving the accuracy and relevance of search pipelines across multiple languages and modalities.
+3. Where to Use (Use Case):
+Ideal for building comprehensive search and retrieval systems that handle text, images, videos, and mixed-modality inputs, such as e-commerce search engines, multimedia content platforms, and multilingual information retrieval systems.</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports custom AMIs (Amazon Machine Images) for Slurm clusters</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/hyperpod-custom-ami-slurm/</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 14:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker HyperPod now allows users to deploy Slurm clusters with custom AMIs for enhanced security and compliance, while maintaining fast startup times.
+2. Outcome (impact):
+This feature enables organizations to deploy AI/ML workloads in a more secure, compliant, and reliable environment, accelerating time-to-training and reducing deployment complexities.
+3. Where to use (use case):
+Ideal for organizations requiring strict security and compliance measures for their AI/ML workloads, such as financial institutions, healthcare providers, and government agencies.</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Amazon EKS Auto Mode now supports Application Recovery Controller zonal shift</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/eks-auto-mode-arc-zonal-shift</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EKS Auto Mode now supports Amazon ARC zonal shift for automatic application recovery during AZ impairments.
+2. Outcome (impact):  
+EKS Auto Mode enhances application availability by automatically managing compute during zonal shifts without additional cost or configuration.
+3. Where to use (use case):  
+Ideal for running highly available applications in Amazon EKS, ensuring resilience against AZ failures.</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Amazon EKS Auto Mode</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>AWS Partner Central subsidiary connections now support qualification sharing</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/subsidiary-qualification-sharing/</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Central now allows partners to share qualifications across connected accounts, enhancing partnership management and visibility.
+2. Outcome (impact):
+Partners can now consolidate their AWS partnership standing, including specializations, certifications, and program enrollments, across connected accounts, leading to a unified public profile and scorecard.
+3. Where to use (use case):
+This feature is ideal for partners managing multiple subsidiary accounts, enabling them to maintain consistent qualifications and enhance their public profile.</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>AWS Partner Network (APN)</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -24144,7 +24552,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11 05:45:54</t>
+          <t>2026-07-14 05:37:10</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24563,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -24165,7 +24573,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4801</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="7">
@@ -24175,7 +24583,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1530</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="8">
@@ -24185,7 +24593,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000341</v>
+        <v>0.00029</v>
       </c>
     </row>
     <row r="9">
@@ -24195,7 +24603,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000435</v>
+        <v>0.000398</v>
       </c>
     </row>
     <row r="10">
@@ -24205,7 +24613,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000775</v>
+        <v>0.000688</v>
       </c>
     </row>
     <row r="11">
@@ -24215,7 +24623,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.039473</v>
+        <v>0.040161</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F649"/>
+  <dimension ref="A1:F664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -24487,6 +24487,563 @@
       <c r="F649" t="inlineStr">
         <is>
           <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery now supports Amazon EBS volume initialization rate</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-drs-fast-hydration/</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 22:00:56 GMT</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elastic Disaster Recovery now supports Amazon EBS volume initialization rate to enhance recovery performance.
+2. Outcome (impact):
+Faster and more predictable recovery times for EBS volumes, especially for I/O-intensive workloads.
+3. Where to use (use case):
+Ideal for databases and other I/O-intensive applications requiring fast and consistent storage performance.</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>AWS Lambda console provides a one-click setup prompt for coding agents</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-lambda-prompt-coding-agents/</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Lambda console introduces a one-click setup for coding agents to configure serverless skills and MCP server, streamlining the development process.
+2. Outcome (impact):  
+   Developers can now easily set up coding agents with necessary AWS Serverless skills and MCP server, reducing setup friction and embedding best practices from the start.
+3. Where to use (use case):  
+   Ideal for developers starting with AWS Lambda, exploring its capabilities, or deploying their first Lambda function, ensuring a smooth onboarding experience.</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center achieves FedRAMP Class C Certification</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-identity-center-fedramp/</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 19:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IAM Identity Center has achieved FedRAMP Class C Certification, enabling secure workforce access to AWS accounts and applications in specified US regions.
+2. Outcome (Impact):
+This certification allows organizations subject to FedRAMP Class C compliance to securely manage and grant access to their AWS resources using IAM Identity Center.
+3. Where to Use (Use Case):
+Use IAM Identity Center to manage workforce access for federal agencies and contractors that require FedRAMP Class C compliance in the specified US regions.</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Introducing Amazon GuardDuty AI Protection for AWS AI workloads</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-guardduty-ai-protection-aws/</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GuardDuty now provides AI Protection to monitor and secure AWS AI services like Amazon Bedrock and SageMaker against specific threats.
+2. Outcome (impact):
+   Enhances security for AI workloads by detecting and mitigating threats such as anomalous model invocations, cost harvesting attacks, and prompt injection attempts.
+3. Where to use (use case):
+   Ideal for organizations utilizing AWS AI services to ensure robust security monitoring and threat detection for AI-specific vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Apache Flink now offers AI Agent Skills to simplify building and operating Flink applications</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-managed-service-flink-agent-skills/</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 18:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+Amazon Managed Service for Apache Flink now includes AI Agent Skills to simplify building and operating Flink applications, offering expert guidance for various tasks.
+2. Outcome (impact)
+This update enables developers to build, troubleshoot, scale, and optimize Flink applications more efficiently, reducing the need for specialized Flink knowledge and accelerating application development.
+3. Where to use (use case)
+Ideal for data engineers and developers working on real-time data processing applications who want to leverage AI-driven guidance to maintain and enhance their Flink applications.</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Apache Flink</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>AWS Security Hub now provides AI inventory for organization-wide visibility of AI assets</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-security-hub-ai/</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Hub now offers an AI inventory feature, providing central security teams with continuous visibility into AI assets and their security posture across the organization.
+2. Outcome (impact):
+This feature enhances security teams' ability to identify, monitor, and secure AI assets, reducing the risk of threats and misconfigurations in AI deployments.
+3. Where to use (use case):
+Ideal for organizations deploying multiple AI agents, models, and pipelines across various AWS services, ensuring comprehensive visibility and security management.</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Personal simplifies bulk PCoIP to DCV protocol migration</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-workspaces-personal-pcoip/</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon WorkSpaces Personal now simplifies large-scale migrations from PCoIP to DCV protocol with automated rollback and support for stopped WorkSpaces.
+2. Outcome (impact):  
+Administrators can perform bulk migrations with minimal manual intervention, ensuring faster and more reliable migrations. Enhanced security and performance are also achieved.
+3. Where to use (use case):  
+Ideal for organizations looking to upgrade their WorkSpaces to the DCV protocol to benefit from improved OS support, security features, and performance.</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL is now available in Europe (Spain)</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-aurora-dsql-available-in-spain/</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora DSQL is now available in Europe (Spain), offering a fast, serverless, distributed SQL database with active-active high availability and multi-Region strong consistency.
+2. Outcome (impact):
+This launch enables developers to build highly available and scalable applications with zero infrastructure management, enhancing application resilience and performance across Europe.
+3. Where to use (use case):
+Ideal for applications requiring high availability, strong consistency, and easy scalability, such as e-commerce platforms, financial services, and real-time analytics systems.</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>AWS Storage Gateway adds console support for copying file shares across gateways</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-storage-gateway-console-copy-file-shares/</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Storage Gateway now supports copying file shares across gateways directly from the console, preserving configurations and reducing migration effort.
+2. Outcome (impact):
+This feature significantly reduces the time and effort required for migrating file shares, especially during upgrades like moving to AL2023, by automating the configuration process.
+3. Where to use (use case):
+Ideal for simplifying migrations and upgrades of file shares in environments requiring frequent data movement between different Storage Gateways.</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Storage Gateway</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront Functions now supports logging to CloudFront access logs</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/cloudfront-functions-access-logs/</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   CloudFront Functions now allow logging custom data directly into CloudFront access logs, enhancing observability and simplifying log analysis.
+2. Outcome (impact):
+   This update enables developers to correlate CloudFront Function decisions with access logs in a unified log stream, improving debugging and monitoring capabilities.
+3. Where to use (use case):
+   Ideal for scenarios requiring detailed logging of custom data such as A/B test variants, authentication results, or routing decisions directly within CloudFront access logs.</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Amazon Redshift Serverless now preserves zero-ETL and Amazon S3 event integrations during snapshot restores</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/redshift-serverless-zetl-autocopy-restore/</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Redshift Serverless now automatically preserves zero-ETL and Amazon S3 event integrations during snapshot restores within the same namespace, reducing manual configuration and errors.
+2. Outcome (impact):
+   This enhancement simplifies data ingestion workflows, reduces administrative overhead, and streamlines disaster recovery and testing processes by maintaining integrations post-restore.
+3. Where to use (use case):
+   Ideal for organizations that rely on automated data pipelines and need to minimize downtime and manual intervention during namespace restores in Redshift Serverless.</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Amazon Redshift Serverless</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8id, M8id, and R8id instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-c8id-m8id-r8id/</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 19:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8id, M8id, and R8id instances are now available in new regions, offering enhanced performance and memory bandwidth.
+2. Outcome (impact):
+   These instances provide up to 43% higher performance and 3.3x more memory bandwidth, making them ideal for a variety of compute-intensive, balanced, and memory-intensive workloads.
+3. Where to use (use case):
+   - C8id: High-performance web servers, batch processing, distributed analytics, ad serving, video encoding, gaming servers.
+   - M8id: Application servers, microservices, enterprise applications, small to medium databases.
+   - R8id: In-memory databases, real-time big data analytics, large in-memory caches, scientific computing applications.</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8gd and R8gd instances are now available in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-m8gd-r8gd-us-govcloud/</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 19:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched M8gd and R8gd instances in AWS GovCloud (US) with high-speed local storage and improved performance.
+2. Outcome (impact):
+   These instances offer up to 11.4 TB of local NVMe-based SSD storage, 30% better performance with AWS Graviton4 processors, and enhanced bandwidth flexibility.
+3. Where to use (use case):
+   Ideal for applications requiring high-speed, low-latency local storage, such as data analytics, high-performance computing, and large-scale databases.</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>AWS Partner Central introduces Partner Lead Prospecting</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-partner-central-prospecting/</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Thu, 09 Jul 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Partner Central introduces Partner Lead Prospecting, an AI-powered tool for APN Customer Engagements (ACE)-eligible partners to quickly convert leads using personalized outreach.
+2. Outcome (impact):  
+Enhances efficiency and effectiveness of lead conversion by providing tailored sales plays, call scripts, and email outreach, reducing manual research and drafting efforts.
+3. Where to use (use case):  
+Ideal for ACE-eligible AWS Partners looking to streamline their lead management process and improve engagement with prospective customers.</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8gd and R8gd instances are now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-m8gd-r8gd-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Wed, 08 Jul 2026 19:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has expanded the availability of M8gd and R8gd instances to new regions, offering high-performance local storage and improved networking capabilities.
+2. Outcome (impact):
+   Users can now deploy high-performance, storage-intensive applications in additional regions with enhanced bandwidth and storage options.
+3. Where to use (use case):
+   Ideal for data analytics, high-performance computing (HPC), and other storage-intensive workloads requiring low latency and high throughput.</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -24552,7 +25109,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14 05:37:10</t>
+          <t>2026-07-15 05:38:15</t>
         </is>
       </c>
     </row>
@@ -24563,7 +25120,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -24573,7 +25130,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4086</v>
+        <v>5509</v>
       </c>
     </row>
     <row r="7">
@@ -24583,7 +25140,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1402</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="8">
@@ -24593,7 +25150,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00029</v>
+        <v>0.000391</v>
       </c>
     </row>
     <row r="9">
@@ -24603,7 +25160,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000398</v>
+        <v>0.000556</v>
       </c>
     </row>
     <row r="10">
@@ -24613,7 +25170,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000688</v>
+        <v>0.000947</v>
       </c>
     </row>
     <row r="11">
@@ -24623,7 +25180,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.040161</v>
+        <v>0.041108</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F664"/>
+  <dimension ref="A1:F679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -25042,6 +25042,562 @@
         </is>
       </c>
       <c r="F664" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs announces intelligent tiering for storage</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-cloudwatch-intelligent-tiering/</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch Logs introduces intelligent storage tiering to automatically classify and store log data across three tiers, reducing costs while maintaining query capabilities.
+2. Outcome (impact):
+   This feature allows customers to store high-volume logs for extended periods at lower costs without operational overhead, improving cost efficiency and operational simplicity.
+3. Where to use (use case):
+   Ideal for organizations needing to retain verbose logs for compliance, auditing, or long-term analysis while minimizing storage costs.</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Amazon MQ now supports configurable storage for RabbitMQ brokers</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-mq-rabbitmq-configurable-storage/</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 18:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MQ now lets you set custom EBS storage sizes for RabbitMQ brokers, separate from instance types, enhancing flexibility for messaging workloads.
+2. Outcome (impact):
+   Users can now optimize storage costs and performance by matching storage capacity to their specific needs without being tied to instance size constraints.
+3. Where to use (use case):
+   Ideal for managing messaging workloads where storage requirements differ from compute needs, allowing for more efficient resource allocation.</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Amazon MQ</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Amazon EC2 G7e instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-g7e-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 18:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 G7e instances with advanced GPUs are now available in three new regions, enhancing performance for AI and spatial computing workloads.
+2. Outcome (impact):
+Customers can achieve up to 2.3x better inference performance for large language models, agentic AI, and multimodal generative AI models.
+3. Where to use (use case):
+Deploying large language models, agentic AI, multimodal generative AI, and physical AI models, especially for spatial computing and graphics-intensive tasks.</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Amazon RDS and Aurora now support R8g and M8g database instances in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/7/amazon-rds-aurora-r8g-m8g-regions/</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS has expanded support for R8g and M8g database instances across multiple regions for Amazon RDS and Aurora, offering enhanced performance and cost savings.
+2. Outcome (impact):  
+   Users can now leverage up to 40% better performance and up to 29% better price/performance for their database workloads in additional regions.
+3. Where to use (use case):  
+   Ideal for database-intensive applications requiring high performance and cost efficiency, such as e-commerce platforms, financial services, and large-scale data analytics.</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Amazon RDS and Aurora expand R8gd and M8gd to additional Regions</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-aurora-r8gd-m8gd-regions/</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS and Aurora now support R8gd and M8gd instances in additional regions, enhancing throughput and price-performance with Optimized Reads.
+2. Outcome (impact):
+Improved query performance and faster index rebuilds for complex queries, with up to 165% better throughput and 120% better price-performance.
+3. Where to use (use case):
+Ideal for workloads requiring high throughput and low-latency access to large datasets, such as data analytics, e-commerce platforms, and financial services.</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Amazon Cognito now supports importing users with password hashes</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-cognito-password-hash-import/</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Cognito now allows importing users with password hashes, enabling immediate sign-in without password resets.
+2. Outcome (impact):  
+This update enhances user experience by eliminating the need for password resets during initial sign-in, improving security and convenience.
+3. Where to use (use case):  
+Use this feature when migrating users from another authentication system to Amazon Cognito, ensuring a seamless transition.</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon Cognito  
+Category: Security</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Amazon MSK Express Brokers adds support for Apache Kafka version 4.2</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-msk-express-version-42/</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MSK Express Brokers now supports Apache Kafka version 4.2, enhancing availability and performance with new protocols and improvements.
+2. Outcome (impact):
+Improved leader election correctness, faster group rebalances, optimized task assignments for Kafka Streams, and increased throughput, scalability, and recovery time.
+3. Where to use (use case):
+Real-time data streaming, event sourcing, log aggregation, and any application requiring high throughput and low-latency message brokering.</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Amazon MSK</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports up to four storage modifications in 24 hours</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-upto-four-storage-modifications-24-hours</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 16:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS now supports up to four storage modifications within 24 hours, enhancing agility for scaling and performance adjustments.
+2. Outcome (impact):  
+This enhancement allows for more frequent and immediate adjustments to storage capacity and performance, minimizing downtime and performance impact.
+3. Where to use (use case):  
+Ideal for scenarios with sudden data growth or unexpected workload spikes, such as e-commerce sites during sales events or applications experiencing rapid user growth.</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>AWS Glue SAP OData connector and zero-ETL integrations are now available in AWS GovCloud (US) regions</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-glue-sap-zero-etl-govcloud</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 15:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue now offers SAP OData connector and zero-ETL integrations in AWS GovCloud (US) regions, supporting Amazon DynamoDB, Salesforce, and SAP OData.
+2. Outcome (impact):
+Customers in regulated environments can now easily replicate data from these sources into Amazon Redshift, Amazon S3, or other destinations without custom pipelines, saving time and resources.
+3. Where to use (use case):
+Ideal for organizations in regulated sectors needing to analyze data from SAP, Salesforce, and DynamoDB in data lakes and warehouses without custom ETL pipelines.</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service now supports the Agent Toolkit for AWS with a curated skill</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-opensearch-service-agent/</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 14:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Service now integrates with the Agent Toolkit for AWS, allowing AI coding agents to manage and query OpenSearch domains and collections using natural language.
+2. Outcome (impact):
+   This integration simplifies the management and querying of OpenSearch domains and collections, enabling users to perform tasks such as migration, operations, search, log analytics, and trace analytics using plain language commands.
+3. Where to use (use case):
+   Ideal for developers and operations teams who want to streamline the management and querying of OpenSearch Service and OpenSearch Serverless using AI-driven coding agents.</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Db2 is now available in additional AWS Commercial regions</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-db2-available-additional-aws-commercial-regions</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 07:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for Db2 is now available in five new regions, offering easy setup, scaling, and high availability for Db2 databases.
+2. Outcome (Impact):
+This expansion enables businesses in new regions to leverage Db2 databases in the cloud with enhanced performance and reliability, supporting global operations.
+3. Where to Use (Use Case):
+Ideal for enterprises requiring high-performance, scalable Db2 databases in regions like Thailand, Malaysia, Taipei, Mexico, and Calgary for applications needing robust data management.</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Db2</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>AWS Lambda announces self-managed code storage</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/lambda-self-managed-code-storage/</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda now supports referencing code directly from self-managed S3 buckets, eliminating storage limits and reducing function activation time.
+2. Outcome (impact):
+   This update allows users to store unlimited code in their own S3 buckets without counting against Lambda's storage limit, simplifying code management and reducing latency.
+3. Where to use (use case):
+   Ideal for customers deploying many Lambda functions and layers, who need more than the 75GB default code storage limit per region.</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery reduces recovery time for AWS-to-AWS workloads</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-drs-fast-recovery/</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 22:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elastic Disaster Recovery now significantly reduces recovery time for AWS-to-AWS workloads by skipping unnecessary preparation steps, enhancing disaster recovery efficiency.
+2. Outcome (impact):  
+Reduces recovery time by up to 65% for Windows and up to 40% for Linux, allowing faster application restoration and minimizing downtime during disasters.
+3. Where to use (use case):  
+Ideal for organizations with AWS-based workloads that need efficient disaster recovery solutions to ensure rapid application availability and business continuity.</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch announces lookup processor for log enrichment</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-cloudwatch-lookup-processor/</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch has introduced a lookup processor to enrich log events by matching log fields against a lookup table, directly within the CloudWatch pipeline.
+2. Outcome (impact):
+This feature allows for immediate enrichment of log data as it is ingested, enhancing query, dashboard, and alarm capabilities with added context without requiring post-processing.
+3. Where to use (use case):
+Use the lookup processor to enrich VPC Flow Logs with team ownership information, map user IDs to user details, or convert error codes to human-readable descriptions.</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8in, M8idn, M8ib, M8idb instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/m8in-m8idn-m8ib-m8idb-new-regions</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched M8in, M8idn, M8ib, and M8idb instances in additional regions, offering enhanced networking and EBS performance.
+2. Outcome (impact):
+   Users can now leverage up to 43% higher performance and improved network/storage capabilities for demanding workloads across multiple regions.
+3. Where to use (use case):
+   Ideal for real-time big data analytics, high-performance file systems, large commercial databases, and NoSQL databases.</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -25109,7 +25665,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15 05:38:15</t>
+          <t>2026-07-16 05:45:53</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25686,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5509</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="7">
@@ -25140,7 +25696,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1956</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="8">
@@ -25150,7 +25706,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000391</v>
+        <v>0.000425</v>
       </c>
     </row>
     <row r="9">
@@ -25160,7 +25716,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000556</v>
+        <v>0.000549</v>
       </c>
     </row>
     <row r="10">
@@ -25170,7 +25726,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000947</v>
+        <v>0.000974</v>
       </c>
     </row>
     <row r="11">
@@ -25180,7 +25736,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.041108</v>
+        <v>0.042082</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F679"/>
+  <dimension ref="A1:F694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -25600,6 +25600,561 @@
       <c r="F679" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana achieves FedRAMP High authorization in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-managed-grafana-fedramp-high/</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 19:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Managed Grafana has achieved FedRAMP High authorization in AWS GovCloud (US), enabling federal agencies and public sector organizations to visualize and analyze their operational metrics securely.
+2. Outcome (impact):  
+This authorization allows federal agencies and other organizations with FedRAMP High compliance requirements to use Amazon Managed Grafana for monitoring and alerting on their AWS and hybrid environments, ensuring they meet stringent security standards.
+3. Where to use (use case):  
+Federal agencies, public sector organizations, and enterprises needing to comply with FedRAMP High standards can use Amazon Managed Grafana to visualize, query, and alert on operational metrics across their cloud and hybrid environments.</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Amazon Managed Grafana</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Track cost efficiency trends directly in Billing and Cost Management Dashboards with the new Cost Efficiency widget</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/monitor-cost-efficiency-using-dashboards</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 18:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces a Cost Efficiency widget in Billing and Cost Management Dashboards to track cost optimization trends and performance.
+2. Outcome (impact):  
+Users can monitor their AWS cost efficiency trends, commitments, and optimization performance in a unified dashboard, facilitating better cost management and savings opportunities.
+3. Where to use (use case):  
+Ideal for finance teams and cost management professionals who need to track and optimize AWS spending across accounts, regions, and services.</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Billing and Cost Management Dashboards</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Amazon EC2 now surfaces the public SSM parameters associated with public AMIs</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/ec2-public-images-ssm-parameters</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 18:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 now displays public SSM parameters linked to public AMIs in the AMI metadata, simplifying AMI updates and configuration.
+2. Outcome (impact):
+   This update streamlines the process of discovering and referencing SSM parameters for public AMIs, reducing manual effort and potential errors.
+3. Where to use (use case):
+   Ideal for automating AMI updates across infrastructure, ensuring configurations always reference the latest AMI versions.</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Amazon S3 Event Notifications now include system-generated tags</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-s3-event-notifications-system-generated-tags/</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon S3 now includes system-generated tags in event notifications, simplifying event filtering across multiple buckets.
+2. Outcome (impact):
+   Simplifies event management and filtering by allowing users to apply a single EventBridge rule to multiple buckets based on tags.
+3. Where to use (use case):
+   Ideal for managing and monitoring events across numerous S3 buckets in a centralized manner, enhancing efficiency in event-driven architectures.</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>PostgreSQL 19 Beta 2 is now available in Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/postgresql-19-beta-2-amazon-rds-database-preview-environment/</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS now offers PostgreSQL 19 Beta 2 in the Database Preview Environment for evaluation. It introduces features like parallel autovacuum and online table repacking.
+2. Outcome (impact):
+   Users can now test PostgreSQL 19's new features, improving maintenance efficiency and database accessibility, while benefiting from AWS's managed service capabilities.
+3. Where to use (use case):
+   Ideal for database administrators and developers looking to test and prepare for PostgreSQL 19's new features in a production-like environment before its official release.</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>AWS Sustainability service now includes water withdrawals data</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-sustainability-water-withdrawals/</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 16:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Sustainability now offers water withdrawals data, providing customers with comprehensive environmental impact insights alongside carbon emissions data.
+2. Outcome (impact):
+Organizations can better understand and manage their environmental footprint by tracking both carbon emissions and water withdrawals associated with their AWS workloads.
+3. Where to use (use case):
+Ideal for organizations aiming to enhance their sustainability reporting and environmental stewardship by gaining visibility into both carbon and water impacts of their cloud usage.</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>AWS Sustainability</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7in-24TB instances now available in AWS Europe (Paris) region</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-high-memory-europe/</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has launched High Memory U7in-24TB instances in the Europe (Paris) region, offering 24 TiB of DDR5 memory and enhanced performance for data-intensive applications.
+2. Outcome (impact):
+Customers can now achieve up to 45% better price performance for in-memory databases and transaction processing workloads, with improved data loading and backup speeds.
+3. Where to use (use case):
+Ideal for mission-critical in-memory databases such as SAP HANA, Oracle, and SQL Server, particularly in fast-growing data environments.</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Amazon Redshift adds rg.large and rg.12xlarge instance sizes</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-redshift-adds-rg-large-12xlarge-instance-sizes</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift has launched two new Graviton-powered instance sizes, rg.large and rg.12xlarge, offering up to 2.4x faster query performance at 30% lower price per vCPU.
+2. Outcome (impact):
+Users can now choose more cost-effective and performant instance sizes for their data warehousing needs, enabling better resource allocation and cost savings.
+3. Where to use (use case):
+Ideal for data-intensive applications, analytics workloads, and large-scale data processing tasks requiring high query performance and cost efficiency.</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Amazon S3 removes 30-day minimum for transitions to S3 Standard-IA and S3 One Zone-IA</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/s3-removes-30-day-transitions-standard-ia-one-zone-ia</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon S3 now allows immediate transition of objects to S3 Standard-IA and S3 One Zone-IA, removing the previous 30-day minimum.
+2. Outcome (impact):
+   Users can achieve up to 40% lower storage costs with immediate access to infrequent data, enhancing cost efficiency for cold data workloads.
+3. Where to use (use case):
+   Ideal for backups, log analytics, and compliance workloads where data becomes less frequently accessed shortly after creation.</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>AWS Backup extends logically air-gapped vault support to six additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-backup-logically-air-gapped-vault-regions/</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Backup now supports logically air-gapped vaults in six new regions, enhancing data security and isolation.
+2. Outcome (impact):  
+This expansion allows customers to store immutable, isolated backups securely across more regions, improving data protection and compliance.
+3. Where to use (use case):  
+Ideal for organizations requiring stringent data security and compliance, such as financial services, healthcare, and government sectors.</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>AWS Backup extends restore testing support to six additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-backup-restore-testing-regions/</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Backup now supports restore testing in six new regions, enhancing disaster recovery and compliance readiness.
+2. Outcome (impact):
+Improves recovery readiness and helps meet regulatory and compliance requirements for disaster recovery and business continuity.
+3. Where to use (use case):
+Businesses needing to ensure data recovery capabilities across multiple regions for compliance and disaster recovery purposes.</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>AWS Control Tower Account Factory for Terraform now re-applies customizations when accounts move between OUs</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-control-tower-account/</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 04:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Control Tower Account Factory for Terraform now automatically re-applies customizations when accounts move between OUs, reducing manual effort and risk.
+2. Outcome (impact):
+   This feature minimizes operational overhead and configuration drift by ensuring accounts maintain their OU-specific configurations without manual intervention.
+3. Where to use (use case):
+   Ideal for organizations enforcing compliance or security baselines tied to OU membership, ensuring consistent configurations across account movements.</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>AWS Control Tower Account Factory for Terraform</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL is now in scope for FedRAMP Moderate</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-aurora-dsql-now-in-scope-for-fedramp-moderate/</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora DSQL is now FedRAMP Moderate compliant in three US regions, enabling secure, high-availability applications.
+2. Outcome (impact):
+Organizations can now build and run FedRAMP Moderate compliant applications using Aurora DSQL, ensuring adherence to federal security standards.
+3. Where to use (use case):
+Ideal for federal agencies and contractors needing high-availability, scalable, and secure SQL databases.</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs Insights adds 25 new query commands and functions</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/7/amazon-cloudwatch-logs-insights-ql/</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 21:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch Logs Insights has introduced 25 new query commands and functions to enhance log analysis capabilities.
+2. Outcome (impact):
+These new features improve the ability to perform complex log analysis, including statistical aggregation, handling null values, comparing logs over time, detecting outliers, and enriching events with lookup data.
+3. Where to use (use case):
+These new commands and functions are ideal for developers, system administrators, and data analysts who need to deeply analyze and visualize log data for troubleshooting, performance monitoring, and security auditing.</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs Insights</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Connect Customer Outbound Campaigns now in Cape Town Africa</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/connect-africa-cape-town/</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Connect Customer Outbound Campaigns are now available in Cape Town, Africa, enabling businesses to run targeted campaigns via SMS, WhatsApp, and email.
+2. Outcome (impact):
+Businesses in Africa can now enhance customer engagement with personalized, multi-channel campaigns, improving service delivery and promotional effectiveness.
+3. Where to use (use case):
+Retail businesses can segment customers based on behavior and run coordinated campaigns to send promotional offers, reminders, and tips through SMS, WhatsApp, and email.</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -25665,7 +26220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16 05:45:53</t>
+          <t>2026-07-17 05:46:59</t>
         </is>
       </c>
     </row>
@@ -25686,7 +26241,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5985</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="7">
@@ -25696,7 +26251,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1932</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="8">
@@ -25706,7 +26261,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000425</v>
+        <v>0.000355</v>
       </c>
     </row>
     <row r="9">
@@ -25716,7 +26271,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000549</v>
+        <v>0.000528</v>
       </c>
     </row>
     <row r="10">
@@ -25726,7 +26281,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000974</v>
+        <v>0.000883</v>
       </c>
     </row>
     <row r="11">
@@ -25736,7 +26291,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.042082</v>
+        <v>0.042965</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F694"/>
+  <dimension ref="A1:F697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -26155,6 +26155,118 @@
       <c r="F694" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams now supports IAM role credentials for stream sessions</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-gamelift-streams-iam/</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Fri, 17 Jul 2026 17:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GameLift Streams now supports IAM role credentials for secure access to AWS resources without embedding long-lived keys.
+2. Outcome (impact):
+This update enhances security by eliminating the need for long-lived access keys, reducing operational complexity and mitigating security risks.
+3. Where to use (use case):
+Ideal for game developers needing to securely access AWS services like S3 and DynamoDB from streamed game sessions.</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch UI now supports one-click dashboard migration</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-opensearch-ui-one-click-dashboard-migration</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Fri, 17 Jul 2026 17:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon OpenSearch Service now offers a one-click migration tool to transfer dashboards from legacy OpenSearch Dashboards to the new OpenSearch UI.
+2. Outcome (impact):  
+Reduces operational complexity and time required to move between interfaces by enabling the reuse of existing tenants and saved objects in OpenSearch UI.
+3. Where to use (use case):  
+Ideal for users managing multiple tenants and dashboards in OpenSearch Service who need to transition to the new OpenSearch UI without manual recreation of their setups.</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Service name: Amazon OpenSearch Service  
+Category: Database</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports partition-level topology for Slurm orchestrated clusters</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/hyperpod-partition-topology-slurm/</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Fri, 17 Jul 2026 15:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker HyperPod now allows partition-level network topology configuration for Slurm clusters, optimizing distributed training performance.
+2. Outcome (impact):
+   Improves GPU-to-GPU communication speed, enhances NCCL collective operations efficiency, and boosts training throughput by aligning job placement with instance interconnect characteristics.
+3. Where to use (use case):
+   Ideal for large-scale distributed training tasks in machine learning workloads that require high-performance computing with varying instance types.</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -26220,7 +26332,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17 05:46:59</t>
+          <t>2026-07-18 05:32:42</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26343,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -26241,7 +26353,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4998</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="7">
@@ -26251,7 +26363,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1860</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8">
@@ -26261,7 +26373,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000355</v>
+        <v>8.2e-05</v>
       </c>
     </row>
     <row r="9">
@@ -26271,7 +26383,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000528</v>
+        <v>0.000105</v>
       </c>
     </row>
     <row r="10">
@@ -26281,7 +26393,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000883</v>
+        <v>0.000186</v>
       </c>
     </row>
     <row r="11">
@@ -26291,7 +26403,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.042965</v>
+        <v>0.043151</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F697"/>
+  <dimension ref="A1:F708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -26267,6 +26267,413 @@
       <c r="F697" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>AWS Data Exports now provides standardized Amazon Bedrock product metadata</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-data-exports-amazon-bedrock-product-metadata/</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 18:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces standardized metadata for Amazon Bedrock in its Data Exports, simplifying cost tracking and analysis for FinOps teams.
+2. Outcome (impact):
+FinOps teams and cloud administrators can now easily attribute and understand Amazon Bedrock costs without needing custom parsing, enhancing cost management efficiency.
+3. Where to use (use case):
+This feature is ideal for organizations utilizing Amazon Bedrock for AI/ML services, enabling better cost visibility and management through AWS Data Exports.</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>AWS Data Exports</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8i and R8i-flex instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-r8i-r8i-flex-instances-in-stockholm-zurich-regions/</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 17:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 R8i and R8i-flex instances are now available in Stockholm and Zurich, offering enhanced performance and memory bandwidth.
+2. Outcome (impact):
+Users can achieve up to 40% faster performance for specific workloads, such as AI deep learning models, and up to 15% better price-performance.
+3. Where to use (use case):
+Ideal for memory-intensive workloads, large-scale applications, and mission-critical SAP environments.</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Selectively log network activity events by identity in AWS CloudTrail</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-cloudtrail-filter-useridentity-advance-selectors/</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 17:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS CloudTrail now allows selective logging of network activity events based on IAM user identity, enabling focused security monitoring.
+2. Outcome (impact):
+   Reduces logging costs and noise by capturing only relevant network activity events, enhancing security monitoring efficiency.
+3. Where to use (use case):
+   Ideal for implementing data perimeter strategies by logging only unauthorized access attempts and potential data exfiltration attempts.</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>AWS CloudTrail</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Amazon Connect delivers more natural agentic voice experiences with expanded language support and speech controls</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-connect-agentic-voice/</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 16:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect enhances voice experiences with expanded language support and improved conversational AI, offering more natural interactions.
+2. Outcome (impact):  
+Businesses can now provide smoother, more natural voice interactions in multiple languages, improving customer satisfaction and engagement.
+3. Where to use (use case):  
+Ideal for customer service centers, contact centers, and any enterprise looking to improve voice-based customer interactions.</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I8ge instances are now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-i8ge-instances-aws-govcloud-us-regions/</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched I8ge instances powered by AWS Graviton4 processors in the AWS GovCloud (US) regions, offering enhanced compute and storage performance.
+2. Outcome (Impact):
+   Users can achieve up to 60% better compute performance and 55% better real-time storage performance per TB compared to previous generations, with lower latency and variability.
+3. Where to Use (Use Case):
+   Ideal for workloads requiring high random read/write performance and low latency access to large datasets, such as data analytics, large-scale databases, and high-performance computing.</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications now supports Microsoft OneDrive and Google Drive on Multi-Session fleets</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/storage-multi-session-fleets/</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon WorkSpaces Applications now supports Microsoft OneDrive and Google Drive on multi-session fleets, enhancing user experience and collaboration.
+2. Outcome (impact):
+Users can now access, save, and sync their cloud-based files directly within their streaming sessions, providing a seamless experience while maintaining cost efficiencies.
+3. Where to use (use case):
+Ideal for organizations looking to maximize cost savings with multi-session fleets while offering users familiar cloud storage solutions.</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Apache Flink now supports Apache Flink 2.3</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-managed-service-flink-2-3/</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Managed Service for Apache Flink now supports Apache Flink 2.3, enhancing backpressure handling and data correctness in CDC pipelines.
+2. Outcome (impact):
+Improved application performance under uneven loads and better data accuracy in change data capture pipelines.
+3. Where to use (use case):
+Real-time data transformation and analysis, particularly for applications requiring robust handling of streaming data.</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Apache Flink</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Announcing the general availability of a new AWS Local Zone in Athens, Greece</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-local-zone-athens-greece/</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched a new Local Zone in Athens, Greece, offering low-latency access to Amazon S3, EBS, and EC2 services to meet local data residency needs.
+2. Outcome (impact):
+This new Local Zone enables businesses in Greece to process and store data locally, ensuring compliance with local regulations and enhancing performance for latency-sensitive applications.
+3. Where to use (use case):
+Ideal for public sector services, financial applications requiring in-country data processing, and real-time gaming and interactive experiences.</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Amazon Elastic Compute Cloud (Amazon EC2)</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch announces coding agent insights</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/cloudwatch-coding-agent-insights/</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 09:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch introduces Coding Agent Insights to provide visibility on AI coding tools' impact, integrating with services like AWS and GitHub Copilot.
+2. Outcome (impact):
+   Engineering leaders can measure ROI from AI coding tools, optimize token budgets, and identify which teams benefit most from these tools.
+3. Where to use (use case):
+   Ideal for organizations scaling AI coding agent adoption, to track usage, efficiency, and cost-effectiveness across different teams and projects.</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Introducing KNFSD File Cache - Now in Preview</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/knfsd-file-cache/</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces KNFSD File Cache, an open-source NFS caching solution for high-speed, scalable file access on AWS, supporting multicloud environments.
+2. Outcome (impact):
+   Improves performance for read-heavy workloads by caching frequently accessed data, reducing latency and bandwidth costs.
+3. Where to use (use case):
+   Ideal for industries like visual effects rendering, simulation, financial services, and health and life sciences requiring fast access to large datasets.</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Synthetics now supports customer managed encryption keys</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/synthetics-customer-managed-keys/</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 20:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon CloudWatch Synthetics now supports customer managed KMS keys for encrypting canary environment variables, enhancing data security.
+2. Outcome (impact):  
+This update provides greater control over encryption, enabling compliance with organizational policies and regulations, especially in regulated industries.
+3. Where to use (use case):  
+Ideal for teams needing to manage sensitive data like API keys and credentials securely, particularly in regulated environments.</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Synthetics</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -26332,7 +26739,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18 05:32:42</t>
+          <t>2026-07-21 05:56:12</t>
         </is>
       </c>
     </row>
@@ -26343,7 +26750,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -26353,7 +26760,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1154</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="7">
@@ -26363,7 +26770,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>368</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="8">
@@ -26373,7 +26780,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.2e-05</v>
+        <v>0.000316</v>
       </c>
     </row>
     <row r="9">
@@ -26383,7 +26790,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000105</v>
+        <v>0.000373</v>
       </c>
     </row>
     <row r="10">
@@ -26393,7 +26800,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000186</v>
+        <v>0.0006890000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -26403,7 +26810,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.043151</v>
+        <v>0.04384</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F708"/>
+  <dimension ref="A1:F720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -26674,6 +26674,451 @@
       <c r="F708" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R6in and R6idn instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-r6in-r6idn/</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 R6in and R6idn instances are now available in AWS Europe (Paris) and Canada (Central) regions, offering enhanced network performance for demanding workloads.
+2. Outcome (impact):
+Customers can now leverage high-performance, network-optimized instances in more regions to scale their network-intensive applications with improved bandwidth and processing capabilities.
+3. Where to use (use case):
+Ideal for memory-intensive databases, in-memory caches, real-time big data analytics, and other network-intensive workloads requiring high throughput and low latency.</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C6in instances are now available in Asia Pacific (Taipei) Region</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-c6in/</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has launched C6in instances in the Asia Pacific (Taipei) region, offering high network bandwidth and optimized performance for various workloads.
+2. Outcome (Impact):
+C6in instances provide up to 200Gbps network bandwidth, doubling that of comparable fifth-generation instances, enhancing application performance in regions with high network demands.
+3. Where to Use (Use Case):
+Ideal for applications requiring high network throughput, such as network virtual appliances, Telco 5G User Plane Function (UPF), data analytics, HPC, and CPU-based AI/ML workloads.</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon EC2  
+Category: Compute</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M6in and M6idn instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-m6in-m6idn/</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 M6in and M6idn instances are now available in AWS Asia Pacific (Hyderabad) and South America (Sao Paulo) regions, offering enhanced network performance.
+2. Outcome (impact):
+Customers can now leverage higher network bandwidth and throughput for network-intensive workloads across additional regions, enhancing scalability and performance.
+3. Where to use (use case):
+Ideal for high-performance file systems, distributed web-scale in-memory caches, real-time big data analytics, and Telco applications such as 5G User Plane Function.</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Amazon ECS advanced deployment strategies now available in AWS European Sovereign Cloud</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/ecs-adv-deployments-eu-sovereign-cloud/</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now offers advanced deployment strategies (blue/green, linear, canary) in the AWS European Sovereign Cloud, enhancing safety and speed of containerized application updates.
+2. Outcome (impact):
+These new strategies reduce the risk of software updates, enable faster release cycles, and provide robust controls for validating new application versions before full traffic shift.
+3. Where to use (use case):
+Ideal for organizations deploying containerized applications that require safe and reliable update processes, ensuring minimal downtime and quick rollbacks if issues arise.</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Amazon SES introduces pricing plans</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ses-pricing-plans/</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 16:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SES has introduced tiered pricing plans (Essentials, Pro, Enterprise) to simplify purchasing and accessing SES capabilities, offering progressively more features at a discount.
+2. Outcome (impact):
+Businesses can now easily select a pricing plan that meets their email needs without the complexity of evaluating and purchasing individual add-ons, ensuring better email deliverability and performance.
+3. Where to use (use case):
+Ideal for businesses of all sizes looking to streamline their email service procurement and enhance email deliverability, from small businesses to large enterprises.</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Amazon ECS now provides Action Logs for deployment and orchestration visibility</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ecs-action-logs/</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 15:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECS introduces Action Logs to provide detailed visibility into service deployments and Managed Daemon updates, enhancing monitoring and troubleshooting capabilities.
+2. Outcome (impact):
+   Action Logs enable users to monitor and troubleshoot service deployments and updates directly, reducing mean time to resolution and improving operational efficiency.
+3. Where to use (use case):
+   Ideal for DevOps teams and system administrators who need detailed insights into ECS service operations to quickly identify and resolve issues.</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus supports 1.5B active metrics and 200K rules per workspace</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-managed-service-prometheus-1500m-metrics-workspace/</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Managed Service for Prometheus now supports up to 1.5 billion active metrics and 200,000 rules per workspace, enabling large-scale monitoring.
+2. Outcome (impact):  
+Customers can now monitor and analyze billions of Prometheus metrics across their organization with enhanced scalability and performance.
+3. Where to use (use case):  
+Ideal for organizations requiring large-scale monitoring and alerting for containerized, serverless, and hybrid environments.</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Amazon Managed Service for Prometheus</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports the latest CU and GDR updates for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-supports-latest-cu-gdr-microsoft-sql-server</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 07:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS now supports the latest CU and GDR updates for Microsoft SQL Server, including SQL Server 2016, 2017, 2019, and 2022.
+2. Outcome (impact):
+This update enhances security and performance by applying the latest Cumulative Updates and General Distribution Releases, addressing vulnerabilities and improving overall database stability.
+3. Where to use (use case):
+Ideal for businesses and organizations running mission-critical applications on Microsoft SQL Server, ensuring they benefit from the latest security patches and performance improvements.</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server now supports Microsoft SQL Server 2025</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/rds-sqlserver-supports-sqlserver-2025</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for SQL Server now supports SQL Server 2025, offering AI integration, new editions, and enhanced features.
+2. Outcome (impact):
+Enables seamless integration of AI capabilities within SQL Server, improves performance, and provides a cost-effective development environment.
+3. Where to use (use case):
+Ideal for businesses looking to leverage AI-powered analytics, automate performance tasks, and integrate with AWS services without re-architecting applications.</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>AWS Partner Central agents expand funding guidance to all programs</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-partner-central/</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 20:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Central agents now provide funding guidance for all AWS Partner funding programs, enhancing efficiency and accuracy.
+2. Outcome (impact):
+Eliminates manual data entry, reduces eligibility errors, and speeds up the funding application process for AWS Partners.
+3. Where to use (use case):
+Ideal for AWS Partners applying for various funding programs, ensuring streamlined and accurate submissions.</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Amazon Q</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches metrics for agent queues on analytics dashboards</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-connect/</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 15:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers real-time and historical metrics for agent queues on analytics dashboards, enabling supervisors to monitor and manage agent performance effectively.
+2. Outcome (Impact):
+Supervisors can now track agent performance in real-time, identify spikes in contact queues, and reassign contacts to prevent long wait times, enhancing customer satisfaction and operational efficiency.
+3. Where to Use (Use Case):
+This feature is ideal for contact centers that need to manage and optimize agent performance, ensuring efficient contact handling and improved customer experience.</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio adds custom visual transforms</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-unified-studio</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Fri, 17 Jul 2026 21:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio now supports custom visual transforms in ETL flows, allowing data engineers to create reusable, business-specific transformation logic without coding.
+2. Outcome (impact):
+This feature reduces duplicated effort, ensures consistent data transformations across multiple ETL jobs, and makes advanced data processing accessible to non-coding team members.
+3. Where to use (use case):
+Ideal for data engineering teams needing to standardize data, mask sensitive information, or apply organization-specific data quality checks in ETL processes.</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -26739,7 +27184,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21 05:56:12</t>
+          <t>2026-07-22 05:55:23</t>
         </is>
       </c>
     </row>
@@ -26750,7 +27195,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -26760,7 +27205,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4445</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="7">
@@ -26770,7 +27215,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1314</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="8">
@@ -26780,7 +27225,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000316</v>
+        <v>0.000332</v>
       </c>
     </row>
     <row r="9">
@@ -26790,7 +27235,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000373</v>
+        <v>0.000442</v>
       </c>
     </row>
     <row r="10">
@@ -26800,7 +27245,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0006890000000000001</v>
+        <v>0.0007739999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -26810,7 +27255,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04384</v>
+        <v>0.044614</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F720"/>
+  <dimension ref="A1:F733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -27119,6 +27119,487 @@
       <c r="F720" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C7a instances are now available in the US West (N. California) Region</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-c7a-instances-us-west-ncalifornia-region/</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 21:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C7a instances, powered by 4th Gen AMD EPYC processors, are now available in the US West (N. California) Region, offering up to 50% higher performance than C6a instances.
+2. Outcome (impact):
+   Enhanced performance and memory bandwidth for compute-intensive workloads, with support for up to 128 EBS volumes per instance.
+3. Where to use (use case):
+   Ideal for batch processing, distributed analytics, HPC, ad serving, scalable gaming, and video encoding.</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8a instances now available in the Asia Pacific (Hyderabad) region</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-m8a-instances-asia-pacific-hyderabad-region/</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 20:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 M8a instances, powered by 5th Gen AMD EPYC processors, are now available in the Asia Pacific (Hyderabad) region, offering higher performance and better price-performance.
+2. Outcome (impact):
+Customers can leverage up to 30% higher performance and 19% better price-performance for latency-sensitive workloads, with additional memory bandwidth and improved benchmarks for specific applications.
+3. Where to use (use case):
+Ideal for financial applications, gaming, rendering, application servers, simulation modeling, mid-size data stores, development environments, and caching fleets.</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>AWS Network Load Balancer now supports Listener Rules for custom traffic routing</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-network-load-balancer-supports-listener-rules/</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 19:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Network Load Balancer now supports listener rules to route IPv4 and IPv6 traffic to appropriate target groups, preserving client IP addresses.
+2. Outcome (impact):
+This update allows for efficient traffic routing within a single dual-stack NLB, eliminating the need for separate load balancers or protocol translation, thus simplifying infrastructure and improving performance.
+3. Where to use (use case):
+Ideal for environments requiring both IPv4 and IPv6 support, such as modern web applications needing to maintain original client IP addresses for logging, security, or compliance purposes.</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Network Load Balancer</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>AWS Entity Resolution now supports advanced real-time matching</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-entity-resolution/</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Entity Resolution now offers advanced real-time matching, enabling complex rule-based record matching in milliseconds.
+2. Outcome (impact):  
+   Customers can now perform sophisticated real-time entity resolution without needing separate infrastructure or application re-architecture.
+3. Where to use (use case):  
+   Ideal for fraud detection, real-time account lookup, and website personalization.</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>AWS Entity Resolution</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>AWS Lambda durable functions now supports customer managed key encryption</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/durablefunctions-cmk/</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now allows durable functions to use customer managed keys for encrypting execution data, enhancing compliance for regulated industries.
+2. Outcome (impact):
+This update provides better control over data encryption, enabling organizations in regulated sectors to meet compliance requirements by managing their own encryption keys.
+3. Where to use (use case):
+Ideal for industries like financial services and healthcare that require strict data governance and compliance with regulations such as GDPR, HIPAA, or PCI DSS.</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Amazon Corretto July 2026 Quarterly Updates</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-corretto-july-2026-quarterly-updates</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Corretto July 2026 updates include new LTS and FR versions with enhanced security, new Docker images based on Amazon Linux 2023, and removal of JavaFX binaries from Corretto 8.
+2. Outcome (impact):
+   These updates ensure improved security, better performance, and compatibility with modern infrastructure, while also guiding users to migrate from older Amazon Linux versions.
+3. Where to use (use case):
+   Ideal for enterprise applications requiring stable, secure, and high-performance Java environments, including web servers, microservices, and cloud-native applications.</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Amazon Corretto</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>AWS Organizations increases RCP quota to 2,000 per organization</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-organizations-resource-control-policy-limit-increase-2000</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>1. Short Summary  
+AWS Organizations has doubled its resource control policies (RCPs) quota to 2,000 per organization, enhancing centralized management of resource permissions.
+2. Outcome (Impact)  
+This change allows organizations to implement more granular and detailed access control configurations across multiple accounts, facilitating better security and compliance management.
+3. Where to Use (Use Case)  
+Ideal for large enterprises with complex, multi-account environments needing fine-tuned, centralized permission management to enforce organization-wide access control policies.</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>AWS Organizations</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports EFA and placement groups on Amazon EKS Auto Mode and Karpenter</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-eks-efa-placement-groups/</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 14:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EKS now supports EFA and placement groups on EKS Auto Mode and Karpenter, optimizing performance and availability for distributed workloads.
+2. Outcome (impact):
+Improved performance and availability for distributed training and inference workloads, with fine-grained control over network interfaces and instance distribution.
+3. Where to use (use case):
+Ideal for optimizing distributed training jobs, high-performance computing, and critical production services requiring fault isolation and maximum throughput.</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager now publishes secret update notifications to Amazon EventBridge</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/secrets-manager-update-notifications</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Secrets Manager now directly publishes secret update events to Amazon EventBridge, enabling real-time responses to secret changes.
+2. Outcome (impact):
+   This update simplifies monitoring and responding to secret changes by eliminating the need to parse multiple CloudTrail events, allowing for more efficient and proactive management of secret updates.
+3. Where to use (use case):
+   Use this feature to refresh cached credentials in applications, restart dependent services, or update compliance reports during secret rotations.</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect announces 100G expansion in Lima, Peru</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-direct-connect-100g-lima/</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Direct Connect now offers 100 Gbps dedicated connections in Lima, Peru, enabling private, high-speed network access to AWS services.
+2. Outcome (Impact):
+Enhanced network performance and security for businesses in Peru, facilitating faster and more reliable connections to AWS services.
+3. Where to Use (Use Case):
+Ideal for enterprises in Lima requiring high-speed, private connections to AWS for applications like data analytics, content delivery, and cloud migration.</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery is now available in six additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-drs-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elastic Disaster Recovery (DRS) is now available in six new regions, enhancing global disaster recovery capabilities.
+2. Outcome (impact):
+This expansion allows organizations to achieve faster, more reliable recovery of applications and databases across a broader geographic range, minimizing downtime and data loss.
+3. Where to use (use case):
+Use AWS Elastic Disaster Recovery for replicating and recovering on-premises and cloud-based applications, including databases and enterprise applications, to AWS in different regions.</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports Amazon OpenSearch</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-unified/</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 17:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now integrates Amazon OpenSearch, allowing seamless querying and analysis of search and log analytics data alongside other data sources.
+2. Outcome (impact):
+   This integration enables data engineers and analysts to correlate operational and analytical data, streamline cross-source workflows, and gain deeper insights into system performance and user behavior.
+3. Where to use (use case):
+   Ideal for combining application logs and metrics stored in OpenSearch with transactional data to analyze system performance and user behavior in a unified environment.</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>AWS Marketplace now supports self-service seller signature management for India-based sellers</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-marketplace-india/</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Tue, 21 Jul 2026 07:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Marketplace now allows India-based sellers to upload and manage their seller signatures directly via AWS Partner Central, streamlining tax invoicing and compliance.
+2. Outcome (impact):
+   This update simplifies the process for Indian sellers, reducing manual workload and ensuring faster compliance with tax regulations by automating signature verification and GSTIN registration.
+3. Where to use (use case):
+   Ideal for software and service providers on AWS Marketplace who need to comply with Indian tax laws and require efficient management of their seller signatures for invoicing.</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -27184,7 +27665,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22 05:55:23</t>
+          <t>2026-07-23 06:06:26</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27676,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -27205,7 +27686,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4671</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="7">
@@ -27215,7 +27696,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1556</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="8">
@@ -27235,7 +27716,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000442</v>
+        <v>0.00047</v>
       </c>
     </row>
     <row r="10">
@@ -27245,7 +27726,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0007739999999999999</v>
+        <v>0.000803</v>
       </c>
     </row>
     <row r="11">
@@ -27255,7 +27736,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.044614</v>
+        <v>0.045417</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F733"/>
+  <dimension ref="A1:F747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -27600,6 +27600,525 @@
       <c r="F733" t="inlineStr">
         <is>
           <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>AWS now supports automatic credit memo application preferences</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/credit-memo-applications/</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 18:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now allows customers to set preferences for automatic credit memo application on outstanding invoices, enhancing payment process efficiency.
+2. Outcome (impact):
+Customers can better align AWS credit memo applications with their internal payment processes, reducing manual intervention and improving financial management.
+3. Where to use (use case):
+This feature is ideal for businesses with complex payment schedules and multiple invoices, ensuring credits are applied according to specific financial policies.</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Billing and Cost Management</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL supports MySQL 9.7 in Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-mysql-long-term-9-7-rds-database-preview/</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 18:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for MySQL now supports MySQL 9.7 in the preview environment, enabling users to test and explore new features before general availability.
+2. Outcome (impact):
+Users can evaluate and test MySQL 9.7 features in a sandbox environment, ensuring compatibility and readiness for future updates.
+3. Where to use (use case):
+Ideal for developers and database administrators who want to test new MySQL capabilities and ensure their applications are compatible with the latest MySQL version.</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>AWS Lambda durable execution SDK for .NET is now generally available</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/lambdadf-dotnet/</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the AWS Lambda Durable Execution SDK for.NET, enabling C# developers to create resilient, long-running workflows using Lambda durable functions.
+2. Outcome (impact):
+Developers can now build complex, multi-step applications such as payment processing pipelines and AI agent orchestrations within their applications, without the need for custom progress tracking or external orchestration services.
+3. Where to use (use case):
+This SDK is ideal for scenarios requiring long-running, event-driven workflows, such as payment processing pipelines, AI agent orchestrations, and human-in-the-loop approval processes.</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore now delivers unified observability with traces and logs in a single log group</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-bedrock-agentcore-unified-observability-single-log-group/</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore now consolidates agent traces, prompts, and logs into a single log group, enhancing observability and debugging efficiency.
+2. Outcome (impact):
+This update simplifies debugging by unifying telemetry in one log group, enabling better access control and encryption management for individual agents.
+3. Where to use (use case):
+Ideal for developers managing AI agents, this feature streamlines the debugging process and improves observability for multi-agent systems.</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Logs now supports Application Load Balancer logs</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-cloudwatch-logs/</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch Logs now supports Application Load Balancer (ALB) logs, enhancing observability and simplifying debugging for network traffic patterns.
+2. Outcome (impact):
+Improves visibility into client connections, traffic distribution, connection status, and target health, enabling faster identification and resolution of network issues.
+3. Where to use (use case):
+Monitoring and debugging network traffic for web applications using ALBs, ensuring consistent monitoring coverage, and analyzing detailed access patterns.</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Amazon EVS is now available in additional Regions</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-evs-available-in-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 16:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EVS is now available in Asia Pacific (Seoul), Europe (Zurich), and Europe (Stockholm) Regions, offering better latency and compliance options for VMware workloads.
+2. Outcome (impact):
+This expansion provides users with lower latency, compliance with data residency requirements, and enhanced redundancy strategies for VMware workloads.
+3. Where to use (use case):
+Ideal for migrating VMware workloads to AWS to eliminate aging infrastructure, reduce operational risks, and meet critical timelines.</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Amazon Elastic VMware Service (Amazon EVS)</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5 is now available on Amazon Bedrock in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/claude-sonnet-5-govcloud/</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 16:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS GovCloud (US) now offers Claude Sonnet 5 on Amazon Bedrock, enhancing coding, professional work, and agentic tasks with improved performance and reliability.
+2. Outcome (impact):
+Users in the US government sector can leverage advanced AI capabilities for coding, professional tasks, and agentic functions with increased efficiency and accuracy.
+3. Where to use (use case):
+Ideal for government agencies needing robust AI tools for coding, document drafting, data analysis, and maintaining compliance with regional data residency requirements.</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Announcing region expansion of G7e instances on SageMaker AI inference</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/g7e-sagemaker-ai/</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 15:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded the availability of G7e instances on SageMaker AI inference to Asia Pacific (Seoul), Europe (London), and Asia Pacific (Tokyo), enhancing inference performance and reducing latency.
+2. Outcome (impact):
+This expansion allows users to deploy inference endpoints closer to their end users in Asia and Europe, resulting in up to 2.3x better inference performance and up to 768 GB of GPU memory per instance.
+3. Where to use (use case):
+Ideal for generative AI workloads, large language model inference, image and video generation, spatial computing, and scientific computing that require high GPU memory and bandwidth.</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Announcing region expansion of G6 instances on SageMaker AI Inference</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/g6-sagemaker-ai-inference/</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 14:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded the availability of G6 instances to the AWS GovCloud (US-East) region for SageMaker AI inference, enhancing deep learning performance.
+2. Outcome (Impact):
+Government agencies and organizations can now deploy high-performance generative AI workloads in a compliant environment, meeting strict data residency and security requirements.
+3. Where to Use (Use Case):
+Ideal for deploying inference endpoints for generative AI tasks such as small-to-medium language models, image generation, and computer vision in a secure, compliant setting.</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>SageMaker</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>AWS Wickr announces Data Retention Service feature</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-wickr-data/</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Wickr introduces a Data Retention Service for Premium users, enabling secure, end-to-end encrypted conversation archiving.
+2. Outcome (impact):
+Organizations can now maintain comprehensive data archives and audit trails, enhancing compliance and data management.
+3. Where to use (use case):
+Ideal for enterprises needing secure, long-term storage of internal and external communications for compliance and historical reference.</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>AWS Wickr</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7i instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-high-memory-u7i/</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 High Memory U7i instances with 16 TiB and 24 TiB of DDR5 memory are now available in new regions, enhancing scalability for large-scale data environments.
+2. Outcome (impact):
+   These new instances enable businesses to handle larger transaction processing loads and support mission-critical applications with higher memory requirements, improving performance and scalability.
+3. Where to use (use case):
+   Ideal for running in-memory databases like SAP HANA, Oracle, and SQL Server, as well as other high-memory applications in fast-growing data environments.</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8id instances are now available in Europe (Ireland) region</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-m8id-europe-ireland/</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 19:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 M8id instances, powered by custom Intel Xeon 6 processors, are now available in Europe (Ireland) with enhanced performance and memory bandwidth.
+2. Outcome (impact):
+   These instances offer up to 43% higher performance and 3.3x more memory bandwidth, making them ideal for I/O intensive workloads, with up to 46% higher performance for databases and 30% faster query results for data analytics.
+3. Where to use (use case):
+   Suitable for balanced workloads such as application servers, microservices, enterprise applications, and small to medium databases.</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI inference now supports G7 instances</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-ai-g7/</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 15:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker now supports G7 instances with RTX PRO 4500 GPUs, offering up to 4.6x better AI inference performance than previous G6 instances.
+2. Outcome (impact):  
+Enhances deployment of generative AI models for production inference with higher GPU throughput and memory capacity, reducing the need for over-provisioning and model quantization.
+3. Where to use (use case):  
+Ideal for serving medium-to-large models in the 7B–30B parameter range, image and video generation workloads, and multi-model inference endpoints.</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon SageMaker  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now available in two additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/healthomics-tokyo-ohio/</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Mon, 20 Jul 2026 18:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS HealthOmics private workflows are now available in two additional regions, Tokyo and Ohio, enhancing global accessibility for bioinformatics.
+2. Outcome (impact):  
+Expands the reach of AWS HealthOmics, enabling more research, drug discovery, and agriculture science initiatives to meet regional compliance requirements.
+3. Where to use (use case):  
+Ideal for healthcare and life sciences organizations needing to perform genomics data analysis in regions with specific regulatory requirements.</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -27665,7 +28184,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23 06:06:26</t>
+          <t>2026-07-24 05:54:49</t>
         </is>
       </c>
     </row>
@@ -27676,7 +28195,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -27686,7 +28205,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4681</v>
+        <v>4948</v>
       </c>
     </row>
     <row r="7">
@@ -27696,7 +28215,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1656</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="8">
@@ -27706,7 +28225,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000332</v>
+        <v>0.000351</v>
       </c>
     </row>
     <row r="9">
@@ -27716,7 +28235,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00047</v>
+        <v>0.000523</v>
       </c>
     </row>
     <row r="10">
@@ -27726,7 +28245,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000803</v>
+        <v>0.000874</v>
       </c>
     </row>
     <row r="11">
@@ -27736,7 +28255,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.045417</v>
+        <v>0.046291</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F747"/>
+  <dimension ref="A1:F757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -28119,6 +28119,376 @@
       <c r="F747" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Amazon Connect now supports audio optimization for Azure Virtual Desktop and Windows 365 Cloud PC</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/06/amazon-connect/</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 23:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect now optimizes audio for calls on Azure Virtual Desktop and Windows 365 Cloud PC, enhancing agent experience.
+2. Outcome (impact):
+Improved audio quality for agents using Microsoft's cloud desktop services, leading to better customer interactions and agent satisfaction.
+3. Where to use (use case):
+Ideal for contact centers utilizing Azure Virtual Desktop or Windows 365 Cloud PC to manage customer service calls efficiently.</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Amazon MWAA now supports Apache Airflow version 2.11.2</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-mwaa-now-supports-apache-airflow-version-2-11-2</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 21:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MWAA now supports Apache Airflow 2.11.2, featuring security improvements, bug fixes, and dependency upgrades.
+2. Outcome (impact):
+   Enhanced security, stability, and performance for workflow orchestration with better task management and logging.
+3. Where to use (use case):
+   Ideal for managing complex data pipelines and workflows in a scalable and secure environment.</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow (MWAA)</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Dedicated Hosts now support host resource groups without self-managed licenses</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/ec2-dedicated-hosts-hrg/</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 Dedicated Hosts now support Host Resource Groups without requiring Self-Managed Licenses, enhancing flexibility for hardware-level isolation.
+2. Outcome (impact):
+   This update simplifies the process of creating Host Resource Groups for EC2 Dedicated Hosts, benefiting EC2 Mac Instance users and those needing hardware isolation without BYOL.
+3. Where to use (use case):
+   Ideal for EC2 Mac Instance customers and those requiring hardware-level isolation without managing licenses, as well as for general use cases needing simplified host management.</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams now supports scaling down ingest capacity with warm throughput</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/kinesis/on-demand-scale-down</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 18:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Kinesis Data Streams now allows scaling down ingest capacity with warm throughput, enabling better control over stream processing performance and cost efficiency.
+2. Outcome (impact):
+Users can now manage their stream's write throughput more effectively, ensuring optimal performance and cost savings by scaling down ingest capacity as needed.
+3. Where to use (use case):
+Ideal for applications with variable data traffic, such as real-time analytics, log processing, and IoT data ingestion, where maintaining optimal capacity is crucial.</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>AWS Lambda now publishes logs for Lambda Managed Instances capacity providers</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-lambda-managed-instances-logs/</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now logs lifecycle events for Lambda Managed Instances (LMI) capacity providers in CloudWatch Logs, enhancing visibility and troubleshooting.
+2. Outcome (impact):
+Improved monitoring, faster troubleshooting, and better optimization of EC2 instances used for Lambda functions.
+3. Where to use (use case):
+Ideal for managing high-volume, predictable workloads requiring specialized compute configurations, leveraging EC2 pricing benefits.</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Amazon SES simplifies sending emails over SMTP using Mail Manager</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ses-simplified-smtp-mail-manager</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 15:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SES now offers a simplified console experience for setting up SMTP email sending through Mail Manager, enabling quick and easy configuration.
+2. Outcome (impact):
+Developers can quickly set up SMTP email sending with minimal manual configuration, speeding up the deployment of applications that require email notifications or transactional messages.
+3. Where to use (use case):
+Ideal for teams building applications that need to send email notifications, password resets, or transactional messages and require a fast setup for production-ready SMTP configurations.</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Claude Opus 5 is now available on AWS</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/claude-opus-5-aws/</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now offers the advanced Claude Opus 5 model, enhancing coding, long-running agents, and complex professional tasks with zero data retention.
+2. Outcome (impact):
+Improved coding efficiency, reliable long-running agents, and enhanced accuracy in complex document analysis for enterprise use.
+3. Where to use (use case):
+Ideal for software development, enterprise-level document analysis, and long-running professional tasks requiring high accuracy and reliability.</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Opus 4.8, Sonnet 5, and User Activity Monitoring now available on Kiro in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/kiro-opus-sonnet-monitoring-launch-aws-govcloud-us/</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS GovCloud (US) now offers new Opus 4.8 and Sonnet 5 models in Kiro, along with enhanced user activity monitoring.
+2. Outcome (impact):
+   Improved model intelligence and cost-performance, better task management, and enhanced organizational usage visibility.
+3. Where to use (use case):
+   Ideal for government agencies needing advanced AI models and detailed user activity monitoring for compliance and efficiency.</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Kiro</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>AWS announces aws-bench, an open-source benchmark for AI agents on AWS</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-bench/</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces aws-bench, an open-source benchmark for evaluating AI agents on AWS tasks, providing a reproducible way to measure performance.
+2. Outcome (impact):
+   Enhances the ability of model providers and researchers to improve AI agent performance on AWS infrastructure through standardized testing and evaluation.
+3. Where to use (use case):
+   Ideal for AI researchers and model providers who need to test and optimize AI agents for tasks involving AWS infrastructure.</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>aws-bench</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I8ge instances are now generally available in additional AWS regions</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-i8ge-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has launched I8ge instances in Europe (London) and Canada (Central) regions, powered by AWS Graviton4 processors, offering enhanced compute and storage performance.
+2. Outcome (impact):  
+Customers can achieve up to 60% better compute performance and up to 55% better storage performance with lower latency compared to previous generations.
+3. Where to use (use case):  
+Ideal for data-intensive workloads requiring high random read/write performance and low latency, such as big data analytics, high-performance computing, and large-scale database applications.</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -28184,7 +28554,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24 05:54:49</t>
+          <t>2026-07-25 05:47:38</t>
         </is>
       </c>
     </row>
@@ -28195,7 +28565,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -28205,7 +28575,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4948</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="7">
@@ -28215,7 +28585,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1840</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="8">
@@ -28225,7 +28595,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000351</v>
+        <v>0.000258</v>
       </c>
     </row>
     <row r="9">
@@ -28235,7 +28605,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000523</v>
+        <v>0.000346</v>
       </c>
     </row>
     <row r="10">
@@ -28245,7 +28615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000874</v>
+        <v>0.000604</v>
       </c>
     </row>
     <row r="11">
@@ -28255,7 +28625,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.046291</v>
+        <v>0.046895</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F757"/>
+  <dimension ref="A1:F765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -28489,6 +28489,305 @@
       <c r="F757" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Amazon Neptune now supports tag-based access control for IAM</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-neptune-tbac/</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Neptune now supports tag-based access control (TBAC) for IAM, enabling dynamic, attribute-based access management for database clusters.
+2. Outcome (impact):
+   This feature enhances security by allowing fine-grained access control based on tags, reducing lateral access risks, and simplifying policy management for large-scale deployments.
+3. Where to use (use case):
+   Ideal for organizations managing multiple Neptune clusters, ensuring that IAM principals can only access clusters with matching tags, thereby enforcing team and project isolation.</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Amazon Neptune</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality now supports anomaly detection and writing results to the AWS Glue Data Catalog</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-glue-data-quality-catalog-anomaly-detection-write-results</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 20:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Data Quality now offers anomaly detection and results storage in the AWS Glue Data Catalog, enhancing data monitoring and quality management.
+2. Outcome (impact):
+This update enables automatic detection of data anomalies and consistent storage of evaluation results, improving data reliability and simplifying monitoring for data engineers.
+3. Where to use (use case):
+Ideal for data engineers managing large datasets in AWS, ensuring data quality and promptly identifying unexpected changes in data statistics.</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality now supports distribution statistics for data profiling</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-glue-data-quality-distribution-profiling</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 20:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Glue Data Quality now offers a Distribution Analyzer to generate frequency distribution profiles for data, aiding in identifying skewness and outliers without custom code.
+2. Outcome (impact):
+   This new feature enhances data profiling capabilities, enabling users to better understand data distributions and integrate these insights into their data quality checks and monitoring workflows.
+3. Where to use (use case):
+   Ideal for data engineers and analysts who need to identify data patterns, detect anomalies, and ensure data reliability in data pipelines, particularly when working with large datasets.</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams now supports Custom Aspect Ratio and Dynamic Resolution</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-gamelift-streams/</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 18:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GameLift Streams now offers Custom Aspect Ratio and Dynamic Resolution to enhance streaming experiences across various devices and network conditions.
+2. Outcome (impact):
+- Improved user experience with tailored resolutions.
+- Reduced visual artifacts like letterboxing and pillarboxing.
+- Smoother playback during bandwidth fluctuations.
+3. Where to use (use case):
+- Tailored streaming for mobile games with different aspect ratios.
+- Ensuring consistent quality in varying network conditions.</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>AWS Security Hub MCP App brings exposure findings into your AI-assisted workflow (Preview)</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-security-hub-mcp-app/</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces the Security Hub MCP App, a local server that integrates Security Hub findings into AI-assisted workflows, enhancing security investigations.
+2. Outcome (impact):
+   Accelerates security investigations by reducing context switching, manual triage, and providing actionable insights directly within the workflow.
+3. Where to use (use case):
+   Ideal for security teams needing to quickly assess and respond to exposure findings without leaving their AI-assisted tools.</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor adds configurable ad timeout and concurrency controls for improved ad fill and faster startup</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/mediatail-configurable-ad-timeout-and-concurrency</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 16:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental MediaTailor now allows direct configuration of ad decision server (ADS) timeouts and concurrency controls, enhancing ad fill rates and startup times.
+2. Outcome (impact):
+Improved ad delivery performance, higher ad fill rates for live events, and faster video startup times for VOD through optimized ADS settings.
+3. Where to use (use case):
+Ideal for streaming services looking to optimize ad delivery in live and VOD workflows, ensuring smoother ad integration and faster video playback.</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server now supports restoring TDE databases on Mult-AZ instances</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/rds-sql-server-supports-tde-for-maz/</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for SQL Server now supports restoring TDE-enabled databases on Multi-AZ instances, simplifying migration and recovery workflows.
+2. Outcome (impact):
+   This update allows customers to restore TDE-encrypted databases directly to Multi-AZ instances, enhancing security and high availability without needing to disable TDE or migrate to Single-AZ configurations.
+3. Where to use (use case):
+   Ideal for organizations requiring both data encryption at rest and high availability, such as financial institutions, healthcare providers, and enterprises with strict compliance requirements.</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms supports larger worker types up to 32 vCPUs for SQL</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-clean-rooms-32-vcpu-worker-types-sql</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Clean Rooms now supports larger worker types up to 32 vCPUs and 244 GB of memory for SQL analyses, enhancing performance for complex queries.
+2. Outcome (impact):
+Improves performance for complex queries on large datasets, accelerates time-to-value, and optimizes costs for customers.
+3. Where to use (use case):
+Ideal for advertisers and publishers running complex feature engineering across large datasets to train multi-touch attribution models.</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25 05:47:38</t>
+          <t>2026-07-28 05:53:24</t>
         </is>
       </c>
     </row>
@@ -28565,7 +28864,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -28575,7 +28874,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3634</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="7">
@@ -28585,7 +28884,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1220</v>
+        <v>989</v>
       </c>
     </row>
     <row r="8">
@@ -28595,7 +28894,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000258</v>
+        <v>0.000197</v>
       </c>
     </row>
     <row r="9">
@@ -28605,7 +28904,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000346</v>
+        <v>0.000281</v>
       </c>
     </row>
     <row r="10">
@@ -28615,7 +28914,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000604</v>
+        <v>0.000478</v>
       </c>
     </row>
     <row r="11">
@@ -28625,7 +28924,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.046895</v>
+        <v>0.047373</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F765"/>
+  <dimension ref="A1:F773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -28786,6 +28786,302 @@
         </is>
       </c>
       <c r="F765" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Amazon EKS Provisioned Control Plane now delivers faster pod autoscaling</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-eks-provisioned-control/</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 17:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EKS now offers faster pod autoscaling for Provisioned Control Plane clusters by increasing HPA sync concurrency.
+2. Outcome (impact):
+This enhancement reduces the time it takes for HPA-driven workloads to scale in response to increased load, improving responsiveness to demand.
+3. Where to use (use case):
+Ideal for applications requiring rapid scaling in response to fluctuating workloads, such as web servers handling variable traffic or microservices architectures.</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Second-generation AWS Outposts racks now supported in the AWS Asia Pacific (Mumbai) Region</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-outposts-asia-pacific-mumbai/</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS has expanded support for second-generation Outposts racks to the Asia Pacific (Mumbai) Region, enabling consistent hybrid experiences for organizations in India and beyond.
+2. Outcome (impact):  
+   This expansion allows customers to run low-latency on-premises workloads while managing applications from their home Region, and meet data residency requirements by processing data locally.
+3. Where to use (use case):  
+   Ideal for organizations needing low-latency access to on-premises systems, such as financial services, manufacturing, and public sector entities, to ensure data remains within specific geographic boundaries.</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>AWS Outposts</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>AWS Console Home now supports the Cost and Usage widget in the AWS European Sovereign Cloud (Germany) Region</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-console-home-cost-and-usage-eu-sovereign-cloud</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Console Home now supports the Cost and Usage widget in the AWS European Sovereign Cloud (Germany) Region, enabling cost tracking and optimization insights.
+2. Outcome (impact):
+Customers can better manage their AWS costs by visualizing month-to-date and forecasted costs, identifying savings opportunities, and understanding their spend by service.
+3. Where to use (use case):
+Ideal for organizations needing to monitor and optimize their AWS spending within the European Sovereign Cloud (Germany) Region.</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Cost and Usage Report</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>AWS DataSync Enhanced mode now supports Amazon EFS and Amazon FSx for Lustre</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-datasync-amazon-efs-fsx-lustre/</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS DataSync Enhanced mode now supports Amazon EFS and FSx for Lustre, enabling parallel data processing and removing file count limitations.
+2. Outcome (impact):
+Customers can now perform large-scale migrations, AI/ML training, HPC, genomics, and media rendering with simplified workflows and detailed metrics.
+3. Where to use (use case):
+Ideal for large-scale data migrations, machine learning training, high-performance computing, genomics processing, and media rendering.</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>AWS DataSync</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>AWS DataSync Enhanced mode adds HDFS, Azure Blob, and object storage locations with Hyper-V agent support</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-datasync-hdfs-azure-blob-hyper-v/</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS DataSync Enhanced mode now supports HDFS, Azure Blob Storage, and self-managed object storage with Hyper-V agent deployment.
+2. Outcome (impact):
+Enables secure, efficient, and high-availability data transfers to and from HDFS, Azure Blob Storage, and other object storage systems, enhancing data migration capabilities.
+3. Where to use (use case):
+Ideal for organizations needing to migrate large-scale, encrypted data from on-premises Hadoop systems to AWS, or integrate with Azure and other object storage services.</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>AWS DataSync</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Amazon S3 Tables now support the Variant data type for Apache Iceberg V3</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-s3-tables-variant-iceberg-v3/</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Tables now support the Variant data type for Apache Iceberg V3, enabling efficient handling of semi-structured data without predefined schemas.
+2. Outcome (impact):
+Faster data ingestion and improved query performance for semi-structured data, with automatic schema evolution and optimization.
+3. Where to use (use case):
+Ideal for data lakes and analytical workloads that handle large volumes of semi-structured data, such as JSON, without the need for upfront schema definitions.</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports AWS PrivateLink for the cluster OIDC endpoint</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-eks-oidc-endpoint-privatelink</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EKS now supports AWS PrivateLink for private access to the cluster OIDC endpoint, enabling IRSA setup and token validation within VPCs without internet egress.
+2. Outcome (impact):  
+This feature enhances security by allowing private access to the OIDC endpoint, reducing the need for internet egress and ensuring secure token validation within VPCs.
+3. Where to use (use case):  
+Use this feature to securely manage IAM roles for service accounts (IRSA) within a VPC, ensuring secure and private access to the OIDC endpoint for tools like eksctl and Terraform.</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Amazon Redshift Serverless now offers All Upfront pricing for 3-year Serverless Reservations</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/redshift-serverless-three-year-auri/</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift Serverless now offers a 3-year All Upfront pricing option for Serverless Reservations, providing up to 50% savings over on-demand rates.
+2. Outcome (impact):
+This new pricing option allows users to optimize their compute costs and improve cost predictability by committing to a specific number of Redshift Processing Units (RPUs) for three years.
+3. Where to use (use case):
+Ideal for organizations with predictable analytics workloads that can commit to a long-term reservation to maximize cost savings.</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Amazon Redshift Serverless</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
@@ -28853,7 +29149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28 05:53:24</t>
+          <t>2026-07-29 05:57:16</t>
         </is>
       </c>
     </row>
@@ -28874,7 +29170,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2781</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="7">
@@ -28884,7 +29180,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>989</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="8">
@@ -28894,7 +29190,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000197</v>
+        <v>0.000178</v>
       </c>
     </row>
     <row r="9">
@@ -28904,7 +29200,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000281</v>
+        <v>0.000297</v>
       </c>
     </row>
     <row r="10">
@@ -28914,7 +29210,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000478</v>
+        <v>0.000475</v>
       </c>
     </row>
     <row r="11">
@@ -28924,7 +29220,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.047373</v>
+        <v>0.047848</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F773"/>
+  <dimension ref="A1:F781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -29084,6 +29084,303 @@
       <c r="F773" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Auto Scaling now supports Instance Refresh in CloudFormation</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/ec2-auto-scaling-instance-refresh-cloudformation</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 Auto Scaling now integrates with CloudFormation to support Instance Refresh, enabling seamless in-place updates with advanced features.
+2. Outcome (impact):
+This integration allows for safer and more controlled application updates, minimizing downtime and maintaining service health.
+3. Where to use (use case):
+Ideal for web applications and services that require frequent updates with minimal disruption, ensuring high availability and reliability.</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Amazon Redshift Data API announces long polling, session management, and flexible batch execution</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-redshift-data-api-longpolling-listsession-flexiblebatchexecute/</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 20:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Redshift Data API now offers long polling, session management, and flexible batch execution to enhance efficiency and control over SQL operations.
+2. Outcome (impact):
+   These new features reduce API call frequency, improve session visibility, and allow partial batch execution success, enhancing performance and reliability for data operations.
+3. Where to use (use case):
+   Ideal for ETL pipelines, administrative scripts, and applications that benefit from reduced polling, better session tracking, and independent batch statement execution.</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>AWS Glue announces VPC support, filter pushdown, and partition support for the REST API connector</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-glue-rest-connector-filtering-partitioning-vpc</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 20:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Glue now supports VPC connections, filter pushdown, and partition support for the REST API connector, enhancing secure and efficient data ingestion from REST-based APIs.
+2. Outcome (impact):
+   Users can securely connect to private data sources, reduce data transfer costs, and speed up data ingestion without custom code, improving ETL pipeline efficiency and performance.
+3. Where to use (use case):
+   Ideal for organizations needing to ingest data from private REST API endpoints, such as proprietary systems or emerging platforms, while maintaining data security and optimizing performance.</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>AWS WAF adds pre-parse text transformations and new text transformations</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-waf/</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS WAF now offers pre-parse text transformations and new text transformations to normalize request content for better inspection.
+2. Outcome (impact):  
+These enhancements help close security gaps by ensuring AWS WAF inspects requests consistently with how applications interpret them, improving detection of malicious activities.
+3. Where to use (use case):  
+Use these transformations in web applications to sanitize and normalize input before processing, enhancing security against HTTP parameter pollution and parser differential attacks.</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>AWS WAF</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>AWS announces AWS Interconnect - multicloud connectivity with Oracle Cloud Infrastructure in GA</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-announces-AWS-interconnect-multicloud-OCI-GA/</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has launched AWS Interconnect, enabling seamless multicloud connectivity with Oracle Cloud Infrastructure (OCI) and simplifying multicloud management.
+2. Outcome (impact):  
+AWS Interconnect simplifies the process of connecting workloads across different cloud providers, reducing complexity and management overhead for customers adopting multicloud strategies.
+3. Where to use (use case):  
+Ideal for organizations utilizing multicloud environments to ensure reliable, scalable, and resilient connections between AWS and OCI, enhancing interoperability and deployment flexibility.</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Service Name: AWS Interconnect  
+Category: Networking</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now automatically finds example agent evaluations for tailored coaching</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-connect-customer-example-evaluations-for-agent-coaching/</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now automatically provides relevant agent evaluation examples for managers to deliver tailored coaching feedback, enhancing coaching effectiveness and efficiency.
+2. Outcome (impact):
+Managers can deliver more actionable and evidence-backed coaching to agents, leading to faster performance improvements and reduced time spent on searching for relevant examples.
+3. Where to use (use case):
+This feature is ideal for customer service managers who need to provide effective coaching to their agents based on real performance data.</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Amazon EFS now supports cross-account Replication in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-efs-cross-account-replication-aws-gov-cloud-us</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EFS now supports cross-account replication in AWS GovCloud (US), enabling data synchronization between accounts.
+2. Outcome (impact):  
+Enhances business continuity, disaster recovery, and compliance by automatically keeping file system replicas up-to-date across accounts.
+3. Where to use (use case):  
+Ideal for organizations using multiple AWS accounts to manage applications and data securely and reliably.</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Amazon EFS</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center extends multi-Region support to Identity Center directory</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-iam-identity-center-extends-multi-region-support-to-identity-center-directory</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IAM Identity Center now supports multi-Region replication for Identity Center directory, enhancing resilience and user access across regions.
+2. Outcome (impact):
+This feature improves the resilience of user access to AWS accounts by allowing automatic replication of identities and entitlements to additional regions, ensuring continued access during disruptions in the primary region.
+3. Where to use (use case):
+Use this feature to deploy AWS applications in regions that align with business needs, such as data residency requirements and user proximity, ensuring seamless access and administration.</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -29149,7 +29446,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29 05:57:16</t>
+          <t>2026-07-30 05:47:58</t>
         </is>
       </c>
     </row>
@@ -29170,7 +29467,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2501</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="7">
@@ -29180,7 +29477,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1047</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8">
@@ -29190,7 +29487,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000178</v>
+        <v>0.000205</v>
       </c>
     </row>
     <row r="9">
@@ -29200,7 +29497,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000297</v>
+        <v>0.000274</v>
       </c>
     </row>
     <row r="10">
@@ -29210,7 +29507,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000475</v>
+        <v>0.00048</v>
       </c>
     </row>
     <row r="11">
@@ -29220,7 +29517,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.047848</v>
+        <v>0.048328</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F781"/>
+  <dimension ref="A1:F795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -29381,6 +29381,529 @@
       <c r="F781" t="inlineStr">
         <is>
           <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio brings richer Git version control to all project tools</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-unified-studio-git/</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 22:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now offers comprehensive Git version control across all project tools, enhancing collaboration and version management.
+2. Outcome (impact):
+   This update provides consistent source control across all project tools, including Notebooks, allowing teams to manage their code and data more effectively and resolve conflicts without leaving the studio.
+3. Where to use (use case):
+   Ideal for data scientists, ML engineers, and developers who need robust version control for their projects within SageMaker Studio, ensuring better collaboration and project management.</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect now supports BGP route visibility on Virtual Interfaces</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-direct-connect-bgp-visibility/</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 20:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Direct Connect now offers BGP route visibility on Virtual Interfaces, enabling administrators to monitor and troubleshoot routing between AWS and on-premises networks.
+2. Outcome (impact):  
+Network administrators can now effectively troubleshoot routing issues, verify route propagation, and monitor hybrid network connectivity, leading to improved network performance and reliability.
+3. Where to use (use case):  
+Ideal for managing complex multi-region architectures, validating BGP policy configurations, and diagnosing unexpected traffic patterns in hybrid cloud environments.</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Amazon Redshift RG large and 12xlarge instances now available on the trailing track</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-redshift-rg-large-12xlarge-trailing-track</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 20:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now offers Graviton-based RG instances on the trailing track, enhancing stability and performance for production workloads.
+2. Outcome (impact):
+Customers can achieve up to 2.4x faster query performance at 30% lower price per vCPU, with the added benefit of stability on the trailing track.
+3. Where to use (use case):
+Ideal for production environments requiring stable, high-performance analytics with cost efficiency.</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>IAM Policy Simulator moves to the IAM console and adds additional capabilities</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/iam-policy-simulator-iam-console/</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 17:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+IAM Policy Simulator is now integrated into the IAM console, enhancing its capabilities to test SCPs and model complex scenarios.
+2. Outcome (impact):
+This update streamlines policy testing, improves detection of over-permissive access, and aids in validating guardrails with better confidence.
+3. Where to use (use case):
+Use it to test and validate IAM policies, SCPs, and simulate "what if" scenarios before deploying them in production.</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>IAM</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock announces up to 80% lower prices for OpenAI GPT‑5.6 models</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/openai-gpt-terra-luna-pricing-bedrock/</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 16:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock is reducing prices for GPT-5.6 Luna and Terra models by up to 80%, effective July 30, 2026, to lower costs and expand application use.
+2. Outcome (impact):
+Customers will benefit from significantly lower costs, enabling them to scale their applications, process larger workloads, and reduce the cost per completed task.
+3. Where to use (use case):
+Ideal for content processing, classification, customer service automation, routine implementation tasks, and everyday production workloads requiring sophisticated reasoning.</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>AWS announces general availability of Policy-Based Routing on AWS Transit Gateway</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-transit-gateway-policy-based-routing/</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 15:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transit Gateway now supports Policy-Based Routing (PBR), enabling granular control over traffic forwarding based on multiple packet attributes.
+2. Outcome (impact):  
+PBR simplifies traffic steering and workload isolation, reducing complexity and operational overhead by eliminating the need for multi-VPC architectures.
+3. Where to use (use case):  
+Use PBR to steer sensitive workloads through inspection appliances, route application traffic based on source/port/protocol, and isolate production from development environments.</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>AWS Transit Gateway</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Amazon MSK Express brokers now delivers Apache Kafka data to Amazon S3</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-msk-express-brokers-delivers-to-amazon-s3</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 14:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MSK Express brokers now deliver Apache Kafka data directly to Amazon S3, offering a fully managed, cost-effective, and scalable solution.
+2. Outcome (impact):
+   Reduces operational complexity and costs by up to 60% compared to self-managed alternatives, while ensuring high-throughput and reliable data delivery.
+3. Where to use (use case):
+   Use cases include log archival, compliance retention, Kafka replay, and training AI/ML models.</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Amazon MSK Express</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Amazon MSK Express brokers now deliver data to streaming tables for Apache Iceberg</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-msk-streaming-tables-for-apache-iceberg</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 14:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MSK Express brokers now deliver data to Apache Iceberg streaming tables on Amazon S3, reducing costs and improving query performance.
+2. Outcome (impact):
+- Reduces data ingestion and delivery costs by up to 60%.
+- Reduces downstream query costs by up to 30%.
+- Eliminates the small-file problem and concurrent writer conflicts.
+3. Where to use (use case):
+Real-time data ingestion for use cases like fraud detection and personalization, unified with near real-time analytics.</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Amazon MSK</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Grok 4.3 from xAI is now available on Amazon Bedrock in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/grok-4-3-bedrock-govcloud/</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+xAI's Grok 4.3 model is now available on Amazon Bedrock in AWS GovCloud (US-West), offering reasoning-first capabilities for enterprise workloads.
+2. Outcome (impact):  
+Enhanced choice for building reliable and cost-effective generative AI applications in secure environments.
+3. Where to use (use case):  
+Ideal for enterprise applications like customer support, web development, case law research, and financial document Q&amp;A.</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Gemma 4 models are now available on Amazon Bedrock in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/gemma-4-bedrock-govcloud/</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has launched the Gemma 4 family of open-weight models from Google DeepMind on Amazon Bedrock in AWS GovCloud (US-West), enabling advanced generative AI applications.
+2. Outcome (impact):  
+Customers can now build sophisticated generative AI applications with improved reasoning, multimodal capabilities, and cost-effective performance using open-source models.
+3. Where to use (use case):  
+Ideal for developing AI applications in reasoning, multimodal understanding, agentic workflows, and software engineering, particularly in environments requiring high security and compliance.</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>AWS Managed Microsoft AD now supports Standard to Enterprise Edition upgrade</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-microsoft-ad-edition-upgrade/</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Managed Microsoft AD now supports in-place upgrades from Standard to Enterprise Edition, preserving existing configurations and integrations.
+2. Outcome (impact):
+   Organizations can scale their directory service to support up to 500,000 objects without the need for migration or reconfiguration.
+3. Where to use (use case):
+   Ideal for businesses that have outgrown the 5,000 user limit of Standard Edition and need enhanced scalability and features.</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>AWS Directory Service</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service now supports OpenSearch version 3.7</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-opensearch-service/</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 02:30:15 GMT</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Service now supports OpenSearch version 3.7, enhancing vector search performance, search relevance, and Query Insights.
+2. Outcome (impact):
+- Improved vector search performance and reduced storage/memory usage with 1-bit scalar quantization.
+- Faster vector retrieval using doc values.
+- Enhanced search relevance with new evaluation metrics and hybrid search optimization.
+- Better query analysis and optimization with Query Insights.
+3. Where to use (use case):
+Use cases include applications requiring efficient vector search, improved search accuracy, and better query performance analytics, such as recommendation systems, semantic search engines, and data analytics platforms.</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>AWS HealthLake identifies and links duplicate patient, provider, and organization records (Preview)</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-healthlake/</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthLake now offers a preview feature to automatically identify and link duplicate patient, provider, and organization records using resource matching.
+2. Outcome (impact):
+Healthcare organizations can build accurate longitudinal patient records and reliable population health datasets without the need for specialized master data management tools, reducing costs and improving data integrity.
+3. Where to use (use case):
+Healthcare providers and organizations can use this feature to manage and consolidate patient data, ensuring that each patient's information is accurately linked and reducing errors and redundancies in patient care and billing.</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>AWS HealthLake</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service now supports node lifecycle actions</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-pcs-node-lifecycle-actions/</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 12:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Parallel Computing Service now supports node lifecycle actions to automate custom scripts at various lifecycle stages.
+2. Outcome (impact):  
+Enhances automation and efficiency in preparing compute nodes for HPC workloads by allowing custom scripts to run automatically at defined points in a node's lifecycle.
+3. Where to use (use case):  
+Ideal for HPC environments where compute nodes need to be configured with specific software, storage, or monitoring setups before they start processing tasks.</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service (PCS)</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -29446,7 +29969,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30 05:47:58</t>
+          <t>2026-07-31 06:18:36</t>
         </is>
       </c>
     </row>
@@ -29457,7 +29980,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -29467,7 +29990,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2891</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="7">
@@ -29477,7 +30000,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>966</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="8">
@@ -29487,7 +30010,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000205</v>
+        <v>0.000385</v>
       </c>
     </row>
     <row r="9">
@@ -29497,7 +30020,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000274</v>
+        <v>0.000508</v>
       </c>
     </row>
     <row r="10">
@@ -29507,7 +30030,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00048</v>
+        <v>0.000894</v>
       </c>
     </row>
     <row r="11">
@@ -29517,7 +30040,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.048328</v>
+        <v>0.049222</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F795"/>
+  <dimension ref="A1:F802"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -29902,6 +29902,265 @@
         </is>
       </c>
       <c r="F795" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL adds multi-Region cluster support in four more Regions</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-aurora-dsql-adds-multi-region-clusters-four-more-regions/</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora DSQL now supports multi-Region clusters in four new regions, enhancing availability and consistency across multiple locations.
+2. Outcome (impact):
+Improved database resilience and availability, allowing businesses to maintain operations even if one region fails.
+3. Where to use (use case):
+Ideal for global applications requiring high availability and strong consistency across multiple geographic locations.</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now offers Reserved Instances for R8i and M8i instances</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-rds-oracle-r8i-m8i/</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for Oracle now offers Reserved Instances for R8i and M8i instances, providing up to 53% cost savings and enhanced performance.
+2. Outcome (impact):  
+Customers can achieve significant cost savings and improved performance for their Oracle databases by using R8i and M8i instances with Reserved Instances.
+3. Where to use (use case):  
+Ideal for production workloads requiring high performance and cost efficiency, such as enterprise applications, data warehousing, and large-scale database management.</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>AWS Lambda now supports Java 8, 11, and 17 on Amazon Linux 2023</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-lambda-java-amazon-linux/</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now supports Java 8, 11, and 17 runtimes on Amazon Linux 2023, allowing migration from AL2 without Java version upgrades.
+2. Outcome (impact):
+Customers can migrate their Lambda functions to AL2023 without needing to upgrade their Java versions immediately, ensuring continued support and security.
+3. Where to use (use case):
+Ideal for running serverless applications and functions that require Java 8, 11, or 17 on a modern operating system, ensuring compliance with AWS support timelines.</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch announces managed Prometheus collectors</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/cloudwatch-managed-collectors/</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 13:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch now offers fully managed Prometheus collectors to monitor AWS services without managing agents, delivering metrics in OpenTelemetry format.
+2. Outcome (impact):
+   This integration simplifies the process of collecting Prometheus metrics, reduces operational overhead, and enables unified monitoring, alarming, and dashboarding across AWS services.
+3. Where to use (use case):
+   Ideal for monitoring Amazon EKS, EC2, ECS, MSK, and OpenSearch Service workloads, allowing users to leverage Prometheus metrics within CloudWatch seamlessly.</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>AWS CodeDeploy now available in five additional AWS regions</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-codedeploy-five-additional-regions</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 10:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CodeDeploy is now available in five new regions, enhancing deployment automation and reducing latency for global users.
+2. Outcome (impact):
+This expansion enables developers and DevOps engineers in new regions to benefit from faster, more reliable application deployments with lower latency and improved data residency compliance.
+3. Where to use (use case):
+Use AWS CodeDeploy for automating deployments to Amazon EC2, on-premises servers, AWS Lambda, and Amazon ECS services, ensuring rapid feature releases with minimal downtime.</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>AWS CodeDeploy</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C7i-flex instances now available in Europe (Milan) region</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-c7i-flex-instances-MXP-region/</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 00:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched C7i-flex instances in Europe (Milan) with custom 4th Gen Intel Xeon Scalable processors, offering up to 15% better performance and 19% better price-performance.
+2. Outcome (Impact):
+   Users in Europe can now leverage enhanced compute performance and cost efficiency for a variety of compute-intensive workloads.
+3. Where to Use (Use Case):
+   Ideal for web and application servers, databases, caches, Apache Kafka, Elasticsearch, and other compute-intensive applications.</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Amazon Elastic Compute Cloud (Amazon EC2)</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C7i instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-ec2-c7i-instances-mxp-yyc-region/</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 00:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C7i instances with custom 4th Gen Intel Xeon processors are now available in Europe (Milan) and Canada West (Calgary), offering enhanced performance and price-performance.
+2. Outcome (Impact):
+Users can leverage up to 15% better performance and price-performance for compute-intensive workloads, improving efficiency and cost-effectiveness.
+3. Where to Use (Use Case):
+Ideal for workloads such as batch processing, distributed analytics, ad-serving, and video encoding.</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
         <is>
           <t>Compute</t>
         </is>
@@ -29969,7 +30228,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31 06:18:36</t>
+          <t>2026-08-01 06:04:50</t>
         </is>
       </c>
     </row>
@@ -29980,7 +30239,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -29990,7 +30249,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5425</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="7">
@@ -30000,7 +30259,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1790</v>
+        <v>903</v>
       </c>
     </row>
     <row r="8">
@@ -30010,7 +30269,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000385</v>
+        <v>0.000186</v>
       </c>
     </row>
     <row r="9">
@@ -30020,7 +30279,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000508</v>
+        <v>0.000256</v>
       </c>
     </row>
     <row r="10">
@@ -30030,7 +30289,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000894</v>
+        <v>0.000443</v>
       </c>
     </row>
     <row r="11">
@@ -30040,7 +30299,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.049222</v>
+        <v>0.049665</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F802"/>
+  <dimension ref="A1:F803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -30163,6 +30163,43 @@
       <c r="F802" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Amazon Location Service adds Search Nearby support for GrabMaps in Southeast Asia</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-location-service-search-nearby-grabmaps</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Location Service now supports proximity-based point of interest discovery with GrabMaps data in Southeast Asia, enabling local discovery applications.
+2. Outcome (impact):
+   Developers can leverage hyperlocal data to create more relevant and efficient local discovery, delivery, and mobility applications in Southeast Asia.
+3. Where to use (use case):
+   Ideal for delivery platforms, ride-hailing apps, and travel services that need to find nearby points of interest such as fuel stations, hospitals, or restaurants.</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Amazon Location Service</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -30228,7 +30265,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01 06:04:50</t>
+          <t>2026-08-02 06:07:35</t>
         </is>
       </c>
     </row>
@@ -30239,7 +30276,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -30249,7 +30286,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2623</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
@@ -30259,7 +30296,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>903</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8">
@@ -30269,7 +30306,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000186</v>
+        <v>2.5e-05</v>
       </c>
     </row>
     <row r="9">
@@ -30279,7 +30316,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000256</v>
+        <v>3.6e-05</v>
       </c>
     </row>
     <row r="10">
@@ -30289,7 +30326,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000443</v>
+        <v>6.1e-05</v>
       </c>
     </row>
     <row r="11">
@@ -30299,7 +30336,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.049665</v>
+        <v>0.049726</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F803"/>
+  <dimension ref="A1:F817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -30200,6 +30200,524 @@
       <c r="F803" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>AWS Transform continuous modernization is now generally available</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/7/aws-transform-continuous-general-available</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform continuous modernization is now generally available, helping teams analyze and remediate technical debt across source code repositories.
+2. Outcome (impact):  
+Enables engineering teams to efficiently manage technical debt, improve code quality, and enhance overall software modernization efforts.
+3. Where to use (use case):  
+Ideal for software development teams looking to streamline the process of identifying and fixing technical debt in their codebases.</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-5.6 Sol, Terra, and Luna now support 1 million token context windows on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/gpt-sol-terra-luna-long-context-bedrock</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   GPT-5.6 Sol, Terra, and Luna now support a 1 million token context window on Amazon Bedrock, enhancing model accuracy and coherence for large-scale text processing.
+2. Outcome (impact):
+   Enables processing of entire codebases, lengthy documents, and full conversation histories in a single request, reducing chunking and information loss.
+3. Where to use (use case):
+   Ideal for code reviews, legal document analysis, and maintaining full conversation history in multi-step workflows.</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams now supports sharing streams with stream URLs</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-gamelift-streams/</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GameLift Streams now allows sharing of playable game streams via URLs, enabling easy access without AWS accounts or software installations.
+2. Outcome (impact):
+   This feature simplifies the sharing of game streams, making it easier for users to join sessions directly from web browsers, potentially increasing user engagement and accessibility.
+3. Where to use (use case):
+   Ideal for game developers and streamers who want to share game sessions with a broader audience without requiring them to set up AWS accounts or install any software.</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>AWS Resilience Hub now provides recommended resilience tests</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-resilience-hub/</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:02:58 GMT</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Resilience Hub now offers automated resilience tests to validate service recovery from failure scenarios.
+2. Outcome (impact):  
+Teams can ensure their services meet recovery objectives and are prepared for disruptions, improving overall system resilience.
+3. Where to use (use case):  
+Ideal for platform engineering and site reliability teams to test and validate the resilience of their services against known failure scenarios.</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>AWS Resilience Hub</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>AWS Organizations now provides maximum account quota visibility in Service Quotas</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-organizations/</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Organizations now allows customers to view and manage their maximum account quota directly in Service Quotas, enhancing visibility and proactive planning.
+2. Outcome (impact):
+   Customers can now easily monitor their account quota utilization and request increases without needing to contact AWS Support, leading to more efficient account management and growth planning.
+3. Where to use (use case):
+   Ideal for organizations managing multiple AWS accounts within AWS Organizations, helping them to proactively manage their account limits and scale effectively.</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Service Quotas</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>AWS Lambda Provisioned Mode for Amazon SQS event source mappings now supports up to 10,000 event pollers</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-Lambda-provisioned-sqs-esm-max-pollers/</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now supports up to 10,000 event pollers for SQS event source mappings, enabling higher concurrency and performance for event-driven applications.
+2. Outcome (impact):
+This increase allows for up to 100,000 concurrent invocations per ESM, facilitating the development of highly responsive, scalable applications with stringent performance needs.
+3. Where to use (use case):
+Ideal for mission-critical applications like real-time order processing, financial transaction pipelines, IoT telemetry ingestion, and large-scale fan-out workloads.</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I7i instances now available in Asia Pacific (Thailand) and Israel (Tel Aviv) Regions</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-i7i-instances-in-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched high-performance I7i instances in Thailand and Tel Aviv, offering enhanced compute and storage capabilities.
+2. Outcome (impact):
+Improved compute performance by up to 23% and better price performance by over 10% compared to previous I4i instances, along with significant storage enhancements.
+3. Where to use (use case):
+Ideal for I/O intensive and latency-sensitive workloads such as databases, real-time analytics, and applications requiring high random IOPS performance.</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI serverless model customization now supports full fine-tuning</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-sagemaker-fft</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker now supports full fine-tuning for over 25 open-source models, enabling deeper adaptation for domain-specific tasks.
+2. Outcome (impact):
+   Users can achieve more thorough model customization, leading to better performance in specialized tasks and deeper learning of domain-specific patterns.
+3. Where to use (use case):
+   Ideal for industries requiring specialized model capabilities, such as healthcare, finance, and custom enterprise solutions.</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>AWS Transform for full-stack Windows modernization now supports offline schema transformation to Aurora PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/7/aws-transform-windows-sql-schema-aurora</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Transform now supports offline schema transformation for modernizing Microsoft SQL Server databases to Amazon Aurora PostgreSQL without needing a live connection.
+2. Outcome (impact):  
+This feature allows enterprises to modernize legacy.NET applications and their SQL Server databases more efficiently, reducing downtime and complexity.
+3. Where to use (use case):  
+Ideal for enterprises looking to migrate their SQL Server databases to Aurora PostgreSQL while maintaining application functionality during the transformation process.</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>AWS Database Migration Service (DMS)</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>AWS WAF now supports Miggo Security managed rule groups for emerging threats and AI/ML application protection</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-waf-miggo-managed-rule-groups</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS WAF now integrates Miggo Security's managed rule groups for enhanced protection against emerging threats and AI/ML application vulnerabilities.
+2. Outcome (impact):
+AWS WAF customers can now benefit from continuously updated protection against actively exploited vulnerabilities and threats specific to AI/ML applications without the need for custom rule maintenance.
+3. Where to use (use case):
+Ideal for organizations utilizing web applications, especially those with AI/ML components, to safeguard against the latest threats and vulnerabilities.</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>AWS WAF</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Amazon ECR now supports image layers up to 200 GB</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ecr-image-layers/</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECR now supports image layers up to 200 GB, simplifying the storage of large datasets within container images.
+2. Outcome (impact):
+   This update eliminates the need to split large data across multiple layers, reducing complexity for users embedding large language models, genomics datasets, or large binary dependencies.
+3. Where to use (use case):
+   Embedding large language models, bundling genomics datasets, or packaging large binary dependencies directly into container images.</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Amazon ECR</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>AWS Config now supports 15 new resource types</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-config-new-resource-types</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Config now supports 15 new resource types, enhancing coverage across Amazon Bedrock, OpenSearch Serverless, and SageMaker services.
+2. Outcome (impact):
+This update enables more comprehensive monitoring, assessment, auditing, and remediation of AWS resources, improving overall environment management.
+3. Where to use (use case):
+Use AWS Config to monitor and manage resources in services like Amazon Bedrock, OpenSearch Serverless, and SageMaker, ensuring compliance and optimal performance.</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>AWS Config</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports Teradata Vantage</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/amazon-sagemaker-unified-teradata</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 20:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio now integrates Teradata Vantage, allowing seamless querying and analysis of enterprise data alongside other data sources.
+2. Outcome (impact):
+   This integration enables deeper insights by correlating Teradata enterprise data with real-time datasets, streamlining workflows, and enhancing data analysis without switching tools.
+3. Where to use (use case):
+   Ideal for data engineers and analysts needing to combine historical enterprise data with real-time datasets for improved customer behavior analysis, financial performance tracking, and operational trend insights.</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Amazon Web Services now introduces Context Ontology Accelerator</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-context--ontology-accelarator-generally-available</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Fri, 31 Jul 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces Context Ontology Accelerator, an open-source tool that helps organizations create a machine-readable business model for AI agents to make accurate and auditable decisions.
+2. Outcome (impact):
+Reduces manual ontology authoring time from months to days, enabling faster deployment of AI agents with explainable and auditable decision-making capabilities.
+3. Where to use (use case):
+Ideal for organizations looking to implement AI agents that require a reliable and consistent context to make informed decisions, such as in finance, healthcare, and customer service.</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Context Ontology Accelerator</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -30265,7 +30783,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02 06:07:35</t>
+          <t>2026-08-04 05:54:05</t>
         </is>
       </c>
     </row>
@@ -30276,7 +30794,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -30286,7 +30804,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>350</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="7">
@@ -30296,7 +30814,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="8">
@@ -30306,7 +30824,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5e-05</v>
+        <v>0.000372</v>
       </c>
     </row>
     <row r="9">
@@ -30316,7 +30834,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6e-05</v>
+        <v>0.000492</v>
       </c>
     </row>
     <row r="10">
@@ -30326,7 +30844,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.1e-05</v>
+        <v>0.000864</v>
       </c>
     </row>
     <row r="11">
@@ -30336,7 +30854,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.049726</v>
+        <v>0.05059</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F817"/>
+  <dimension ref="A1:F830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -30718,6 +30718,488 @@
       <c r="F817" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>[Preview Announcement] Re-introducing Forward Proxy as AWS Network Firewall Functionality</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-network-firewall-forward-proxy-preview/</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 22:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>1. Short Summary  
+AWS Network Firewall now integrates explicit forward proxy functionality, allowing centralized security controls with existing filtering capabilities.
+2. Outcome (impact)  
+This integration simplifies security management by enabling a unified policy for both proxy and transparent firewall functionalities, enhancing data protection and threat defense.
+3. Where to use (use case)  
+Ideal for organizations needing centralized security controls to prevent data exfiltration and malware injection across their network traffic.</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Network Firewall</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now lets you export cases to CSV from the agent workspace</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-export-cases/</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now allows agents to export cases to CSV directly from the workspace, enhancing data sharing capabilities.
+2. Outcome (impact):
+This feature improves efficiency and collaboration by enabling agents to easily share case data with internal teams and external stakeholders.
+3. Where to use (use case):
+Use this feature for better data management and collaboration in customer service operations, legal reviews, vendor communications, and business partnerships.</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock launches Web Search for OpenAI GPT models</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-bedrock-web/</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Bedrock has launched Web Search, enabling GPT models to access current web knowledge securely within AWS without data egress.
+2. Outcome (Impact):
+   Simplifies grounding GPT models with web data, reduces complexity and compliance concerns by eliminating third-party dependencies.
+3. Where to Use (Use Case):
+   Ideal for applications requiring real-time, accurate web-grounded responses from GPT models, such as customer support, content generation, and research tools.</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Run interactive workloads on Amazon EMR on EC2 with Spark Connect</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-emr-ec2-spark-connect/</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 20:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EMR on EC2 now supports interactive Apache Spark sessions with Spark Connect, enabling seamless development and debugging from managed notebooks and IDEs.
+2. Outcome (impact):  
+Data engineers and data scientists can develop and debug Spark applications interactively, improving productivity and debugging efficiency.
+3. Where to use (use case):  
+Ideal for ad hoc data exploration, iterative debugging, and incremental PySpark job development before deploying to production.</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Amazon EMR</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>AWS Security Hub Extended adds supply chain security as its 10th category</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-security-hub-extended-adds-supply-chain-security</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 19:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Security Hub Extended now includes Supply Chain Security, adding Chainguard and Socket as partners to ensure open-source libraries are secure.
+2. Outcome (impact):
+Developers can detect and block malicious dependencies in their applications, enhancing overall security posture with streamlined activation and pay-as-you-go pricing.
+3. Where to use (use case):
+Ideal for organizations that extensively use open-source libraries and need to ensure these packages are free from malicious code before integration into applications.</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>AWS Security Hub</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8g instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-c8g-instances-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8g instances, powered by AWS Graviton4 processors, are now available in four new regions, offering up to 30% better performance.
+2. Outcome (impact):
+   Users can leverage enhanced compute performance and energy efficiency for a variety of compute-intensive workloads across additional regions.
+3. Where to use (use case):
+   Ideal for high performance computing (HPC), batch processing, gaming, video encoding, scientific modeling, distributed analytics, CPU-based machine learning inference, and ad serving.</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>AWS Application and Network Load Balancers now support RFC 9151 compliant security policies</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-application-network/</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS ALB and NLB now support RFC 9151 compliant TLS security policies for CNSA 1.0 suite.
+2. Outcome (impact):  
+Customers can now meet CNSA 1.0 TLS security requirements, ensuring secure communications while maintaining compatibility with non-CNSA clients.
+3. Where to use (use case):  
+Ideal for organizations needing to comply with CNSA 1.0 requirements, such as government agencies and enterprises in regulated industries.</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Elastic Load Balancing</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors is now available in the AWS European Sovereign Cloud (Germany) Region</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-s3-vectors-european-sovereign-cloud-germany/</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 18:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Vectors is now available in the AWS European Sovereign Cloud (Germany) Region, offering purpose-built vector storage for AI applications at a large scale.
+2. Outcome (impact):
+This launch enables customers in Germany to leverage advanced AI capabilities with scalable, durable, and available vector storage, enhancing AI agent, inference, and semantic search applications.
+3. Where to use (use case):
+Ideal for AI agents, inference, Retrieval Augmented Generation (RAG), and semantic search applications requiring efficient vector storage at a billion-vector scale.</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Amazon S3 Vectors</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports capacity planning in 15 or 30 minute intervals</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-customer-interval-capacity-plan</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers capacity planning in 15 or 30-minute intervals, enhancing workforce management accuracy.
+2. Outcome (impact):
+Improves planning accuracy, reduces over- and under-staffing, and enhances service levels and operational efficiency.
+3. Where to use (use case):
+Useful for contact centers managing Voice, Chat, Task, and Email channels to align staffing with demand fluctuations.</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Amazon EC2 I8g instances now available in AWS Europe (Paris), Asia Pacific (Jakarta) regions</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-i8g-instances-aws-paris-jakarta-regions/</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched Amazon EC2 Storage Optimized I8g instances in Europe (Paris) and Asia Pacific (Jakarta) regions, powered by AWS Graviton4 processors for enhanced storage performance.
+2. Outcome (impact):
+These instances offer up to 65% better storage performance, 50% lower I/O latency, and 60% lower I/O latency variability, making them ideal for I/O intensive workloads.
+3. Where to use (use case):
+Ideal for transactional databases (MySQL, PostgreSQL), NoSQL solutions (MongoDB, Aerospike), real-time analytics (Apache Spark), and AI LLM pre-processing.</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server now support BYOM in additional commercial regions</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/rds-sql-server-supports-byom-in-additional-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for SQL Server now supports Bring Your Own Media (BYOM) in 10 new regions, allowing customers to use their existing SQL Server licenses with Software Assurance.
+2. Outcome (impact):  
+Customers can reduce costs by leveraging their existing Microsoft SQL Server licenses while using Amazon RDS as a managed service, with simplified license tracking via AWS License Manager.
+3. Where to use (use case):  
+Ideal for enterprises looking to migrate to AWS without incurring additional licensing costs, particularly those with existing SQL Server deployments covered by Software Assurance.</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server supports Developer Edition in additional AWS regions</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/rds-sql-server-supports-developer-edition-in-additional-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for SQL Server now offers Developer Edition in 13 new regions, enabling developers to build and test applications closer to their users.
+2. Outcome (impact):
+This expansion allows developers to reduce latency and simplify workflows by deploying applications in regions closer to their end users.
+3. Where to use (use case):
+Ideal for developers and testers who need a free, fully-featured SQL Server environment to build, test, and deploy applications in multiple regions.</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>RDS SQL Server now supports publishing SQL Server Audit logs to CloudWatch</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/rds-sqlserver-publish-sql-audit-to-cw/</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for SQL Server now supports publishing SQL Server Audit logs to CloudWatch, enabling real-time analysis and retention.
+2. Outcome (impact):  
+This feature enhances security and compliance by allowing real-time monitoring and analysis of SQL Server events, improving auditing and troubleshooting capabilities.
+3. Where to use (use case):  
+Use this feature for enhanced security auditing, compliance monitoring, and real-time log analysis of SQL Server databases hosted on Amazon RDS.</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon RDS  
+Category: Database</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -30783,7 +31265,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04 05:54:05</t>
+          <t>2026-08-05 05:51:33</t>
         </is>
       </c>
     </row>
@@ -30794,7 +31276,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -30804,7 +31286,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5242</v>
+        <v>4686</v>
       </c>
     </row>
     <row r="7">
@@ -30814,7 +31296,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1733</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="8">
@@ -30824,7 +31306,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000372</v>
+        <v>0.000333</v>
       </c>
     </row>
     <row r="9">
@@ -30834,7 +31316,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000492</v>
+        <v>0.000461</v>
       </c>
     </row>
     <row r="10">
@@ -30844,7 +31326,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000864</v>
+        <v>0.000794</v>
       </c>
     </row>
     <row r="11">
@@ -30854,7 +31336,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05059</v>
+        <v>0.051384</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F830"/>
+  <dimension ref="A1:F838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -31200,6 +31200,302 @@
       <c r="F830" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>AWS Lambda announces scalable network bandwidth up to 3,000 Mbps for functions outside a VPC</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-lambda-network-bandwidth/</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 21:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now offers scalable network bandwidth up to 3,000 Mbps for functions outside a VPC, enhancing data transfer speeds for latency-sensitive workloads.
+2. Outcome (impact):
+This update reduces function execution times and per-invocation costs, improving overall performance and efficiency for data-intensive applications.
+3. Where to use (use case):
+Ideal for latency-sensitive data processing workloads requiring large data transfers, such as real-time analytics, data ingestion, and high-throughput ETL processes.</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces (for Apache Cassandra) is now available in the Canada West (Calgary) Region (ca-west-1)</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2025/11/amazon-keyspaces-apache-cassandra-canada-west/</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 20:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Keyspaces (for Apache Cassandra) is now available in the Canada West (Calgary) Region, enabling low-latency, scalable applications with data residency.
+2. Outcome (impact):
+Customers in Canada can now build Cassandra-compatible applications with reduced latency and ensure data stays within the region, meeting local data residency requirements.
+3. Where to use (use case):
+Ideal for organizations needing to deploy low-latency, scalable applications in Canada, such as financial services, healthcare, and e-commerce.</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Amazon Keyspaces</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality makes ETL anomaly detection free and improves anomaly predictions</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-glue-data-quality-anomaly-detection-free</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 18:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Data Quality now offers free anomaly detection with improved accuracy and a new observation mode, reducing false alerts and enhancing data quality monitoring.
+2. Outcome (impact):
+Data teams can now focus on genuine anomalies with reduced noise, leading to more efficient data quality monitoring and fewer distractions from false alerts.
+3. Where to use (use case):
+Ideal for exploratory data analysis, datasets with irregular patterns, and varying data arrival intervals, especially in interactive environments like notebooks.</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Quality</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>AWS Marketplace adds AI Insights so buyers can understand pricing before they buy</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-marketplace-ai-insights/</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Marketplace now offers AI Insights to simplify product pricing understanding before purchase, providing clear explanations directly on the listing.
+2. Outcome (impact):  
+Users can make more informed purchasing decisions by easily understanding product pricing without navigating multiple sources, enhancing transparency and efficiency.
+3. Where to use (use case):  
+Ideal for businesses and individuals looking to deploy AWS services, enabling them to evaluate costs accurately and confidently before committing to a purchase.</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB now supports real-time vector search</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-dynamodb-vector-search</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces real-time vector search for Amazon DynamoDB, enabling efficient indexing and searching of vectors at scale with high accuracy and low latency.
+2. Outcome (impact):
+   This feature allows for scalable, high-performance vector searches, improving applications like semantic retrieval, product similarity, and recommendation systems.
+3. Where to use (use case):
+   Ideal for AI agents' memory retrieval, product similarity search, personalized advertising, retrieval augmented generation, and recommendation systems.</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center makes management of AWS account access optional for new organization instances</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-identity-center-accounts-optional/</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS IAM Identity Center now allows optional management of AWS account access for new organization instances, enabling separate control over application and account access.
+2. Outcome (impact):
+   Organizations can now selectively manage access to AWS applications without managing access to AWS accounts, reducing complexity and potential security risks.
+3. Where to use (use case):
+   Ideal for organizations that want to streamline access management for AWS applications while maintaining separate control over AWS account access.</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Amazon Aurora serverless now scales faster to support agentic AI and other bursty workloads</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aurora-serverless-instant-12-acu-scaling</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora serverless now scales up to 12 ACUs in a second and up to 256 ACUs as needed, automatically scaling down to zero when idle.
+2. Outcome (impact):
+This enhancement allows for faster and more efficient scaling to meet bursty workloads, particularly for agentic AI applications, reducing costs by only charging for used capacity.
+3. Where to use (use case):
+Ideal for agentic AI applications with unpredictable traffic patterns, ensuring optimal performance during peak times and cost savings during idle periods.</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now supports task-level timeout for WDL workflows</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-healthomics-wdl-task-level-timeout/</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS HealthOmics now supports task-level timeout for WDL workflows, allowing users to set maximum execution durations for individual tasks.
+2. Outcome (impact):
+This feature helps control costs and enables automated error recovery by preventing tasks from running indefinitely.
+3. Where to use (use case):
+Use case: Managing bioinformatics workflows in healthcare and life sciences to ensure efficient resource usage and cost management.</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -31265,7 +31561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05 05:51:33</t>
+          <t>2026-08-06 05:55:31</t>
         </is>
       </c>
     </row>
@@ -31276,7 +31572,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -31286,7 +31582,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4686</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="7">
@@ -31296,7 +31592,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1623</v>
+        <v>977</v>
       </c>
     </row>
     <row r="8">
@@ -31306,7 +31602,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000333</v>
+        <v>0.000197</v>
       </c>
     </row>
     <row r="9">
@@ -31316,7 +31612,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000461</v>
+        <v>0.000277</v>
       </c>
     </row>
     <row r="10">
@@ -31326,7 +31622,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000794</v>
+        <v>0.000474</v>
       </c>
     </row>
     <row r="11">
@@ -31336,7 +31632,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.051384</v>
+        <v>0.051858</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F838"/>
+  <dimension ref="A1:F859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -31496,6 +31496,787 @@
       <c r="F838" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Amazon ECS now supports fractional GPU scheduling with Amazon EC2 G6f instances</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ecs-fractional-gpu/</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now supports fractional GPU scheduling with G6f instances, allowing for GPU partitions as small as one-eighth of an L4 Tensor Core GPU.
+2. Outcome (impact):
+This feature provides flexibility to right-size GPU resources for various workloads, reducing infrastructure costs and improving resource utilization.
+3. Where to use (use case):
+Ideal for small-model AI inference, model experimentation, graphics rendering, and other tasks that do not require a full GPU.</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>AWS Lambda console extends console-to-IDE integration to Kiro and Cursor</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-lambda-ide-kiro-cursor/</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Lambda now supports console-to-IDE integration with Kiro and Cursor, enabling seamless transitions between cloud and local development.
+2. Outcome (impact):  
+Developers can start from the Lambda console and easily transition to Kiro or Cursor for local development, preserving existing code and configurations, and simplifying IaC practices.
+3. Where to use (use case):  
+Ideal for serverless developers who prefer Kiro or Cursor IDEs, facilitating easier conversion to AWS SAM templates and enhancing CI/CD pipeline integration.</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Amazon EC2 G7 instances are now available in the AWS Europe (Spain) Region</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-g7-available-spain</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 G7 instances with advanced GPUs are now available in the AWS Europe (Spain) Region, offering enhanced AI inference and graphics performance.
+2. Outcome (impact):
+Customers can leverage improved AI inference performance (up to 4.6x) and graphics performance (up to 2.1x) for tasks like language translation, video analysis, and real-time graphics rendering.
+3. Where to use (use case):
+Ideal for deploying AI models, accelerating graphics workloads, video transcoding, spatial computing, and data analytics tasks such as recommender systems and real-time data pipelines.</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>AgentCore runtime instances are now generally available</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-bedrock-agentcore-runtime-instances-generally-available/</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces runtime instances for Amazon Bedrock AgentCore, enabling agents to run on custom EC2 instances with simplified infrastructure management.
+2. Outcome (impact):
+Teams can deploy resource-intensive or specialized-hardware agents securely at scale without managing infrastructure, enhancing flexibility and efficiency.
+3. Where to use (use case):
+Ideal for sustained, resource-intensive, or specialized-hardware agents, allowing for diverse EC2 instance types and long-running sessions.</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache now supports Graviton4-based M8g, R8g, and C8gn nodes</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-elasticache-graviton4-m8g-r8g-c8gn/</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ElastiCache introduces Graviton4-based M8g, R8g, and C8gn nodes, offering improved performance and cost-efficiency.
+2. Outcome (impact):
+   Users can achieve up to 47% higher throughput, 43% lower P99 latency, and 31% better price-performance with these new nodes.
+3. Where to use (use case):
+   Ideal for high-performance caching, real-time analytics, and network-intensive workloads requiring scalable and cost-effective solutions.</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Amazon ElastiCache</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>AWS Glue Schema Registry is now available in ten more AWS regions</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-gsr-10-more-regions</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Schema Registry is now available in ten additional regions, enabling centralized management of streaming data schemas for improved data quality and reduced application failures.
+2. Outcome (impact):
+- Eliminates the need for data validation logic and cross-team coordination.
+- Improves streaming data quality.
+- Reduces downstream application failures.
+3. Where to use (use case):
+- Data streaming systems requiring schema management.
+- Applications using Apache Kafka, Kinesis Data Streams, Apache Flink, and AWS Lambda.</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>AWS Glue Schema Registry</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>AWS Transform for migrations automates post-launch actions</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-transform-for-migrations-automates-post-launch-actions</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Transform now automates post-launch actions in migration workflows, reducing manual configuration and errors.
+2. Outcome (impact):
+   Teams can migrate more servers with less manual effort, ensuring consistent and reliable post-launch configurations.
+3. Where to use (use case):
+   Ideal for multi-account migrations where consistent post-launch actions are required across various target accounts.</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>AWS Systems Manager (SSM)</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>AWS Security Agent now supports email-based MFA for penetration testing</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-security-agent-mfa/</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Security Agent now supports email-based MFA for automated penetration testing, allowing interception of MFA emails.
+2. Outcome (impact):  
+Expands penetration testing capabilities for applications using email-based MFA, enhancing security coverage.
+3. Where to use (use case):  
+Ideal for security teams conducting automated penetration tests on web applications that require email-based multi-factor authentication.</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>AWS Security Agent</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Amazon RDS now provides visibility into storage volume initialization status</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-storage-volume-initialization-visibility</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS now offers real-time visibility into the initialization status of storage volumes created from snapshots, ensuring readiness for performance-sensitive workloads.
+2. Outcome (impact):
+Users can now accurately time their database workloads to align with storage initialization completion, reducing latency and improving performance.
+3. Where to use (use case):
+Ideal for scenarios requiring immediate access to fully provisioned performance post-restore, such as high-availability databases and latency-sensitive applications.</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces now publishes enhanced observability metrics</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-workspaces-observability-metrics</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon WorkSpaces now offers enhanced observability metrics in CloudWatch for better performance and session health monitoring.
+2. Outcome (impact):
+   IT administrators can proactively identify and troubleshoot issues impacting end-user experience, leading to reduced mean time to resolution.
+3. Where to use (use case):
+   Monitoring and maintaining the performance and health of virtual desktop workloads in enterprise environments.</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications now publishes enhanced observability metrics</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-workspaces-applications-observability-metrics</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon WorkSpaces Applications now offers enhanced observability metrics in CloudWatch, providing deeper insights into application streaming workloads.
+2. Outcome (impact):
+IT administrators can proactively identify and troubleshoot performance and session health issues, leading to improved end-user experience and reduced mean time to resolution.
+3. Where to use (use case):
+Monitoring and managing the performance and health of application streaming workloads in enterprise environments.</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>AWS Marketplace now lets sellers configure net payment terms on private offers</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-marketplace-net-payment-terms-for-private-offers</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Marketplace now allows sellers to set custom net payment terms (Net 30, Net 45, Net 60, Net 90) on private offers, providing buyers with clearer payment expectations.
+2. Outcome (impact):
+   This feature enhances cash flow predictability for sellers and offers buyers more favorable payment terms, improving negotiation flexibility and financial planning.
+3. Where to use (use case):
+   Ideal for businesses engaging in private offers on AWS Marketplace, allowing both buyers and sellers to align payment terms with their financial strategies.</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Amazon MSK now delivers Kafka Authorizer Logs to customers</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-msk-kafka-authorizer-logs/</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon MSK now offers Authorizer Log Delivery for Provisioned clusters, providing detailed access logs at no extra cost.
+2. Outcome (impact):  
+Enhanced visibility into user and application access, improved security compliance, and easier identification of authorization issues.
+3. Where to use (use case):  
+Use case: Monitoring and securing Kafka clusters to ensure compliance with organizational security policies and to quickly identify unauthorized access attempts.</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Amazon MSK</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>AWS Backup for Amazon S3 now supports direct access to backup data</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-backup-amazon-s3-direct-access/</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   AWS Backup for Amazon S3 now allows direct read-only access to backup data via S3 Access Points without restoring.
+2. Outcome (impact)
+   This feature enables faster data validation, compliance auditing, and forensic investigations while keeping backup data secure.
+3. Where to use (use case)
+   Ideal for targeted file recovery, compliance checks, and real-time data validation without disrupting backup integrity.</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Amazon SES now helps identify automated open and click events in event notifications</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ses-automated-email-interactions/</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SES now identifies automated email interactions via an `isBotEvent` field in event notifications, helping distinguish between human and automated recipients.
+2. Outcome (impact):
+   This feature enhances email campaign analysis by providing insights into the proportion of human versus automated engagement, improving email marketing strategies.
+3. Where to use (use case):
+   Useful for marketers and email service providers to refine their audience targeting and engagement metrics by filtering out automated interactions.</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>AWS Backup extends logically air-gapped vault support for Amazon Neptune to three additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-backup-logically-air-gapped-vault-neptune-regions/</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+AWS Backup now supports logically air-gapped vaults for Amazon Neptune backups in three new regions: Asia Pacific (Melbourne), Europe (Spain), and Europe (Zurich).
+2. Outcome (impact)
+This expansion enhances data security and compliance by allowing immutable, encrypted backups with multi-party approval, reducing recovery time and meeting disaster recovery needs.
+3. Where to use (use case)
+Ideal for organizations requiring stringent data protection and compliance in geographically diverse locations, ensuring data is stored securely and can be easily recovered.</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Amazon Quick supports multi-dataset analytical capabiity</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-quick/</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 06:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon QuickSight now supports multi-dataset topics, allowing users to model relationships across multiple datasets in a single topic for dashboards and natural language queries.
+2. Outcome (impact):
+This feature simplifies data preparation, reduces manual effort, and enhances efficiency by automatically handling joins at runtime, thereby minimizing the need for pre-joining datasets.
+3. Where to use (use case):
+Ideal for data analysts and business users who need to build comprehensive dashboards and perform natural language queries across multiple datasets without extensive data preparation.</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Amazon QuickSight</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Announcing temporal policies and rate limiting in Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/temporal-policies-agentcore/</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore introduces temporal policies for stateful authorization and rate limiting to manage AI traffic efficiently.
+2. Outcome (impact):
+These new controls enhance security by ensuring actions are contextually safe and manage traffic to maintain service availability and fairness.
+3. Where to use (use case):
+Ideal for applications requiring secure, context-aware authorization and efficient traffic management for AI-driven services.</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8g instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-m8g-instances-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 00:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 M8g instances, powered by AWS Graviton4 processors, are now available in additional regions with enhanced performance and efficiency.
+2. Outcome (impact):
+   Users can achieve up to 30% better performance and improved energy efficiency for general-purpose workloads across various regions.
+3. Where to use (use case):
+   Ideal for application servers, microservices, gaming servers, midsize data stores, and caching fleets.</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>AWS Glue Data Catalog now supports  metadata exports to S3 Tables (Preview)</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-glue-data-catalog-s3-tables/</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue Data Catalog now allows exporting metadata to S3 Tables in Apache Iceberg format, enhancing querying and analysis capabilities.
+2. Outcome (impact):
+This feature enables users to query and analyze metadata using standard SQL, facilitating better data auditing, historical analysis, and integration with other AWS services.
+3. Where to use (use case):
+Use this feature to audit metadata changes, perform historical analysis, and integrate catalog metadata with other data sources for comprehensive data governance and analysis.</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Studio notebooks now support G7 instance types</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/03/g7-new-launch-sagemaker-studio-notebooks/</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker Studio notebooks now support G7 instances, offering enhanced AI inference performance with up to 8 GPUs and 700 Gbps of network bandwidth.
+2. Outcome (impact):  
+Users can leverage G7 instances for significantly improved AI inference, graphics, and data analytics workloads, achieving up to 4.6x better performance than previous-generation G6 instances.
+3. Where to use (use case):  
+Ideal for deploying conversational AI assistants, scaling video streaming, and running large-scale data processing pipelines.</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon SageMaker  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -31561,7 +32342,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06 05:55:31</t>
+          <t>2026-08-07 04:59:14</t>
         </is>
       </c>
     </row>
@@ -31572,7 +32353,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -31582,7 +32363,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2775</v>
+        <v>7813</v>
       </c>
     </row>
     <row r="7">
@@ -31592,7 +32373,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>977</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="8">
@@ -31602,7 +32383,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000197</v>
+        <v>0.000555</v>
       </c>
     </row>
     <row r="9">
@@ -31612,7 +32393,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000277</v>
+        <v>0.000722</v>
       </c>
     </row>
     <row r="10">
@@ -31622,7 +32403,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000474</v>
+        <v>0.001277</v>
       </c>
     </row>
     <row r="11">
@@ -31632,7 +32413,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.051858</v>
+        <v>0.053135</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F859"/>
+  <dimension ref="A1:F870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -32277,6 +32277,410 @@
       <c r="F859" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8i and R8i-Flex instances are now available in Europe (Milan) region</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-r8i-r8i-flex/</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched R8i and R8i-flex instances in Europe (Milan), powered by custom Intel Xeon 6 processors, offering enhanced performance and price-performance.
+2. Outcome (impact):
+These instances provide up to 15% better price-performance, 2.5x more memory bandwidth, and up to 60% faster performance for specific workloads compared to previous generations.
+3. Where to use (use case):
+Ideal for memory-intensive workloads such as PostgreSQL databases, NGINX web applications, AI deep learning models, and mission-critical SAP workloads.</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB now supports backup and restore</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/timestream-influxdb-backup-restore/</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Timestream for InfluxDB now supports on-demand and automated backups and restores, available via console, CLI, and API.
+2. Outcome (impact):
+Enhanced data protection and control over backup strategies, reducing risk during migrations or configuration changes.
+3. Where to use (use case):
+Ideal for managing data integrity and protection in time-series databases, especially during risky operations.</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Amazon Cognito now available as a skill in the Agent Toolkit for AWS</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-auth-agent-skill/</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:00:48 GMT</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Cognito is now a core skill in the Agent Toolkit for AWS, enabling faster implementation of secure user authentication flows.
+2. Outcome (impact):
+Developers can quickly set up, configure, and secure Amazon Cognito with best-practice workflows, improving efficiency and security in user and service authentication.
+3. Where to use (use case):
+Use this skill to manage user pools, app clients, OAuth 2.0 flows, and identity pools for web and mobile applications, enhancing the security of sign-in processes.</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Amazon Cognito</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>AWS IAM Identity Center supports one-click multi-Region option for new organization instances</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-iam-identity-center-supports-one-click-multi-region-option-new-organization-instances</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IAM Identity Center now allows users to enable multi-Region support with a single click when creating a new organization instance.
+2. Outcome (impact):
+This update simplifies the process of setting up multi-Region support, reducing complexity and time required to configure multi-Region access for IAM Identity Center.
+3. Where to use (use case):
+Ideal for organizations requiring high availability and disaster recovery for their identity and access management across multiple AWS Regions.</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>IAM Identity Center</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore adds memory, policy, and harness in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/agentcore-memory-policy-harness-govcloud/</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore enhances its platform in AWS GovCloud (US-West) with memory, policy, and harness features to support context-aware agents in regulated environments.
+2. Outcome (impact):
+Teams can now build and scale intelligent, personalized agents faster with improved security and compliance, reducing the complexity of managing memory infrastructure and policy controls.
+3. Where to use (use case):
+Regulated industries such as healthcare, finance, and government sectors can leverage these capabilities to create compliant, context-aware agents for customer interactions and internal processes.</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers now supports 21 new EC2 instance types</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/gamelift-ec2-instance-expansion/</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GameLift Servers now supports 21 new EC2 instance types, enhancing flexibility and performance for game developers.
+2. Outcome (impact):
+Game developers gain access to the latest compute-optimized and general-purpose instances, allowing for better performance, cost optimization, and engine compatibility.
+3. Where to use (use case):
+Ideal for running CPU-intensive multiplayer game server logic and scaling general-purpose fleets cost-effectively.</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service announces additional upgrade runway for existing domains and support dates for additional versions</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-opensearch-service-additional-upgrade-runway-support-dates</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Service extends support for legacy versions until November 2027 and announces support dates for additional versions.
+2. Outcome (impact):
+Customers gain more time to upgrade to newer versions, ensuring continued security and OS patches. New support dates are provided for additional versions, with varying Extended Support periods.
+3. Where to use (use case):
+Use case for organizations needing more time to migrate from legacy versions of Elasticsearch and OpenSearch to newer versions while maintaining security and OS patch coverage.</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service is now in scope for FedRAMP, SOC, ISO, CSA STAR, and PCI</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-pcs-august/</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 04:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>1. Short Summary: AWS Parallel Computing Service (PCS) now meets FedRAMP, SOC, ISO, CSA STAR, and PCI compliance, enabling secure HPC workloads.
+2. Outcome (impact): Federal agencies, public sector organizations, and regulated enterprises can confidently use PCS for sensitive and mission-critical HPC workloads.
+3. Where to use (use case): Use PCS for running high-performance computing (HPC) workloads in regulated environments such as government, finance, and healthcare.</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>AWS Parallel Computing Service (PCS)</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>AWS WAF now supports a Salt Security managed rule group for API and MCP threat detection</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-waf-salt-security-managed-rules/</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 21:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS WAF now integrates with Salt Security's managed rule group for enhanced API and MCP threat detection, available via AWS Marketplace.
+2. Outcome (impact):
+This integration provides AWS WAF customers with robust protection against API-focused attacks and MCP endpoint threats, without the need for custom rule maintenance.
+3. Where to use (use case):
+Ideal for organizations that need to secure APIs and MCP endpoints from common and complex attacks, such as credential brute force and SSRF, while also managing traffic from AI agents.</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>AWS WAF</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch UI now supports Network Access Control</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/opensearch-ui-network-access-control</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 18:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon OpenSearch Service now offers network access controls for its UI, enhancing security by restricting access to approved networks.
+2. Outcome (impact):  
+This update improves security by allowing administrators to control access to OpenSearch UI applications more effectively, reducing the risk of unauthorized access.
+3. Where to use (use case):  
+Ideal for organizations that require stringent network access controls to protect sensitive data and comply with security policies.</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer adds one-click drill-down on real-time metrics dashboards</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-drill-down-metrics/</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now offers one-click drill-down on real-time metrics dashboards, enabling supervisors to quickly analyze and respond to performance issues.
+2. Outcome (impact):
+Supervisors can efficiently identify and address performance bottlenecks, such as spikes in queue wait times, by quickly accessing detailed agent activity data and reassigning tasks to reduce backlogs.
+3. Where to use (use case):
+Ideal for contact center supervisors managing real-time performance metrics to ensure optimal agent utilization and customer service levels.</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -32342,7 +32746,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07 04:59:14</t>
+          <t>2026-08-08 04:14:08</t>
         </is>
       </c>
     </row>
@@ -32353,7 +32757,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -32363,7 +32767,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7813</v>
+        <v>4332</v>
       </c>
     </row>
     <row r="7">
@@ -32373,7 +32777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2544</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="8">
@@ -32383,7 +32787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000555</v>
+        <v>0.000308</v>
       </c>
     </row>
     <row r="9">
@@ -32393,7 +32797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000722</v>
+        <v>0.000391</v>
       </c>
     </row>
     <row r="10">
@@ -32403,7 +32807,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001277</v>
+        <v>0.000699</v>
       </c>
     </row>
     <row r="11">
@@ -32413,7 +32817,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.053135</v>
+        <v>0.053834</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F870"/>
+  <dimension ref="A1:F871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -32681,6 +32681,43 @@
       <c r="F870" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Amazon VPC IPAM now supports BGP route protection monitoring and delegated RPKI for BYOIP prefixes</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-vpc-ipam-bgp-rpki-byoip/</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS VPC IPAM now offers BGP route protection monitoring and delegated RPKI for BYOIP prefixes, enhancing security and automation.
+2. Outcome (impact):
+   Network administrators can centrally monitor and manage BGP route protection and RPKI for BYOIP prefixes, reducing manual effort and improving route security.
+3. Where to use (use case):
+   Ideal for organizations managing multiple AWS accounts and regions, needing centralized monitoring and automated management of BYOIP prefixes.</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Amazon VPC IPAM</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Networking</t>
         </is>
       </c>
     </row>
@@ -32746,7 +32783,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08 04:14:08</t>
+          <t>2026-08-09 04:21:56</t>
         </is>
       </c>
     </row>
@@ -32757,7 +32794,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -32767,7 +32804,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4332</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7">
@@ -32777,7 +32814,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1378</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
@@ -32787,7 +32824,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000308</v>
+        <v>3.2e-05</v>
       </c>
     </row>
     <row r="9">
@@ -32797,7 +32834,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000391</v>
+        <v>3.4e-05</v>
       </c>
     </row>
     <row r="10">
@@ -32807,7 +32844,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000699</v>
+        <v>6.7e-05</v>
       </c>
     </row>
     <row r="11">
@@ -32817,7 +32854,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.053834</v>
+        <v>0.053901</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F871"/>
+  <dimension ref="A1:F879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -32718,6 +32718,304 @@
       <c r="F871" t="inlineStr">
         <is>
           <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>FLUX.2-small-decoder and gemma-4-12B-it models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/flux.2-small-decoder-gemma-4-12B-it-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS SageMaker JumpStart now offers FLUX.2-small-decoder for faster image decoding and gemma-4-12B-it for efficient multimodal understanding.
+2. Outcome (impact):
+Customers can deploy high-performance, scalable AI solutions with improved efficiency and reduced resource consumption for image generation and multimodal tasks.
+3. Where to use (use case):
+Ideal for production-grade image generation workloads and enterprise-level multimodal AI applications requiring efficient resource usage.</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>langcache-embed-v3-small, Mellum2-12B-A2.5B-Thinking, and LightOnOCR-2-1B models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/langcache-embed-v3-small-mellum2-12B-A2.5B-thinking-lightOnOCR-2-1B-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS SageMaker JumpStart now offers three new models: langcache-embed-v3-small for semantic caching, Mellum2-12B-A2.5B-Thinking for code reasoning, and LightOnOCR-2-1B for document OCR.
+2. Outcome (impact):
+These models enhance AWS's AI capabilities by providing specialized tools for semantic optimization, code-focused reasoning, and efficient document-to-text conversion, improving performance and scalability for various AI applications.
+3. Where to use (use case):
+- langcache-embed-v3-small: Ideal for applications requiring semantic search and caching in large language models to reduce redundant calls.
+- Mellum2-12B-A2.5B-Thinking: Suitable for code generation, debugging, and multi-step reasoning tasks, especially in environments needing high-throughput and low-latency responses.
+- LightOnOCR-2-1B: Perfect for applications needing accurate, multilingual document-to-text conversion from PDFs, scans, and images.</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7i instances now available in AWS South America (São Paulo) region</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-high-memory-u7i-south-america</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 High Memory U7in-24TB instances are now available in the South America (São Paulo) region, offering 24 TiB of DDR5 memory and 896 vCPUs.
+2. Outcome (impact):
+Customers can now leverage these powerful instances to handle large-scale transaction processing and in-memory databases in the South America region.
+3. Where to use (use case):
+Ideal for mission-critical applications such as SAP HANA, Oracle, and SQL Server databases requiring high memory and processing power.</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>GLM-5.2 FP8, NVIDIA-Nemotron-Nano-12B-v2 and GLM-OCR models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/glm-5.2-fp8-nemotron-nano-12b-v2-glm-ocr-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 23:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS SageMaker JumpStart now offers GLM-5.2 FP8, Nemotron-Nano-12B-v2, and GLM-OCR models for enhanced AI capabilities.
+2. Outcome (impact):  
+Customers can leverage advanced AI models for long-horizon engineering tasks, efficient reasoning, and comprehensive document understanding.
+3. Where to use (use case):  
+Ideal for software development, enterprise applications requiring high accuracy and efficiency, and large-scale document processing.</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams Now Offers Service-managed Shader Caching</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/Amazon-GameLift-Streams-Shader-Caching/</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GameLift Streams now automatically manages shader cache capture and distribution, reducing loading times and visual stuttering without requiring application changes.
+2. Outcome (impact):
+   Improved game performance and player experience by minimizing loading times and visual stuttering through efficient shader caching.
+3. Where to use (use case):
+   Ideal for game developers using Amazon GameLift to stream games, particularly those running on Linux (Ubuntu 22.04), Proton, and Windows Server 2022 runtimes.</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Streams</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Amazon EC2 introduces application status checks</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-application-status-checks</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 17:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 introduces application status checks to monitor and alert on application-level issues, complementing existing system status checks.
+2. Outcome (impact):
+   This new feature allows customers to detect and respond to application issues directly within EC2, reducing the need for custom monitoring solutions and improving operational efficiency.
+3. Where to use (use case):
+   Application status checks are ideal for web servers, Docker containers, and any application running on EC2 instances where monitoring application health is critical.</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Serverless now supports up to 10,000 collections per collection group</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-opensearch-serverless-supports-10000-collections-per-collection-group/</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon OpenSearch Serverless now supports up to 10,000 collections per collection group, up from 1,500, enhancing scalability and cost efficiency.
+2. Outcome (impact):
+This increase allows for better cost management and improved compute utilization, particularly for multi-tenant applications, by consolidating more collections under a shared compute pool.
+3. Where to use (use case):
+Ideal for multi-tenant applications that require a collection per tenant, enabling cost savings and efficient resource management without compromising on security and access controls.</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Serverless</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery now preserves UEFI boot mode for Linux servers</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-drs-linux-uefi</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elastic Disaster Recovery now automatically preserves UEFI boot mode for Linux servers during recovery, eliminating post-recovery configuration.
+2. Outcome (impact):
+Ensures recovered Linux instances match the source environment's UEFI boot mode, reducing post-recovery steps and potential issues.
+3. Where to use (use case):
+Ideal for organizations needing precise replication of their Linux server environments, especially those with applications dependent on UEFI boot behavior.</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -32783,7 +33081,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09 04:21:56</t>
+          <t>2026-08-11 04:24:31</t>
         </is>
       </c>
     </row>
@@ -32794,7 +33092,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -32804,7 +33102,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>455</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="7">
@@ -32814,7 +33112,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="8">
@@ -32824,7 +33122,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2e-05</v>
+        <v>0.000227</v>
       </c>
     </row>
     <row r="9">
@@ -32834,7 +33132,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4e-05</v>
+        <v>0.000323</v>
       </c>
     </row>
     <row r="10">
@@ -32844,7 +33142,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.7e-05</v>
+        <v>0.0005509999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -32854,7 +33152,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.053901</v>
+        <v>0.054452</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F879"/>
+  <dimension ref="A1:F891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -33016,6 +33016,453 @@
       <c r="F879" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8a instances are now available in Canada (Central) region</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-r8a-instances-canada-central/</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 22:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 R8a instances, powered by 5th Gen AMD EPYC processors, are now available in Canada (Central) Region, offering enhanced performance and memory bandwidth.
+2. Outcome (Impact):
+   These instances deliver up to 30% higher performance and 45% more memory bandwidth compared to R7a instances, making them ideal for high-performance, memory-intensive workloads.
+3. Where to Use (Use Case):
+   Suitable for SQL and NoSQL databases, in-memory caches, real-time big data analytics, EDA applications, and business-critical applications requiring high throughput and low latency.</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock expands IAM principal cost allocation to the bedrock-mantle endpoint</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-bedrock-expands-iam-principal-cost-allocation-bedrock-mantle/</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 20:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock now supports cost allocation by IAM principal for model inference requests via the bedrock-mantle endpoint, extending previous capabilities.
+2. Outcome (impact):  
+Customers can better attribute and manage inference costs across different teams, projects, and applications using IAM principal tags.
+3. Where to use (use case):  
+This feature is useful for organizations aiming to track and manage costs associated with generative AI applications in a more granular and accountable manner.</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon Bedrock  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>LocateAnything-3B, Qwen-AgentWorld-35B-A3B, and Qwen3.5-122B-A10B models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/locateAnything-3B-qwen-agentworld-35B-A3B-qwen3.5-122B-A10B-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS SageMaker JumpStart now offers LocateAnything-3B, Qwen-AgentWorld-35B-A3B, and Qwen3.5-122B-A10B models, enhancing AI capabilities for visual grounding, agent environment simulation, and multimodal reasoning.
+2. Outcome (impact):
+These models enable AWS customers to deploy high-performance, scalable AI solutions tailored for specific enterprise challenges, improving efficiency and accuracy in various AI applications.
+3. Where to use (use case):
+- LocateAnything-3B: For applications requiring precise object localization and visual grounding.
+- Qwen-AgentWorld-35B-A3B: For simulating complex agent environments and interactions across multiple domains.
+- Qwen3.5-122B-A10B: For large-scale multimodal reasoning tasks with high efficiency and minimal latency.</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>NVIDIA Nemotron 3.5 Lightning model is now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/nvidia-nemotron-3.5-lightning-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   NVIDIA's Nemotron 3.5 Lightning model is now available on Amazon SageMaker JumpStart, offering faster task execution and higher throughput for enterprise automation.
+2. Outcome (Impact):
+   AWS customers can leverage this advanced model for persistent agents, achieving up to 4x the throughput and 30% faster task completion, enhancing productivity and efficiency in various enterprise applications.
+3. Where to Use (Use Case):
+   Ideal for personal assistants, financial document processing, cybersecurity triage, and telecom operations, among other high-throughput automation tasks.</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>AWS Glue adds one-click access to SageMaker Unified Studio from the AWS console</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/smus-glue-access</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Glue now offers one-click access to SageMaker Unified Studio, streamlining data querying and pipeline building.
+2. Outcome (impact):  
+This integration allows data engineers and analysts to seamlessly transition from data cataloging in Glue to data analysis and AI model development in SageMaker Unified Studio, enhancing productivity.
+3. Where to use (use case):  
+Ideal for data engineers and analysts who need to query data, run data quality checks, and build data pipelines using both AWS Glue and SageMaker.</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager adds managed external secrets support for Jenkins and SonarQube</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/secrets-manager-integration-jenkins-sonarqube/</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 14:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Secrets Manager now supports automatic rotation of Jenkins API Tokens and SonarQube Tokens, enhancing security and simplifying credential management.
+2. Outcome (impact):
+This update allows for seamless and secure rotation of third-party credentials directly from the AWS console, reducing the need for custom code and minimizing downtime in CI/CD pipelines.
+3. Where to use (use case):
+Ideal for organizations using Jenkins and SonarQube that require secure, automated management of API tokens to maintain robust security practices in their CI/CD processes.</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer launches performance dashboard for Cases</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-cases-dashboard/</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer has introduced a performance dashboard for cases, enabling managers to monitor and analyze case metrics and SLA adherence.
+2. Outcome (impact):
+Managers can effectively track case performance, identify areas for improvement, and ensure SLA compliance by leveraging detailed metrics and trend analysis.
+3. Where to use (use case):
+This dashboard is ideal for customer support and service teams to enhance operational efficiency and improve customer satisfaction by managing case resolutions more effectively.</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms supports exporting privacy-enhanced analysis logs for SQL</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-clean-rooms-export-analysis-log-sql</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Clean Rooms now allows exporting privacy-enhanced analysis logs for SQL queries, enhancing optimization and troubleshooting capabilities.
+2. Outcome (impact):
+   Users can better optimize and troubleshoot SQL queries by analyzing Spark execution details, leading to faster resolution times and cost savings.
+3. Where to use (use case):
+   Ideal for data analysts and data scientists working within AWS Clean Rooms collaborations to improve query performance and efficiency.</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MariaDB now supports MariaDB 12.3</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-mariadb-1232-available/</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for MariaDB now supports MariaDB 12.3, featuring Oracle TO_DATE() compatibility, IS JSON predicate, and improved query performance.
+2. Outcome (impact):
+   Enhanced compatibility with Oracle, native JSON validation, and better query performance, facilitating easier migration and optimized database operations.
+3. Where to use (use case):
+   Ideal for applications migrating from Oracle to MariaDB, those requiring native JSON validation, and systems needing improved query performance.</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>AWS Identity and Access Management streamlines assignment of IAM roles to workforce users with account access manager</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-iam-aam/</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS IAM now offers an Account Access Manager to simplify assigning IAM roles to workforce users, combining centralized federation with IAM role flexibility.
+2. Outcome (Impact):  
+This feature enhances the efficiency of managing user permissions across multiple AWS accounts, reducing administrative overhead and improving security through centralized role assignments.
+3. Where to Use (Use Case):  
+Ideal for organizations with multiple AWS accounts that need to manage user access centrally while leveraging the granular control of IAM roles.</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>AWS Identity and Access Management (IAM)</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Alarms now supports wall clock evaluation windows</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/cloudwatch-alarms-wallclock-evaluation</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch now supports wall clock evaluation windows for metric alarms, allowing alignment with fixed calendar boundaries to avoid false alarms.
+2. Outcome (impact):
+   This feature helps prevent false alarms by evaluating each calendar day independently, ensuring more accurate monitoring for scheduled or business-aligned workloads.
+3. Where to use (use case):
+   Ideal for scenarios such as daily backups, business-hour monitoring, and any scheduled tasks where alignment with fixed calendar times is critical.</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now provides schedule adherence metrics on dashboards</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/schedule-adherence-metrics/</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now offers schedule adherence metrics on dashboards, providing supervisors with insights into agent schedule compliance.
+2. Outcome (impact):
+   Supervisors can identify adherence patterns and address specific issues like late returns from breaks, leading to improved agent performance and coaching.
+3. Where to use (use case):
+   Ideal for contact center supervisors to monitor and enhance agent performance by analyzing adherence to scheduled activities.</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -33081,7 +33528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11 04:24:31</t>
+          <t>2026-08-12 04:52:20</t>
         </is>
       </c>
     </row>
@@ -33092,7 +33539,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -33102,7 +33549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3204</v>
+        <v>4367</v>
       </c>
     </row>
     <row r="7">
@@ -33112,7 +33559,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1139</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="8">
@@ -33122,7 +33569,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000227</v>
+        <v>0.00031</v>
       </c>
     </row>
     <row r="9">
@@ -33132,7 +33579,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000323</v>
+        <v>0.000451</v>
       </c>
     </row>
     <row r="10">
@@ -33142,7 +33589,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0005509999999999999</v>
+        <v>0.000761</v>
       </c>
     </row>
     <row r="11">
@@ -33152,7 +33599,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.054452</v>
+        <v>0.055213</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F891"/>
+  <dimension ref="A1:F899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -33463,6 +33463,302 @@
       <c r="F891" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>AWS Global View now offers an interactive map view for AWS Regions and AWS Local Zones</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-global-view-map-view/</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>1. Short Summary  
+AWS Global View now features an interactive map view for AWS Regions and Local Zones, enhancing visualization of global infrastructure.
+2. Outcome (impact)  
+This update simplifies infrastructure planning by allowing users to easily visualize enabled and available AWS locations on an interactive map.
+3. Where to use (use case)  
+Ideal for infrastructure planning and decision-making, helping organizations understand their global AWS footprint more effectively.</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>AWS Global View</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>AWS IAM now provides role manager to set up IAM roles automatically</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-iam-role-manager</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS IAM's role manager automates the setup of IAM roles for supported services, simplifying initial configuration and ensuring necessary permissions.
+2. Outcome (impact):  
+This feature reduces manual setup time, minimizes configuration errors, and ensures that services have the appropriate permissions from the start, enhancing security and operational efficiency.
+3. Where to use (use case):  
+Use role manager when deploying AWS services like AWS Lambda or Amazon EventBridge to automatically configure the required IAM roles, allowing for quicker service onboarding and easier management of permissions.</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>AWS IAM</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports advanced Kubernetes control plane configuration parameters</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-eks-control-plane-configuration-parameters</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EKS now allows advanced configuration of Kubernetes control plane parameters to optimize resource utilization and performance.
+2. Outcome (impact):  
+Cluster administrators can fine-tune Kubernetes components for better resource management, improved performance, and enhanced control over pod placement and autoscaling.
+3. Where to use (use case):  
+Ideal for managing workloads in environments requiring optimized resource usage, such as high-density deployments or cost-sensitive applications.</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Amazon Quick adds deny by default for custom permissions</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/whats-new/2026/08/amazon-quick-deny-by-default-permissions/</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 17:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick now includes a "deny by default" setting for custom permissions, automatically restricting new AI capabilities until explicitly allowed by administrators.
+2. Outcome (impact):
+   This governance setting improves security and control over new AI capabilities, ensuring they are reviewed and approved before being made available to users.
+3. Where to use (use case):
+   Ideal for organizations that require stringent control over the deployment of new AI features, ensuring compliance and reducing the risk of unauthorized access.</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer supports manual assignment of queued agent-first callbacks</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-agent-callbacks/</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 17:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now allows agents to manually assign queued callbacks, improving efficiency by enabling them to prioritize and handle tasks directly.
+2. Outcome (impact):
+   This feature enhances agent productivity by reducing unnecessary handoffs and allowing agents to resolve issues faster by leveraging their existing context.
+3. Where to use (use case):
+   Use this feature in customer service scenarios where agents need to quickly follow up on callbacks, ensuring that the most knowledgeable agent handles the issue.</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports data loss prevention with Microsoft Purview</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/whats-new/2026/08/amazon-quick-dlp-purview/</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 17:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now integrates with Microsoft Purview to enforce DLP policies, ensuring sensitive files are not shared outside approved channels.
+2. Outcome (impact):
+Organizations can enforce granular control over sensitive file sharing in Quick, extending existing Microsoft Purview governance policies seamlessly.
+3. Where to use (use case):
+Financial services companies can block "Highly Confidential" files from being uploaded to shared spaces while allowing "Internal" files with a warning notification.</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Amazon Quick agentic AI capabilities are now available in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-quick-aws-govcloud-us-west/</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched Amazon Quick's agentic AI capabilities in AWS GovCloud (US-West), enabling government and regulated industry teams to drive mission-critical decisions faster within a secure, FedRAMP High environment.
+2. Outcome (impact):
+This launch allows government and regulated industry teams to enhance productivity by automating workflows and integrating with existing tools, all while maintaining stringent security and compliance standards.
+3. Where to use (use case):
+Use cases include procurement, ATO compliance, and grants management, where custom chat agents can be built to streamline mission-specific tasks.</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>AWS Marketplace now supports category-based notification subscriptions and multi-channel delivery for buyers</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-marketplace-managed-buyer-notifications/</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:00:12 GMT</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Marketplace now allows buyers to subscribe to category-based notifications and deliver them through multiple channels, enhancing notification management and team collaboration.
+2. Outcome (impact):
+This update enables teams to receive only relevant notifications, reducing information overload and ensuring critical updates are not missed, thus improving procurement, renewals, and cost management processes.
+3. Where to use (use case):
+Ideal for organizations managing multiple AWS subscriptions, where different teams need tailored notifications for tasks like procurement, renewals, and cost management.</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -33528,7 +33824,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12 04:52:20</t>
+          <t>2026-08-13 04:56:53</t>
         </is>
       </c>
     </row>
@@ -33539,7 +33835,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -33549,7 +33845,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4367</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="7">
@@ -33559,7 +33855,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1587</v>
+        <v>976</v>
       </c>
     </row>
     <row r="8">
@@ -33569,7 +33865,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00031</v>
+        <v>0.000189</v>
       </c>
     </row>
     <row r="9">
@@ -33579,7 +33875,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000451</v>
+        <v>0.000277</v>
       </c>
     </row>
     <row r="10">
@@ -33589,7 +33885,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000761</v>
+        <v>0.000466</v>
       </c>
     </row>
     <row r="11">
@@ -33599,7 +33895,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.055213</v>
+        <v>0.055679</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F899"/>
+  <dimension ref="A1:F911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -33759,6 +33759,455 @@
       <c r="F899" t="inlineStr">
         <is>
           <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>AWS Billing and Cost Management introduces Managed Dashboards</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-billing-and-cost-management-managed-dashboards/</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 02:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Billing and Cost Management introduces Managed Dashboards, preconfigured read-only dashboards for actionable cost insights without setup.
+2. Outcome (impact):
+Users gain immediate cost visibility and insights, enabling faster decision-making and optimization of cloud spending.
+3. Where to use (use case):
+Ideal for organizations starting their FinOps journey or needing standardized cost visibility across multiple accounts.</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>AWS Billing and Cost Management</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>AWS Client VPN now supports CLI, administration controls, and faster connections</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-client-vpn-cli/</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 20:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Client VPN v6.0.x introduces CLI support, admin controls, and faster connections for enhanced automation and management.
+2. Outcome (impact):
+   Simplifies VPN integration into automation workflows, centralizes device management, and reduces connection time.
+3. Where to use (use case):
+   Ideal for organizations needing streamlined VPN management and faster, more secure remote access.</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>AWS Client VPN</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Claude Opus 5 is now available in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/claude-opus-5-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 18:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS GovCloud (US) now offers the advanced Claude Opus 5 model, compatible with zero data retention, enhancing coding and complex professional tasks.
+2. Outcome (impact):
+Enhanced capabilities in coding, long-running agents, and complex professional work for teams, ensuring high-level productivity and compliance with data governance.
+3. Where to use (use case):
+Ideal for government and regulated industries requiring advanced AI capabilities with strict data retention policies.</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Amazon Quick Microsoft 365 extensions are now generally available</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/amazon-quick-microsoft-365-extensions-generally-available</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick has launched Microsoft 365 extensions for Excel, PowerPoint, Word, and Outlook, enabling AI-driven task automation within M365 environments.
+2. Outcome (impact):
+These extensions streamline complex tasks like document redlining, financial modeling, presentation creation, and inbox management, significantly boosting productivity across various teams.
+3. Where to use (use case):
+- Finance: Complex model creation
+- Sales: Automated proposal drafting
+- Marketing: Presentation creation
+- Legal: Contract review
+- Operations: Email and meeting management
+- IT: Routine data analysis automation</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Spot Placement Score now includes Local Zones</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/spot-placement-score-local-zones/</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 17:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has expanded Spot Placement Score to include Local Zones, providing more comprehensive insights into Spot capacity success likelihood.
+2. Outcome (impact):
+Users can now make more informed decisions on where to place their Spot Instances by considering Local Zones alongside traditional Availability Zones and Regions.
+3. Where to use (use case):
+Ideal for users managing large-scale workloads who need to optimize their Spot Instance placements to maximize availability and minimize costs.</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>EC2</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Daybreak Red and Daybreak Blue from OpenAI are now available to eligible customers on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/openai-daybreak-red-and-blue-on-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 16:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Daybreak Red and Daybreak Blue from OpenAI are now available on Amazon Bedrock for eligible customers, enhancing cybersecurity workflows.
+2. Outcome (Impact):
+   Security teams can leverage advanced AI models for improved vulnerability discovery, detection engineering, incident response, and advanced research tasks.
+3. Where to Use (Use Case):
+   Ideal for cybersecurity professionals for tasks such as vulnerability detection, exploit research, and incident response.</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>AWS Certificate Manager supports switching from e-mail to DNS validation</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/AWS-Certificate-Manager-Email-DNS-Switch</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Certificate Manager now allows switching from email to DNS validation for existing certificates without reissuing them, ahead of the CA/B Forum's email validation deprecation.
+2. Outcome (impact):
+   This change ensures compliance with the CA/B Forum's deprecation of email validation, enabling automated renewals and maintaining uninterrupted service for applications using ACM certificates.
+3. Where to use (use case):
+   Ideal for organizations needing to update their certificate validation method to DNS for compliance and automated renewals, particularly for applications integrated with AWS services.</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>AWS Certificate Manager</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Amazon S3 adds additional policy details to access denied error messages</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/s3-additional-policy-details-access-denied-error-messages/</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon S3 now includes specific IAM and AWS Organizations policy ARNs in Access Denied error messages to help quickly identify and remediate denied requests.
+2. Outcome (impact):
+   This update simplifies troubleshooting by directly pointing to the exact policy causing the access denial, reducing manual inspection time and improving efficiency.
+3. Where to use (use case):
+   Ideal for administrators managing complex IAM and AWS Organizations policies to quickly resolve access issues within their AWS environment.</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms supports minimum aggregation thresholds in custom analysis rules</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-clean-rooms-minimum-aggregation-custom-analysis-rules</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Clean Rooms now allows data providers to enforce minimum aggregation thresholds on custom SQL queries to protect individual privacy, without needing pre-approved templates.
+2. Outcome (impact):
+This update enhances data privacy by preventing the disclosure of sensitive information about individuals or small groups, ensuring compliance with privacy regulations.
+3. Where to use (use case):
+Use this feature in collaborations between companies (e.g., publishers and advertisers) to enable ad-hoc queries while maintaining privacy, especially in scenarios involving sensitive demographic data.</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>AWS Clean Rooms</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports approval policies for sharing</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/whats-new/2026/08/amazon-quick-approval-policies-sharing/</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 22:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now supports approval policies for sharing assets, ensuring controlled and compliant sharing within organizations.
+2. Outcome (impact):
+Enhanced governance and compliance for asset sharing, reducing the risk of unauthorized access to sensitive information.
+3. Where to use (use case):
+Organizations that need to manage and control the sharing of knowledge bases, spaces, and custom chat agents within their teams.</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports per-user resource limits</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/whats-new/2026/08/amazon-quick-per-user-resource-limits/</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 22:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now allows administrators to set per-user limits on index storage and agent hours, providing better control over subscription costs and preventing unexpected overages.
+2. Outcome (impact):
+Administrators can efficiently manage subscription entitlements, avoid cost overruns, and ensure resources are allocated according to user needs by setting and managing per-user limits.
+3. Where to use (use case):
+Ideal for organizations deploying Amazon Quick to a large number of users, such as enterprises needing to balance resource usage across different roles while maintaining cost predictability.</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Amazon Nova Multimodal Embeddings is now available in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-nova-mme-govcloud/</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 14:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Nova Multimodal Embeddings is now available in AWS GovCloud (US-West), offering a unified model for text, documents, images, video, and audio.
+2. Outcome (impact):
+This service simplifies cross-modal retrieval and reduces complexity, costs, and data silos by using a single model for diverse content types.
+3. Where to use (use case):
+Ideal for applications requiring cross-modal search capabilities, such as video archives, product image searches, and financial documentation.</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Amazon Nova Multimodal Embeddings</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -33824,7 +34273,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13 04:56:53</t>
+          <t>2026-08-14 04:53:36</t>
         </is>
       </c>
     </row>
@@ -33835,7 +34284,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -33845,7 +34294,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2666</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="7">
@@ -33855,7 +34304,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>976</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="8">
@@ -33865,7 +34314,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000189</v>
+        <v>0.000317</v>
       </c>
     </row>
     <row r="9">
@@ -33875,7 +34324,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000277</v>
+        <v>0.000411</v>
       </c>
     </row>
     <row r="10">
@@ -33885,7 +34334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000466</v>
+        <v>0.000727</v>
       </c>
     </row>
     <row r="11">
@@ -33895,7 +34344,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.055679</v>
+        <v>0.056406</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F911"/>
+  <dimension ref="A1:F914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -34208,6 +34208,117 @@
       <c r="F911" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now supports Oracle Application Express (APEX) version 26.1</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-oracle-apex-26-1/</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for Oracle now supports Oracle APEX version 26.1, enhancing the ability to build scalable, secure enterprise applications in the cloud.
+2. Outcome (impact):
+Developers can now leverage the latest features of Oracle APEX 26.1 to create modern, user-friendly applications with improved performance and security.
+3. Where to use (use case):
+Ideal for enterprise application development, rapid prototyping, and deploying scalable web applications in the cloud.</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Amazon SES click tracking now supports custom URL paths for mobile app deep linking</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ses-supports-customurl-deeplinking</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SES now supports custom URL paths for mobile app deep linking, enabling engagement tracking without disabling it.
+2. Outcome (impact):
+This feature allows mobile apps to use deep linking while maintaining email engagement tracking, enhancing user experience and data collection.
+3. Where to use (use case):
+Ideal for mobile applications that need to track user interactions from emails, such as marketing campaigns, user notifications, and app engagement metrics.</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Amazon Redshift adds rg.large and rg.12xlarge instance sizes in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-redshift-adds-rg-large-12xlarge-aws-govcloud-regions/</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 19:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Redshift introduces rg.large and rg.12xlarge instances in AWS GovCloud (US) Regions, offering up to 2.4x faster performance at 30% lower price per vCPU.
+2. Outcome (impact):  
+Enhanced performance and cost-efficiency for data warehouse and data lake workloads in sensitive environments.
+3. Where to use (use case):  
+Ideal for government agencies and regulated industries requiring high-performance analytics in a secure, compliant environment.</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -34273,7 +34384,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14 04:53:36</t>
+          <t>2026-08-15 03:44:46</t>
         </is>
       </c>
     </row>
@@ -34284,7 +34395,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -34294,7 +34405,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4461</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7">
@@ -34304,7 +34415,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1446</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8">
@@ -34314,7 +34425,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000317</v>
+        <v>7.4e-05</v>
       </c>
     </row>
     <row r="9">
@@ -34324,7 +34435,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000411</v>
+        <v>0.000103</v>
       </c>
     </row>
     <row r="10">
@@ -34334,7 +34445,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000727</v>
+        <v>0.000176</v>
       </c>
     </row>
     <row r="11">
@@ -34344,7 +34455,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.056406</v>
+        <v>0.056582</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F914"/>
+  <dimension ref="A1:F929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -34319,6 +34319,561 @@
       <c r="F914" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock expands API support and introduces Cross Region Inferencing for OpenAI models</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-bedrock-cross-region-openai-v2/</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 20:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock now supports OpenAI GPT-5.6 models and introduces cross-Region inference for higher throughput and lower costs.
+2. Outcome (impact):  
+Customers can access higher throughput and lower inference costs by leveraging cross-Region inference, with expanded API support for the new models.
+3. Where to use (use case):  
+Ideal for applications requiring high availability and scalability, such as real-time chatbots, content generation, and large-scale data analysis.</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Amazon ECR now supports 25 replication rules per registry</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ecr-increased-replication-rules-limit</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 19:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECR now allows up to 25 replication rules per registry, up from 10, enhancing multi-region and multi-account replication strategies.
+2. Outcome (Impact):
+   This update enables more precise and flexible replication configurations, improving efficiency and performance for complex architectures.
+3. Where to Use (Use Case):
+   Ideal for distributing container images across multiple regions for low-latency access or replicating images to various production and staging accounts.</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Amazon ECR</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Auto Scaling now supports batch instance termination</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-auto-scaling-batch-termination</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 18:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 Auto Scaling now allows batch termination of up to 100 instances in a single API call, facilitating rapid scale-down for specific workloads.
+2. Outcome (impact):
+   Reduces the number of API calls needed to scale down Auto Scaling groups, enhancing efficiency and performance for workloads that require quick scaling adjustments.
+3. Where to use (use case):
+   Ideal for AI/ML training jobs, container orchestrators, and event-driven architectures that need to temporarily spin up and then rapidly scale down large fleets of instances.</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Amazon EC2 Auto Scaling</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Amazon MSK now supports configuring custom domain names for MSK Provisioned clusters</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/17/amazon-msk-custom-domain-names/</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 18:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   Amazon MSK now allows configuring custom domain names for Provisioned clusters, simplifying connection management and cluster operations.
+2. Outcome (impact)
+   Simplifies cluster migrations, disaster recovery, and scaling operations by maintaining consistent connection endpoints without manual reconfiguration.
+3. Where to use (use case)
+   Ideal for customers needing persistent endpoints, routing traffic through Network Load Balancers, or adhering to organizational naming conventions.</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Amazon MSK</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8i and R8i-Flex instances are now available in Canada West (Calgary) region</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-r8i-r8i-flex-calgary/</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 17:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched R8i and R8i-flex instances in Canada West (Calgary), offering enhanced performance and price-performance for memory-intensive workloads.
+2. Outcome (impact):
+These new instances provide up to 15% better price-performance, 2.5x more memory bandwidth, and up to 40% faster performance for specific workloads compared to previous generations.
+3. Where to use (use case):
+Ideal for memory-intensive applications such as PostgreSQL databases, NGINX web applications, AI deep learning models, and mission-critical SAP workloads.</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer dashboards now support reporting on routing steps and agent proficiencies</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-routing-steps/</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 17:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer dashboards now offer enhanced reporting on routing steps and agent proficiencies, allowing supervisors to better match contacts with agents based on skills.
+2. Outcome (impact):
+Supervisors can now optimize contact routing by monitoring wait times and adjusting routing criteria to ensure highly skilled agents are matched with appropriate tasks, reducing wait times and improving customer satisfaction.
+3. Where to use (use case):
+This feature is ideal for contact centers aiming to improve efficiency by ensuring that contacts are routed to the most suitable agents based on their skills and proficiencies.</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall Now Supports Stateful Rule Hit Counts</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-network-firewall-stateful-rule-hit-counts/</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Network Firewall now offers rule hit counts for stateful rules, enhancing visibility and actionable insights for network traffic inspection.
+2. Outcome (impact):
+   Network administrators and security engineers can better monitor rule effectiveness, accelerate incident response, identify policy gaps, and validate rule changes.
+3. Where to use (use case):
+   Ideal for enhancing network security by providing detailed insights into rule usage and traffic patterns, improving overall firewall policy management.</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>AWS Network Firewall</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Amazon Quick Microsoft 365 extensions are now generally available</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-quick-microsoft-365-extensions-generally-available</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 15:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick has launched Microsoft 365 extensions for Excel, PowerPoint, Word, and Outlook, enabling AI-driven task automation within M365 environments.
+2. Outcome (impact):
+These extensions streamline complex tasks such as document redlining, financial modeling, presentation creation, and email management, significantly enhancing productivity across various teams.
+3. Where to use (use case):
+Ideal for finance, sales, marketing, legal, operations, and IT teams to automate routine tasks, improve efficiency, and reduce manual effort.</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service now supports automatic semantic enrichment for VPC domains</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-opensearch-service-vpc/</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 15:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Service now supports automatic semantic enrichment for VPC domains, enabling private, secure AI-powered semantic search.
+2. Outcome (impact):
+   This enhancement allows customers with private network configurations to improve search relevance and user experience without compromising on security.
+3. Where to use (use case):
+   Ideal for organizations requiring high-security configurations, such as financial institutions, healthcare providers, and government agencies, to leverage advanced search capabilities within their private networks.</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>AWS CloudShell now includes a built-in visual file editor</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-cloudshell-visual-file-editor/</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CloudShell now features a built-in visual file editor accessible via a simple 'edit' command, enhancing productivity by eliminating the need for local file editing.
+2. Outcome (impact):
+This enhancement streamlines workflows by reducing friction in file editing processes, allowing developers and engineers to make changes directly within their shell session without switching contexts.
+3. Where to use (use case):
+Ideal for developers, DevOps engineers, and cloud administrators who manage scripts, infrastructure-as-code, agentic workflows, and AWS Lambda functions directly from the AWS CloudShell environment.</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>AWS CloudShell</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports per-user resource limits</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-quick-per-user-resource-limits/</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 21:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now allows administrators to set per-user limits on index storage and agent hours to manage subscription costs effectively.
+2. Outcome (impact):
+Administrators can prevent unexpected overage charges and ensure efficient use of subscription entitlements by setting and managing per-user resource limits.
+3. Where to use (use case):
+Ideal for organizations deploying Amazon Quick to thousands of users, enabling cost predictability and tailored resource allocation based on user roles.</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports data loss prevention with Microsoft Purview</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-quick-dlp-purview/</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 21:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now integrates with Microsoft Purview to enforce DLP policies, ensuring sensitive files are managed securely across chat, spaces, and knowledge bases.
+2. Outcome (impact):
+Organizations can extend their existing Microsoft Purview governance policies into Amazon Quick, enhancing data security and compliance by controlling sensitive file sharing.
+3. Where to use (use case):
+Financial services companies can prevent the sharing of "Highly Confidential" files in shared spaces while managing "Internal" files with warnings.</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports approval policies for sharing</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-quick-approval-policies-sharing/</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now supports approval policies for sharing assets, ensuring controlled and compliant sharing within organizations.
+2. Outcome (impact):
+Administrators can enforce governance and compliance by requiring approvals for sharing sensitive assets, enhancing security and auditability.
+3. Where to use (use case):
+Use case: Ensuring that sensitive knowledge bases, spaces, and custom chat agents are shared only after proper review and approval within an organization.</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Amazon Quick now supports customizable no data messages for visuals</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2025/08/amazon-quick-custom-no-data-message/</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick now allows authors to customize no data messages for visuals, providing tailored context and next steps for readers.
+2. Outcome (impact):
+Enhances user experience by offering more relevant and actionable information when visuals return no data, improving clarity and guidance.
+3. Where to use (use case):
+Ideal for dashboards and reports where data might occasionally be absent, ensuring users understand the context and potential actions.</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud Now Supports EBS Persistent Volume Cost Tracking</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-deadline-cloud-now-supports-ebs-persistent-volume-cost-tracking/</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Deadline Cloud now tracks and displays costs for Amazon EBS persistent volumes in the Usage Explorer, helping manage storage expenses effectively.
+2. Outcome (impact):  
+Customers can now monitor and manage storage costs for EBS volumes used with Deadline Cloud, aiding in identifying idle volumes and optimizing resource usage.
+3. Where to use (use case):  
+Ideal for teams running compute-intensive workloads in the cloud who need to manage and optimize their storage costs alongside compute and license expenses.</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -34384,7 +34939,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15 03:44:46</t>
+          <t>2026-08-18 03:49:47</t>
         </is>
       </c>
     </row>
@@ -34395,7 +34950,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -34405,7 +34960,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="7">
@@ -34415,7 +34970,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="8">
@@ -34425,7 +34980,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.4e-05</v>
+        <v>0.000368</v>
       </c>
     </row>
     <row r="9">
@@ -34435,7 +34990,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000103</v>
+        <v>0.000525</v>
       </c>
     </row>
     <row r="10">
@@ -34445,7 +35000,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000176</v>
+        <v>0.000893</v>
       </c>
     </row>
     <row r="11">
@@ -34455,7 +35010,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.056582</v>
+        <v>0.057475</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F929"/>
+  <dimension ref="A1:F994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -34874,6 +34874,2421 @@
       <c r="F929" t="inlineStr">
         <is>
           <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Amazon ECS now automatically detects and repairs container instances with impaired agent connectivity</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ecs-agent-connectivity-health</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 22:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now automatically detects and repairs container instances with impaired agent connectivity, enhancing application availability.
+2. Outcome (impact):
+Reduces undetected workload failures and improves application availability by automatically managing impaired container instances.
+3. Where to use (use case):
+Ideal for applications requiring high availability and minimal manual intervention to handle infrastructure issues.</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>SageMaker MLflow now supports customer managed keys</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/sagemaker-mlflow-custom-keys</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 19:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   SageMaker MLflow now supports encryption with customer-managed keys via AWS KMS, enhancing security and compliance.
+2. Outcome (impact):  
+   Organizations can now manage their own encryption keys, providing better security control and audit capabilities for their data.
+3. Where to use (use case):  
+   Ideal for organizations with strict security and compliance requirements that need to encrypt data using their own keys.</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>SageMaker MLflow</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports multiple external OIDC identity providers per cluster</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-eks-multiple-oidc-providers</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 18:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EKS now allows up to 10 external OIDC identity providers per cluster, enhancing authentication flexibility.
+2. Outcome (impact):  
+Organizations can authenticate diverse user populations (employees, contractors, CI/CD systems) using their preferred identity providers without consolidating them into a single provider.
+3. Where to use (use case):  
+Ideal for organizations with multiple user groups requiring separate identity management, such as large enterprises with varied user access needs.</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Amazon Aurora now supports PostgreSQL 18.4, 17.10, 16.14, 15.18, and 14.23</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-aurora-postgresql-18-4-17-10-16-14-15-18-14-23/</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora now supports PostgreSQL versions 18.4, 17.10, 16.14, 15.18, and 14.23, featuring bug fixes and enhancements.
+2. Outcome (impact):
+Users can upgrade to the latest PostgreSQL versions to address CVEs and benefit from improved performance and security.
+3. Where to use (use case):
+Ideal for applications requiring high availability, scalability, and security, such as e-commerce platforms, financial services, and enterprise applications.</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod enhances support for Ray</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-sagemaker-hyperpod-ray</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker HyperPod now enhances Ray support with improved observability, resilient training, and accelerated inference, simplifying the management of large-scale AI workloads.
+2. Outcome (impact):
+Simplifies the operational burden of running Ray on Kubernetes, improves productivity with interactive development environments, and ensures high availability and performance of AI training and inference tasks.
+3. Where to use (use case):
+Ideal for data scientists and machine learning engineers who need to scale AI workloads, from data processing to model serving, in a managed and efficient environment.</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports information extraction for agent voice and chat conversations</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-customer-information/</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 14:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now supports automatic information extraction from voice and chat interactions, enhancing productivity by capturing key data points.
+2. Outcome (impact):
+Reduces manual data entry, speeds up handle time, and improves agent and supervisor efficiency by providing actionable insights from conversations.
+3. Where to use (use case):
+Ideal for industries like travel, banking, and customer support where extracting specific information from customer interactions can streamline follow-up processes and improve service delivery.</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>AWS ParallelCluster 3.16 adds an on-node diagnostics tool</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-parallelcluster/</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS ParallelCluster 3.16 introduces an on-node diagnostics tool, pcluster-diag, enhancing cluster stability and updating software stack.
+2. Outcome (impact):
+   Improved cluster diagnostics and stability, easier troubleshooting, and updated software for better HPC and AI/ML performance.
+3. Where to use (use case):
+   Ideal for R&amp;D teams and IT administrators managing HPC clusters on AWS for scientific and engineering workloads.</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>AWS ParallelCluster</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-5.6 Terra and Luna now available on Amazon Bedrock in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/openai-gpt-terra-luna-govcloud/</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   - GPT-5.6 Terra and Luna models are now available on Amazon Bedrock in AWS GovCloud (US), offering enhanced performance and cost efficiency.
+2. Outcome (impact):
+   - Users can leverage advanced AI capabilities for tasks such as autonomous coding, genomics research, and cybersecurity with improved efficiency and reduced costs.
+3. Where to use (use case):
+   - Ideal for building autonomous coding agents, conducting long-horizon genomics and biology analyses, and performing advanced cybersecurity research.</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MySQL now supports new minor version 8.4.11</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-mysql-8411-available/</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 08:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for MySQL now supports minor version 8.4.11, featuring post-quantum TLS key exchange and various improvements.
+2. Outcome (impact):
+   Users can benefit from enhanced security with post-quantum cryptography, bug fixes, and performance improvements.
+3. Where to use (use case):
+   Ideal for applications requiring secure data encryption in-transit and those needing the latest MySQL features and fixes.</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>AWS Neuron 2.32 introduces expanded NKI programming, MXFP8 training kernels, and variable-size collectives for Trn2 and Trn</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-announce-neuron-2-32-0</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 21:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Neuron 2.32.0 introduces NKI 0.6.0 with new features, 13 new NKI Library kernels for MoE training, and variable-size collectives for Trn2 and Trn3.
+2. Outcome (impact):
+   Enhanced performance and flexibility for training large-scale machine learning models, particularly for Mixture of Experts and sparse attention applications.
+3. Where to use (use case):
+   Ideal for AI/ML workloads requiring efficient distributed training on AWS Inferentia and Trainium instances.</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>AWS Neuron</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock announces reduced pricing for OpenAI GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/bedrock-openai-gpt-56-sol-reduced-pricing/</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 20:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+OpenAI has reduced API prices for GPT-5.6 Sol, now $4 per million input tokens and $20 per million output tokens, available until November 21, 2026.
+2. Outcome (impact):
+The reduced pricing makes GPT-5.6 Sol more affordable for high-volume workloads, encouraging experimentation and scaling of advanced AI applications.
+3. Where to use (use case):
+Ideal for building autonomous coding agents, complex multi-step analyses, and advanced research workflows.</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now lets managers chat with their data</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-customer-ai-data-analytics</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now enables managers to query performance data in natural language, receiving actionable insights and recommendations in seconds.
+2. Outcome (impact):
+   Managers can quickly identify performance issues and receive prioritized action plans, reducing the time spent on data analysis from weeks to seconds.
+3. Where to use (use case):
+   This feature is ideal for customer service managers who need to optimize agent performance, queue management, and self-service metrics.</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now tracks automatic download status in the Deadline Cloud Monitor</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-deadline-cloud-auto-download-status-tracking/</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Deadline Cloud now tracks automatic download status in the Deadline Cloud Monitor, ensuring job outputs are successfully downloaded.
+2. Outcome (impact):
+This update reduces manual verification efforts, ensures output availability, and enhances confidence in large-scale render pipelines.
+3. Where to use (use case):
+Ideal for visual effects, animation, product design, simulation, and gaming teams running compute-intensive workloads in the cloud.</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Amazon EKS Capability for Argo CD now supports custom configuration</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-eks-argo-cd-configuration</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EKS now allows custom configurations for Argo CD via a ConfigMap, enhancing GitOps delivery and application health monitoring.
+2. Outcome (impact):
+   Users gain more control over Argo CD's application health reporting, ensuring resources are fully provisioned before marking applications as healthy.
+3. Where to use (use case):
+   Ideal for Kubernetes clusters managed by Amazon EKS, particularly for teams needing precise control over continuous delivery processes and application health checks.</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>AWS Glue 6.0 delivers 30% price reduction and Iceberg v3 support</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-glue-6-0-price-reduction-iceberg-v3</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 16:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue 6.0 is now available with a 30% price reduction, Apache Iceberg v3 support, and new features to enhance developer productivity and performance.
+2. Outcome (impact):
+AWS Glue 6.0 offers significant cost savings and improved performance for ETL jobs, streaming analytics, and AI application development, making it more efficient and powerful for data processing.
+3. Where to use (use case):
+Ideal for large-scale ETL, recurring batch workloads, streaming analytics, and AI application development in various industries such as finance, healthcare, and retail.</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Amazon SES now supports open and click tracking override parameters</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ses-adds-open-click-tracking-override/</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SES now allows senders to enable or disable open and click tracking on a per-request basis, simplifying compliance with data protection regulations.
+2. Outcome (impact):
+This update reduces configuration overhead and provides more precise control over tracking preferences, making it easier to comply with GDPR and CNIL guidelines.
+3. Where to use (use case):
+Use this feature when sending emails where you need to honor individual recipient preferences for tracking, such as marketing campaigns requiring GDPR compliance.</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>AWS announces the general availability of a new AWS Local Zone in Las Vegas, Nevada</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-local-zones-las-vegas-nevada/</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 21:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched a new Local Zone in Las Vegas, Nevada, offering low-latency access to various AWS services.
+2. Outcome (impact):
+This new Local Zone will provide developers and businesses with reduced latency, improved performance, and better compliance with data residency requirements.
+3. Where to use (use case):
+Ideal for applications requiring real-time processing, AI/ML inference, and content delivery to users in the Las Vegas metropolitan area.</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Service Name: AWS Local Zone  
+Category: Compute</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB now supports customer managed keys</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-timestream-influxdb-cmk/</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Timestream for InfluxDB now allows customers to use their own encryption keys for securing data at rest, enhancing data security and compliance.
+2. Outcome (impact):
+This update provides customers with greater control over their data encryption, ensuring that their data is protected with keys they manage, which is crucial for compliance with various regulatory requirements.
+3. Where to use (use case):
+Ideal for organizations needing strict control over their data encryption keys, such as those in highly regulated industries like finance and healthcare, to ensure data security and compliance.</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8gd, M8gd and R8gd instances are now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-c8gd-m8gd/</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8gd, M8gd, and R8gd instances with up to 11.4 TB of local storage are now available in new regions, powered by AWS Graviton4 processors.
+2. Outcome (impact):
+   These instances offer up to 30% better performance, 40% higher I/O performance for databases, and 20% faster query results for data analytics compared to previous generations.
+3. Where to use (use case):
+   - C8gd: High-performance web servers, batch processing, distributed analytics.
+   - M8gd: Application servers, microservices, small to medium databases.
+   - R8gd: In-memory databases, real-time big data analytics, scientific computing.</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Amazon Elastic Compute Cloud (Amazon EC2)</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Amazon Redshift now supports concurrency scaling of streaming ingestion workloads from Amazon Kinesis data streams</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/redshift-concurrencyscaling-for-kds-streams/</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now supports concurrency scaling for streaming ingestion from Kinesis Data Streams, allowing automatic scaling of streaming workloads.
+2. Outcome (impact):
+This feature enables users to handle higher data ingestion rates efficiently, freeing up resources for other tasks and ensuring predictable performance.
+3. Where to use (use case):
+Ideal for real-time analytics applications that require low-latency data ingestion and processing from Kinesis Data Streams.</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory now supports extracting memories from non-conversational JSON payloads</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/agentcore-memory-json-payloads</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Memory now supports extracting memories from non-conversational JSON payloads, allowing agents to consolidate long-term memories from structured data.
+2. Outcome (impact):
+Developers can now integrate diverse data sources directly into their agents, enhancing memory extraction and improving agent intelligence without needing to convert data into synthetic conversation messages.
+3. Where to use (use case):
+Use this feature to enhance customer service agents by incorporating behavioral events, activity logs, and system events into their memory, leading to more informed and personalized interactions.</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B300 instances are now available in the Asia Pacific (Seoul) Region</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-p6-b300/</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 18:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 P6-B300 instances, equipped with advanced GPU and networking capabilities, are now available in the Asia Pacific (Seoul) Region, enhancing performance for large-scale AI workloads.
+2. Outcome (impact):
+P6-B300 instances offer significant improvements in networking bandwidth, GPU memory, and TFLOPS, enabling faster training and deployment of large foundation and language models, thus reducing training times and increasing throughput for AI applications.
+3. Where to use (use case):
+Ideal for training and deploying large trillion-parameter foundation models (FMs) and large language models (LLMs) in AI research, data science, and machine learning applications requiring high computational power and memory.</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Amazon EKS now supports certificate authority (CA) rotation with automated lifecycle management</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-eks-certificate-authority-ca-rotation-automated-lifecycle-management</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EKS now supports automated CA rotation to maintain cluster security and operational integrity.
+2. Outcome (impact):  
+Ensures clusters remain secure and operational by automatically managing CA lifecycle and updates.
+3. Where to use (use case):  
+Ideal for managing security and compliance in Kubernetes clusters by ensuring CAs are rotated before expiration.</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront now supports Origin Access Control (OAC) for Amazon S3 Multi-Region Access Points</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-cloudfront-oac-s3-mrap</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudFront now natively supports Origin Access Control (OAC) for Amazon S3 Multi-Region Access Points, enhancing security and performance for global content delivery.
+2. Outcome (impact):
+Customers can now protect their Amazon S3 Multi-Region Access Points using CloudFront OAC, ensuring only designated CloudFront distributions can access the origins. This eliminates the need for custom Lambda@Edge functions to compute SigV4a Authorization headers, leading to faster cache-miss fills and improved security.
+3. Where to use (use case):
+This feature is ideal for global applications requiring high-performance, low-latency content delivery from Amazon S3, such as media streaming services, e-commerce platforms, and content management systems.</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>AWS Partner Central agents MCP Server now supports OAuth with AWS Sign-In</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/8/aws-partner-central-mcp/</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 18:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Central agents MCP Server now supports OAuth with AWS Sign-In, allowing partners to access Partner Central agents using their existing tools and AWS identities.
+2. Outcome (impact):
+This update simplifies authentication for AWS Partners, reducing the need for additional software and enabling seamless access to Partner Central agents for various engagements and applications.
+3. Where to use (use case):
+Use OAuth for co-sell engagements, AWS funding applications, and AWS Marketplace seller setup, leveraging tools like Amazon Quick and Kiro.</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>AWS Identity and Access Management (IAM)</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>ARC Region switch adds Amazon RDS Switchover Read Replica execution block</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/region-switch-rds-switchover-execution-block/</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 17:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces the RDS Switchover Read Replica execution block in ARC Region switch to automate failover and recovery for Amazon RDS databases using Oracle Data Guard across multiple regions.
+2. Outcome (impact):  
+This feature automates the failover process, ensuring zero data loss and rapid recovery during planned or unplanned failovers, enhancing application resilience and minimizing downtime.
+3. Where to use (use case):  
+Ideal for organizations running critical applications across multiple AWS regions that require automated failover and recovery mechanisms to maintain high availability and disaster recovery.</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Generative AI Inference Recommendation for Amazon SageMaker now available in the SageMaker AI Studio</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/generative-ai-inference-recommendation-for-amazon-sagemaker-now-available-in-the-sagemaker-ai-studio</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 17:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker AI Studio now provides Generative AI Inference Recommendations, offering a guided, low-code/no-code path to optimize inference configurations based on workload priorities.
+2. Outcome (impact):  
+Customers can achieve optimal inference configurations in hours instead of weeks, reducing manual benchmarking and trial-and-error, and ensuring validated performance data.
+3. Where to use (use case):  
+Deploying generative AI models in production environments where latency, throughput, or cost optimization is critical.</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon SageMaker  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL now supports Amazon CloudWatch Database Insights</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aurora-dsql-cloudwatch-database-insights/</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Aurora DSQL now integrates with Amazon CloudWatch Database Insights to provide per-statement, cluster-level performance monitoring.
+2. Outcome (impact):
+   Users can diagnose performance issues and identify resource-heavy queries more effectively, leading to optimized database performance.
+3. Where to use (use case):
+   Ideal for database administrators managing Aurora DSQL clusters to monitor and troubleshoot performance issues.</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect introduces inbound prefix controls and higher prefix scale</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-direct-connect-new-prefix-controls</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Direct Connect now allows up to 1,000 IPv4 and IPv6 prefixes per VIF, enabling more efficient route management.
+2. Outcome (impact):  
+This enhancement allows for better scalability and management of route prefixes, eliminating the need for route summarization or segmentation across multiple VIFs.
+3. Where to use (use case):  
+Ideal for organizations with large and growing networks that require detailed route management and efficient use of IP address space.</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>AWS Direct Connect</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Amazon Redshift introduces long-term system table retention with Amazon S3 Tables integration</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/redshift-long-term-system-table-retention/</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Redshift now supports long-term retention of system table data in Amazon S3 Tables, eliminating the need for custom ETL pipelines.
+2. Outcome (impact):  
+This feature reduces development and operational overhead, simplifies compliance and auditing, and enables cross-warehouse observability and analysis.
+3. Where to use (use case):  
+Ideal for customers needing extended retention of system table data for compliance, auditing, and performance monitoring across multiple Redshift clusters.</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon Redshift  
+Category: Analytics</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>AWS Marketplace now supports category-based notifications and multi-channel delivery for partners</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-marketplace/</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 00:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Marketplace now allows partners to configure category-based notifications and multi-channel delivery for better management of marketplace events.
+2. Outcome (impact):
+Partners can now efficiently manage and route notifications to the appropriate teams, improving responsiveness and accountability for marketplace activities.
+3. Where to use (use case):
+This feature is useful for managing product listings, offers, payments, and account management activities within AWS Marketplace.</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>AWS User Notifications</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Launching External Web Access for Web Search on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-bedrock-web-access-web-search/</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock's Web Search now supports external web access, allowing models to ground responses in the latest web information while optionally keeping data within AWS.
+2. Outcome (Impact):
+This update enables more dynamic and up-to-date responses for models, enhancing their utility in scenarios requiring the latest information, while offering flexibility in data handling.
+3. Where to Use (Use Case):
+Use cases include real-time information retrieval such as live sports scores, dynamic pricing updates, and accessing newly released documentation.</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Web Search in Amazon Bedrock AgentCore adds domain and published date filtering, expands to Europe and Asia Pacific</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/web-search-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 22:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore's Web Search now supports domain and published-date filtering, expanding to Europe and Asia Pacific.
+2. Outcome (impact):
+Agents can now filter web search results by domain and publication date, ensuring responses are grounded in relevant and trusted sources, enhancing accuracy and reliability.
+3. Where to use (use case):
+Ideal for regulated industries, research workflows, and applications requiring strict control over information sources and recency.</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Amazon EC2 enables AMI creation with local snapshots from instances on Outposts</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/ec2-create-image-local-snapshot-outpost</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 21:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 now allows creating AMIs using local snapshots on AWS Outposts, ensuring data residency compliance.
+2. Outcome (impact):
+   Simplifies AMI creation for Outposts instances, meeting data residency requirements without manual intervention.
+3. Where to use (use case):
+   Ideal for organizations needing to comply with data residency laws by keeping data on-premises while leveraging AWS services.</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch log Centralization now supports log group tag propagation</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-cloudwatch-centralization-tag-propogation/</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 21:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch Centralization now propagates log group tags from source accounts to destination log groups, ensuring cost and compliance tags are maintained.
+2. Outcome (impact):
+   This feature allows teams to preserve important tags on centralized log groups, facilitating better cost management, access control, and compliance reporting.
+3. Where to use (use case):
+   Ideal for organizations that need to centralize logs across multiple accounts and regions while maintaining tag-based access control and cost allocation.</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB Streams now supports attribute-based access control</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-dynamodb-streams-abac/</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 21:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DynamoDB Streams now supports attribute-based access control (ABAC) to simplify access management using tag-based conditions in IAM policies.
+2. Outcome (impact):
+   This feature allows teams to enforce different access levels for multiple applications and environments using fewer IAM policies, enhancing security and scalability.
+3. Where to use (use case):
+   Ideal for teams managing DynamoDB Streams access across various applications and environments, needing finer-grained access control for compliance and isolation.</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB Streams</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker notebooks now support trusted identity propagation</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-sagemaker/</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 20:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Notebooks now support Trusted Identity Propagation (TIP) with Athena, Redshift, and EMR Serverless, enabling secure, per-user data access control.
+2. Outcome (impact):
+Enterprises can enforce per-user data boundaries, ensuring users see only the data they are permitted to access, enhancing security and simplifying administration.
+3. Where to use (use case):
+Data analytics scenarios where multiple users need to access data through SageMaker Notebooks while maintaining strict access controls based on individual permissions.</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch pipelines adds GeoIP, RDS, and XML processors</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/cloudwatch-geoip-rds-xml/</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 20:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudWatch pipelines now feature new RDS, XML, and GeoIP processors to enhance log data parsing and enrichment.
+2. Outcome (impact):
+   These new processors improve log data queryability and enrich logs with geographic context, simplifying compliance and security analysis.
+3. Where to use (use case):
+   Use these processors for compliance reporting from RDS logs, extracting XML data from application logs, and enriching IP addresses with location data for security investigations.</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>AWS Security Agent (now part of AWS Continuum) now supports budget controls and finding revalidation</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-security-agent/</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 18:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Security Agent, now part of AWS Continuum, introduces budget controls and finding revalidation for on-demand penetration testing.
+2. Outcome (impact):  
+Security teams can now cap test costs and efficiently verify remediation of vulnerabilities without full re-tests, enhancing cost management and security assurance.
+3. Where to use (use case):  
+Ideal for DevSecOps engineers and security teams to manage costs and validate fixes in web applications during continuous security testing.</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>AWS Security Agent</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaConnect Router now supports configurable recovery latency modes</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/mediaconnect-router-latency-modes/</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Elemental MediaConnect Router now allows users to configure latency settings for inputs and outputs, offering balanced and low-latency modes.
+2. Outcome (impact):
+   Users gain better control over latency for different workflows, improving performance for latency-sensitive applications.
+3. Where to use (use case):
+   Ideal for live streaming and other real-time media applications where minimizing latency is crucial.</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>MediaConnect Router</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>AWS Cost Anomaly Detection supports third-party models on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-cost-anomaly-detection-bedrock-3P/</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 17:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Cost Anomaly Detection now monitors and alerts on unusual spend for third-party models on Amazon Bedrock, enhancing cost management for generative AI workloads.
+2. Outcome (Impact):  
+Teams can automatically detect and respond to cost anomalies in their third-party model usage on Amazon Bedrock, ensuring better cost management and optimization of generative AI expenses.
+3. Where to Use (Use Case):  
+Ideal for organizations running production generative AI workloads on Amazon Bedrock who need to monitor and manage costs associated with third-party models.</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>AWS Cost Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Ingestion is now available in GovCloud Regions</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/opensearch-ingestion-available-govcloud-regions</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 17:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Ingestion is now available in AWS GovCloud regions, enabling secure data ingestion into OpenSearch Service.
+2. Outcome (impact):
+   This launch enhances data ingestion capabilities for government and regulated industries, ensuring compliance and secure data processing.
+3. Where to use (use case):
+   Ideal for government agencies and regulated industries needing secure, compliant data ingestion into Amazon OpenSearch Service.</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Ingestion</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>AWS Marketplace launches support for Amazon Lightsail</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-marketplace-launch-ami-amazon-lightsail</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 17:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Marketplace now supports launching select AMIs on Amazon Lightsail, offering a streamlined, cost-effective deployment option.
+2. Outcome (impact):
+Customers can easily deploy eligible AWS Marketplace products on Amazon Lightsail with predictable pricing and simplified instance creation.
+3. Where to use (use case):
+Ideal for small to medium-sized applications and websites requiring a simple, cost-effective hosting solution.</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>Amazon Lightsail</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>AWS announces a new Availability Zone in the Europe (London) Region</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-new-availability-zone-europe/</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has launched a new Availability Zone (eu-west-2d) in the Europe (London) Region, enhancing AI/ML and compute capacity.
+2. Outcome (impact):  
+This expansion provides greater infrastructure capacity, improved fault tolerance, and supports high availability for AI/ML workloads in the London Region.
+3. Where to use (use case):  
+Ideal for running model training and inference workloads, distributing applications for fault tolerance, and building resilient architectures.
+AWS Service: AWS Trainium | Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>AWS Lambda MicroVMs is now available in 5 additional AWS regions</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/lambda-microvms-5-additional-regions</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 16:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda MicroVMs are now available in 5 new regions, enhancing global accessibility and performance for developers.
+2. Outcome (impact):
+Developers can now deploy isolated compute environments in 10 regions, improving latency and meeting data residency requirements.
+3. Where to use (use case):
+Ideal for applications requiring secure, stateful, and responsive code execution, such as AI coding assistants, interactive development environments, and vulnerability scanners.</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Amazon Quick adds deny by default for custom permissions</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-quick-deny-by-default/</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 15:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick now includes a "deny by default" feature for custom permissions, automatically restricting new AI capabilities until explicitly allowed by administrators.
+2. Outcome (impact):
+   This governance setting enhances security and control by preventing new AI capabilities from being available to users until administrators explicitly allow them, reducing the risk of unauthorized access.
+3. Where to use (use case):
+   This feature is useful for organizations that require stringent access controls and want to ensure that new AI capabilities are thoroughly vetted before being made available to users.</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>AWS IAM now supports 20 managed policies per role by default</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-iam-quota-increase/</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS IAM has increased the default limit for managed policies per role from 10 to 20, enhancing flexibility for managing permissions.
+2. Outcome (Impact):
+This change simplifies adherence to IAM best practices and streamlines onboarding processes for AWS Partner products by reducing the need for quota requests.
+3. Where to Use (Use Case):
+Ideal for environments requiring separation of permissions into purpose-specific policies or when integrating with AWS Partner products that need multiple managed policies.</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Service Name: AWS Identity and Access Management (IAM)  
+Category: Security</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications now offers in-console monitoring capabilities</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-workspaces-applications-console-monitoring</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon WorkSpaces Applications now offers built-in monitoring capabilities directly in the console, providing real-time metrics without third-party tools.
+2. Outcome (impact):  
+Administrators can easily monitor active sessions, resource utilization, and performance metrics, simplifying management for large deployments.
+3. Where to use (use case):  
+Ideal for managing and monitoring large-scale WorkSpaces Applications deployments, ensuring optimal performance and resource allocation.</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>AWS Storage Gateway now supports FIPS-compliant private connectivity for Tape and Volume Gateway</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/storage-gateway-fips-privatelink/</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Storage Gateway now supports FIPS 140-3 validated endpoints over AWS PrivateLink for Tape and Volume Gateway, enabling private, FIPS-compliant connectivity.
+2. Outcome (impact):  
+This update allows regulated workloads to use Storage Gateway with FIPS-compliant traffic on the private AWS network, enhancing security and compliance.
+3. Where to use (use case):  
+Ideal for organizations that need to comply with FIPS standards and require secure, private connectivity for their Storage Gateway workloads.</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>AWS Storage Gateway</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8a instances are now available in Asia Pacific (Taipei) region</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-r8a-asia-pacific-taipei/</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 07:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 R8a instances, featuring 5th Gen AMD EPYC processors, are now available in the Asia Pacific (Taipei) region, offering enhanced performance and memory bandwidth.
+2. Outcome (impact):
+   Users can achieve up to 30% higher performance and 19% better price-performance, with 45% more memory bandwidth compared to R7a instances, ideal for latency-sensitive and memory-intensive workloads.
+3. Where to use (use case):
+   Suitable for SQL and NoSQL databases, in-memory caches, real-time big data analytics, EDA applications, and business-critical applications requiring high throughput and low response times.</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock now supports SpaceXAI Grok 4.6 with Cross Region Inferencing</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-bedrock-grok-4-6/</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 05:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock now supports SpaceXAI Grok 4.6 with US Geo and Global cross-Region inference, enhancing scalability and cost-efficiency.
+2. Outcome (impact):
+Customers can now leverage Grok 4.6 at scale with higher throughput and lower costs, meeting data residency requirements and handling demand spikes efficiently.
+3. Where to use (use case):
+Ideal for coding assistance, agentic tasks, and knowledge work, especially where high scalability and cost-efficiency are crucial.</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock now supports OpenAI models in India</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-bedrock-openai-india-v1/</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 23:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock now supports OpenAI's GPT-5.6 models (Terra and Luna) in India with cross-Region inference, ensuring data stays within the country.
+2. Outcome (impact):
+Customers can now use OpenAI models at scale in India while meeting regulatory data residency requirements, enhancing data security and compliance.
+3. Where to use (use case):
+Ideal for businesses needing to process sensitive data within India, such as financial services, healthcare, and government entities.</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>AWS IAM identity federation to external services is now available in AWS European Sovereign Cloud Region</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-iam-european-sovereign-cloud/</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 22:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS IAM now supports identity federation to external services in the European Sovereign Cloud using short-lived JWTs.
+2. Outcome (impact):  
+Enhances security and simplifies access management for AWS workloads in the EU by eliminating the need for long-term credentials.
+3. Where to use (use case):  
+Useful for organizations needing to securely authenticate AWS workloads with third-party cloud providers, SaaS applications, and self-hosted services within the EU.</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Service Name: AWS Identity and Access Management (IAM)  
+Category: Security</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>Amazon Corretto August 2026 Critical Security Patch Updates</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-corretto-august-2026-security-updates</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 21:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has released critical security patch updates for multiple versions of Amazon Corretto on August 18, 2026. Available versions include Corretto 26, 25, 21, 17, 11, and 8.
+2. Outcome (impact):
+The updates address critical security vulnerabilities, ensuring that users can maintain secure and stable Java environments in production.
+3. Where to use (use case):
+These updates are essential for maintaining the security of production applications running on Amazon Corretto across various platforms.</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Amazon Corretto</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>AgentCore payments is now generally available in Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/bedrock-agentcore-payments-ga/</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 19:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has launched AgentCore payments, enabling AI agents to autonomously manage payments for APIs and content.
+2. Outcome (impact):  
+This release allows enterprises to deploy transacting AI agents securely and at scale, with robust observability and payment management features.
+3. Where to use (use case):  
+Ideal for businesses needing AI agents to handle microtransactions, access paid APIs, and manage content payments seamlessly.</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon Bedrock AgentCore  
+Category: AI/ML</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio now supports data profiling and anomaly detection</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/05/smus-data-profiling</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 18:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon SageMaker Unified Studio now offers data profiling and anomaly detection powered by AWS Glue Data Quality, enabling better data understanding and monitoring.
+2. Outcome (impact):  
+Data stewards, engineers, and analysts can generate statistical profiles of their data and detect anomalies without predefined thresholds, improving data quality and reliability.
+3. Where to use (use case):  
+Ideal for data-driven organizations to monitor data quality in both static datasets and real-time ETL jobs, ensuring data integrity and consistency.</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon SageMaker  
+Category: Analytics</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Amazon MWAA Serverless now supports PythonOperator and BashOperator</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/mwaa-serverless-pythonoperator-bashoperator/</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MWAA Serverless now supports PythonOperator and BashOperator, enabling data engineering teams to run custom Python functions and shell scripts directly in the serverless runtime.
+2. Outcome (impact):
+   This update allows teams to execute daily code patterns like data transformations and quality checks without provisioning additional infrastructure, enhancing efficiency and consistency.
+3. Where to use (use case):
+   Ideal for data engineering tasks such as data transformations, format conversions, and data quality checks within the serverless environment.</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow (Amazon MWAA)</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8i instances are now available in Israel (Tel Aviv) region</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-r8i-israel-tel-aviv/</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 17:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched R8i instances in the Israel (Tel Aviv) region, offering enhanced performance and memory bandwidth for memory-intensive workloads.
+2. Outcome (Impact):
+Users in Israel can now leverage high-performance computing for demanding applications with improved price-performance and speed.
+3. Where to Use (Use Case):
+Ideal for large-scale databases, web applications, AI deep learning, and mission-critical SAP workloads.</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>IAM Policy Autopilot now supports Terraform plan files</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/iam-policy-autopilot-now-supports-terraform-plan-files</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 17:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+IAM Policy Autopilot now generates IAM policies from Terraform plan files, reducing manual policy writing and troubleshooting.
+2. Outcome (impact):  
+Reduces time spent on writing IAM policies and troubleshooting access issues by generating scoped-down policies from Terraform plans.
+3. Where to use (use case):  
+Ideal for teams using Terraform to manage AWS infrastructure, ensuring generated IAM policies are tightly scoped to the resources defined in the Terraform plan.</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>IAM Policy Autopilot</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>PostgreSQL 19 Beta 3 is now available in Amazon RDS Database Preview Environment</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/postgresql-19-beta-3-amazon-rds-database-preview-environment/</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon RDS now offers PostgreSQL 19 Beta 3 in its Database Preview Environment, featuring enhanced query performance and autovacuum management.
+2. Outcome (impact):  
+   Users can evaluate new PostgreSQL 19 capabilities, improving query performance and maintenance efficiency, while benefiting from stability improvements.
+3. Where to use (use case):  
+   Ideal for database administrators and developers looking to test and optimize PostgreSQL 19 features before general availability.</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Amazon EC2 High Memory U7i instances now available in AWS Europe (Zurich) region</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-high-memory-u7i-aws-europe/</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 High Memory U7i-6TB instances are now available in the Europe (Zurich) region, offering 6 TiB of DDR5 memory and 448 vCPUs.
+2. Outcome (impact):
+Customers can achieve up to 45% better price performance for high-memory workloads, enhancing transaction processing throughput in data-intensive environments.
+3. Where to use (use case):
+Ideal for mission-critical in-memory databases such as SAP HANA, Oracle, and SQL Server.</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces now supports Nested Virtualization</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/nested-virtualization-workspaces/</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon WorkSpaces now supports nested virtualization, allowing developers to run hypervisor-dependent tools directly on their WorkSpaces without additional hardware.
+2. Outcome (impact):
+Developers can efficiently run Docker Desktop, WSL2, KVM-based workloads, and more on their WorkSpaces, enhancing productivity and reducing the need for separate physical environments.
+3. Where to use (use case):
+Ideal for software development, testing environments, and running multiple virtualized applications on a single WorkSpace.</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Amazon S3 Metadata and annotations are now available in AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-s3-metadata-annotations-govcloud-regions</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon S3 Metadata and annotations are now available in AWS GovCloud (US) Regions, enhancing data discovery and enrichment for business analytics and AI applications.
+2. Outcome (impact):
+This update simplifies the process of discovering, understanding, and enriching S3 data, making it easier to perform business analytics and real-time inference applications with enriched data context.
+3. Where to use (use case):
+Use this feature for government agencies and organizations that require secure, compliant storage solutions with enriched metadata and annotations to support advanced analytics and AI applications.</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>AWS Console-to-Code adds 26 services and cross-region recording​</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/console-to-code-adds-26-services</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Console-to-Code now supports 26 new services and introduces cross-region and cross-browser-tab action recording, expanding its service coverage and enhancing automation capabilities.
+2. Outcome (impact):
+This update allows developers, DevOps engineers, and cloud architects to more easily convert manual console workflows into infrastructure as code (IaC), improving efficiency and reducing manual errors in complex, multi-region deployments.
+3. Where to use (use case):
+Ideal for automating the setup and configuration of AWS resources across different regions and browser tabs, making it easier to manage and deploy infrastructure consistently.</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>AWS Console-to-Code</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Amazon Location Service now supports POI category and density filtering in map styles</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-location-service/amazon-location-poi-categorization-density-map-styles</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 14:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Location Service now allows developers to filter POIs by category and density directly through server-side settings.
+2. Outcome (impact):  
+Developers can now tailor map displays to specific use cases by controlling which POI categories and densities are shown, improving map relevance and performance.
+3. Where to use (use case):  
+Ideal for applications like property-listing sites, logistics fleet management, and tourist maps that require specific POI categories to be highlighted.</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon Location Service</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -34939,7 +37354,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18 03:49:47</t>
+          <t>2026-08-25 08:49:28</t>
         </is>
       </c>
     </row>
@@ -34950,7 +37365,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -34960,7 +37375,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5181</v>
+        <v>24086</v>
       </c>
     </row>
     <row r="7">
@@ -34970,7 +37385,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1850</v>
+        <v>8199</v>
       </c>
     </row>
     <row r="8">
@@ -34980,7 +37395,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000368</v>
+        <v>0.00171</v>
       </c>
     </row>
     <row r="9">
@@ -34990,7 +37405,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000525</v>
+        <v>0.002329</v>
       </c>
     </row>
     <row r="10">
@@ -35000,7 +37415,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000893</v>
+        <v>0.004039</v>
       </c>
     </row>
     <row r="11">
@@ -35010,7 +37425,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.057475</v>
+        <v>0.061514</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F994"/>
+  <dimension ref="A1:F1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -37289,6 +37289,487 @@
       <c r="F994" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>AWS IoT Core now supports native InfluxDB routing for time-series data</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-iot-core-influxdb/</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 19:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS IoT Core now natively supports InfluxDB routing, allowing IoT data to be sent directly to InfluxDB databases without custom code or intermediate services.
+2. Outcome (impact):  
+This integration simplifies the process of managing time-series data from IoT devices, optimizing cost and throughput through device-side and server-side batching.
+3. Where to use (use case):  
+Ideal for industries like life sciences, where real-time monitoring of scientific instruments is crucial, enabling direct data flow to InfluxDB for analysis.</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>AWS IoT Core</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>AWS Batch now supports Amazon ECS Managed Instances</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-batch-on-ecs-managed-instances/</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 19:36:00 GMT</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Batch now supports Amazon ECS Managed Instances, allowing GPU-accelerated batch workloads to run on AWS-managed infrastructure with automatic updates and patching.
+2. Outcome (impact):
+This update reduces operational overhead for users by automating AMI updates, security patching, and instance lifecycle management, enabling them to focus on their workloads.
+3. Where to use (use case):
+Ideal for GPU-intensive and compute-heavy batch processing tasks such as deep learning, scientific simulations, and large-scale data processing.</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>AWS Batch</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Capacity Reservation Resource Groups now support Amazon EC2 Capacity Blocks and interruptible Capacity Reservations</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/capacity-reservation-resource-groups-ec2</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS now allows Capacity Reservation Resource Groups to include Amazon EC2 Capacity Blocks for ML and interruptible Capacity Reservations, simplifying instance launches across reserved capacities.
+2. Outcome (impact):
+This update enhances flexibility and management of reserved EC2 capacity, enabling users to efficiently launch instances across various reservation types and prioritize capacity usage.
+3. Where to use (use case):
+Ideal for organizations managing diverse workloads with varying capacity needs, such as machine learning projects requiring Capacity Blocks for ML and cost-effective, interruptible reservations.</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>AWS Lambda MicroVMs now supports AWS PrivateLink</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/lambda-microvms-supports-privatelink</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 16:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda MicroVMs now supports AWS PrivateLink, enabling secure, private connectivity from VPCs without public internet exposure.
+2. Outcome (impact):
+   This enhancement helps regulated industries like finance, healthcare, and government meet strict network isolation requirements for workloads using Lambda MicroVMs.
+3. Where to use (use case):
+   Ideal for scenarios requiring secure, private communication between VPC resources and Lambda MicroVMs, such as deploying sensitive applications in highly regulated environments.</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>AWS Lambda MicroVMs</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL supports minor versions 18.6, 17.11, 16.15, 15.19, and 14.24</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-postgresql-18-6-17-11-16-15-15-19-14-24/</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for PostgreSQL now supports minor versions 18.6, 17.11, 16.15, 15.19, and 14.24, addressing CVEs and enhancing performance.
+2. Outcome (impact):
+Upgrading to the latest minor versions ensures security against vulnerabilities and leverages improvements from the PostgreSQL community.
+3. Where to use (use case):
+Ideal for businesses running PostgreSQL databases that require regular updates to maintain security and performance.</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>Amazon RDS for PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now lets you update the customer profile on a case or add a profile after a case is opened</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-cases-flexible-profiles/</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now allows agents to update customer profiles on cases or add profiles post-case creation to ensure accurate case histories.
+2. Outcome (impact):
+   This update improves case management accuracy by enabling agents to correct customer profiles and add profiles when necessary, ensuring better customer service and data integrity.
+3. Where to use (use case):
+   This feature is useful in customer service scenarios where cases might be linked to the wrong customer initially or when customer identity needs verification after case creation.</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>IAM Roles Anywhere now provides a Java plugin for the AWS SDK</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/iam-roles-anywhere-java/</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 13:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+IAM Roles Anywhere now offers a Java plugin for AWS SDK v2, enabling Java applications to obtain temporary AWS credentials directly within the JVM.
+2. Outcome (impact):
+This update simplifies credential management for Java applications running outside of AWS, enhancing security and reducing complexity.
+3. Where to use (use case):
+Ideal for Java applications that need to access AWS resources securely without managing separate credential processes.</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>IAM Roles Anywhere</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>AWS Lambda introduces managed runtimes in public preview for Node.js 26 and Python 3.15</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-lambda-node-js-python-public-preview/</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda has launched managed runtimes in public preview for Node.js 26 and Python 3.15, allowing early testing before general availability.
+2. Outcome (impact):
+Developers can test upcoming runtimes, provide feedback, and ensure compatibility for production use, while avoiding potential breaking changes post-GA.
+3. Where to use (use case):
+Ideal for development and testing environments to validate applications against new runtimes before deploying to production.</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports the latest CU for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-supports-latest-cu-microsoft-sql-server/</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon RDS for SQL Server now supports the latest Cumulative Update (CU6) for Microsoft SQL Server 2025, enhancing performance and security.
+2. Outcome (impact):  
+Users can benefit from the latest features, improvements, and security fixes provided by Microsoft SQL Server 2025 CU6.
+3. Where to use (use case):  
+Ideal for businesses requiring the latest SQL Server updates for improved database performance, security, and compliance.</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now supports July 2026 Release Update</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-oracle-july-2026-release-update</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 07:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for Oracle now supports the July 2026 Release Update, including security patches for Oracle Database versions 19c, 21c, and 26ai.
+2. Outcome (impact):
+Enhanced security and performance for Oracle databases hosted on Amazon RDS, ensuring they are up-to-date with the latest Oracle fixes and improvements.
+3. Where to use (use case):
+Ideal for businesses running Oracle databases on Amazon RDS that require regular security updates and want to automate the upgrade process.</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager adds managed external secrets support for Cisco Security Platform and Netskope</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/secrets-manager-cisco-netskope/</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Secrets Manager now supports automatic rotation of Cisco Security Platform and Netskope API keys, enhancing credential management and security.
+2. Outcome (impact):
+This update simplifies the management of external secrets, reduces manual intervention, and improves security by ensuring credentials are always up-to-date.
+3. Where to use (use case):
+Ideal for organizations using Cisco Security Platform and Netskope that require secure and automated management of API keys and tokens.</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>AWS Lambda functions now support full IAM resource-based policies</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-lambda-full-iam-resource-based-policies/</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 02:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now supports comprehensive IAM resource-based policies, allowing for more flexible and scalable permissions management.
+2. Outcome (impact):
+This update enables platform admins and security teams to define granular access permissions using AWS IAM's full capabilities, simplifying policy management for multi-account architectures and multiple resources.
+3. Where to use (use case):
+Ideal for managing permissions at scale in environments with multiple services and resources, such as multi-account setups or when needing to restrict access based on conditions like source IP or principal tags.</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>MSK Replicator now supports OAuth 2.0 (SASL/OAUTHBEARER) authentication for replication from external Apache Kafka clusters to Amazon MSK</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-msk-replicator-OAuth-support</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon MSK Replicator now supports OAuth 2.0 authentication for replicating data from external Kafka clusters to Amazon MSK.
+2. Outcome (impact):  
+This enhancement enables secure data replication from external Kafka clusters using OAuth 2.0, facilitating migration, disaster recovery, and multi-cloud data distribution.
+3. Where to use (use case):  
+Use this feature to migrate workloads to Amazon MSK, set up disaster recovery, and distribute data across hybrid and multi-cloud environments.</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Amazon Managed Streaming for Apache Kafka (MSK)</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -37354,7 +37835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25 08:49:28</t>
+          <t>2026-08-26 03:57:15</t>
         </is>
       </c>
     </row>
@@ -37365,7 +37846,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -37375,7 +37856,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24086</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="7">
@@ -37385,7 +37866,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8199</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="8">
@@ -37395,7 +37876,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00171</v>
+        <v>0.000348</v>
       </c>
     </row>
     <row r="9">
@@ -37405,7 +37886,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002329</v>
+        <v>0.000465</v>
       </c>
     </row>
     <row r="10">
@@ -37415,7 +37896,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004039</v>
+        <v>0.000813</v>
       </c>
     </row>
     <row r="11">
@@ -37425,7 +37906,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.061514</v>
+        <v>0.062327</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1007"/>
+  <dimension ref="A1:F1018"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -37770,6 +37770,414 @@
       <c r="F1007" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Amazon Cognito adds admin API operation to reset user TOTP configurations</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-cognito-totp-reset/</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Cognito now allows admins to reset user TOTP MFA configurations via a new API, facilitating recovery when users lose access to their devices.
+2. Outcome (impact):
+   This new feature enables administrators to reset users' TOTP MFA configurations without recreating accounts, ensuring MFA enforcement and providing a recovery path for locked-out users.
+3. Where to use (use case):
+   Use this feature in environments where users may lose access to their TOTP devices, ensuring seamless recovery and maintaining security through MFA.</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Amazon Cognito</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports unplanned shrinkage in agent schedules</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-customer-unplanned-shrinkage/</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 20:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect Customer now allows managers to account for unplanned agent absences in schedules, enhancing staffing accuracy and service level projections.
+2. Outcome (impact):  
+Improves scheduling accuracy by adjusting metrics like scheduled headcount and projected service levels based on unplanned agent unavailability, helping maintain target service levels.
+3. Where to use (use case):  
+Useful for workforce managers in contact centers to proactively address staffing gaps due to unscheduled absences, ensuring better service delivery.</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Mountpoint for Amazon S3 adds memory usage controls</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/mountpoint-for-S3-adds-memory-usage-controls</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Mountpoint for Amazon S3 now includes memory usage controls to prevent performance issues in memory-intensive environments.
+2. Outcome (impact):  
+This update allows for better resource management and stability when running Mountpoint alongside other memory-intensive applications.
+3. Where to use (use case):  
+Ideal for machine learning training and analytics workloads where memory allocation is critical.</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now supports points-based scoring in performance evaluations</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-customer-points-based-scoring-evaluations/</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer introduces points-based scoring for performance evaluations, offering managers more flexibility in assessing human and AI agent performance.
+2. Outcome (impact):
+This update allows managers to tailor evaluations to business priorities by assigning specific points to various criteria, enhancing the relevance and accuracy of performance assessments.
+3. Where to use (use case):
+Use this feature in customer service operations to create customized performance metrics that align with specific business goals, improving the effectiveness of agent evaluations.</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>AWS Glue 5.1 is now available in AWS European Sovereign Cloud Region</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-glue-5-1-european-sovereign-cloud</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 16:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Glue 5.1 is now available in the AWS European Sovereign Cloud Region, featuring upgraded engines, enhanced security, and expanded support for data formats and access controls.
+2. Outcome (impact):
+This update enhances data integration capabilities with improved performance, security, and access control, enabling more efficient and secure data management for users in the European Sovereign Cloud Region.
+3. Where to use (use case):
+Ideal for organizations requiring robust data integration, enhanced security, and fine-grained access control for data processing and management in the European region.</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>AWS Backup adds cross-Region backup copy and logically air-gapped vault support for Amazon DocumentDB in nine additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-backup-cross-region-air-gapped-docdb/</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Backup now supports cross-Region backup copies and logically air-gapped vaults for Amazon DocumentDB in nine new regions, enhancing disaster recovery and compliance.
+2. Outcome (impact):  
+This update improves disaster recovery capabilities, business continuity, and compliance by allowing cross-Region backup copies and secure, isolated storage of DocumentDB backups.
+3. Where to use (use case):  
+Use this feature to meet regulatory compliance, ensure data protection across multiple regions, and enhance disaster recovery strategies for Amazon DocumentDB.</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R8id instances are now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-r8id/</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 R8id instances are now available in more regions, offering enhanced performance and local storage for memory-intensive workloads.
+2. Outcome (impact):
+   Users can leverage higher performance and local storage in additional regions, optimizing workloads like real-time big data analytics and in-memory databases.
+3. Where to use (use case):
+   Ideal for memory-intensive applications such as in-memory databases, real-time big data analytics, large in-memory caches, and data processing.</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8id and M8id instances are now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-c8id-m8id-aws-regions/</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C8id and M8id instances with up to 22.8 TB of local NVMe-based SSD storage are now available in additional regions, offering enhanced compute and memory performance.
+2. Outcome (impact):
+These instances provide up to 43% higher compute performance and 3.3 times more memory bandwidth, along with improved I/O performance for database and data analytics workloads.
+3. Where to use (use case):
+- C8id instances: Ideal for compute-intensive tasks like video encoding and media processing.
+- M8id instances: Best for balanced compute and memory needs with high-speed storage, suitable for data logging and medium-sized data stores.</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M8i and M8i-flex instances are now available in Canada West (Calgary) region</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/ec2-m8i-m8i-flex-canada-west/</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has launched M8i and M8i-flex instances in Canada West (Calgary), powered by custom Intel Xeon 6 processors, offering enhanced performance and price-performance.
+2. Outcome (impact):
+   Users can achieve up to 20% better performance and up to 15% better price-performance for various workloads, including databases, web applications, and AI models.
+3. Where to use (use case):
+   Ideal for web and application servers, microservices, data stores, virtual desktops, enterprise applications, and large-scale SAP workloads.</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Amazon GameLift Servers enhanced DDoS Protection now available</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-gamelift-servers-enhanced-ddos-protection</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon GameLift Servers now offers Enhanced DDoS Protection, providing proactive mitigations against common DDoS attacks at no extra cost.
+2. Outcome (impact):
+   Enhanced protection against volumetric DDoS attacks, ensuring smoother gameplay and better server availability for gamers.
+3. Where to use (use case):
+   Ideal for game developers running servers on Amazon GameLift Servers to safeguard against common DDoS threats.</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>Amazon GameLift</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>AWS Glue now supports catalog federation for remote Apache Iceberg catalogs in AWS GovCloud (US) regions</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-glue-catalog-federation-iceberg-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 20:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Glue now supports catalog federation for remote Iceberg catalogs in AWS GovCloud (US) regions, enabling secure access to Iceberg tables in Amazon S3 via various AWS analytics engines.
+2. Outcome (impact):
+   This feature allows data teams to query Iceberg tables in remote catalogs without moving data, ensuring real-time metadata synchronization and up-to-date query results, while maintaining consistent security controls.
+3. Where to use (use case):
+   Ideal for organizations requiring secure, real-time access to Iceberg tables stored in Amazon S3 and cataloged in remote Iceberg catalogs, using preferred AWS analytics engines like Amazon Redshift, Amazon EMR, and Amazon Athena.</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -37835,7 +38243,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-26 03:57:15</t>
+          <t>2026-08-27 14:00:58</t>
         </is>
       </c>
     </row>
@@ -37846,7 +38254,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -37856,7 +38264,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4896</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="7">
@@ -37866,7 +38274,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1637</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="8">
@@ -37876,7 +38284,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000348</v>
+        <v>0.000294</v>
       </c>
     </row>
     <row r="9">
@@ -37886,7 +38294,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000465</v>
+        <v>0.00041</v>
       </c>
     </row>
     <row r="10">
@@ -37896,7 +38304,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000813</v>
+        <v>0.000704</v>
       </c>
     </row>
     <row r="11">
@@ -37906,7 +38314,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.062327</v>
+        <v>0.063031</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1018"/>
+  <dimension ref="A1:F1031"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -38178,6 +38178,490 @@
       <c r="F1018" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Cosmos3-Edge, Cosmos3-Nano, and Cosmos3-Super models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/cosmos3-edge-cosmos3-nano-cosmos3-super-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 22:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+NVIDIA's Cosmos3-Edge, Cosmos3-Nano, and Cosmos3-Super models are now available on Amazon SageMaker JumpStart, enhancing physical AI capabilities for robotics and autonomous systems.
+2. Outcome (Impact):
+These models enable AWS customers to build advanced AI systems with real-time reasoning, physics-aware world generation, and high-fidelity simulation, improving the efficiency and effectiveness of AI applications in physical environments.
+3. Where to Use (Use Case):
+- Cosmos3-Edge: On-device robot control and real-time visual reasoning on edge hardware.
+- Cosmos3-Nano: Physics-aware world generation and physical reasoning for compact AI systems.
+- Cosmos3-Super: Large-scale simulation, synthetic data generation, and policy learning workflows.</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Muse-Glimmer-30B and Qwen 3.8-27B models now available on Amazon SageMaker JumpStart</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/01/muse-glimmer-30b-qwen-3.8-27b-on-sagemaker-jumpstart/</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 22:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Meta's Muse-Glimmer-30B and Alibaba's Qwen 3.8-27B models are now available on Amazon SageMaker JumpStart, enhancing enterprise AI capabilities.
+2. Outcome (impact):  
+These models enable high-performance, scalable AI solutions for autonomous agentic tasks and multimodal reasoning, improving efficiency and reliability in enterprise applications.
+3. Where to use (use case):  
+Ideal for autonomous local agentic workflows, multi-step reasoning tasks, and multimodal understanding in enterprise settings.</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Amazon Redshift streaming can now ingest 10MiB records from Amazon Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/redshift-streaming-supports-kds-10mib-records</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 21:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now supports streaming ingestion of 10 MiB records from Amazon Kinesis Data Streams, simplifying high-volume data pipelines.
+2. Outcome (impact):
+This update allows for larger data payloads to be streamed directly into Redshift, enhancing efficiency and enabling new use cases for large-record workloads.
+3. Where to use (use case):
+Ideal for scenarios requiring high-volume data ingestion, such as real-time analytics, large-scale data processing, and applications needing to handle significant data payloads.</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Amazon Redshift integrates with Agent Toolkit for AWS for AI-assisted data warehouse management</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/redshift-agenttoolkit-for-ai-assisted-datawarehouse-mgmt</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 20:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Redshift now integrates with the Agent Toolkit for AWS, enabling AI agents to manage and migrate data warehouses more effectively.
+2. Outcome (impact):  
+This integration allows for more efficient data warehouse management and migrations by leveraging AI agents, reducing manual effort and errors.
+3. Where to use (use case):  
+Ideal for data analysts and engineers who need to build, query, troubleshoot, and migrate data warehouses using AI-assisted tools.</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>Service name: Amazon Redshift  
+Category: Analytics</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Amazon EC2 X8i instances are now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-x8i-europe-milan-spain/</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 18:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 X8i instances are now available in Europe (Milan) and Europe (Spain), offering enhanced performance and memory capacity for memory-intensive workloads.
+2. Outcome (impact):
+   Users can now leverage higher performance and memory bandwidth for applications like SAP HANA, large databases, and data analytics in additional regions.
+3. Where to use (use case):
+   Ideal for memory-intensive workloads such as SAP HANA, large databases, data analytics, and Electronic Design Automation (EDA).</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery introduces Recovery Plans for orchestrated application recovery</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/elastic-disaster-recovery-plans/</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Elastic Disaster Recovery now offers Recovery Plans to automate the sequential launch of multi-server applications during recovery and drills.
+2. Outcome (impact):
+   This feature reduces recovery time, eliminates errors during high-stress scenarios, and ensures consistent and predictable application recovery.
+3. Where to use (use case):
+   Ideal for organizations running complex applications composed of databases, application tiers, and supporting services that require a specific launch order.</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>AWS Elastic Disaster Recovery</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore expands to two new regions</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/bedrock-agentcore-two-new-regions/</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore is now available in US West (N. California) and Asia Pacific (Hyderabad) regions, enabling faster agent deployment with enhanced security.
+2. Outcome (impact):
+Customers in these regions can now deploy agents with lower latency, benefiting from improved performance and reduced response times.
+3. Where to use (use case):
+Ideal for enterprises needing to build and run agents closer to their end users, ensuring faster, more reliable service delivery.</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer expands conversational analytics capabilities in the Africa (Cape Town) Region</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/connect-customer-analytics-cape-town/</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Connect Customer now offers enhanced conversational analytics in the Africa (Cape Town) Region, including generative AI summaries, real-time call analytics, and real-time rules.
+2. Outcome (impact):  
+Companies can improve customer experience, agent performance, and operational efficiency with AI-powered insights and reduced manual workload.
+3. Where to use (use case):  
+Use in customer service operations to monitor and improve live interactions, streamline post-contact analysis, and automate response actions.</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now automatically refreshes scheduling metrics</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-customer-scheduling-metrics/</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 17:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now automatically updates scheduling metrics, providing managers with real-time insights into schedule changes.
+2. Outcome (impact):
+   Workforce managers can quickly see the impact of schedule updates, such as changes in net available headcount and projected service levels, enabling faster and more informed decision-making.
+3. Where to use (use case):
+   Ideal for workforce management in contact centers to ensure optimal staffing levels and service quality.</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Amazon FSx for NetApp ONTAP now supports copying backups across AWS Regions and accounts</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/fsx-ontap-cross-region-backup-copy/</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 17:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon FSx for NetApp ONTAP now supports cross-Region and cross-account backup copying, enhancing data protection and compliance.
+2. Outcome (impact):  
+This update provides enhanced data protection, business continuity, and compliance by allowing users to store backup copies in different Regions and accounts.
+3. Where to use (use case):  
+Ideal for organizations needing to meet stringent data protection, compliance, and business continuity requirements by distributing backup copies across multiple AWS accounts and Regions.</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Amazon FSx for NetApp ONTAP</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>AWS Backup adds cross-Region and cross-account backup support for Amazon FSx for NetApp ONTAP</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-backup-amazon-fsx-netapp-cross-account-region/</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 17:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Backup now supports copying Amazon FSx for NetApp ONTAP backups across Regions and accounts for enhanced disaster recovery and protection.
+2. Outcome (impact):
+   This feature helps organizations meet cross-Region disaster recovery and business continuity goals while safeguarding backups from accidental deletion or account compromise.
+3. Where to use (use case):
+   Ideal for organizations needing to ensure data resilience and protection across multiple AWS accounts and Regions.</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Amazon EVS now supports i7i.metal-48xl Amazon EC2 instance type</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-evs-i7i-48xl</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 16:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EVS now supports the i7i.metal-48xl EC2 instance, providing enhanced compute performance and cost benefits for VMware workloads.
+2. Outcome (impact):  
+Users can achieve up to 23% better compute performance and over 10% better price performance, enabling more efficient scaling and cost management for their VMware environments.
+3. Where to use (use case):  
+Ideal for businesses needing high compute power for large-scale VMware-based applications, such as data analytics, large databases, and complex virtualized environments.</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Amazon Elastic VMware Service (Amazon EVS)</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL now supports foreign key constraints</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aurora-dsql-foreign-key-constraints/</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Aurora DSQL now supports foreign key constraints, allowing developers to enforce referential integrity across tables.
+2. Outcome (impact):
+   This feature enhances data integrity by ensuring that references between tables are valid, preventing orphaned records and maintaining consistent data relationships.
+3. Where to use (use case):
+   Ideal for applications requiring strict data integrity, such as e-commerce platforms, CRM systems, and any application where data consistency between related tables is critical.</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Amazon Aurora DSQL</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -38243,7 +38727,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 14:00:58</t>
+          <t>2026-08-28 15:12:42</t>
         </is>
       </c>
     </row>
@@ -38254,7 +38738,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -38264,7 +38748,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4140</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="7">
@@ -38274,7 +38758,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1443</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="8">
@@ -38284,7 +38768,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000294</v>
+        <v>0.000331</v>
       </c>
     </row>
     <row r="9">
@@ -38294,7 +38778,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00041</v>
+        <v>0.000478</v>
       </c>
     </row>
     <row r="10">
@@ -38304,7 +38788,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000704</v>
+        <v>0.000809</v>
       </c>
     </row>
     <row r="11">
@@ -38314,7 +38798,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.063031</v>
+        <v>0.06383999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1031"/>
+  <dimension ref="A1:F1039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -38662,6 +38662,303 @@
       <c r="F1031" t="inlineStr">
         <is>
           <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8gn instances are now available in AWS Europe (Paris) region</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-c8gn-europe-paris/</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8gn instances, powered by AWS Graviton4 processors, are now available in the Europe (Paris) region, offering up to 30% better compute performance and enhanced networking capabilities.
+2. Outcome (impact):
+   Users can now leverage improved compute performance and higher network bandwidth for network-intensive workloads, leading to better scalability and cost optimization.
+3. Where to use (use case):
+   Ideal for network virtual appliances, data analytics, CPU-based AI/ML inference, and tightly coupled cluster workloads requiring lower latency and improved performance.</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory now supports fine-grained access control</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/agentcorememory-fine-grained-access-control</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock AgentCore Memory now supports fine-grained access control (FGAC) for secure, per-user memory isolation.
+2. Outcome (impact):  
+This update allows for enhanced security by enforcing memory isolation and restricting access based on user identity without custom authorization logic.
+3. Where to use (use case):  
+Use this feature to secure user data in multi-tenant applications, ensuring that each user can only access their own data and specific operations are permitted based on user roles.</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>Service name: Amazon Bedrock  
+Category: Security</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory now supports flexible namespace variables</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/agentcorememory-flexible-namespaces</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Memory now allows developers to define flexible namespace variables to manage long-term memories in multi-tenant and complex-hierarchy applications.
+2. Outcome (impact):
+This update provides fine-grained control over memory organization, isolation, and access, preventing the creation of duplicate strategies and overloading built-in variables.
+3. Where to use (use case):
+Ideal for multi-tenant applications, complex-hierarchy systems, or any application requiring scoped long-term memory management based on organization, tenant, team, or environment.</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>AWS Transform now in scope for FedRAMP Class C</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-transform-fedramp-class-c/</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 19:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform is now FedRAMP Class C compliant in the US East (Ohio) Region, enabling secure application and workload deployment for federal agencies.
+2. Outcome (impact):
+Federal agencies can now use AWS Transform for migrations and modernizations while meeting FedRAMP Moderate baseline compliance requirements, accelerating project timelines.
+3. Where to use (use case):
+Government agencies needing to migrate and modernize their IT infrastructures to the cloud while adhering to FedRAMP Class C security standards.</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B300 instances are now available in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-p6-b300-instances-available-additional-regions</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 17:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 P6-B300 instances are now available in Asia Pacific (Hyderabad) and South America (Sao Paulo) Regions, offering enhanced GPU, networking, and memory capabilities for AI workloads.
+2. Outcome (impact):
+P6-B300 instances provide significant improvements in networking bandwidth, GPU memory, and TFLOPS, enabling faster training times and higher throughput for large-scale AI models.
+3. Where to use (use case):
+Ideal for training and deploying large foundation models (FMs) and large language models (LLMs) with sophisticated techniques.</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Amazon Aurora MySQL 3.13 (compatible with MySQL 8.0.45) is generally available</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-aurora-mysql-313-available/</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Aurora MySQL 3.13, compatible with MySQL 8.0.45, is now available with community fixes and Aurora-specific enhancements.
+2. Outcome (impact):
+Aurora users can now leverage the latest MySQL 8.0.45 features and improvements, ensuring better performance, security, and compatibility.
+3. Where to use (use case):
+Ideal for applications requiring high availability, scalability, and global resilience with full MySQL compatibility.</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch agent adds support for journald logs</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-cloudwatch-agent-journald/</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CloudWatch agent now natively supports collecting systemd journal logs from Linux instances, preserving metadata and reducing configuration complexity.
+2. Outcome (impact):
+This update simplifies log collection for modern Linux distributions using systemd, allowing direct ingestion of logs into CloudWatch Logs without intermediate file writes, thus improving efficiency and reducing costs.
+3. Where to use (use case):
+Ideal for administrators managing Linux-based infrastructures, particularly those using Amazon Linux 2023 or other systemd-based distributions, to streamline log monitoring and management.</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>SpaceXAI Grok 4.6 now available on Amazon Bedrock in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/spacexai-grok-4-6-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 13:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock in AWS GovCloud (US) now offers SpaceXAI Grok 4.6, a powerful model for coding, agentic tasks, and knowledge work, with a 500k context window and configurable reasoning efforts.
+2. Outcome (impact):
+Customers can leverage Grok 4.6 for advanced coding, interactive, and visual tasks at scale, enhancing productivity and efficiency in knowledge-intensive work.
+3. Where to use (use case):
+Ideal for software development, data analysis, research, and complex problem-solving tasks requiring long-term context and high reasoning capabilities.</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -38727,7 +39024,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:12:42</t>
+          <t>2026-08-29 09:54:26</t>
         </is>
       </c>
     </row>
@@ -38738,7 +39035,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -38748,7 +39045,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4667</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="7">
@@ -38758,7 +39055,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1683</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8">
@@ -38768,7 +39065,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000331</v>
+        <v>0.000205</v>
       </c>
     </row>
     <row r="9">
@@ -38778,7 +39075,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000478</v>
+        <v>0.000308</v>
       </c>
     </row>
     <row r="10">
@@ -38788,7 +39085,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000809</v>
+        <v>0.000512</v>
       </c>
     </row>
     <row r="11">
@@ -38798,7 +39095,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06383999999999999</v>
+        <v>0.06435200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1039"/>
+  <dimension ref="A1:F1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -38959,6 +38959,820 @@
       <c r="F1039" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB now supports direct major version upgrades to version 8.0</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/documentdb-major-version-upgrade-8-0/</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 22:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon DocumentDB now allows direct upgrades from versions 3.6 and 4.0 to 8.0, preserving data and settings.
+2. Outcome (impact):
+   Users can access the latest features, security patches, and performance improvements without intermediate steps.
+3. Where to use (use case):
+   Ideal for applications requiring the latest MongoDB features and enhanced security, such as modern web apps and real-time analytics.</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Amazon DocumentDB</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Partner Revenue Measurement expands service coverage for User Agent string capability</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/partner-revenue-measurement-user-agent-expansion/</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Partner Revenue Measurement now supports additional services through User Agent string, enhancing visibility on revenue impact and product consumption.
+2. Outcome (impact):
+Partners gain increased visibility into the revenue driven by their solutions across more AWS services, improving their understanding of product consumption patterns.
+3. Where to use (use case):
+This is useful for AWS Partners who want to track and analyze the revenue impact of their solutions across a broader range of AWS services.</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>AWS Partner Central</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>AWS Agent Registry agents and MCP servers now available in Amazon Quick</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-agent-registry-agents-mcp-servers-quick/</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 21:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Agent Registry agents and MCP servers are now accessible within Amazon Quick, streamlining resource discovery and integration for users.
+2. Outcome (impact):
+This integration reduces manual configuration efforts, allowing business users to easily access and share technical resources within their Amazon Quick workspace.
+3. Where to use (use case):
+Ideal for organizations using Amazon Bedrock AgentCore to build agents and tools, enabling seamless access and collaboration between technical and business teams.</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Amazon Redshift now supports AWS IAM Identity Center authentication with enhanced VPC routing</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-redshift-supports-idc-evr</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 21:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Redshift now supports IAM Identity Center authentication with enhanced VPC routing, enabling secure, private access to clusters and serverless workgroups.
+2. Outcome (impact):  
+   This update allows organizations to meet data residency, regulatory, and network-isolation requirements by keeping all Redshift traffic within the AWS network, enhancing security and compliance.
+3. Where to use (use case):  
+   Ideal for organizations that need to restrict public internet egress for analytics workloads, ensuring all data traffic remains within the AWS network and VPC.</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB is now available in 8 additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-timestream-influxdb-regions/</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 19:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Timestream for InfluxDB is now available in 8 new regions, enabling developers to run managed InfluxDB databases on AWS.
+2. Outcome (impact):
+This expansion allows developers to deploy real-time time-series applications globally with enhanced durability, high availability, and scalability.
+3. Where to use (use case):
+Ideal for IoT applications, monitoring solutions, and any real-time analytics requiring time-series data storage.</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Amazon Connect Global Resiliency now supports cross-region routing of contacts across two active AWS regions</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-connect-global-resiliency-cross-region-routing/</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 19:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect now supports cross-region routing of contacts across two active AWS regions, enhancing contact center resiliency and availability.
+2. Outcome (impact):
+   Improves contact center reliability by routing contacts to the longest-available agent in either region, ensuring continuous operation and minimizing downtime.
+3. Where to use (use case):
+   Ideal for contact centers requiring high availability and disaster recovery capabilities, ensuring seamless agent connectivity and operational continuity.</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Amazon Redshift now supports Apache Iceberg v3 tables</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-redshift-supports-apache-iceberg-v3</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 18:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift now supports Apache Iceberg v3 tables, enabling advanced features like default column values, row lineage, and deletion vectors for efficient data lake operations.
+2. Outcome (impact):
+This update simplifies schema evolution, enhances incremental data processing, and improves performance for high-frequency update and delete operations.
+3. Where to use (use case):
+Ideal for data lakes requiring efficient schema changes, incremental data pipelines, and high-performance update and delete operations.</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>Amazon EC2 R9g and R9gd memory optimized instances are now available</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-ec2-r9g-and-r9gd-memory-optimized-instances-are-now-available/</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 18:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 introduces R9g and R9gd instances with AWS Graviton5 processors, offering enhanced performance for memory-intensive workloads.
+2. Outcome (impact):
+Up to 25% better compute performance, up to 30% faster for databases, and up to 35% faster for web applications and machine learning.
+3. Where to use (use case):
+Ideal for databases, in-memory caches, real-time big data analytics, containerized applications, and various programming languages.</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Amazon Cognito now supports machine-to-machine authorization without a user pool domain</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-cognito-get-client-token/</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Cognito now supports machine-to-machine authorization without a user pool domain using the GetClientToken API, enabling seamless service-to-service communication.
+2. Outcome (impact):
+   This update allows applications, microservices, and automated workloads to authenticate and obtain access tokens directly, simplifying M2M authorization processes.
+3. Where to use (use case):
+   Ideal for applications requiring secure service-to-service communication, such as microservices, serverless functions, and automated workloads.</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>Amazon Cognito</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>AWS Lambda recursive loop detection is now available in all commercial AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/lambda-recursion-regions</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 17:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda's recursive loop detection is now available in all commercial regions, automatically preventing runaway workloads caused by misconfigurations or code defects.
+2. Outcome (impact):
+This feature helps prevent unintended usage and unexpected billing by stopping recursive loops between Lambda functions and event sources like S3, SQS, and SNS.
+3. Where to use (use case):
+Ideal for applications using AWS Lambda with event-driven architectures to ensure stability and cost efficiency by avoiding recursive loops.</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>Amazon Aurora serverless is now available with 30% better performance and smarter scaling in additional AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-aurora-serverless-performance-improvement-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 16:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Aurora serverless now offers 30% better performance and smarter scaling in five new regions, enhancing efficiency for unpredictable workloads.
+2. Outcome (impact):
+   Users can expect improved database performance and cost-efficiency, particularly for applications with fluctuating traffic like agentic AI services.
+3. Where to use (use case):
+   Ideal for web applications, API services, and agentic AI applications that experience traffic bursts and idle periods.</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service adds new Cluster Insights for faster diagnosis of cluster status</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/opensearch-cluster-status-insight/</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 15:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Service introduces 17 new Cluster Insights to quickly diagnose and resolve Red and Yellow cluster status issues.
+2. Outcome (impact):
+   These new insights enable faster identification and resolution of cluster problems, reducing downtime and improving cluster stability.
+3. Where to use (use case):
+   Ideal for managing and maintaining OpenSearch clusters, ensuring optimal performance and quick troubleshooting of issues.</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Service</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>AWS Agent Registry for centralized agent discovery and governance is now generally available</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-agent-registry-generally-available</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 15:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Agent Registry is now fully available, offering a centralized, governed catalog for discovering and managing agents and tools within your organization.
+2. Outcome (Impact):
+   Enhances visibility and governance of AI tools and agents, reduces redundancy, and streamlines the discovery process across teams and accounts.
+3. Where to Use (Use Case):
+   Ideal for organizations looking to manage and discover AI agents, tools, and custom resources efficiently, ensuring compliance and optimizing resource utilization.</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>AWS Agent Registry</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>AWS announces AWS Interconnect - multicloud connectivity with Microsoft Azure in preview</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-announces-AWS-interconnect-multicloud-microsoft-azure-preview/</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched a public preview of AWS Interconnect, enabling seamless multicloud connectivity with Microsoft Azure, simplifying the management of private connections between AWS and Azure.
+2. Outcome (impact):
+AWS Interconnect simplifies the complexities of managing multicloud environments by providing a single, managed experience for private connections between AWS and Azure, reducing the need for DIY network management and enhancing interoperability.
+3. Where to use (use case):
+This service is ideal for organizations adopting multicloud strategies who need to connect their applications across AWS and Azure, ensuring high-speed, secure, and reliable data transfer between the two cloud platforms.</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>AWS Interconnect</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>Amazon MSK Connect now supports restarting connectors</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-msk-connect-restart/</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MSK Connect now allows restarting connectors and tasks, enabling seamless recovery for streaming data pipelines without downtime.
+2. Outcome (impact):
+This feature reduces operational overhead and downtime by allowing quick recovery from failures and transient issues.
+3. Where to use (use case):
+Ideal for managing streaming data pipelines in Amazon MSK, ensuring continuous data flow and minimizing disruptions.</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Amazon MSK Connect</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications is now available in three new AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-workspaces-applications-region-expansion</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS has expanded Amazon WorkSpaces Applications to three new regions: Europe (Zurich), Asia Pacific (Osaka), and Canada West (Calgary).
+2. Outcome (impact):
+   This expansion enables users to deploy applications closer to their end users, providing a more responsive experience and meeting data residency and compliance requirements.
+3. Where to use (use case):
+   Ideal for organizations needing to stream desktop applications to users in Europe, Asia Pacific, and Canada, ensuring low latency and compliance with local data regulations.</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>AWS Workload Credentials Provider is now available as a one-click install for Linux and Windows</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/workload-credentials-provider-install/</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Workload Credentials Provider (AWCP) is now available as a one-click install on Amazon Linux and Windows, simplifying secret management.
+2. Outcome (impact):  
+   Reduces setup complexity from a multi-step process to a single command, making it easier for developers to manage secrets and certificates.
+3. Where to use (use case):  
+   Ideal for developers and DevOps teams managing secrets and certificates for applications running on Amazon EC2 instances.</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>AWS Secrets Manager</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>Automated Security Response on AWS adds AI Toolkit for custom remediations</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/automated-security-response-adds-AI-toolkit/</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces an AI-driven toolkit for Automated Security Response, enabling custom remediations and expanding coverage to Amazon Inspector, GuardDuty, and Macie.
+2. Outcome (impact):  
+Reduces remediation development time, minimizes misconfigurations, and enhances response to security threats with automated actions and centralized management.
+3. Where to use (use case):  
+Ideal for organizations needing efficient, automated security responses to threats like credential compromises, unpatched vulnerabilities, and sensitive data exposure.</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Automated Security Response on AWS</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>AWS Elastic Beanstalk now supports Active Directory domain join for Windows Server environments</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/elastic-beanstalk-active-directory-domain-join/</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Elastic Beanstalk now natively supports Active Directory domain join for Windows Server environments, eliminating the need for custom scripts.
+2. Outcome (impact):
+   Simplifies the management of domain-joined Windows workloads, enhances security with Windows-integrated authentication, and ensures seamless integration with existing Active Directory infrastructure.
+3. Where to use (use case):
+   Ideal for organizations needing to run domain-joined Windows applications on Elastic Beanstalk, ensuring compliance with internal security policies and leveraging existing domain resources.</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>Elastic Beanstalk</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams announces data delivery to general purpose Amazon S3 buckets</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/kinesis/data-delivery-general-purpose-s3-buckets</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Sat, 29 Aug 2026 06:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Kinesis Data Streams now directly delivers streaming data to general purpose S3 buckets, reducing costs and complexity.
+2. Outcome (impact):
+Reduces data delivery costs by up to 60% and simplifies the process of ingesting streaming data into S3.
+3. Where to use (use case):
+Ideal for batch analytics, log delivery, compliance retention, and data replay scenarios.</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams announces streaming tables, delivering data to Apache Iceberg tables on Amazon S3 Tables</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/kinesis/data-delivery-s3-tables</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 23:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Kinesis Data Streams now offers streaming tables, a fully serverless feature that delivers data to Apache Iceberg tables on Amazon S3, reducing costs and improving query performance.
+2. Outcome (impact):
+Reduces data delivery costs by up to 50% and downstream query costs by up to 30% by eliminating the need for custom pipelines and managing small file issues.
+3. Where to use (use case):
+Ideal for real-time analytics and AI/ML feature pipelines that require the freshest data, enabling efficient data ingestion and query performance.</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>Amazon EMR on EKS now supports job run concurrency controls</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-emr-eks/</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 17:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EMR on EKS now supports job run concurrency controls, allowing you to limit the number of concurrent jobs and queue depth in multi-tenant environments.
+2. Outcome (impact):
+This feature helps prevent EKS cluster overload, avoids noisy-neighbor issues, and ensures critical workloads run predictably under heavy demand.
+3. Where to use (use case):
+Ideal for multi-tenant environments where multiple users or teams share EKS clusters and need to manage job execution efficiently.</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>Amazon EMR on EKS</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -39024,7 +39838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29 09:54:26</t>
+          <t>2026-09-01 08:30:23</t>
         </is>
       </c>
     </row>
@@ -39035,7 +39849,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -39045,7 +39859,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2882</v>
+        <v>8509</v>
       </c>
     </row>
     <row r="7">
@@ -39055,7 +39869,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1084</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="8">
@@ -39065,7 +39879,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000205</v>
+        <v>0.000604</v>
       </c>
     </row>
     <row r="9">
@@ -39075,7 +39889,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000308</v>
+        <v>0.00076</v>
       </c>
     </row>
     <row r="10">
@@ -39085,7 +39899,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000512</v>
+        <v>0.001364</v>
       </c>
     </row>
     <row r="11">
@@ -39095,7 +39909,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06435200000000001</v>
+        <v>0.065716</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1061"/>
+  <dimension ref="A1:F1072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -39773,6 +39773,413 @@
       <c r="F1061" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>Amazon Quick now lets you build custom apps with natural language  -</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-quick-custom-apps-natural-language/</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 21:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick enables users to create custom applications using natural language, simplifying app development and integration with existing business tools.
+2. Outcome (impact):
+Reduces app development time from months to minutes, enhances productivity, and streamlines business processes by integrating with various tools and data sources.
+3. Where to use (use case):
+Ideal for product managers, finance leads, HR partners, and ops analysts to quickly build project trackers, customer dashboards, and training portals without coding.</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>AWS Deadline Cloud now supports sharing job bundles</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/deadline-cloud/job-bundle-sharing</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 20:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+   AWS Deadline Cloud now enables teams to share job bundles easily, streamlining the distribution and reuse of render job templates without manual file transfers.
+2. Outcome (impact)
+   This update significantly enhances collaboration and efficiency within teams by simplifying the process of sharing job templates, reducing manual effort, and ensuring consistency across projects.
+3. Where to use (use case)
+   Ideal for visual effects, animation, product design, simulation, and gaming teams that rely on compute-intensive workloads in the cloud.</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>Deadline Cloud</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Database Insights now supports self-managed PostgreSQL</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/database-insights-self-managed-postgresql/</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS CloudWatch Database Insights now supports self-managed PostgreSQL, enabling unified monitoring of PostgreSQL instances on EC2, RDS, and Aurora.
+2. Outcome (impact):  
+This update allows for comprehensive monitoring and troubleshooting of self-managed PostgreSQL databases, improving database fleet management and performance.
+3. Where to use (use case):  
+Ideal for organizations managing PostgreSQL databases on EC2, providing them with the same monitoring capabilities as AWS-managed databases.</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch Database Insights</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams now supports a dry run feature to validate API requests</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-kinesis-data-streams-api/</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 19:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Kinesis Data Streams now offers a dry run feature to validate API requests without executing them, ensuring correct permissions before production use.
+2. Outcome (impact):
+   This feature prevents unintended data writes into production streams by allowing customers to safely test their API requests, reducing the risk of errors due to permission issues.
+3. Where to use (use case):
+   Ideal for developers and operations teams who need to ensure their applications have the correct permissions to interact with Kinesis Data Streams before making actual requests.</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>Amazon Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>AWS Backup now supports protecting more than 1,000 Amazon S3 buckets per account</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-backup-more-than-1000-s3-buckets/</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Backup now supports protecting more than 1,000 Amazon S3 buckets per account, aligning with your account's S3 bucket quota.
+2. Outcome (impact):  
+This update allows users to back up all general-purpose S3 buckets in their account, enhancing data protection capabilities without requiring changes to existing backup plans.
+3. Where to use (use case):  
+Ideal for organizations with large numbers of S3 buckets, ensuring comprehensive backup and restore capabilities for all their S3 data.</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>AWS Backup</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer dashboards now support compact mode</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/connect-dashboards-compact-mode/</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer dashboards now feature a compact mode, enhancing data density and visibility for supervisors.
+2. Outcome (impact):
+Supervisors can view more operational data at once, improving efficiency and enabling quicker identification of non-adherent agents.
+3. Where to use (use case):
+Ideal for contact center supervisors managing multiple agents on smaller screens, ensuring they can monitor their team without excessive scrolling.</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>Amazon MWAA supports Apache Airflow version 3.3.1</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-mwaa-apache-airflow-3-3-1/</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon MWAA now supports Apache Airflow 3.3.1, introducing stateful tasks, multi-language support, and enhanced stability.
+2. Outcome (impact):  
+Users can leverage stateful tasks for better job management and write task logic in Java or Go, expanding their workflow capabilities.
+3. Where to use (use case):  
+Ideal for orchestrating complex data pipelines and workflows in the cloud with improved reliability and flexibility.</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>Amazon MWAA</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Claude Fable 5.1, Anthropic's new frontier model is now available on AWS</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-fable-5-1-aws/</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Anthropic's latest model, Claude Fable 5.1, is now available on AWS, offering enhanced reasoning capabilities for coding, research, and enterprise tasks.
+2. Outcome (Impact):  
+   Improved performance in complex reasoning tasks, reduced incorrect confident answers, and better handling of long-running projects.
+3. Where to Use (Use Case):  
+   Ideal for software development, scientific research, and enterprise workflows requiring extended, high-stakes analysis.</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch now supports warm-up periods for alarms</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-cloudwatch-alarms-warmup-period</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon CloudWatch now supports warm-up periods for alarms, delaying evaluation to avoid false notifications during resource startup.
+2. Outcome (impact):  
+   Reduces unnecessary notifications and noise from missing data during the initial startup phase of new resources or services.
+3. Where to use (use case):  
+   Ideal for CI/CD pipelines where new microservices are deployed and need time to start publishing metrics without triggering alarms.</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom now supports the latest CU and GDR updates for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-custom-supports-latest-cu-gdr-microsoft-sql-server/</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS Custom now supports the latest CU and GDR updates for Microsoft SQL Server 2019 and 2022, including security fixes.
+2. Outcome (impact):
+   Enhanced security and performance for SQL Server instances on Amazon RDS Custom, addressing critical vulnerabilities.
+3. Where to use (use case):
+   Ideal for enterprise applications requiring the latest SQL Server updates for compliance and security.</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>Amazon RDS Custom</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor introduces in-console analytics dashboard for ad monetization and streaming performance</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/mediatailor-analytics-dashboard</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 21:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental MediaTailor now features an in-console analytics dashboard for monitoring ad monetization and streaming performance across regions.
+2. Outcome (impact):
+Publishers can now effectively track and analyze key performance metrics, enabling better decision-making and optimization of ad monetization strategies.
+3. Where to use (use case):
+Ideal for media streaming services and content providers looking to maximize ad revenue and improve viewer experience by monitoring and adjusting ad delivery performance.</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -39838,7 +40245,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 08:30:23</t>
+          <t>2026-09-02 07:47:48</t>
         </is>
       </c>
     </row>
@@ -39849,7 +40256,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -39859,7 +40266,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8509</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="7">
@@ -39869,7 +40276,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2675</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="8">
@@ -39879,7 +40286,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000604</v>
+        <v>0.000288</v>
       </c>
     </row>
     <row r="9">
@@ -39889,7 +40296,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00076</v>
+        <v>0.00037</v>
       </c>
     </row>
     <row r="10">
@@ -39899,7 +40306,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001364</v>
+        <v>0.0006579999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -39909,7 +40316,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.065716</v>
+        <v>0.066374</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1072"/>
+  <dimension ref="A1:F1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -40180,6 +40180,487 @@
       <c r="F1072" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Web Search on Amazon Bedrock is now available in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-web-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 17:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock's Web Search tool is now available in AWS GovCloud (US-West), providing grounded web results for government and public-sector workloads.
+2. Outcome (impact):  
+Enhanced ability for supported GPT models to provide accurate, up-to-date information with traceable sources, improving reliability and compliance for sensitive applications.
+3. Where to use (use case):  
+Ideal for government and public-sector applications requiring real-time, accurate information, such as current events, recent releases, and live pricing.</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer expands automated performance evaluations to Malay</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-connect-customer-automated-evaluations-malay/</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect Customer now automates performance evaluations for agents in Malay using generative AI, supporting cross-language assessments.
+2. Outcome (impact):
+   Enables multilingual contact centers to standardize performance evaluations across different languages, improving efficiency and consistency.
+3. Where to use (use case):
+   Ideal for multilingual contact centers that need to evaluate agent performance in multiple languages, ensuring unbiased and consistent evaluations.</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Amazon Quick adds new tool settings and Model Context Protocol (MCP) sync support for connectors</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-quick-adds-tool-settings-mcp-sync/</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 16:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Quick introduces enhanced tool settings and Model Context Protocol (MCP) sync to improve control and update management for its connectors.
+2. Outcome (impact):
+   Admins and connector owners can better manage which tools are available to end users, ensuring compliance and up-to-date information.
+3. Where to use (use case):
+   Ideal for organizations utilizing Amazon Quick connectors in various workflows across chat, agents, apps, flows, and research to streamline tool management and ensure up-to-date information.</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer announces general availability of agentic CX designer</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/agentic-cx-designer/</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Connect introduces Agentic CX Designer, a no-code tool for creating AI-powered self-service experiences, enabling rapid deployment of voice and digital customer service solutions.
+2. Outcome (Impact):
+   Businesses can significantly reduce the time to market for new customer service experiences, enhance customer satisfaction through more efficient and accurate service, and empower non-technical teams to innovate without coding.
+3. Where to Use (Use Case):
+   Ideal for customer service operations, helpdesks, and contact centers aiming to improve response times and service accuracy through AI-driven self-service tools.</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Amazon Connect</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Second-generation AWS Outposts racks now in the AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-outposts-govcloud-us-regions/</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Second-gen AWS Outposts racks are now available in AWS GovCloud (US) Regions, enabling consistent hybrid experiences with low latency and data residency compliance.
+2. Outcome (impact):  
+   Organizations can now deploy Outposts in the AWS GovCloud Regions, optimizing latency and ensuring data residency, thus enhancing hybrid cloud capabilities for public sector and sensitive workloads.
+3. Where to use (use case):  
+   Ideal for government agencies and enterprises needing to run sensitive workloads locally while maintaining connectivity to AWS services in the home Region for management and processing.</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>AWS Outposts</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>AWS Config now supports 60 new resource types</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-config-new-resource-types/</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Config now supports 60 new resource types, enhancing coverage across services like Amazon Bedrock, EC2, SageMaker, and AWS Organizations.
+2. Outcome (impact):
+This expansion allows for more comprehensive monitoring, assessment, auditing, and remediation of AWS resources, improving overall environment management.
+3. Where to use (use case):
+Use AWS Config to monitor and manage compliance and security across the newly supported resources in all available AWS Regions.</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>AWS Config</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>AWS User Experience Customization (UXC) is now available in all commercial AWS Regions</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/aws-uxc-aws-regions</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS User Experience Customization (UXC) is now available globally, allowing administrators to personalize the AWS Management Console from any region.
+2. Outcome (impact):
+This update simplifies the management of console customizations, enabling administrators to configure settings more conveniently and integrate them with existing infrastructure automation.
+3. Where to use (use case):
+UXC is ideal for organizations that need to standardize the AWS Management Console experience across multiple regions, ensuring consistent branding and service visibility for their users.</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>AWS Management Console</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>AWS Lambda now supports SnapStart for container image functions</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/07/aws-lambda-snapstart-container/</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda now supports SnapStart for container image functions, reducing startup times to sub-second levels.
+2. Outcome (impact):
+   This enhancement improves the responsiveness and scalability of applications by significantly decreasing the initialization time for Lambda functions packaged as container images.
+3. Where to use (use case):
+   Ideal for latency-sensitive workloads such as machine learning inference and interactive APIs that require quick response times.</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio CI/CD adds notebook promotion and AI-assisted manifest generation</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/sagemaker-cicd-notebook-ai-manifest/</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Unified Studio CI/CD introduces AI-assisted manifest generation and native notebook promotion to streamline project deployment across environments.
+2. Outcome (impact):
+   These new capabilities accelerate the transition from project to production, ensuring best-practice defaults and reducing manual effort for data teams.
+3. Where to use (use case):
+   Ideal for data science teams working in SageMaker Unified Studio, these features help manage and deploy machine learning projects more efficiently across different stages of development.</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Amazon RDS for SQL Server supports additional SQL trace flags</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/rds-sqlserver-supports-additional-trace-flags/</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for SQL Server now supports 18 additional SQL trace flags for fine-tuning performance and addressing specific challenges.
+2. Outcome (impact):
+   This update provides database administrators with greater flexibility to optimize and stabilize SQL Server workloads in a managed RDS environment.
+3. Where to use (use case):
+   Use these trace flags to optimize query plan, improve DDL performance, enhance availability group replication, and mitigate known engine bugs.</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>AWS Marketplace reduces listing fee for professional services in multi-product solutions</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-marketplace-fee-professional-services/</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Marketplace now offers a 0% listing fee for professional services included in multi-product solutions, reducing costs for service providers.
+2. Outcome (impact):
+This change lowers the cost for Partners selling professional services through AWS Marketplace, enhancing their profitability while maintaining billing benefits.
+3. Where to use (use case):
+Ideal for Partners offering bundled software and professional services, allowing them to attract more customers by reducing transaction costs.</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>AWS Marketplace now supports auto-renewals for private offers</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-marketplace-auto-renewals-for-private-offers</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Marketplace now supports auto-renewals for private offers, ensuring seamless subscription continuity with negotiated terms.
+2. Outcome (impact):  
+   Reduces procurement overhead and prevents subscription lapses by automatically renewing agreements with agreed terms.
+3. Where to use (use case):  
+   Ideal for businesses that rely on consistent access to specific software and services, ensuring uninterrupted operations.</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Claude Fable 5.1, Anthropic's new frontier model is now available on AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/claude-fable-5-1-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Anthropic's latest model, Claude Fable 5.1, is now available on AWS GovCloud (US), designed for long-running, high-stakes tasks in coding, research, and enterprise workflows.
+2. Outcome (impact):
+   Fable 5.1 enhances productivity and reliability for regulated industries by providing robust, long-duration task support with improved safety and data retention features.
+3. Where to use (use case):
+   Ideal for complex coding projects, scientific research, and enterprise workflows requiring extended, reliable AI assistance.</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -40245,7 +40726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 07:47:48</t>
+          <t>2026-09-03 07:56:31</t>
         </is>
       </c>
     </row>
@@ -40256,7 +40737,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -40266,7 +40747,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4061</v>
+        <v>5061</v>
       </c>
     </row>
     <row r="7">
@@ -40276,7 +40757,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1302</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="8">
@@ -40286,7 +40767,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000288</v>
+        <v>0.000359</v>
       </c>
     </row>
     <row r="9">
@@ -40296,7 +40777,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00037</v>
+        <v>0.000452</v>
       </c>
     </row>
     <row r="10">
@@ -40306,7 +40787,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0006579999999999999</v>
+        <v>0.000811</v>
       </c>
     </row>
     <row r="11">
@@ -40316,7 +40797,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.066374</v>
+        <v>0.06718499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1085"/>
+  <dimension ref="A1:F1103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -40661,6 +40661,677 @@
       <c r="F1085" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Amazon ECS Managed Daemons now support non-critical daemons</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ecs-managed-daemons-non-critical/</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 22:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon ECS now supports non-critical Managed Daemons, ensuring mission-critical tasks remain uninterrupted even if auxiliary daemons fail.
+2. Outcome (impact):
+   Enhances reliability of mission-critical applications by allowing non-critical daemon failures to not affect application task execution, ensuring consistent service availability.
+3. Where to use (use case):
+   Ideal for environments where certain auxiliary tasks (e.g., logging, metrics collection) are not critical to the main application's operation, ensuring high availability of core services.</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B200 instances are now available in the AWS Asia Pacific (Hyderabad) Region</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ec2-p6-b200-instances-available-asia-pacific-hyderabad</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 19:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 P6-B200 instances with advanced GPUs are now available in the AWS Asia Pacific (Hyderabad) Region, offering enhanced performance for AI workloads.
+2. Outcome (Impact):
+These instances provide up to 2x performance improvement for AI training and inference, making them ideal for large-scale AI applications.
+3. Where to Use (Use Case):
+Ideal for AI training, machine learning inference, and data processing tasks requiring high computational power.</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Amazon EC2 P6-B300 instances are now available in the AWS Asia Pacific (Jakarta) Region</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ec2-p6-b300-instances-available-asia-pacific-jakarta</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 19:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon has launched P6-B300 instances in the AWS Asia Pacific (Jakarta) Region, featuring enhanced GPUs, memory, and networking for AI workloads.
+2. Outcome (impact):
+P6-B300 instances offer significant improvements in GPU performance, memory, and networking, enabling faster training and deployment of large AI models.
+3. Where to use (use case):
+Ideal for training and deploying large foundation models, including large language models (LLMs), requiring high computational power and memory.</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront announces API support for flat-rate pricing plans</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/cloudfront-flat-rate-pricing-plans-api/</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon CloudFront now supports API-driven management of flat-rate pricing plans, allowing automated subscription, upgrades, downgrades, and cancellations.
+2. Outcome (impact):
+   This update streamlines the management of CloudFront distributions by enabling programmatic control over flat-rate pricing plans, reducing manual intervention and improving operational efficiency.
+3. Where to use (use case):
+   Ideal for organizations that require automated and scalable infrastructure management, such as large enterprises, DevOps teams, and cloud service providers.</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Introducing Amazon Quick Max: 5x the usage for power users who want the most out of Quick</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-quick-max-5x-usage-power-users/</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 17:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick introduces Quick Max, a premium plan offering 5x the usage and storage of the Plus plan, designed for power users.
+2. Outcome (impact):
+Power users can handle larger workloads with increased efficiency and flexibility, maximizing their use of Amazon Quick.
+3. Where to use (use case):
+Ideal for businesses and individuals needing extensive use of Amazon Quick, such as managing large-scale agents, workflows, and custom applications.</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>AWS Gateway Load Balancer now supports TCP Reset for faster failure recovery</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-gateway-load-balancer-tcp-reset/</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Gateway Load Balancer now supports TCP Reset for faster failure recovery, reducing traffic interruptions from minutes to seconds.
+2. Outcome (impact):
+This feature minimizes downtime and improves application reliability by quickly detecting failed connections and establishing new TCP flows through healthy targets.
+3. Where to use (use case):
+Ideal for applications requiring high availability and minimal downtime, such as web servers, API gateways, and other critical services.</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Elastic Load Balancing (ELB)</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications adds support for NVIDIA Blackwell GPU instances</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-workspaces-applications-nvidia-blackwell-gpu-instances/</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon WorkSpaces Applications now supports Graphics G7 instances with advanced GPUs and processors, enhancing performance for graphics-intensive tasks.
+2. Outcome (impact):
+Graphics G7 instances offer up to 2.1× better performance for applications like CAD, 3D rendering, and AI-assisted design, enabling higher fidelity and frame rates.
+3. Where to use (use case):
+Ideal for professionals in CAD/CAM, 3D rendering, scientific visualization, video editing, and AI-assisted design workflows.</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Amazon WorkSpaces Applications</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Amazon Redshift rg.large instances now support single-node clusters</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/redshift-rg-large-single-node</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 16:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Redshift rg.large instances now support single-node clusters, offering faster performance and cost savings for smaller workloads.
+2. Outcome (impact):  
+Customers can now deploy cost-effective, high-performance single-node clusters for smaller workloads, enabling quicker proofs of concept and tests.
+3. Where to use (use case):  
+Ideal for smaller workloads, data analysis, testing, and proof of concepts where high availability is not required.</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>Amazon Aurora MySQL 8.4.8 (compatible with MySQL 8.4.8) is now generally available</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-aurora-mysql-848-available/</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 16:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon Aurora MySQL 8.4.8 is now available with new features like post-quantum TLS, transaction timeout, multi-source replication, and delayed replication.
+2. Outcome (impact):  
+   Enhanced security, improved performance, and better data management capabilities, reducing risks of performance issues and accidental data loss.
+3. Where to use (use case):  
+   Ideal for applications requiring high availability, multi-source data consolidation, and protection against accidental data loss.</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Amazon Aurora MySQL now supports multi-source replication and delayed replication</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-aurora-mysql-multisourcerep-delayedrep/</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon Aurora MySQL now supports multi-source replication and delayed replication for enhanced data consolidation and protection.
+2. Outcome (impact):
+   These new features provide greater flexibility and stronger data protection, enabling easier data consolidation and safer recovery from errors.
+3. Where to use (use case):
+   Ideal for merging shards, aggregating data from separate databases, and safeguarding against human error and data corruption.</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Amazon Aurora</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Unified Studio Workflows support Python and Bash operators</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/sagemaker-workflows-python-bash/</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker Unified Studio now supports PythonOperator and BashOperator for running custom Python functions and shell commands within serverless workflows.
+2. Outcome (impact):
+This enhancement allows users to execute custom logic directly in their workflows without needing to provision additional compute resources, streamlining data transformations and script executions.
+3. Where to use (use case):
+Ideal for data scientists and developers who need to integrate custom Python functions and shell commands into their serverless workflows for tasks such as data preprocessing, transformations, or running shell scripts.</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>Amazon MWAA adds built-in monitoring with Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-mwaa-cloudwatch-monitoring/</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MWAA now offers integrated monitoring with Amazon CloudWatch, featuring a new metrics dashboard and alarms table for enhanced environment oversight.
+2. Outcome (impact):
+   Users can now easily monitor and manage their MWAA environments with a consolidated view of key metrics and alarms, improving environment health and performance oversight.
+3. Where to use (use case):
+   Ideal for data engineers and DevOps teams managing Apache Airflow workflows on AWS, ensuring proactive monitoring and quick issue resolution.</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow (MWAA)</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Amazon Linux 2027 is now available in public preview</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/announcing-amazon-linux-2027/</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the public preview of Amazon Linux 2027 (AL2027), designed for cloud-native workloads with enhanced security, performance, and scalability.
+2. Outcome (impact):
+AL2027 provides improved cryptographic performance, better support for AI/ML workloads, and a more secure environment with SELinux enabled by default, ensuring stability and security for cloud applications.
+3. Where to use (use case):
+Ideal for web applications, databases, containerized microservices, AI/ML workloads, and large-scale infrastructure requiring a secure and AWS-native OS.</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Amazon Linux</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Amazon SES now supports S/MIME email signing</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ses-supports-smime-signing</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SES now supports S/MIME email signing, enabling automatic digital signatures for email authenticity without manual pre-signing.
+2. Outcome (impact):
+- Enhances email security by verifying the authenticity and integrity of emails.
+- Simplifies the process for senders by automating S/MIME signing.
+- Allows recipients to confirm email authenticity without needing S/MIME-supporting clients.
+3. Where to use (use case):
+- Secure corporate communications.
+- Financial institutions sending sensitive information.
+- Any organization needing to ensure email authenticity and integrity.</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>Amazon SES</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Amazon S3 now supports PrivateLink for FIPS endpoints</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-s3-privatelink-fips-endpoints</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon S3 now supports AWS PrivateLink for FIPS endpoints, enabling secure, VPC-contained traffic for FIPS-compliant cryptographic modules.
+2. Outcome (impact):  
+Customers can now meet stringent security and compliance requirements by using FIPS-validated cryptographic modules while keeping their S3 traffic within their VPC.
+3. Where to use (use case):  
+Ideal for organizations that need to comply with FIPS standards and require secure, internal traffic to Amazon S3, such as financial institutions and government agencies.</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>Service Name: Amazon S3  
+Category: Storage</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>AWS Transform announces general availability of Amazon FSx for NetApp ONTAP support</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-transform-fsx-netapp-ontap-support/</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 03:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform now supports Amazon FSx for NetApp ONTAP as a storage target, enabling seamless block storage migrations alongside compute and networks.
+2. Outcome (impact):
+This integration simplifies migrations by allowing direct block storage migration to FSx for ONTAP, reducing complexity and eliminating the need for intermediate storage platforms.
+3. Where to use (use case):
+Ideal for organizations migrating from NetApp ONTAP, other block storage platforms, or VMware environments, ensuring consistent data access patterns and operational processes.</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>AWS Transform for migrations</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Amazon MemoryDB now supports AWS PrivateLink in the AWS GovCloud (US) Regions</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-memorydb-privatelink/</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 14:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MemoryDB now supports AWS PrivateLink in AWS GovCloud (US) Regions, enabling private access from VPCs.
+2. Outcome (impact):
+Enhances security by keeping data within the AWS network and preventing exposure to the public internet.
+3. Where to use (use case):
+Ideal for government and defense applications requiring stringent data security and compliance within AWS GovCloud.</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>Amazon MemoryDB</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Identity now offers a managed consent portal</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-agentcore/</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 21:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon Bedrock AgentCore Identity introduces a managed consent portal, simplifying OAuth 2.0 authorization for connecting agents with third-party services.
+2. Outcome (impact):  
+Eliminates the need for custom OAuth infrastructure, reducing development time and maintenance efforts for developers and administrators.
+3. Where to use (use case):  
+Ideal for developers using AgentCore Gateway to integrate agents with external services like GitHub, Salesforce, and Slack.</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Identity</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -40726,7 +41397,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 07:56:31</t>
+          <t>2026-09-04 07:52:47</t>
         </is>
       </c>
     </row>
@@ -40737,7 +41408,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -40747,7 +41418,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5061</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="7">
@@ -40757,7 +41428,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1590</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="8">
@@ -40767,7 +41438,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000359</v>
+        <v>0.00047</v>
       </c>
     </row>
     <row r="9">
@@ -40777,7 +41448,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000452</v>
+        <v>0.000637</v>
       </c>
     </row>
     <row r="10">
@@ -40787,7 +41458,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000811</v>
+        <v>0.001107</v>
       </c>
     </row>
     <row r="11">
@@ -40797,7 +41468,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06718499999999999</v>
+        <v>0.06829200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1103"/>
+  <dimension ref="A1:F1114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -41332,6 +41332,415 @@
       <c r="F1103" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base introduces user-managed setup for SharePoint, OneDrive, and Confluence data sources</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-managed-knowledge-base-user-managed-setup-sharepoint-onedrive-confluence/</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 21:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS introduces user-managed setup for SharePoint, OneDrive, and Confluence in Amazon Bedrock, simplifying data source configuration.
+2. Outcome (impact):  
+   Teams can now quickly set up managed knowledge bases using their own credentials, reducing dependency on IT admins and speeding up the onboarding process.
+3. Where to use (use case):  
+   Ideal for prototyping AI assistants using internal documentation and files stored in SharePoint, OneDrive, or Confluence.</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base now supports ServiceNow as a native data source connector</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-managed-knowledge-base-servicenow-native-data-source-connector/</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 21:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has introduced a native ServiceNow data source connector for Amazon Bedrock Managed Knowledge Base, simplifying the integration of ServiceNow content into AI agents.
+2. Outcome (impact):
+This update eliminates the need for custom pipelines, enabling automatic crawling, metadata extraction, and incremental sync of ServiceNow knowledge articles and service catalog items.
+3. Where to use (use case):
+Ideal for creating employee-facing IT assistants, HR helpdesks, or customer support agents that leverage up-to-date ServiceNow content.</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base now supports automatic sync scheduling for data source connectors</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-managed-knowledge-base-automatic-sync-scheduling-data-source-connectors/</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 21:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS introduces automatic sync scheduling for Amazon Bedrock Managed Knowledge Base, enabling regular data updates from various sources.
+2. Outcome (impact):  
+This feature reduces manual effort and operational overhead by automating the synchronization process, ensuring AI agents have access to the latest data.
+3. Where to use (use case):  
+Ideal for enterprise environments where data updates frequently, such as customer support, policy management, and reference material storage.</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Amazon EC2 now supports specifying compatible instance types on AMIs</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-images-supported-instances</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 19:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   Amazon EC2 now allows AMI owners to specify compatible instance types, blocking launches on non-permitted instances.  
+2. Outcome (impact):  
+   Reduces the risk of failed launches due to incompatible instance-AMI pairings, ensuring smoother deployments.
+3. Where to use (use case):  
+   Ideal for organizations that need to ensure their AMIs are only launched on compatible instances to avoid failures and maintain operational integrity.</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Amazon ECS introduces Early Success Criteria for service deployments</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ecs-deployments-early-success/</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now allows early success criteria for rolling service deployments, enabling quicker deployment success based on task health percentages.
+2. Outcome (impact):
+This feature accelerates deployment completion, unblocks subsequent operations, and provides more control over deployment rollbacks and task cleanup.
+3. Where to use (use case):
+Ideal for workloads on constrained capacity, such as GPU-accelerated inference, where task launch times can be extended.</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>AWS MCP Server adds a serverless capability for AWS Lambda functions</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-mcp-server-serverless/</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 16:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS MCP Server now offers serverless capabilities to help coding agents diagnose issues in AWS Lambda functions and their connected resources.
+2. Outcome (impact):
+Enhanced troubleshooting efficiency for AWS Lambda functions, reducing the need for multiple API calls and lowering token consumption.
+3. Where to use (use case):
+Ideal for developers and DevOps teams needing to quickly identify and resolve issues in Lambda functions and their associated AWS services.</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>AWS Model Context Protocol Server</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C8g instances now available in additional regions</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ec2-c8g-instances-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 14:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 C8g instances, powered by AWS Graviton4 processors, are now available in new regions with enhanced performance and energy efficiency.
+2. Outcome (impact):
+   Users can leverage up to 30% better performance and improved energy efficiency for compute-intensive workloads across additional regions.
+3. Where to use (use case):
+   Ideal for high performance computing (HPC), batch processing, gaming, video encoding, scientific modeling, distributed analytics, CPU-based machine learning inference, and ad serving.</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family SFTP Connectors now support continuing file transfers during credential rotation</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/transfer-family-sftp-credential-rotation/</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Transfer Family SFTP Connectors now support uninterrupted file transfers during credential rotation, eliminating manual updates.
+2. Outcome (impact):
+   Reduces manual intervention and potential transfer failures during credential rotation, ensuring continuous file transfer operations.
+3. Where to use (use case):
+   Ideal for environments requiring secure, automated file transfers with minimal downtime during credential changes, such as financial data exchanges or continuous integration pipelines.</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>AWS Transfer Family</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker AI Batch Transform now supports G6e instances</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/sagemaker-batch-transform-g6e-instances/</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker AI Batch Transform now supports G6e instances, enabling enhanced performance for GPU-intensive offline inference workloads.
+2. Outcome (impact):
+This update allows users to leverage powerful G6e instances for large-scale, GPU-intensive batch inference tasks, improving efficiency and performance for applications like large language models and media generation.
+3. Where to use (use case):
+Ideal for running predictions on large datasets stored in Amazon S3, particularly for tasks requiring significant GPU resources such as image, video, and audio generation.</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Amazon EC2 C9g and C9gd instances are now available in Asia Pacific (Tokyo) region</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-c9g-c9gd-asia-pacific-tokyo/</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 C9g and C9gd instances, powered by AWS Graviton5 processors, are now available in Asia Pacific (Tokyo) region, offering up to 25% better performance.
+2. Outcome (Impact):
+Enhanced compute performance for a variety of workloads, improved security with the Nitro Isolation Engine, and cost efficiency for customers.
+3. Where to Use (Use Case):
+High-performance computing (HPC), batch processing, gaming, video encoding, scientific modeling, distributed analytics, CPU-based machine learning inference, real-time analytics, and ad serving.</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Amazon EC2 M9g and M9gd instances are now available in four additional regions</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-m9g-m9gd-four-regions/</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon EC2 M9g and M9gd instances, powered by AWS Graviton5 processors, are now available in four new regions, offering enhanced performance and security.
+2. Outcome (impact):
+- Up to 25% better performance compared to previous generations.
+- Up to 30% faster for databases.
+- Enhanced security with the Nitro Isolation Engine.
+3. Where to use (use case):
+- Ideal for memory-intensive workloads such as open-source databases, in-memory caches, big data analytics, and applications requiring high-speed local storage.</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Compute</t>
         </is>
       </c>
     </row>
@@ -41397,7 +41806,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04 07:52:47</t>
+          <t>2026-09-05 07:33:31</t>
         </is>
       </c>
     </row>
@@ -41408,7 +41817,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -41418,7 +41827,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6620</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="7">
@@ -41428,7 +41837,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2242</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="8">
@@ -41438,7 +41847,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00047</v>
+        <v>0.000293</v>
       </c>
     </row>
     <row r="9">
@@ -41448,7 +41857,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000637</v>
+        <v>0.000386</v>
       </c>
     </row>
     <row r="10">
@@ -41458,7 +41867,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001107</v>
+        <v>0.000679</v>
       </c>
     </row>
     <row r="11">
@@ -41468,7 +41877,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06829200000000001</v>
+        <v>0.068971</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1114"/>
+  <dimension ref="A1:F1130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -41741,6 +41741,598 @@
       <c r="F1114" t="inlineStr">
         <is>
           <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>OpenAI GPT-6 Astra is now generally available on Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/openai-gpt-6-astra-on-amazon-bedrock/</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 22:49:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS has launched GPT-6 Astra from OpenAI on Amazon Bedrock, offering advanced reasoning, professional-quality writing, and enhanced browser-use capabilities for business workflows.
+2. Outcome (impact):  
+Businesses can now leverage deeper reasoning, professional-grade writing, and advanced browser-use capabilities to automate complex tasks, analyze large document sets, and create applications requiring judgment.
+3. Where to use (use case):  
+Use GPT-6 Astra for building autonomous agents, analyzing extensive document collections, investigating complex software issues, and creating applications that require sophisticated judgment.</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB 3 now supports custom plugins</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/timestream-influxdb-custom-plugins/</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 21:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Timestream for InfluxDB now supports custom Python plugins, allowing users to run their own code directly within the managed InfluxDB environment.
+2. Outcome (impact):
+This feature enables users to implement custom data transformations, alerting, and integrations without needing separate infrastructure, enhancing efficiency and reducing operational overhead.
+3. Where to use (use case):
+Ideal for scenarios requiring custom data processing, real-time analytics, and integration with proprietary services directly within the database.</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Amazon Timestream for InfluxDB</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Feature Store now supports individual feature updates to lower write latency</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/sgm-feature-store-update-record/</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 21:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon SageMaker Feature Store now allows individual feature updates, reducing write latency and costs.
+2. Outcome (impact):
+   This update enables data scientists to modify specific features without rewriting entire records, improving efficiency and lowering costs.
+3. Where to use (use case):
+   Ideal for scenarios where features need frequent updates, such as real-time data ingestion pipelines or batch processing jobs.</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker Feature Store</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>AWS Transform is now available in AWS GovCloud (US-West)</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-transform-govcloud-us-west/</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform is now available in AWS GovCloud (US-West), enabling secure and automated large-scale migrations for government agencies and regulated organizations.
+2. Outcome (impact):
+Facilitates the migration of VMware, bare metal, Hyper-V, and database workloads to AWS GovCloud, reducing manual effort and risk for federal agencies and regulated industries.
+3. Where to use (use case):
+Ideal for federal agencies, defense contractors, and regulated industries needing to migrate sensitive and regulated workloads within the AWS GovCloud (US) boundary.</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>Amazon API Gateway now supports mutual TLS for backend integrations</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-api-gateway-mutual-tls-backend/</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 19:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon API Gateway now supports mutual TLS for backend integrations, allowing the use of trusted certificates for secure API-to-backend connections.
+2. Outcome (impact):
+   This update enhances security by enabling mutual TLS for backend integrations, ensuring secure communication between API Gateway and backend services.
+3. Where to use (use case):
+   Ideal for regulated industries such as financial services and healthcare, where mutual authentication is crucial for securing both client-to-API and API-to-backend connections.</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Amazon API Gateway</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MariaDB now supports community MariaDB minor versions 10.6.28, 10.11.19, 11.4.13, 11.8.9, and 12.3.3</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-mariadb-community-versions/</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for MariaDB now supports the latest community minor versions, including support for post-quantum TLS key exchange.
+2. Outcome (impact):
+Users can upgrade to the latest MariaDB versions for enhanced security, performance improvements, and new features, including post-quantum cryptography for data encryption.
+3. Where to use (use case):
+Ideal for database administrators and developers managing MariaDB databases in the cloud, ensuring they have the latest security patches and performance enhancements.</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Amazon RDS for MariaDB</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock AgentCore Memory now supports direct ingestion to long-term memory</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/agentcore-memory-direct-ingest</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Bedrock AgentCore Memory now allows direct ingestion of content into long-term memory without needing to store it as a short-term memory event first.
+2. Outcome (impact):
+This update enables developers to independently manage long-term memory extraction, improving efficiency and flexibility in memory management.
+3. Where to use (use case):
+Ideal for applications requiring efficient long-term memory management, such as customer service bots, behavioral analytics, and system monitoring.</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics introduces resource fallback order for WDL workflows</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-healthomics-resourcefallback-wdl/</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS HealthOmics now allows users to define a fallback order for preferred accelerator types in WDL workflows, ensuring continuous operation even when preferred resources are unavailable.
+2. Outcome (impact):
+   Researchers and bioinformaticians can minimize downtime and reduce the need for resubmitting workflows due to accelerator constraints, enhancing productivity and reliability of bioinformatics tasks.
+3. Where to use (use case):
+   Ideal for bioinformatics workflows in healthcare and life sciences where consistent and uninterrupted processing is critical, such as genomic data analysis and large-scale scientific research.</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>Dynamic Image Transformation for Amazon CloudFront adds four new features</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/dynamic-image-transfromation-adds-new-features/</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 14:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has enhanced Dynamic Image Transformation for Amazon CloudFront with smart cropping, automatic optimization, and an interactive playground, ensuring optimal image delivery across all devices.
+2. Outcome (impact):
+Customers can now deliver perfectly optimized images to a broader range of devices, improving user experience and reducing bandwidth costs.
+3. Where to use (use case):
+E-commerce platforms, media-rich websites, and any application requiring responsive image delivery across various devices.</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>AWS Builder ID adds recovery options and multi-factor authentication for third-party logins</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-builder-id-recovery-mfa-third-party/</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Builder ID now supports recovery options and MFA for third-party logins, enhancing account security and recovery.
+2. Outcome (impact):
+Improved account security and easier recovery options reduce the need for AWS Support intervention and enhance user experience.
+3. Where to use (use case):
+Ideal for developers and users who access AWS services through AWS Builder ID, ensuring secure and recoverable access.</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>AWS Builder ID</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>AWS announces Nx Plugin for AWS for scaffolding full-stack applications</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/nx-plugin-for-aws/</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has launched the Nx Plugin for AWS, an open-source toolkit for quickly scaffolding full-stack applications on AWS with built-in security and observability.
+2. Outcome (impact):
+Developers can rapidly set up full-stack applications on AWS with enhanced security, observability, and type-safety, reducing the time and effort needed to get applications production-ready.
+3. Where to use (use case):
+Ideal for developers building AI-powered applications, microservices, and full-stack web applications that require quick setup and integration with AWS services.</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Nx Plugin for AWS</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Amazon RDS now supports the latest CU and GDR updates for Microsoft SQL Server</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/amazon-rds-supports-latest-cu-gdr-microsoft-sql-server/</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 07:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon RDS for SQL Server now supports the latest CU and GDR updates for SQL Server 2016, 2017, 2019, 2022, and 2025, addressing critical vulnerabilities.
+2. Outcome (impact):
+   Enhanced security and stability for RDS SQL Server instances by applying the latest updates, reducing the risk of vulnerabilities.
+3. Where to use (use case):
+   Ideal for businesses running critical applications on SQL Server databases hosted on Amazon RDS, ensuring they are protected against the latest security threats.</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>Amazon S3 Object Lock now supports variable retention with event holds</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-s3-object-lock-variable-retention/</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 04:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon S3 Object Lock now supports variable retention with event holds, enabling WORM protection based on future events.
+2. Outcome (impact):
+   This feature allows organizations to comply with event-based retention requirements without unnecessarily retaining data longer than required.
+3. Where to use (use case):
+   Ideal for industries needing compliance with regulations such as SEC Rule 17a-4(f), FINRA Rule 4511, and CFTC Regulation 1.31, where data retention periods are event-triggered.</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Amazon MWAA Serverless is now available in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-mwaa-serverless-aws-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 22:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon MWAA Serverless is now available in AWS GovCloud (US-East and US-West), offering automatic provisioning and scaling with a pay-per-use model.
+2. Outcome (impact):
+   Reduces operational overhead for managing Apache Airflow infrastructure, enabling users to focus on workflow automation without worrying about underlying compute resources.
+3. Where to use (use case):
+   Ideal for government and defense agencies needing secure, compliant, and scalable workflow automation solutions in AWS GovCloud regions.</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>Amazon Managed Workflows for Apache Airflow (MWAA) Serverless</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty adds optional threat detection rules</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/guardduty-optional-detection-rules/</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 17:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon GuardDuty introduces Custom Detection Rules, offering 35 prebuilt, opt-in rules for CloudTrail events to enhance threat detection tailored to your environment.
+2. Outcome (impact):
+This feature allows users to extend their threat detection capabilities with minimal setup, focusing on specific, environment-relevant threat indicators without needing to manage log ingestion or storage.
+3. Where to use (use case):
+Custom Detection Rules are ideal for environments where certain activities, like sharing AMIs or disabling flow logs, may be routine in some contexts but suspicious in others. It helps in fine-tuning security monitoring to avoid false positives.</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>Amazon GuardDuty</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation now supports contract tests v2 for resource types</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-cloudformation-contract-tests-v2-resource-types/</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 15:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS CloudFormation now supports enhanced contract tests v2, offering deeper validation of resource type implementations and live-state verification.
+2. Outcome (impact):
+Contract tests v2 significantly reduces iteration cycles by identifying issues early, ensuring resource states match requests, and providing detailed reports.
+3. Where to use (use case):
+Ideal for developers creating and testing new AWS resource types, ensuring robust implementation before registry submission.</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>CloudFormation</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
         </is>
       </c>
     </row>
@@ -41806,7 +42398,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05 07:33:31</t>
+          <t>2026-09-09 08:00:54</t>
         </is>
       </c>
     </row>
@@ -41817,7 +42409,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -41827,7 +42419,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4127</v>
+        <v>6061</v>
       </c>
     </row>
     <row r="7">
@@ -41837,7 +42429,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1358</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="8">
@@ -41847,7 +42439,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000293</v>
+        <v>0.00043</v>
       </c>
     </row>
     <row r="9">
@@ -41857,7 +42449,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000386</v>
+        <v>0.000584</v>
       </c>
     </row>
     <row r="10">
@@ -41867,7 +42459,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000679</v>
+        <v>0.001014</v>
       </c>
     </row>
     <row r="11">
@@ -41877,7 +42469,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.068971</v>
+        <v>0.06998500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1130"/>
+  <dimension ref="A1:F1143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -42333,6 +42333,484 @@
       <c r="F1130" t="inlineStr">
         <is>
           <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer now lets you set specific capacity limits for different types of Tasks and Emails</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-connect-capacity-limits/</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer now allows managers to set specific capacity limits for different types of Task and Email contacts based on complexity or priority.
+2. Outcome (impact):
+This update enables more efficient workload management by allowing contact center managers to allocate agent resources more effectively, ensuring high-priority tasks receive adequate attention.
+3. Where to use (use case):
+Ideal for contact centers needing to balance high-effort and low-effort tasks, ensuring agents are not overwhelmed while critical tasks are handled promptly.</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>AWS Transform for .NET modernization is now generally available via CLI</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-transform-dotnet-cli</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>1. Short Summary
+AWS Transform for.NET modernization is now available via CLI, enabling organizations to modernize code at scale with a single command.
+2. Outcome (impact)
+Organizations can efficiently upgrade language versions, migrate frameworks, and optimize performance with minimal manual effort, accelerating.NET modernization projects.
+3. Where to use (use case)
+Ideal for enterprises looking to modernize legacy.NET applications by integrating the transformation into CI/CD pipelines or running it interactively for targeted updates.</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>AWS Transform</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>AWS Lambda now supports 90-minute function timeout on Lambda Managed Instances</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-lambda-90-minute-function/</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now supports a 90-minute function timeout for asynchronous and event source mapping invocations on Lambda Managed Instances, enabling longer continuous execution for data-intensive workloads.
+2. Outcome (impact):
+This update allows customers to run data processing, media transcoding, financial calculations, AI inference, and batch workloads without needing to re-architect their applications.
+3. Where to use (use case):
+Ideal for data-intensive tasks such as media transcoding, financial calculations (e.g., Monte Carlo simulations), and AI inference that require longer execution times.</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>AWS Lambda now supports Graviton5-powered EC2 instances on Lambda Managed Instances</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-lambda-graviton5-ec2/</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS Lambda now supports Graviton5-powered instances on Lambda Managed Instances, offering up to 25% better compute performance.
+2. Outcome (impact):  
+   Enhanced compute performance and cost efficiency for Lambda functions running on EC2 instances.
+3. Where to use (use case):  
+   Ideal for workloads requiring high compute performance, such as data processing, machine learning inference, and real-time analytics.</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base adds APIs and console support for debugging document-level access control</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-knowledge-base-debugging-document-access-control/</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 16:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces new APIs and console features for Amazon Bedrock Managed Knowledge Base to help debug and audit document-level access control issues.
+2. Outcome (impact):
+Administrators can now easily verify user access to specific documents and audit document permissions, reducing the complexity and time needed to diagnose and resolve access control issues.
+3. Where to use (use case):
+Use these features to troubleshoot and manage access control for documents within enterprise knowledge bases, ensuring that users have the appropriate permissions without needing to involve support.</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base now supports Confluence Data Center as a native data source connector</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-managed-knowledge-base-confluence-data-center-native-data-source-connector/</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 14:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS introduces a native Confluence Data Center connector for Amazon Bedrock Managed Knowledge Base, enabling seamless integration of Confluence content into AI agents.
+2. Outcome (impact):
+This update simplifies the ingestion of Confluence Data Center content into Amazon Bedrock, eliminating the need for custom pipelines and enhancing the efficiency and relevance of internal AI assistants.
+3. Where to use (use case):
+Ideal for organizations using Confluence Data Center to manage internal documentation, engineering wikis, and team knowledge bases, allowing AI agents to access and utilize this content effectively.</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Amazon EBS Volume Clones now supports copying volumes across accounts</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ebs-volume-clones-cross-account-copy/</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EBS Volume Clones now supports copying volumes across AWS accounts with re-encryption.
+2. Outcome (impact):  
+This feature allows organizations to securely copy production data into development environments across different accounts, ensuring data isolation and compliance with encryption policies.
+3. Where to use (use case):  
+Use this for securely cloning production database volumes into isolated development accounts, enabling safe experimentation and maintaining separate encryption keys for production and non-production environments.</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Amazon EBS Volume Clones</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>AWS Systems Manager now diagnoses more issues that cause EC2 instances to be unmanaged</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/systems-manager-diagnoses-ec2-unmanaged/</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>1. Short Summary: AWS Systems Manager now diagnoses six additional issue categories preventing EC2 instances from being managed, offering actionable insights and remediation options.
+2. Outcome (impact): Faster identification and resolution of issues causing EC2 instances to be unmanaged, enabling quicker patching, command execution, and inventory collection.
+3. Where to use (use case): Ideal for administrators managing large fleets of EC2 instances, ensuring they are properly managed by Systems Manager for effective operations.</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>AWS Systems Manager</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>AWS Private CA EKS add-on and Connector for AD now available in AWS GovCloud (US)</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/private-ca-eks-addon-ad-govcloud/</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Private CA introduces new connectors for Kubernetes and Active Directory in AWS GovCloud (US), enhancing certificate management for government workloads.
+2. Outcome (impact):  
+These new connectors simplify certificate automation, improve security for Kubernetes clusters, and extend certificate issuance capabilities for Active Directory-enrolled objects in AWS GovCloud (US).
+3. Where to use (use case):  
+Ideal for government organizations managing sensitive workloads in AWS GovCloud (US) that require secure certificate management for Kubernetes clusters and Active Directory-enrolled resources.</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>AWS Private Certificate Authority (AWS Private CA)</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>AWS Entity Resolution adds record-level confidence scores for ML matching</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/entity-resolution-record-confidence/</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Entity Resolution now offers record-level confidence scores for ML-based matching, enabling precise match quality assessment and differentiated thresholds for record activation.
+2. Outcome (impact):
+   This update allows for more accurate identity resolution by distinguishing near-certain matches from borderline ones, leading to improved lead conversions and larger addressable audiences while maintaining compliance.
+3. Where to use (use case):
+   Ideal for data management scenarios requiring high-precision identity matching, such as customer data consolidation, fraud detection, and audience targeting in marketing.</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>AWS Entity Resolution</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer Profiles now sends events when customers enter or exit segments</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/connect-customer-profiles-segment-events/</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Connect Customer Profiles now sends real-time notifications when customer profiles enter or exit specific segments, improving efficiency and reducing delays.
+2. Outcome (impact):
+Reduces manual effort, minimizes errors, and accelerates response times for customer segmentation changes, enabling faster activation of campaigns and workflows.
+3. Where to use (use case):
+Ideal for marketing teams, customer success managers, and data analysts who need to respond quickly to changes in customer profiles and their segments.</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Amazon Connect Customer Profiles</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Dynamic Image Transformation for Amazon CloudFront adds four new features</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/08/dynamic-image-transformation-adds-new-features/</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 14:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS has enhanced Dynamic Image Transformation for Amazon CloudFront with smart cropping, automatic optimization, an interactive playground, and feature parity across architectures.
+2. Outcome (impact):
+Improved image quality and performance, better device compatibility, and easier testing and validation of image transformations, leading to optimized user experiences across various devices.
+3. Where to use (use case):
+E-commerce platforms, content management systems, and any web application requiring responsive and optimized image delivery.</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Amazon CloudFront</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Amazon EMR extends support at no additional cost for customers migrating off older releases</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/emr-extended-support-migration/</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+Amazon EMR extends support for older releases at no extra cost to help customers migrate to current versions.
+2. Outcome (impact):  
+Customers gain more time to migrate workloads from older EMR releases to current ones without incurring additional costs, ensuring continued support and security.
+3. Where to use (use case):  
+Ideal for organizations running data processing workloads on Amazon EMR that need extra time to upgrade from older releases to newer, supported versions.</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>Amazon EMR</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Analytics</t>
         </is>
       </c>
     </row>
@@ -42398,7 +42876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 08:00:54</t>
+          <t>2026-09-10 08:00:23</t>
         </is>
       </c>
     </row>
@@ -42409,7 +42887,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -42419,7 +42897,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6061</v>
+        <v>5072</v>
       </c>
     </row>
     <row r="7">
@@ -42429,7 +42907,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2055</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="8">
@@ -42439,7 +42917,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00043</v>
+        <v>0.00036</v>
       </c>
     </row>
     <row r="9">
@@ -42449,7 +42927,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000584</v>
+        <v>0.00046</v>
       </c>
     </row>
     <row r="10">
@@ -42459,7 +42937,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001014</v>
+        <v>0.00082</v>
       </c>
     </row>
     <row r="11">
@@ -42469,7 +42947,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.06998500000000001</v>
+        <v>0.07080500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1143"/>
+  <dimension ref="A1:F1163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -42811,6 +42811,746 @@
       <c r="F1143" t="inlineStr">
         <is>
           <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>AWS Lambda recursive loop detection is now available in Europe Sovereign Cloud</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/lambda-recursion-europe-sovereign-cloud</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda now offers recursive loop detection in Europe Sovereign Cloud, preventing unintended recursive loops and unexpected billing.
+2. Outcome (impact):
+This feature helps prevent cost overruns and system instability by automatically detecting and stopping recursive invocations between Lambda functions and other services.
+3. Where to use (use case):
+Ideal for event-driven applications using services like Amazon S3, SQS, and SNS to trigger Lambda functions, ensuring safer and more reliable operation.</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>AWS Transform for .NET now generates unit tests for modernized code</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-transform-net-unit-tests</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Transform for.NET now automatically generates unit tests for modernized code, streamlining the migration process and ensuring immediate test coverage.
+2. Outcome (impact):
+This feature reduces manual effort in writing test coverage for modernized.NET applications, accelerates the migration process, and enhances the reliability and maintainability of the transformed codebase.
+3. Where to use (use case):
+Ideal for development teams looking to modernize legacy.NET applications to modern.NET while ensuring comprehensive test coverage without additional manual effort.</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>AWS Transform for.NET</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Amazon API Gateway now supports 1 MB execution logs with configurable delivery destinations</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-api-gateway-1-mb-execution-logs/</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon API Gateway now supports 1 MB execution logs with configurable delivery destinations to CloudWatch Logs, S3, or Firehose.
+2. Outcome (impact):
+   Enhanced visibility and flexibility in managing API execution logs, allowing for better analysis and real-time monitoring.
+3. Where to use (use case):
+   Ideal for developers needing detailed API request and response data for debugging, compliance, and performance monitoring.</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Amazon API Gateway</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Developer Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>AWS Lambda durable functions integrates with Pydantic AI</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-lambda-durable-pydantic-ai/</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 18:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Lambda durable functions now integrate with Pydantic AI, enabling fault-tolerant AI agents that resume from the last step after interruptions.
+2. Outcome (impact):
+This integration ensures that expensive model calls and operations are not repeated, saving costs and avoiding side-effects like double billing.
+3. Where to use (use case):
+Ideal for applications requiring reliable execution of AI workflows, such as document review, research tasks, and other repetitive, costly operations.</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Amazon MQ now supports RabbitMQ 4.3</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-mq-rabbitmq-43/</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 18:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon MQ now supports RabbitMQ 4.3, featuring enhanced quorum queues, improved memory management, and bug fixes.
+2. Outcome (impact):
+Improved performance and reliability for message queues, better resource management, and more flexible configuration options.
+3. Where to use (use case):
+Ideal for applications requiring robust message brokering with advanced queue management features, such as microservices architecture and event-driven systems.</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Amazon MQ</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Announcing second-generation single-rack AWS Outposts</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/single-rack-aws-outposts/</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 17:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS introduces second-generation single-rack Outposts, a compact 42U rack integrating compute, storage, and networking for low latency and local data processing in space-constrained environments.
+2. Outcome (impact):
+   Enables organizations with limited rack space to modernize and leverage AWS services on-premises, supporting up to 2,688 vCPUs and 100 TB of EBS storage.
+3. Where to use (use case):
+   Ideal for industries like manufacturing and gaming where rack space is limited, allowing for local data processing and residency.</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>AWS Outposts</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Serverless is now available on v0 by Vercel</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-opensearch-serverless-available-V0-vercel/</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon OpenSearch Serverless is now available on Vercel's v0, enabling rapid development of search and AI applications with automatic infrastructure management.
+2. Outcome (impact):
+   Developers can focus on building applications without managing infrastructure, leading to faster development cycles and reduced operational overhead.
+3. Where to use (use case):
+   Ideal for building full-stack search and AI applications, particularly for full-text search and vector search in retrieval-augmented generation (RAG) workloads.</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Amazon OpenSearch Serverless</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Amazon ECS expands IAM condition key support for RunTask and StartTask APIs</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-ecs-expands-condition-key-support/</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 16:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon ECS now supports IAM condition keys for CPU and memory resources on RunTask and StartTask APIs, ensuring consistent resource limits across all task launching methods.
+2. Outcome (Impact):
+Administrators can enforce consistent CPU and memory limits, preventing unexpected cost overruns and aligning workloads with resource policies.
+3. Where to Use (Use Case):
+Use this feature to maintain uniform resource allocation policies across all task launching methods in Amazon ECS, ensuring cost efficiency and policy compliance.</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>Amazon ECS</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Amazon Redshift RG instances now available in Europe (Zurich) Region</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-redshift-rg-available-zurich</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Redshift RG instances, powered by AWS Graviton processors, are now available in the Europe (Zurich) Region, offering up to 2.4x better performance at 30% lower price per vCPU.
+2. Outcome (impact):
+Customers can now leverage enhanced performance and cost-efficiency for their data warehouse and data lake workloads in the Europe (Zurich) Region.
+3. Where to use (use case):
+Ideal for running SQL analytics across data warehouses and data lakes using a single engine, suitable for businesses requiring high-performance data processing in Europe.</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Amazon Redshift</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch now supports network health indicator for TGW inter-Region peering using synthetic monitors</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/cloudwatch-network-monitoring-tgw-support/</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 11:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon CloudWatch now supports network health indicators for TGW inter-Region peering using synthetic monitors, helping to isolate network performance issues.
+2. Outcome (impact):
+Network operators and developers can quickly determine if network performance issues on inter-Region paths are caused by the AWS network, reducing troubleshooting time.
+3. Where to use (use case):
+Monitoring and troubleshooting network performance issues across AWS Transit Gateway inter-Region peering connections.</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Networking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>AWS Elemental Inference now generates contextual metadata from live video in real time</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/elemental-inference-contextual-metadata/</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental Inference now provides real-time contextual metadata from live video streams using AI, enhancing ad decisioning and content discovery.
+2. Outcome (impact):
+Enables broadcasters and content platforms to improve monetization and enrich media assets with minimal infrastructure and integration efforts.
+3. Where to use (use case):
+Contextual advertising, media asset management, content discovery, and personalized content recommendations.</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>AWS Elemental Inference</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor now offers Yield Optimization to automatically fill ad breaks with Amazon Ads demand</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/mediatailor-yield-optimization/</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Elemental MediaTailor introduces Yield Optimization to automatically fill unused ad slots with Amazon Ads demand, enhancing monetization for publishers in the APS Streaming TV program.
+2. Outcome (Impact):
+Increased ad revenue for publishers by monetizing previously unfilled ad inventory without additional costs or infrastructure changes, ensuring seamless ad playback on all devices.
+3. Where to Use (Use Case):
+Ideal for large-scale live streaming events like sports championships, where maximizing ad fill during peak times is crucial for revenue generation.</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaLive adds support for A/B forensic watermarking</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/medialive-ab-forensic-watermarking/</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elemental MediaLive now supports A/B forensic watermarking to trace unauthorized redistribution of live video content.
+2. Outcome (impact):  
+Content owners can identify the source of leaked live video content with distinct, transparent watermarks.
+3. Where to use (use case):  
+Ideal for live streaming services to protect against unauthorized redistribution and piracy.</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaLive</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor now supports Low-Latency HLS ad insertion</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-elemental-mediatailor-low-latency-hls-ad-insertion</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elemental MediaTailor now supports Low-Latency HLS ad insertion, enabling video providers to insert ads into live streams with minimal latency.
+2. Outcome (impact):  
+Video providers can deliver ads into low-latency live streams while maintaining the reduced latency expected by viewers, improving user experience for live content.
+3. Where to use (use case):  
+Ideal for live sports, news, betting and wagering, watch-party, and interactive live formats where low latency is critical.</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaTailor</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>AWS Elemental introduces Dynamic Multiview for live video</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-elemental-dynamic-multiview-video/</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Elemental MediaPackage introduces Dynamic Multiview, enabling live video sources to be composed into viewer-selected tiled layouts on demand.
+2. Outcome (impact):  
+Content providers can offer multi-angle, multi-game, and personalized viewing experiences without custom player development, enhancing viewer engagement.
+3. Where to use (use case):  
+Ideal for live sports, concerts, and events where multiple camera angles are needed, providing a seamless viewing experience on standard devices.</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>AWS Elemental MediaPackage</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>AWS Storage Gateway now supports FIPS-compliant private connectivity for Amazon S3 File Gateway</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/storage-gateway-fips-privatelink-s3/</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+AWS Storage Gateway now supports FIPS-compliant private connectivity for Amazon S3 File Gateway over AWS PrivateLink.
+2. Outcome (impact):  
+Easier compliance for regulated workloads by keeping FIPS-compliant traffic on the private AWS network.
+3. Where to use (use case):  
+Regulated industries requiring FIPS 140-3 compliance for data transfers to Amazon S3.</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Storage Gateway</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Amazon EVS is now available in more regions</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-evs-available-in-additional-regions/</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EVS is now available in four new regions: Asia Pacific (Osaka), Asia Pacific (Taipei), Europe (Spain), and Israel (Tel Aviv).
+2. Outcome (impact):
+   This expansion provides users with lower latency, compliance with data residency requirements, and enhanced redundancy options for running VMware workloads in the cloud.
+3. Where to use (use case):
+   Ideal for migrating VMware workloads to AWS to modernize infrastructure, reduce operational risks, and meet critical timelines for exiting data centers.</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Amazon Elastic VMware Service (Amazon EVS)</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Amazon Quick adds always-on agents, a sharper feed, and enterprise controls</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-quick-always-on-agents-sharper-feed-enterprise-controls/</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 15:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick introduces always-on agents, enhanced activity feed, and enterprise controls for better work organization and collaboration.
+2. Outcome (impact):
+Improved productivity and trust in AI-driven insights, with better management, richer collaboration, and enhanced security controls.
+3. Where to use (use case):
+Enterprise environments requiring efficient task management, collaboration, and compliance with data loss prevention policies.</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Amazon Quick activity feed now available on iOS and Android mobile devices</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-quick-activity-feed-available-ios-android-mobile-devices/</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 15:39:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick activity feed is now accessible on mobile devices for iOS and Android, offering a unified view of work notifications.
+2. Outcome (impact):
+Users can stay updated with important work notifications without switching between apps, enhancing productivity and reducing notification noise.
+3. Where to use (use case):
+Ideal for enterprise communications, task management, and ensuring no time-sensitive information is missed, whether on the go or at the desk.</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Amazon Quick desktop app is now generally available on macOS and Windows</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-quick-desktop-app-generally-available-macos-windows/</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 15:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon Quick desktop app is now available on macOS and Windows, offering seamless integration with local files and business apps, and continuous background processing.
+2. Outcome (impact):
+Enhances productivity by allowing users to start tasks on desktop and continue on mobile, ensuring uninterrupted progress even when away from the computer.
+3. Where to use (use case):
+Ideal for professionals needing to manage tasks across devices, ensuring work continuity and efficiency in hybrid work environments.</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Amazon Quick</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
         </is>
       </c>
     </row>
@@ -42876,7 +43616,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10 08:00:23</t>
+          <t>2026-09-11 07:56:48</t>
         </is>
       </c>
     </row>
@@ -42887,7 +43627,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -42897,7 +43637,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5072</v>
+        <v>7578</v>
       </c>
     </row>
     <row r="7">
@@ -42907,7 +43647,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1619</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="8">
@@ -42917,7 +43657,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00036</v>
+        <v>0.000538</v>
       </c>
     </row>
     <row r="9">
@@ -42927,7 +43667,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00046</v>
+        <v>0.000679</v>
       </c>
     </row>
     <row r="10">
@@ -42937,7 +43677,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00082</v>
+        <v>0.001217</v>
       </c>
     </row>
     <row r="11">
@@ -42947,7 +43687,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07080500000000001</v>
+        <v>0.072022</v>
       </c>
     </row>
   </sheetData>

--- a/aws_feed_master.xlsx
+++ b/aws_feed_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1163"/>
+  <dimension ref="A1:F1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -43551,6 +43551,304 @@
       <c r="F1163" t="inlineStr">
         <is>
           <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Amazon EC2 X2idn instances are now available in Asia Pacific (Hong Kong)</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/ec2-x2idn-asia-pacific-hong-kong/</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 18:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   Amazon EC2 X2idn instances are now available in Hong Kong, offering enhanced performance for memory-intensive workloads.
+2. Outcome (impact):
+   Users in Asia Pacific (Hong Kong) can now leverage high-performance, memory-optimized instances for critical applications, improving efficiency and reducing latency.
+3. Where to use (use case):
+   Ideal for running SAP workloads, data warehousing, and other memory-intensive applications requiring high performance.</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Amazon EC2</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod now supports model caching for faster inference autoscaling and reduced cold starts</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/sgm-hyperpod-model-caching-inf/</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 18:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon SageMaker HyperPod now offers model caching to significantly speed up inference autoscaling and reduce cold starts by pre-loading model weights and container images.
+2. Outcome (impact):
+- Approximately 60% faster scale-out times.
+- Over two minutes reduction in image-pull time (97% reduction).
+- Improved reliability and performance for large language model (LLM) inference.
+3. Where to use (use case):
+Ideal for workloads such as chat assistants, agentic pipelines, Retrieval-Augmented Generation (RAG), and document analysis that require fast inference at scale.</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Amazon SageMaker HyperPod</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>AWS Lambda now supports direct read configuration for Amazon S3 Files</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-lambda-direct-read-s3files/</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS Lambda now allows direct read configuration for Amazon S3 Files, optimizing read performance based on application needs.
+2. Outcome (impact):
+   Users can now fine-tune the throughput and latency of file reads for their Lambda functions, enhancing performance and cost-efficiency.
+3. Where to use (use case):
+   Ideal for scalable data processing pipelines and stateful workloads requiring high performance and simplicity of a file system.</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>AWS Lambda</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Managed Knowledge Base now supports multimodal embeddings for video, audio, and image content with TwelveLabs Marengo 3.0</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-bedrock-managed-knowledge-base-multimodal-embeddings-twelvelabs-marengo/</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 15:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>1. Short Summary:  
+   AWS introduces TwelveLabs Marengo 3.0 in Amazon Bedrock for creating multimodal embeddings from video, audio, and image content.
+2. Outcome (impact):  
+   Enhanced media search capabilities with improved retrieval accuracy and the ability to directly jump to relevant video segments.
+3. Where to use (use case):  
+   Ideal for applications in sports analytics, media and entertainment, security, education, and retail.</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Amazon Bedrock Knowledge Base</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics now publishes real-time run metrics to Amazon CloudWatch</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-healthomics-realtime-run-metrics/</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+   AWS HealthOmics now provides real-time run metrics to Amazon CloudWatch, enhancing visibility into resource utilization during workflow execution.
+2. Outcome (impact):
+   Users can identify bottlenecks, detect resource exhaustion, and optimize compute and storage configurations for their bioinformatics workflows without needing to open support cases.
+3. Where to use (use case):
+   Ideal for healthcare and life sciences customers running large-scale bioinformatics workflows who need to monitor and optimize resource usage in real-time.</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>AWS HealthOmics</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>AWS DevOps Agent adds support for bidirectional Slack communication</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-devops-agent-bidirectional-slack-communication</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS DevOps Agent now integrates with Slack to streamline incident management and investigation workflows, allowing teams to handle operations directly within Slack.
+2. Outcome (impact):
+This integration reduces context-switching, enhances collaboration, and improves efficiency during high-severity incidents by consolidating communication and investigation in one platform.
+3. Where to use (use case):
+Ideal for DevOps teams and on-call engineers managing production operations across AWS, multicloud, and on-premises environments, especially during critical incident response.</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>AWS DevOps Agent</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>Amazon RDS for Oracle now supports Supplemental Patch Bundle for July 2026 Release Update</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/amazon-rds-oracle-supports-spatial-patch-bundle-jul-2026-ru/</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 07:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+Amazon RDS for Oracle now supports the July 2026 Supplemental Patch Bundle for versions 19c and 26ai, enhancing database performance and security.
+2. Outcome (impact):
+This update provides improved security and performance for Oracle databases on Amazon RDS, ensuring they are up-to-date with the latest recommended patches.
+3. Where to use (use case):
+Ideal for production and non-production environments requiring enhanced security and performance for Oracle databases, such as financial services, geospatial applications, and data warehousing.</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>AWS Marketplace sellers now receive qualified demo and private offer requests in minutes</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/about-aws/whats-new/2026/09/aws-marketplace-demo-private-offer-requests-qualification</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 21:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>1. Short Summary:
+AWS Marketplace sellers can now respond to demo and private offer requests within minutes, thanks to an automated qualification process that eliminates manual delays.
+2. Outcome (impact):
+This update accelerates the sales process by allowing sellers to act on leads immediately, enhancing customer engagement and potentially increasing conversion rates.
+3. Where to use (use case):
+Ideal for SaaS providers and software sellers on AWS Marketplace looking to improve lead response times and streamline their sales process.</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>AWS Marketplace</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -43616,7 +43914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11 07:56:48</t>
+          <t>2026-09-12 07:49:06</t>
         </is>
       </c>
     </row>
@@ -43627,7 +43925,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -43637,7 +43935,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7578</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="7">
@@ -43647,7 +43945,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2392</v>
+        <v>993</v>
       </c>
     </row>
     <row r="8">
@@ -43657,7 +43955,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000538</v>
+        <v>0.000216</v>
       </c>
     </row>
     <row r="9">
@@ -43667,7 +43965,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000679</v>
+        <v>0.000282</v>
       </c>
     </row>
     <row r="10">
@@ -43677,7 +43975,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001217</v>
+        <v>0.000498</v>
       </c>
     </row>
     <row r="11">
@@ -43687,7 +43985,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.072022</v>
+        <v>0.07252</v>
       </c>
     </row>
   </sheetData>
